--- a/results/chronological/consolidated/Stress_Testing.xlsx
+++ b/results/chronological/consolidated/Stress_Testing.xlsx
@@ -2201,10 +2201,10 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.000167338709506263</v>
+        <v>0.000168012848226876</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0097282721593076</v>
+        <v>0.00973553854254884</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
@@ -2225,19 +2225,19 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00016694904461557</v>
+        <v>0.000166562801048128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00968908970052993</v>
+        <v>0.00968450603949255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000171246830958149</v>
+        <v>0.000166381990293448</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00989423141066958</v>
+        <v>0.00976701803883266</v>
       </c>
       <c r="I3" t="n">
-        <v>2.50970270137648</v>
+        <v>-0.108672071034827</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -2257,19 +2257,19 @@
         <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000166273032978298</v>
+        <v>0.000167472880396247</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00972104359547128</v>
+        <v>0.00972364448675293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000170363819880313</v>
+        <v>0.0001669427015022</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00972051165496244</v>
+        <v>0.00965139999178962</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4012063740349</v>
+        <v>-0.317581355325513</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -2291,10 +2291,10 @@
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.0000422625620498182</v>
+        <v>0.0000394838595218529</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00482940968620762</v>
+        <v>0.00479387637026704</v>
       </c>
       <c r="I5"/>
       <c r="J5" t="n">
@@ -2317,10 +2317,10 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000438876891413479</v>
+        <v>0.0000389778236759456</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00514898050110327</v>
+        <v>0.00477347833269457</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2341,19 +2341,19 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000388562837594689</v>
+        <v>0.0000388303679581553</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00475041421030791</v>
+        <v>0.00474517618359948</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0000419880225707598</v>
+        <v>0.0000399185335244449</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00495227550513501</v>
+        <v>0.0048028757742464</v>
       </c>
       <c r="I7" t="n">
-        <v>7.45864801328332</v>
+        <v>2.72596578635137</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -2373,19 +2373,19 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000400060765290929</v>
+        <v>0.0000385844270637529</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00483343208135201</v>
+        <v>0.00475809503347129</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000397873313333907</v>
+        <v>0.0000396218173989364</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00492168239140334</v>
+        <v>0.00485875183121341</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.549786045888173</v>
+        <v>2.61823006435671</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -2407,10 +2407,10 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9" t="n">
-        <v>0.0000926791147096347</v>
+        <v>0.0000909163197171449</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00390954362936765</v>
+        <v>0.00367913244714291</v>
       </c>
       <c r="I9"/>
       <c r="J9" t="n">
@@ -2431,19 +2431,19 @@
         <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000908454839267332</v>
+        <v>0.0000908374727731589</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00366199150819604</v>
+        <v>0.00366289628874536</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0000949521482055205</v>
+        <v>0.0000909780585583841</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00401506233124322</v>
+        <v>0.00368940049730537</v>
       </c>
       <c r="I10" t="n">
-        <v>4.32498301133595</v>
+        <v>0.154527132643754</v>
       </c>
       <c r="J10" t="n">
         <v>1356</v>
@@ -2463,19 +2463,19 @@
         <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000908828530074653</v>
+        <v>0.0000909839146952137</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00367813724764925</v>
+        <v>0.00367050050416535</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0000922089378502767</v>
+        <v>0.0000909876459286935</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00379964214465874</v>
+        <v>0.00367675730170656</v>
       </c>
       <c r="I11" t="n">
-        <v>1.43813048249684</v>
+        <v>0.00410081329360218</v>
       </c>
       <c r="J11" t="n">
         <v>1356</v>
@@ -2497,10 +2497,10 @@
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12" t="n">
-        <v>0.000212762118067463</v>
+        <v>0.000210879445356703</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00407892915224426</v>
+        <v>0.00384133893310973</v>
       </c>
       <c r="I12"/>
       <c r="J12" t="n">
@@ -2521,19 +2521,19 @@
         <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000210663168684988</v>
+        <v>0.000210491823218152</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00380992332723629</v>
+        <v>0.00381030342674765</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000214600421629237</v>
+        <v>0.000210763566417222</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0042495280269817</v>
+        <v>0.00382248703932163</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8346902183874</v>
+        <v>0.128932720056797</v>
       </c>
       <c r="J13" t="n">
         <v>1356</v>
@@ -2553,19 +2553,19 @@
         <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000211122758081149</v>
+        <v>0.00021060201633372</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00382129068408</v>
+        <v>0.00381036124671783</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000211718658056734</v>
+        <v>0.000210894180591132</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00396250150622476</v>
+        <v>0.00384833573944941</v>
       </c>
       <c r="I14" t="n">
-        <v>0.28145841328063</v>
+        <v>0.138535950396102</v>
       </c>
       <c r="J14" t="n">
         <v>1356</v>
@@ -2587,10 +2587,10 @@
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15" t="n">
-        <v>0.0000245671294617168</v>
+        <v>0.0000223524231367376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00372027336724541</v>
+        <v>0.00347565341858694</v>
       </c>
       <c r="I15"/>
       <c r="J15" t="n">
@@ -2611,19 +2611,19 @@
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000022062084350987</v>
+        <v>0.0000220775924997776</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00344429003925299</v>
+        <v>0.00344472098097703</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000026005222132184</v>
+        <v>0.0000226853640530436</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00382235343497044</v>
+        <v>0.00349702121223252</v>
       </c>
       <c r="I16" t="n">
-        <v>15.162869062045</v>
+        <v>2.67913511039511</v>
       </c>
       <c r="J16" t="n">
         <v>1356</v>
@@ -2643,19 +2643,19 @@
         <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000221830253166196</v>
+        <v>0.0000220933183744288</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00344428787950229</v>
+        <v>0.00344561254483767</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000245070317005776</v>
+        <v>0.0000221917077748464</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00368471797741077</v>
+        <v>0.00345762203315949</v>
       </c>
       <c r="I17" t="n">
-        <v>9.48301863870073</v>
+        <v>0.443361103236576</v>
       </c>
       <c r="J17" t="n">
         <v>1356</v>
@@ -2677,10 +2677,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000244012669619701</v>
+        <v>0.0000224495910178183</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00371383276661242</v>
+        <v>0.00348469207961156</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2701,19 +2701,19 @@
         <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000022204786025354</v>
+        <v>0.000022192621335879</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0034507074577907</v>
+        <v>0.00344902075624517</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0000268207976869003</v>
+        <v>0.000022618362592109</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00386456877088416</v>
+        <v>0.00349553787471214</v>
       </c>
       <c r="I19" t="n">
-        <v>17.2105681398163</v>
+        <v>1.88228150687865</v>
       </c>
       <c r="J19" t="n">
         <v>1356</v>
@@ -2733,19 +2733,19 @@
         <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000224132230990985</v>
+        <v>0.0000221862920587954</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00346526803236772</v>
+        <v>0.00344777439975394</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000023680800834454</v>
+        <v>0.0000222949695610232</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00357951838948941</v>
+        <v>0.00346402184601575</v>
       </c>
       <c r="I20" t="n">
-        <v>5.35276549225156</v>
+        <v>0.487453019078507</v>
       </c>
       <c r="J20" t="n">
         <v>1356</v>
@@ -2767,10 +2767,10 @@
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21" t="n">
-        <v>0.000121606586046539</v>
+        <v>0.000118104628623601</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00999467741583503</v>
+        <v>0.00996703116283773</v>
       </c>
       <c r="I21"/>
       <c r="J21" t="n">
@@ -2791,19 +2791,19 @@
         <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000116038064891963</v>
+        <v>0.000116096883877524</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00987324107360582</v>
+        <v>0.00987541333067351</v>
       </c>
       <c r="G22" t="n">
-        <v>0.000120997272429945</v>
+        <v>0.00011779484283482</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00991051612651033</v>
+        <v>0.00994643555308831</v>
       </c>
       <c r="I22" t="n">
-        <v>4.09861101691603</v>
+        <v>1.44145441042515</v>
       </c>
       <c r="J22" t="n">
         <v>904</v>
@@ -2823,19 +2823,19 @@
         <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000118422443270331</v>
+        <v>0.000117863898597105</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00997400059235815</v>
+        <v>0.00996194855665492</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000119857246921851</v>
+        <v>0.000117576650393178</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00998068477120853</v>
+        <v>0.00994260516877633</v>
       </c>
       <c r="I23" t="n">
-        <v>1.19709378312</v>
+        <v>-0.244307184263673</v>
       </c>
       <c r="J23" t="n">
         <v>904</v>
@@ -2857,10 +2857,10 @@
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24" t="n">
-        <v>0.000247451314657986</v>
+        <v>0.000237924019937213</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0117092292124397</v>
+        <v>0.0117325121427731</v>
       </c>
       <c r="I24"/>
       <c r="J24" t="n">
@@ -2881,19 +2881,19 @@
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000240366891856749</v>
+        <v>0.000240027542340218</v>
       </c>
       <c r="F25" t="n">
-        <v>0.011753120273935</v>
+        <v>0.0117413709217668</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000243291327844803</v>
+        <v>0.000234691761195535</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0119241957490533</v>
+        <v>0.0115964821194843</v>
       </c>
       <c r="I25" t="n">
-        <v>1.20203050966098</v>
+        <v>-2.27352725016914</v>
       </c>
       <c r="J25" t="n">
         <v>143</v>
@@ -2913,19 +2913,19 @@
         <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000237327909036281</v>
+        <v>0.000237576440500113</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0116307438020987</v>
+        <v>0.0116666923026084</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00023888396697163</v>
+        <v>0.000238722857025175</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0116995149332823</v>
+        <v>0.0117013659047123</v>
       </c>
       <c r="I26" t="n">
-        <v>0.65138650997647</v>
+        <v>0.480229056969</v>
       </c>
       <c r="J26" t="n">
         <v>143</v>
@@ -2947,10 +2947,10 @@
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27" t="n">
-        <v>0.0000985720382338994</v>
+        <v>0.0000995129810803254</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0073175621979428</v>
+        <v>0.00755756152295052</v>
       </c>
       <c r="I27"/>
       <c r="J27" t="n">
@@ -2973,10 +2973,10 @@
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28" t="n">
-        <v>0.211933762091933</v>
+        <v>0.292582175522293</v>
       </c>
       <c r="H28" t="n">
-        <v>0.07013166281927</v>
+        <v>0.0833950533585992</v>
       </c>
       <c r="I28"/>
       <c r="J28" t="n">
@@ -2997,19 +2997,19 @@
         <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0000969907023434988</v>
+        <v>0.0000969830334655324</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00738551615866471</v>
+        <v>0.00737682990190657</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000103798124160138</v>
+        <v>0.0000948206981424455</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00788114538424834</v>
+        <v>0.00730920197224464</v>
       </c>
       <c r="I29" t="n">
-        <v>6.55832836259841</v>
+        <v>-2.28044653271638</v>
       </c>
       <c r="J29" t="n">
         <v>59</v>
@@ -3029,19 +3029,19 @@
         <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0000979876917096885</v>
+        <v>0.0000962990727686393</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00748127682916317</v>
+        <v>0.00735211799936693</v>
       </c>
       <c r="G30" t="n">
-        <v>0.000100524579281494</v>
+        <v>0.0000955396205013617</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00762466380711711</v>
+        <v>0.00735827515496806</v>
       </c>
       <c r="I30" t="n">
-        <v>2.52364903184646</v>
+        <v>-0.794908189180898</v>
       </c>
       <c r="J30" t="n">
         <v>59</v>
@@ -3063,10 +3063,10 @@
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31" t="n">
-        <v>0.000104996787965288</v>
+        <v>0.000103469299681138</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00466476482507241</v>
+        <v>0.00456600302431706</v>
       </c>
       <c r="I31"/>
       <c r="J31" t="n">
@@ -3087,19 +3087,19 @@
         <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000103374505565653</v>
+        <v>0.00010358484523185</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00454861400920361</v>
+        <v>0.0045488013143906</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000107243309760345</v>
+        <v>0.000103780232663501</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00487866439690688</v>
+        <v>0.00456031986314871</v>
       </c>
       <c r="I32" t="n">
-        <v>3.60750167384544</v>
+        <v>0.188270373495941</v>
       </c>
       <c r="J32" t="n">
         <v>1356</v>
@@ -3119,19 +3119,19 @@
         <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000103295934867319</v>
+        <v>0.000103479301034791</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00454603669339408</v>
+        <v>0.00455198431025287</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000104193330809082</v>
+        <v>0.000103467514539824</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00464654906078993</v>
+        <v>0.00455643765317813</v>
       </c>
       <c r="I33" t="n">
-        <v>0.861279637376199</v>
+        <v>-0.0113914932811296</v>
       </c>
       <c r="J33" t="n">
         <v>1356</v>
@@ -3153,10 +3153,10 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.000224661253602725</v>
+        <v>0.000222689674794028</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0048334256242709</v>
+        <v>0.00470639606659162</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
@@ -3177,19 +3177,19 @@
         <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000222255877392908</v>
+        <v>0.000222899865221556</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00469830248792421</v>
+        <v>0.0046950535944229</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000224672675449902</v>
+        <v>0.00022233574224847</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00503988851853466</v>
+        <v>0.004715386664599</v>
       </c>
       <c r="I35" t="n">
-        <v>1.07569736825123</v>
+        <v>-0.253725724609545</v>
       </c>
       <c r="J35" t="n">
         <v>1356</v>
@@ -3209,19 +3209,19 @@
         <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.000222973500743311</v>
+        <v>0.000222657099915918</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00473010680542789</v>
+        <v>0.0046971628550312</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00022400726753054</v>
+        <v>0.00022289278399334</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00480155389906315</v>
+        <v>0.00469636719445802</v>
       </c>
       <c r="I36" t="n">
-        <v>0.461488057340585</v>
+        <v>0.105738765158737</v>
       </c>
       <c r="J36" t="n">
         <v>1356</v>
@@ -3243,10 +3243,10 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37" t="n">
-        <v>0.0000369428398724581</v>
+        <v>0.0000354850101297475</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00451073859921557</v>
+        <v>0.00434752632850846</v>
       </c>
       <c r="I37"/>
       <c r="J37" t="n">
@@ -3267,19 +3267,19 @@
         <v>46</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0000352384037647769</v>
+        <v>0.0000352632451049437</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00432892599988354</v>
+        <v>0.00432952817316515</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0000386905729328181</v>
+        <v>0.0000360503228540325</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00457346906950677</v>
+        <v>0.00439270892941174</v>
       </c>
       <c r="I38" t="n">
-        <v>8.92250723202122</v>
+        <v>2.18327517419379</v>
       </c>
       <c r="J38" t="n">
         <v>1356</v>
@@ -3299,19 +3299,19 @@
         <v>47</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0000355613546157108</v>
+        <v>0.0000352584464270468</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00435742562970708</v>
+        <v>0.00432944210135638</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000372248107866446</v>
+        <v>0.0000352804169931256</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00448574683070765</v>
+        <v>0.00434821739079862</v>
       </c>
       <c r="I39" t="n">
-        <v>4.46867596041776</v>
+        <v>0.0622741111112526</v>
       </c>
       <c r="J39" t="n">
         <v>1356</v>
@@ -3333,10 +3333,10 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40" t="n">
-        <v>0.0000370868931594583</v>
+        <v>0.0000352589255565391</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00448158716995799</v>
+        <v>0.00434582816655067</v>
       </c>
       <c r="I40"/>
       <c r="J40" t="n">
@@ -3357,19 +3357,19 @@
         <v>46</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0000353369609033629</v>
+        <v>0.0000353359900355605</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00433367975801518</v>
+        <v>0.00433337932653729</v>
       </c>
       <c r="G41" t="n">
-        <v>0.000039657222498109</v>
+        <v>0.000035523145871124</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00464009559991254</v>
+        <v>0.00437914514010886</v>
       </c>
       <c r="I41" t="n">
-        <v>10.8940095210956</v>
+        <v>0.526856028580774</v>
       </c>
       <c r="J41" t="n">
         <v>1356</v>
@@ -3389,19 +3389,19 @@
         <v>47</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0000353220223082574</v>
+        <v>0.0000352993334686903</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00433477787317185</v>
+        <v>0.00433590492373329</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0000369800930557463</v>
+        <v>0.0000354714422896823</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00446973850144232</v>
+        <v>0.00435047976478737</v>
       </c>
       <c r="I42" t="n">
-        <v>4.48368462726528</v>
+        <v>0.485203898918008</v>
       </c>
       <c r="J42" t="n">
         <v>1356</v>
@@ -3423,10 +3423,10 @@
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43" t="n">
-        <v>0.000133897234861267</v>
+        <v>0.000131827964784891</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0102497247506259</v>
+        <v>0.0101806329983924</v>
       </c>
       <c r="I43"/>
       <c r="J43" t="n">
@@ -3449,10 +3449,10 @@
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44" t="n">
-        <v>0.000122198431536417</v>
+        <v>0.000118803372758431</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00964795703637472</v>
+        <v>0.00954154013277616</v>
       </c>
       <c r="I44"/>
       <c r="J44" t="n">
@@ -3473,19 +3473,19 @@
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>0.000141502877164376</v>
+        <v>0.0001414857018751</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0106220271868505</v>
+        <v>0.0106222637269262</v>
       </c>
       <c r="G45" t="n">
-        <v>0.000127772511521327</v>
+        <v>0.000126356938748648</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00985321518023107</v>
+        <v>0.00989127942739404</v>
       </c>
       <c r="I45" t="n">
-        <v>-10.7459464321144</v>
+        <v>-11.9730370775652</v>
       </c>
       <c r="J45" t="n">
         <v>904</v>
@@ -3505,19 +3505,19 @@
         <v>47</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000133447478733364</v>
+        <v>0.000133570781644775</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0102595939214372</v>
+        <v>0.0102577867023216</v>
       </c>
       <c r="G46" t="n">
-        <v>0.000130879166273236</v>
+        <v>0.000130276196310112</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0101292944274033</v>
+        <v>0.010102478483756</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.96235392787124</v>
+        <v>-2.52892349329941</v>
       </c>
       <c r="J46" t="n">
         <v>904</v>
@@ -3539,10 +3539,10 @@
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47" t="n">
-        <v>0.000508344630050593</v>
+        <v>0.000516616822406843</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0163037629992431</v>
+        <v>0.0165168297565646</v>
       </c>
       <c r="I47"/>
       <c r="J47" t="n">
@@ -3563,19 +3563,19 @@
         <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000511873301416927</v>
+        <v>0.000512806842840657</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0164899573990582</v>
+        <v>0.0165127970776505</v>
       </c>
       <c r="G48" t="n">
-        <v>0.000525803939646777</v>
+        <v>0.000517788662744236</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0167671981562544</v>
+        <v>0.0164971593411957</v>
       </c>
       <c r="I48" t="n">
-        <v>2.64939784194254</v>
+        <v>0.962133832203817</v>
       </c>
       <c r="J48" t="n">
         <v>143</v>
@@ -3595,19 +3595,19 @@
         <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000509688369915021</v>
+        <v>0.000514185326971938</v>
       </c>
       <c r="F49" t="n">
-        <v>0.016396132697346</v>
+        <v>0.0164066911021035</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000511098530314523</v>
+        <v>0.000513591561800653</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0164512604613712</v>
+        <v>0.0164713489784217</v>
       </c>
       <c r="I49" t="n">
-        <v>0.275907739087808</v>
+        <v>-0.115610382928344</v>
       </c>
       <c r="J49" t="n">
         <v>143</v>
@@ -3629,10 +3629,10 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.000271051675146639</v>
+        <v>0.00025887137451676</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0123155248033045</v>
+        <v>0.0121919229021894</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
@@ -3653,19 +3653,19 @@
         <v>46</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000256146073095472</v>
+        <v>0.000256458779390605</v>
       </c>
       <c r="F51" t="n">
-        <v>0.012040988538152</v>
+        <v>0.0120478853153263</v>
       </c>
       <c r="G51" t="n">
-        <v>0.000258886068528215</v>
+        <v>0.00025262803724549</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0122080131343205</v>
+        <v>0.0119162024329556</v>
       </c>
       <c r="I51" t="n">
-        <v>1.058378864618</v>
+        <v>-1.51635669060443</v>
       </c>
       <c r="J51" t="n">
         <v>59</v>
@@ -3685,19 +3685,19 @@
         <v>47</v>
       </c>
       <c r="E52" t="n">
-        <v>0.000258299069762375</v>
+        <v>0.000258105524459544</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0121591926880391</v>
+        <v>0.0120810685791986</v>
       </c>
       <c r="G52" t="n">
-        <v>0.000271732322428224</v>
+        <v>0.000259288302320898</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0125285981782203</v>
+        <v>0.0120670563421511</v>
       </c>
       <c r="I52" t="n">
-        <v>4.94356083435638</v>
+        <v>0.456163217070273</v>
       </c>
       <c r="J52" t="n">
         <v>59</v>
@@ -3719,10 +3719,10 @@
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53" t="n">
-        <v>0.000165992981054517</v>
+        <v>0.000162906224822172</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00792483004015833</v>
+        <v>0.0077507945516883</v>
       </c>
       <c r="I53"/>
       <c r="J53" t="n">
@@ -3743,19 +3743,19 @@
         <v>46</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000162708256110624</v>
+        <v>0.000163444483383347</v>
       </c>
       <c r="F54" t="n">
-        <v>0.00776891354848142</v>
+        <v>0.00777072663832541</v>
       </c>
       <c r="G54" t="n">
-        <v>0.000164770649223152</v>
+        <v>0.000162666790246751</v>
       </c>
       <c r="H54" t="n">
-        <v>0.00785023834891788</v>
+        <v>0.00775820310463819</v>
       </c>
       <c r="I54" t="n">
-        <v>1.25167505393214</v>
+        <v>-0.478089679778036</v>
       </c>
       <c r="J54" t="n">
         <v>1356</v>
@@ -3775,19 +3775,19 @@
         <v>47</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000162864236757384</v>
+        <v>0.000162344675989324</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00772428198492726</v>
+        <v>0.00771087495893431</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000164985233282001</v>
+        <v>0.00016255809225367</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00785651675072787</v>
+        <v>0.00773755598539883</v>
       </c>
       <c r="I55" t="n">
-        <v>1.28556749135952</v>
+        <v>0.131286152160834</v>
       </c>
       <c r="J55" t="n">
         <v>1356</v>
@@ -3809,10 +3809,10 @@
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56" t="n">
-        <v>0.000288231527932738</v>
+        <v>0.000283212431303479</v>
       </c>
       <c r="H56" t="n">
-        <v>0.00806310338698721</v>
+        <v>0.00787760802375231</v>
       </c>
       <c r="I56"/>
       <c r="J56" t="n">
@@ -3833,19 +3833,19 @@
         <v>46</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00028115698931472</v>
+        <v>0.000282815668879992</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0079195707392106</v>
+        <v>0.00792005079901508</v>
       </c>
       <c r="G57" t="n">
-        <v>0.000282130068118603</v>
+        <v>0.000282196361704233</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00798713905650174</v>
+        <v>0.00791488543901683</v>
       </c>
       <c r="I57" t="n">
-        <v>0.344904323871481</v>
+        <v>-0.219459659939844</v>
       </c>
       <c r="J57" t="n">
         <v>1356</v>
@@ -3865,19 +3865,19 @@
         <v>47</v>
       </c>
       <c r="E58" t="n">
-        <v>0.00028375294783617</v>
+        <v>0.000281480184614982</v>
       </c>
       <c r="F58" t="n">
-        <v>0.00790373227100284</v>
+        <v>0.00784388874615388</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000285930074011153</v>
+        <v>0.000283006146848539</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0079447622915977</v>
+        <v>0.00789952222352718</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7614190925916</v>
+        <v>0.539197558268408</v>
       </c>
       <c r="J58" t="n">
         <v>1356</v>
@@ -3899,10 +3899,10 @@
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.0000978631090830383</v>
+        <v>0.0000940229083161743</v>
       </c>
       <c r="H59" t="n">
-        <v>0.00771879882101761</v>
+        <v>0.00752134277093106</v>
       </c>
       <c r="I59"/>
       <c r="J59" t="n">
@@ -3923,19 +3923,19 @@
         <v>46</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0000941224338183126</v>
+        <v>0.000094142197351141</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00755237606353896</v>
+        <v>0.00755450300734596</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0000989471224092776</v>
+        <v>0.0000934753542243088</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00774606646980578</v>
+        <v>0.00750695747425842</v>
       </c>
       <c r="I60" t="n">
-        <v>4.87602718855073</v>
+        <v>-0.71338924828459</v>
       </c>
       <c r="J60" t="n">
         <v>1356</v>
@@ -3955,19 +3955,19 @@
         <v>47</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0000935994392372772</v>
+        <v>0.0000936171558442319</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00748458914384838</v>
+        <v>0.00749339743158192</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0000969067431472442</v>
+        <v>0.0000942811552980978</v>
       </c>
       <c r="H61" t="n">
-        <v>0.00765191642483417</v>
+        <v>0.00753898218570277</v>
       </c>
       <c r="I61" t="n">
-        <v>3.4128728327416</v>
+        <v>0.704275898790669</v>
       </c>
       <c r="J61" t="n">
         <v>1356</v>
@@ -3989,10 +3989,10 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.0000971851104534074</v>
+        <v>0.0000947962811010623</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00765261569964386</v>
+        <v>0.00755875345228711</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -4013,19 +4013,19 @@
         <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0000942139759765595</v>
+        <v>0.0000941958059141655</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00755592390069766</v>
+        <v>0.00755668532245322</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0000970361278812972</v>
+        <v>0.0000938142965855758</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0076443988059651</v>
+        <v>0.0075175861579488</v>
       </c>
       <c r="I63" t="n">
-        <v>2.90835173080075</v>
+        <v>-0.406664381096431</v>
       </c>
       <c r="J63" t="n">
         <v>1356</v>
@@ -4045,19 +4045,19 @@
         <v>47</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0000941575001953163</v>
+        <v>0.0000935772020226656</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00751115493445657</v>
+        <v>0.00749055676435012</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0000968269350784458</v>
+        <v>0.0000942778270800512</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00762860343487871</v>
+        <v>0.0075251859606301</v>
       </c>
       <c r="I64" t="n">
-        <v>2.75691353957129</v>
+        <v>0.74314934813958</v>
       </c>
       <c r="J64" t="n">
         <v>1356</v>
@@ -4079,10 +4079,10 @@
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000222300678289073</v>
+        <v>0.000217078768001028</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0123977159315187</v>
+        <v>0.0123170236265169</v>
       </c>
       <c r="I65"/>
       <c r="J65" t="n">
@@ -4103,19 +4103,19 @@
         <v>46</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000226729811889205</v>
+        <v>0.000226774658862064</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0126542100721938</v>
+        <v>0.0126567294583957</v>
       </c>
       <c r="G66" t="n">
-        <v>0.000216282973600581</v>
+        <v>0.000215394276598182</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0122220884624758</v>
+        <v>0.0122400174835535</v>
       </c>
       <c r="I66" t="n">
-        <v>-4.83017137905478</v>
+        <v>-5.28351191295214</v>
       </c>
       <c r="J66" t="n">
         <v>904</v>
@@ -4135,19 +4135,19 @@
         <v>47</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000211747017352141</v>
+        <v>0.000210230636751771</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0120872073594698</v>
+        <v>0.0120586133573266</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000218829012524211</v>
+        <v>0.000218369603078567</v>
       </c>
       <c r="H67" t="n">
-        <v>0.012345414319127</v>
+        <v>0.0123428273035239</v>
       </c>
       <c r="I67" t="n">
-        <v>3.2363145500581</v>
+        <v>3.72715167864653</v>
       </c>
       <c r="J67" t="n">
         <v>904</v>
@@ -4169,10 +4169,10 @@
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.00372186680950052</v>
+        <v>0.00356738074628703</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0493646538250132</v>
+        <v>0.0491665162131087</v>
       </c>
       <c r="I68"/>
       <c r="J68" t="n">
@@ -4193,19 +4193,19 @@
         <v>46</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0035913543597061</v>
+        <v>0.00359417098707252</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0493299246263095</v>
+        <v>0.0493769851300678</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00369795254613748</v>
+        <v>0.00356547121089913</v>
       </c>
       <c r="H69" t="n">
-        <v>0.050855575467963</v>
+        <v>0.0493410102398191</v>
       </c>
       <c r="I69" t="n">
-        <v>2.88262721334051</v>
+        <v>-0.804936415855917</v>
       </c>
       <c r="J69" t="n">
         <v>143</v>
@@ -4225,19 +4225,19 @@
         <v>47</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00360062887324331</v>
+        <v>0.00357142072037244</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0494858631492759</v>
+        <v>0.0493017215544986</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0035752429869851</v>
+        <v>0.00358463161868233</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0489484253669652</v>
+        <v>0.049377752825185</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.710046459796484</v>
+        <v>0.368542704389443</v>
       </c>
       <c r="J70" t="n">
         <v>143</v>
@@ -4259,10 +4259,10 @@
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71" t="n">
-        <v>0.00348572231245313</v>
+        <v>0.00341654496767278</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0455207373335085</v>
+        <v>0.0450729748215993</v>
       </c>
       <c r="I71"/>
       <c r="J71" t="n">
@@ -4283,19 +4283,19 @@
         <v>48</v>
       </c>
       <c r="E72" t="n">
-        <v>4.41684395709928</v>
+        <v>4.41781437905188</v>
       </c>
       <c r="F72" t="n">
-        <v>2.10080220174362</v>
+        <v>2.10103526254686</v>
       </c>
       <c r="G72" t="n">
-        <v>3.68566600288009</v>
+        <v>3.63959608111757</v>
       </c>
       <c r="H72" t="n">
-        <v>1.91453941863216</v>
+        <v>1.90398638880817</v>
       </c>
       <c r="I72" t="n">
-        <v>-19.8384214317799</v>
+        <v>-21.3819962597432</v>
       </c>
       <c r="J72" t="n">
         <v>59</v>
@@ -4315,19 +4315,19 @@
         <v>46</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00346990185364706</v>
+        <v>0.00346597714960312</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0454712915259321</v>
+        <v>0.045441537595296</v>
       </c>
       <c r="G73" t="n">
-        <v>0.00391899231351151</v>
+        <v>0.00346035435447877</v>
       </c>
       <c r="H73" t="n">
-        <v>0.049836995773817</v>
+        <v>0.0453335981152301</v>
       </c>
       <c r="I73" t="n">
-        <v>11.4593350519244</v>
+        <v>-0.162491888065416</v>
       </c>
       <c r="J73" t="n">
         <v>59</v>
@@ -4347,19 +4347,19 @@
         <v>47</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00347544074867073</v>
+        <v>0.0034721922497019</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0456228420534828</v>
+        <v>0.045571673780738</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00346873881060529</v>
+        <v>0.00349527415221793</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0452936528452536</v>
+        <v>0.0457786519248969</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.193209648560062</v>
+        <v>0.66037459469045</v>
       </c>
       <c r="J74" t="n">
         <v>59</v>
@@ -4381,10 +4381,10 @@
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75" t="n">
-        <v>0.00129626818307667</v>
+        <v>0.00126949174070929</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0256525941629883</v>
+        <v>0.0253883913569005</v>
       </c>
       <c r="I75"/>
       <c r="J75" t="n">
@@ -4405,19 +4405,19 @@
         <v>48</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0012670094215497</v>
+        <v>0.00126830026415411</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0253298961345562</v>
+        <v>0.0253599391870407</v>
       </c>
       <c r="G76" t="n">
-        <v>0.00160143370409244</v>
+        <v>0.00129977802592766</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0294933328970742</v>
+        <v>0.0258020806307223</v>
       </c>
       <c r="I76" t="n">
-        <v>20.8828053067774</v>
+        <v>2.42177980744703</v>
       </c>
       <c r="J76" t="n">
         <v>1356</v>
@@ -4437,19 +4437,19 @@
         <v>46</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00126824169221098</v>
+        <v>0.00126859220588297</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0252712127079269</v>
+        <v>0.0252680416011099</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00139451071224808</v>
+        <v>0.00128442262970654</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0272721566004055</v>
+        <v>0.0256080947054334</v>
       </c>
       <c r="I77" t="n">
-        <v>9.05471854235834</v>
+        <v>1.23249337542304</v>
       </c>
       <c r="J77" t="n">
         <v>1356</v>
@@ -4469,19 +4469,19 @@
         <v>47</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00127249961874037</v>
+        <v>0.00126995970422846</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0254048629279272</v>
+        <v>0.0253760635545864</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00127632710003346</v>
+        <v>0.00127101209670812</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0254164054910052</v>
+        <v>0.0253582808200466</v>
       </c>
       <c r="I78" t="n">
-        <v>0.299882474718803</v>
+        <v>0.0827995644088251</v>
       </c>
       <c r="J78" t="n">
         <v>1356</v>
@@ -4503,10 +4503,10 @@
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79" t="n">
-        <v>0.0014442570185463</v>
+        <v>0.00140419518819495</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0261888712223259</v>
+        <v>0.025481153790619</v>
       </c>
       <c r="I79"/>
       <c r="J79" t="n">
@@ -4527,19 +4527,19 @@
         <v>48</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00141492459282529</v>
+        <v>0.00139712173476602</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0257537346099248</v>
+        <v>0.0254733982020694</v>
       </c>
       <c r="G80" t="n">
-        <v>0.00177803864402828</v>
+        <v>0.001425484568641</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0300438489352775</v>
+        <v>0.0258826651453883</v>
       </c>
       <c r="I80" t="n">
-        <v>20.4221686869711</v>
+        <v>1.98969771395195</v>
       </c>
       <c r="J80" t="n">
         <v>1356</v>
@@ -4559,19 +4559,19 @@
         <v>46</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00139757162305339</v>
+        <v>0.00139813813367398</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0254134976408773</v>
+        <v>0.0254133277403025</v>
       </c>
       <c r="G81" t="n">
-        <v>0.00149302589928738</v>
+        <v>0.00141856559100391</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0269507071792154</v>
+        <v>0.0258847669183924</v>
       </c>
       <c r="I81" t="n">
-        <v>6.39334363051204</v>
+        <v>1.44000795306687</v>
       </c>
       <c r="J81" t="n">
         <v>1356</v>
@@ -4591,19 +4591,19 @@
         <v>47</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00139702584240939</v>
+        <v>0.00139945268126122</v>
       </c>
       <c r="F82" t="n">
-        <v>0.025501277290897</v>
+        <v>0.0255091669592029</v>
       </c>
       <c r="G82" t="n">
-        <v>0.00140663322890127</v>
+        <v>0.00139967000198347</v>
       </c>
       <c r="H82" t="n">
-        <v>0.025692518644255</v>
+        <v>0.025516387553182</v>
       </c>
       <c r="I82" t="n">
-        <v>0.683005796712045</v>
+        <v>0.0155265685440839</v>
       </c>
       <c r="J82" t="n">
         <v>1356</v>
@@ -4625,10 +4625,10 @@
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.00123898994666074</v>
+        <v>0.00119422204118529</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0258446143701992</v>
+        <v>0.0252613519128394</v>
       </c>
       <c r="I83"/>
       <c r="J83" t="n">
@@ -4649,19 +4649,19 @@
         <v>48</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00118769630847341</v>
+        <v>0.00118679336985931</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0251783080859435</v>
+        <v>0.0251152137543551</v>
       </c>
       <c r="G84" t="n">
-        <v>0.00156378953998741</v>
+        <v>0.00124412109096161</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0298206564479356</v>
+        <v>0.0259156960012802</v>
       </c>
       <c r="I84" t="n">
-        <v>24.050118119925</v>
+        <v>4.60788917724988</v>
       </c>
       <c r="J84" t="n">
         <v>1356</v>
@@ -4681,19 +4681,19 @@
         <v>46</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00118763913979194</v>
+        <v>0.00118778533927516</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0250759285466703</v>
+        <v>0.0250749117734855</v>
       </c>
       <c r="G85" t="n">
-        <v>0.00128698010399308</v>
+        <v>0.00120601175593113</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0268340105008005</v>
+        <v>0.0254706531847801</v>
       </c>
       <c r="I85" t="n">
-        <v>7.71891996565586</v>
+        <v>1.51129676525456</v>
       </c>
       <c r="J85" t="n">
         <v>1356</v>
@@ -4713,19 +4713,19 @@
         <v>47</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00119246265248424</v>
+        <v>0.00118902653318703</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0252168674083149</v>
+        <v>0.0251750857397259</v>
       </c>
       <c r="G86" t="n">
-        <v>0.00119200245531524</v>
+        <v>0.00118943823214851</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0252531444509098</v>
+        <v>0.0251594834864654</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0386070655267369</v>
+        <v>0.0346128912248868</v>
       </c>
       <c r="J86" t="n">
         <v>1356</v>
@@ -4747,10 +4747,10 @@
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.00125583390155627</v>
+        <v>0.00119969768924166</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0258376377937866</v>
+        <v>0.0252553485936688</v>
       </c>
       <c r="I87"/>
       <c r="J87" t="n">
@@ -4771,19 +4771,19 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0011976841131088</v>
+        <v>0.00119569414050085</v>
       </c>
       <c r="F88" t="n">
-        <v>0.025263407409928</v>
+        <v>0.0252105032247734</v>
       </c>
       <c r="G88" t="n">
-        <v>0.00152762709141913</v>
+        <v>0.00124047862842381</v>
       </c>
       <c r="H88" t="n">
-        <v>0.02913321773005</v>
+        <v>0.0258516978783029</v>
       </c>
       <c r="I88" t="n">
-        <v>21.5983979443454</v>
+        <v>3.61025872568759</v>
       </c>
       <c r="J88" t="n">
         <v>1356</v>
@@ -4803,19 +4803,19 @@
         <v>46</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00119329749386675</v>
+        <v>0.00119317092850798</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0251061650932384</v>
+        <v>0.0251027954498308</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0013114260329817</v>
+        <v>0.00120390651881475</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0267006747579379</v>
+        <v>0.0253751563985663</v>
       </c>
       <c r="I89" t="n">
-        <v>9.00764024383189</v>
+        <v>0.891729560309629</v>
       </c>
       <c r="J89" t="n">
         <v>1356</v>
@@ -4835,19 +4835,19 @@
         <v>47</v>
       </c>
       <c r="E90" t="n">
-        <v>0.00119878933979737</v>
+        <v>0.00119417568972794</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0251871856442138</v>
+        <v>0.025188313775438</v>
       </c>
       <c r="G90" t="n">
-        <v>0.00120136866182028</v>
+        <v>0.00119257133030756</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0253253046903007</v>
+        <v>0.0251337000886586</v>
       </c>
       <c r="I90" t="n">
-        <v>0.214698627064214</v>
+        <v>-0.134529430618063</v>
       </c>
       <c r="J90" t="n">
         <v>1356</v>
@@ -4869,10 +4869,10 @@
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.00108729264824224</v>
+        <v>0.00107171596067512</v>
       </c>
       <c r="H91" t="n">
-        <v>0.023360779583794</v>
+        <v>0.022935504523937</v>
       </c>
       <c r="I91"/>
       <c r="J91" t="n">
@@ -4893,19 +4893,19 @@
         <v>46</v>
       </c>
       <c r="E92" t="n">
-        <v>0.00107565201046262</v>
+        <v>0.0010755597003059</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0230204974000532</v>
+        <v>0.0230195832292353</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00114277638576353</v>
+        <v>0.00106160866552392</v>
       </c>
       <c r="H92" t="n">
-        <v>0.023957907713482</v>
+        <v>0.0227152253529482</v>
       </c>
       <c r="I92" t="n">
-        <v>5.87379789582006</v>
+        <v>-1.31414100459448</v>
       </c>
       <c r="J92" t="n">
         <v>904</v>
@@ -4925,19 +4925,19 @@
         <v>47</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00104914752963215</v>
+        <v>0.00105006788309468</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0226119173031135</v>
+        <v>0.0226109310151397</v>
       </c>
       <c r="G93" t="n">
-        <v>0.00106585687328676</v>
+        <v>0.00105559105450692</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0229137519600784</v>
+        <v>0.0227205444155499</v>
       </c>
       <c r="I93" t="n">
-        <v>1.56769112939904</v>
+        <v>0.523230221463248</v>
       </c>
       <c r="J93" t="n">
         <v>904</v>
@@ -4959,10 +4959,10 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.0016976450227354</v>
+        <v>0.0016629924424144</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0311091028958468</v>
+        <v>0.0305983889368759</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -4983,19 +4983,19 @@
         <v>46</v>
       </c>
       <c r="E95" t="n">
-        <v>0.00167606988689527</v>
+        <v>0.00167503372265746</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0308430443537615</v>
+        <v>0.0308214105538606</v>
       </c>
       <c r="G95" t="n">
-        <v>0.00165773653733674</v>
+        <v>0.00165700077894368</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0304951012985309</v>
+        <v>0.03054740541421</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.10592661412784</v>
+        <v>-1.08828818567431</v>
       </c>
       <c r="J95" t="n">
         <v>143</v>
@@ -5015,19 +5015,19 @@
         <v>47</v>
       </c>
       <c r="E96" t="n">
-        <v>0.00166596998299187</v>
+        <v>0.0016625104376959</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0306697319591124</v>
+        <v>0.0306435767036062</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00166131489770445</v>
+        <v>0.00166535765885425</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0307329989542437</v>
+        <v>0.0306967340726227</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.280204872288817</v>
+        <v>0.170967548214427</v>
       </c>
       <c r="J96" t="n">
         <v>143</v>
@@ -5049,10 +5049,10 @@
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00224171460103908</v>
+        <v>0.00222235977088024</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0351746205767337</v>
+        <v>0.0352393461219392</v>
       </c>
       <c r="I97"/>
       <c r="J97" t="n">
@@ -5073,19 +5073,19 @@
         <v>46</v>
       </c>
       <c r="E98" t="n">
-        <v>0.00221534984947431</v>
+        <v>0.00221471440718524</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0350894597936468</v>
+        <v>0.0350340858182158</v>
       </c>
       <c r="G98" t="n">
-        <v>0.00229445742491078</v>
+        <v>0.00222317765715165</v>
       </c>
       <c r="H98" t="n">
-        <v>0.036057386910258</v>
+        <v>0.0350007528363568</v>
       </c>
       <c r="I98" t="n">
-        <v>3.44776828620174</v>
+        <v>0.380682575645363</v>
       </c>
       <c r="J98" t="n">
         <v>59</v>
@@ -5105,19 +5105,19 @@
         <v>47</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00222260739535522</v>
+        <v>0.00221741788104407</v>
       </c>
       <c r="F99" t="n">
-        <v>0.035169965834285</v>
+        <v>0.0351100416011255</v>
       </c>
       <c r="G99" t="n">
-        <v>0.00217498678631723</v>
+        <v>0.00221121439533158</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0349342038595005</v>
+        <v>0.0350610154199865</v>
       </c>
       <c r="I99" t="n">
-        <v>-2.18946659067436</v>
+        <v>-0.280546550600572</v>
       </c>
       <c r="J99" t="n">
         <v>59</v>
@@ -5139,10 +5139,10 @@
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.00044376093999116</v>
+        <v>0.00044093681053862</v>
       </c>
       <c r="H100" t="n">
-        <v>0.013921851926044</v>
+        <v>0.0138513787439611</v>
       </c>
       <c r="I100"/>
       <c r="J100" t="n">
@@ -5163,19 +5163,19 @@
         <v>46</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000440124602590329</v>
+        <v>0.000439311628114974</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0138140572509386</v>
+        <v>0.0138107058102261</v>
       </c>
       <c r="G101" t="n">
-        <v>0.000441562730420638</v>
+        <v>0.000440783986579755</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0139355277305428</v>
+        <v>0.013852439801653</v>
       </c>
       <c r="I101" t="n">
-        <v>0.325690492252205</v>
+        <v>0.334031750156272</v>
       </c>
       <c r="J101" t="n">
         <v>1356</v>
@@ -5195,19 +5195,19 @@
         <v>47</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000440431187095363</v>
+        <v>0.000439496550493423</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0138423044377014</v>
+        <v>0.0138350546445429</v>
       </c>
       <c r="G102" t="n">
-        <v>0.000441796694624639</v>
+        <v>0.000440834250232135</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0138830053857449</v>
+        <v>0.0138370229172925</v>
       </c>
       <c r="I102" t="n">
-        <v>0.309080521853258</v>
+        <v>0.303447324704921</v>
       </c>
       <c r="J102" t="n">
         <v>1356</v>
@@ -5229,10 +5229,10 @@
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.000564858762304383</v>
+        <v>0.000559468640765309</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0140671564798817</v>
+        <v>0.0139976827511502</v>
       </c>
       <c r="I103"/>
       <c r="J103" t="n">
@@ -5253,19 +5253,19 @@
         <v>46</v>
       </c>
       <c r="E104" t="n">
-        <v>0.000560516652292832</v>
+        <v>0.000558226037271329</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0139655847104556</v>
+        <v>0.0139596113089262</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00056408405295911</v>
+        <v>0.000559754006059833</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0142161005631278</v>
+        <v>0.0140653818557902</v>
       </c>
       <c r="I104" t="n">
-        <v>0.63242359849812</v>
+        <v>0.272971478892965</v>
       </c>
       <c r="J104" t="n">
         <v>1356</v>
@@ -5285,19 +5285,19 @@
         <v>47</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000559461538078573</v>
+        <v>0.000558433917692732</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0139888964260703</v>
+        <v>0.0139808410180449</v>
       </c>
       <c r="G105" t="n">
-        <v>0.000562782614424102</v>
+        <v>0.000558647688288992</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0141212500832475</v>
+        <v>0.013969263166289</v>
       </c>
       <c r="I105" t="n">
-        <v>0.590117082583973</v>
+        <v>0.0382657264571899</v>
       </c>
       <c r="J105" t="n">
         <v>1356</v>
@@ -5319,10 +5319,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.000373772193124131</v>
+        <v>0.00037099982872742</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0137131200979191</v>
+        <v>0.0135891021428979</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -5343,19 +5343,19 @@
         <v>46</v>
       </c>
       <c r="E107" t="n">
-        <v>0.000372137727686211</v>
+        <v>0.000372200312311268</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0135927323049435</v>
+        <v>0.013593885199505</v>
       </c>
       <c r="G107" t="n">
-        <v>0.000379412073733604</v>
+        <v>0.000372359424094623</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0137696821406829</v>
+        <v>0.0136147701958315</v>
       </c>
       <c r="I107" t="n">
-        <v>1.9172679392644</v>
+        <v>0.0427306986366075</v>
       </c>
       <c r="J107" t="n">
         <v>1356</v>
@@ -5375,19 +5375,19 @@
         <v>47</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000372720504757171</v>
+        <v>0.000372538656917855</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0136161094999015</v>
+        <v>0.0136226666468386</v>
       </c>
       <c r="G108" t="n">
-        <v>0.000373375184782994</v>
+        <v>0.000373395376005613</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0136897684261827</v>
+        <v>0.0136398574458481</v>
       </c>
       <c r="I108" t="n">
-        <v>0.175341065101267</v>
+        <v>0.229440197391443</v>
       </c>
       <c r="J108" t="n">
         <v>1356</v>
@@ -5409,10 +5409,10 @@
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.000380441174929307</v>
+        <v>0.000372306715581013</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0138172799320856</v>
+        <v>0.0136329797466528</v>
       </c>
       <c r="I109"/>
       <c r="J109" t="n">
@@ -5433,19 +5433,19 @@
         <v>46</v>
       </c>
       <c r="E110" t="n">
-        <v>0.000372174551259793</v>
+        <v>0.000372186054354876</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0135973938642859</v>
+        <v>0.0135936079494866</v>
       </c>
       <c r="G110" t="n">
-        <v>0.000376688887847094</v>
+        <v>0.000371919996639911</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0136871488075422</v>
+        <v>0.0135997143779944</v>
       </c>
       <c r="I110" t="n">
-        <v>1.19842573883763</v>
+        <v>-0.0715362759112003</v>
       </c>
       <c r="J110" t="n">
         <v>1356</v>
@@ -5465,19 +5465,19 @@
         <v>47</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000373081029839233</v>
+        <v>0.000372210902709852</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0136357831018719</v>
+        <v>0.013619147429444</v>
       </c>
       <c r="G111" t="n">
-        <v>0.000376534370887316</v>
+        <v>0.000374031234839224</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0137040989825758</v>
+        <v>0.0136501264448723</v>
       </c>
       <c r="I111" t="n">
-        <v>0.917138331872592</v>
+        <v>0.4866791753783</v>
       </c>
       <c r="J111" t="n">
         <v>1356</v>
@@ -5499,10 +5499,10 @@
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.000438295870791116</v>
+        <v>0.000429655701055872</v>
       </c>
       <c r="H112" t="n">
-        <v>0.014624338635448</v>
+        <v>0.0144611958542264</v>
       </c>
       <c r="I112"/>
       <c r="J112" t="n">
@@ -5525,10 +5525,10 @@
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.328831821254654</v>
+        <v>0.329150150998404</v>
       </c>
       <c r="H113" t="n">
-        <v>0.572157839324694</v>
+        <v>0.573271859594898</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5549,19 +5549,19 @@
         <v>46</v>
       </c>
       <c r="E114" t="n">
-        <v>0.000474739813892681</v>
+        <v>0.00047475521125153</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0158005580287145</v>
+        <v>0.0158016264005254</v>
       </c>
       <c r="G114" t="n">
-        <v>0.000435515066189596</v>
+        <v>0.000432182878986002</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0147268476291082</v>
+        <v>0.0145789638922094</v>
       </c>
       <c r="I114" t="n">
-        <v>-9.00651911913632</v>
+        <v>-9.85053650561368</v>
       </c>
       <c r="J114" t="n">
         <v>904</v>
@@ -5581,19 +5581,19 @@
         <v>47</v>
       </c>
       <c r="E115" t="n">
-        <v>0.000428286947653284</v>
+        <v>0.000426179164350369</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0144229923460815</v>
+        <v>0.0143833648165557</v>
       </c>
       <c r="G115" t="n">
-        <v>0.000430160598001538</v>
+        <v>0.000427008189826589</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0144939498279481</v>
+        <v>0.0144123676336341</v>
       </c>
       <c r="I115" t="n">
-        <v>0.435569960837513</v>
+        <v>0.194147441658177</v>
       </c>
       <c r="J115" t="n">
         <v>904</v>
@@ -5615,10 +5615,10 @@
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.0026072504086142</v>
+        <v>0.00264745262372193</v>
       </c>
       <c r="H116" t="n">
-        <v>0.039407786758122</v>
+        <v>0.0396499856306016</v>
       </c>
       <c r="I116"/>
       <c r="J116" t="n">
@@ -5639,19 +5639,19 @@
         <v>46</v>
       </c>
       <c r="E117" t="n">
-        <v>0.00265252591244933</v>
+        <v>0.00265653562230783</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0397758084329997</v>
+        <v>0.0397869536390067</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00281395251769936</v>
+        <v>0.00268704149904935</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0411194665306281</v>
+        <v>0.0397417273526017</v>
       </c>
       <c r="I117" t="n">
-        <v>5.73664993402244</v>
+        <v>1.135296077575</v>
       </c>
       <c r="J117" t="n">
         <v>143</v>
@@ -5671,19 +5671,19 @@
         <v>47</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0026532705284309</v>
+        <v>0.00263903803503108</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0395796398708843</v>
+        <v>0.0395032577301121</v>
       </c>
       <c r="G118" t="n">
-        <v>0.00264790308933924</v>
+        <v>0.00265474186475337</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0397437947066948</v>
+        <v>0.0396722225635807</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.202705269436479</v>
+        <v>0.591538858477626</v>
       </c>
       <c r="J118" t="n">
         <v>143</v>
@@ -5705,10 +5705,10 @@
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.0011244027128117</v>
+        <v>0.00111524711761984</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0263010177752659</v>
+        <v>0.0252367693964405</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5731,10 +5731,10 @@
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>5192823771941584737280286608628008064486444040</v>
+        <v>1061400423109867481920204606040400802462086840</v>
       </c>
       <c r="H120" t="n">
-        <v>13267551562839170744020</v>
+        <v>15215459857134428094424</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5755,19 +5755,19 @@
         <v>46</v>
       </c>
       <c r="E121" t="n">
-        <v>0.00109903705094383</v>
+        <v>0.00109416670218656</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0251735996904272</v>
+        <v>0.0250529562835777</v>
       </c>
       <c r="G121" t="n">
-        <v>0.00147255519541193</v>
+        <v>0.00119594310269944</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0289874332656437</v>
+        <v>0.0260970928929715</v>
       </c>
       <c r="I121" t="n">
-        <v>25.365306891849</v>
+        <v>8.51013733706484</v>
       </c>
       <c r="J121" t="n">
         <v>59</v>
@@ -5787,19 +5787,19 @@
         <v>47</v>
       </c>
       <c r="E122" t="n">
-        <v>0.00111108827606429</v>
+        <v>0.00109437617745845</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0253434681119135</v>
+        <v>0.0251561893670149</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0011156504225414</v>
+        <v>0.00108928546754795</v>
       </c>
       <c r="H122" t="n">
-        <v>0.025482950102331</v>
+        <v>0.0250610931299064</v>
       </c>
       <c r="I122" t="n">
-        <v>0.408922578698436</v>
+        <v>-0.467343966495385</v>
       </c>
       <c r="J122" t="n">
         <v>59</v>
@@ -5821,10 +5821,10 @@
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000620319002021495</v>
+        <v>0.000586995491744777</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0173270587774749</v>
+        <v>0.0164017351130259</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5845,19 +5845,19 @@
         <v>46</v>
       </c>
       <c r="E124" t="n">
-        <v>0.000584198433255287</v>
+        <v>0.000585466945058359</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0164471211693836</v>
+        <v>0.0164453706189652</v>
       </c>
       <c r="G124" t="n">
-        <v>0.000719408944846248</v>
+        <v>0.000586413707104618</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0187891242617543</v>
+        <v>0.0166235280978523</v>
       </c>
       <c r="I124" t="n">
-        <v>18.7946664493946</v>
+        <v>0.161449508220675</v>
       </c>
       <c r="J124" t="n">
         <v>1356</v>
@@ -5877,19 +5877,19 @@
         <v>47</v>
       </c>
       <c r="E125" t="n">
-        <v>0.000584394869424817</v>
+        <v>0.000580142073780285</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0164133159922302</v>
+        <v>0.0163515627437534</v>
       </c>
       <c r="G125" t="n">
-        <v>0.000586049567678583</v>
+        <v>0.000584767352877175</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0165803246652946</v>
+        <v>0.0164377105200668</v>
       </c>
       <c r="I125" t="n">
-        <v>0.282347832849732</v>
+        <v>0.790960554506467</v>
       </c>
       <c r="J125" t="n">
         <v>1356</v>
@@ -5911,10 +5911,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000732940374480162</v>
+        <v>0.000707910633596739</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0173847471990101</v>
+        <v>0.0166493072121474</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5935,19 +5935,19 @@
         <v>46</v>
       </c>
       <c r="E127" t="n">
-        <v>0.000707732556174469</v>
+        <v>0.00070442559884505</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0166048479423859</v>
+        <v>0.0165962765560253</v>
       </c>
       <c r="G127" t="n">
-        <v>0.000838149031576283</v>
+        <v>0.000707833401836747</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0191843496374151</v>
+        <v>0.0167588100816374</v>
       </c>
       <c r="I127" t="n">
-        <v>15.5600579954788</v>
+        <v>0.481441393250684</v>
       </c>
       <c r="J127" t="n">
         <v>1356</v>
@@ -5967,19 +5967,19 @@
         <v>47</v>
       </c>
       <c r="E128" t="n">
-        <v>0.000704325470850274</v>
+        <v>0.000698774432717714</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0165347954230346</v>
+        <v>0.0165251785149179</v>
       </c>
       <c r="G128" t="n">
-        <v>0.000711310226448536</v>
+        <v>0.000700737274871891</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0168458023197193</v>
+        <v>0.0165204560081845</v>
       </c>
       <c r="I128" t="n">
-        <v>0.981956302404927</v>
+        <v>0.28011099517084</v>
       </c>
       <c r="J128" t="n">
         <v>1356</v>
@@ -6001,10 +6001,10 @@
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.00056425841043017</v>
+        <v>0.000519826254758784</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0171378061586341</v>
+        <v>0.0163068180535817</v>
       </c>
       <c r="I129"/>
       <c r="J129" t="n">
@@ -6025,19 +6025,19 @@
         <v>46</v>
       </c>
       <c r="E130" t="n">
-        <v>0.000518187113502041</v>
+        <v>0.00051822502876104</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0162312124823055</v>
+        <v>0.0162266448161833</v>
       </c>
       <c r="G130" t="n">
-        <v>0.000649573640486017</v>
+        <v>0.000522915259878459</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0189034443362333</v>
+        <v>0.0163527723336984</v>
       </c>
       <c r="I130" t="n">
-        <v>20.2265792198204</v>
+        <v>0.896939041042455</v>
       </c>
       <c r="J130" t="n">
         <v>1356</v>
@@ -6057,19 +6057,19 @@
         <v>47</v>
       </c>
       <c r="E131" t="n">
-        <v>0.000514589620179475</v>
+        <v>0.000514865255436474</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0161902928407273</v>
+        <v>0.0161710972725239</v>
       </c>
       <c r="G131" t="n">
-        <v>0.000526142042741444</v>
+        <v>0.000514327095079015</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0164636468088553</v>
+        <v>0.0161431967780579</v>
       </c>
       <c r="I131" t="n">
-        <v>2.19568512369302</v>
+        <v>-0.104633872609065</v>
       </c>
       <c r="J131" t="n">
         <v>1356</v>
@@ -6091,10 +6091,10 @@
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000568957804632787</v>
+        <v>0.000522682156854144</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0173476667970886</v>
+        <v>0.0163710524446327</v>
       </c>
       <c r="I132"/>
       <c r="J132" t="n">
@@ -6115,19 +6115,19 @@
         <v>46</v>
       </c>
       <c r="E133" t="n">
-        <v>0.000518502797897635</v>
+        <v>0.000518341850431891</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0162263536632862</v>
+        <v>0.016231461766293</v>
       </c>
       <c r="G133" t="n">
-        <v>0.000643702051172421</v>
+        <v>0.000523283222417222</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0187372840871895</v>
+        <v>0.0163859860336213</v>
       </c>
       <c r="I133" t="n">
-        <v>19.4498763902883</v>
+        <v>0.94430162742564</v>
       </c>
       <c r="J133" t="n">
         <v>1356</v>
@@ -6147,19 +6147,19 @@
         <v>47</v>
       </c>
       <c r="E134" t="n">
-        <v>0.000514613835616715</v>
+        <v>0.000514148273950815</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0161368544020783</v>
+        <v>0.0161594361819877</v>
       </c>
       <c r="G134" t="n">
-        <v>0.000519624721111095</v>
+        <v>0.000515815709934471</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0163857037207726</v>
+        <v>0.016184711931186</v>
       </c>
       <c r="I134" t="n">
-        <v>0.96432777171659</v>
+        <v>0.323261961887067</v>
       </c>
       <c r="J134" t="n">
         <v>1356</v>
@@ -6181,10 +6181,10 @@
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000530209370103707</v>
+        <v>0.000490130995429692</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0173812256101252</v>
+        <v>0.0163429665557648</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
@@ -6205,19 +6205,19 @@
         <v>46</v>
       </c>
       <c r="E136" t="n">
-        <v>0.000491004042743723</v>
+        <v>0.000490908252541121</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0163574593426195</v>
+        <v>0.016355628970026</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000634068255927843</v>
+        <v>0.000497600435591791</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0186046322548119</v>
+        <v>0.0165690221960083</v>
       </c>
       <c r="I136" t="n">
-        <v>22.5629042057581</v>
+        <v>1.34489091487844</v>
       </c>
       <c r="J136" t="n">
         <v>904</v>
@@ -6237,19 +6237,19 @@
         <v>47</v>
       </c>
       <c r="E137" t="n">
-        <v>0.000477625536118788</v>
+        <v>0.000479845638706473</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0160584016265942</v>
+        <v>0.0160787606248338</v>
       </c>
       <c r="G137" t="n">
-        <v>0.00051266278039916</v>
+        <v>0.000489341235945051</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0168367551086995</v>
+        <v>0.0163074426162949</v>
       </c>
       <c r="I137" t="n">
-        <v>6.83436473642425</v>
+        <v>1.94048580848501</v>
       </c>
       <c r="J137" t="n">
         <v>904</v>
@@ -6297,13 +6297,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00119604696887727</v>
+        <v>0.00119452173996487</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00134844619151556</v>
+        <v>0.00121114039720704</v>
       </c>
       <c r="F2" t="n">
-        <v>9.22462757841247</v>
+        <v>1.27624843127922</v>
       </c>
     </row>
     <row r="3">
@@ -6317,13 +6317,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.41684395709928</v>
+        <v>4.41781437905188</v>
       </c>
       <c r="E3" t="n">
-        <v>1298205942985396184320824402482002046624666060</v>
+        <v>265350105777466870480806404060600208648024260</v>
       </c>
       <c r="F3" t="n">
-        <v>-19.8384214317799</v>
+        <v>-21.3819962597432</v>
       </c>
     </row>
     <row r="4">
@@ -6337,13 +6337,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00120090487634857</v>
+        <v>0.00119616255541606</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00119523670875117</v>
+        <v>0.00119837062588644</v>
       </c>
       <c r="F4" t="n">
-        <v>0.823945026629781</v>
+        <v>0.36532819497343</v>
       </c>
     </row>
     <row r="5">
@@ -6360,7 +6360,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00121062098362238</v>
+        <v>0.0011920033452153</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -6377,13 +6377,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00147318989948999</v>
+        <v>0.0014741895863778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00151833061660388</v>
+        <v>0.00147139598385423</v>
       </c>
       <c r="F6" t="n">
-        <v>2.31241359770252</v>
+        <v>-0.36299900215923</v>
       </c>
     </row>
     <row r="7">
@@ -6397,13 +6397,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00147219311609928</v>
+        <v>0.00146536730682795</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00146746788186588</v>
+        <v>0.00147066471043633</v>
       </c>
       <c r="F7" t="n">
-        <v>0.355924003596233</v>
+        <v>0.19634773829944</v>
       </c>
     </row>
     <row r="8">
@@ -6420,7 +6420,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00149164948251083</v>
+        <v>0.00146672991716572</v>
       </c>
       <c r="F8" t="e">
         <v>#NUM!</v>
@@ -6437,13 +6437,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000420944436840762</v>
+        <v>0.000420930068118874</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00044623541090547</v>
+        <v>0.000408489673047228</v>
       </c>
       <c r="F9" t="n">
-        <v>1.32544603136478</v>
+        <v>-4.27248019590366</v>
       </c>
     </row>
     <row r="10">
@@ -6460,7 +6460,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.164477009843095</v>
+        <v>0.164634477185581</v>
       </c>
       <c r="F10" t="e">
         <v>#NUM!</v>
@@ -6477,13 +6477,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000403112825460009</v>
+        <v>0.000402959667190862</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000413040946234458</v>
+        <v>0.000406360488343403</v>
       </c>
       <c r="F11" t="n">
-        <v>1.88478003866128</v>
+        <v>0.601964078781648</v>
       </c>
     </row>
     <row r="12">
@@ -6500,7 +6500,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000422267064722324</v>
+        <v>0.000409752336428368</v>
       </c>
       <c r="F12" t="e">
         <v>#NUM!</v>
@@ -6517,13 +6517,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000441582162276601</v>
+        <v>0.00044187293007411</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000487074749117331</v>
+        <v>0.000444840900809925</v>
       </c>
       <c r="F13" t="n">
-        <v>6.22653920385312</v>
+        <v>0.265447076693608</v>
       </c>
     </row>
     <row r="14">
@@ -6537,13 +6537,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0012670094215497</v>
+        <v>0.00126830026415411</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00160143370409244</v>
+        <v>0.00129977802592766</v>
       </c>
       <c r="F14" t="n">
-        <v>20.8828053067774</v>
+        <v>2.42177980744703</v>
       </c>
     </row>
     <row r="15">
@@ -6557,13 +6557,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000442394783315453</v>
+        <v>0.00044106770337025</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00044426014404634</v>
+        <v>0.000442271158756603</v>
       </c>
       <c r="F15" t="n">
-        <v>0.746048073442392</v>
+        <v>0.216867152632253</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000454002834803128</v>
+        <v>0.000442452647868856</v>
       </c>
       <c r="F16" t="e">
         <v>#NUM!</v>
@@ -6597,13 +6597,13 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000563316144485552</v>
+        <v>0.000562832854518344</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000602777024836752</v>
+        <v>0.000566908111545069</v>
       </c>
       <c r="F17" t="n">
-        <v>4.30685285583318</v>
+        <v>0.308361360119654</v>
       </c>
     </row>
     <row r="18">
@@ -6617,13 +6617,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00141492459282529</v>
+        <v>0.00139712173476602</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00177803864402828</v>
+        <v>0.001425484568641</v>
       </c>
       <c r="F18" t="n">
-        <v>20.4221686869711</v>
+        <v>1.98969771395195</v>
       </c>
     </row>
     <row r="19">
@@ -6637,13 +6637,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000563110342999812</v>
+        <v>0.000561900055422715</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000567063678228722</v>
+        <v>0.000562641346096227</v>
       </c>
       <c r="F19" t="n">
-        <v>0.626574124152293</v>
+        <v>0.186229260665894</v>
       </c>
     </row>
     <row r="20">
@@ -6660,7 +6660,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000577951842488962</v>
+        <v>0.000564726002335202</v>
       </c>
       <c r="F20" t="e">
         <v>#NUM!</v>
@@ -6677,13 +6677,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000371564483819044</v>
+        <v>0.000371615619217221</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000413268122614496</v>
+        <v>0.000375582913505933</v>
       </c>
       <c r="F21" t="n">
-        <v>9.8040284345596</v>
+        <v>1.09999792353966</v>
       </c>
     </row>
     <row r="22">
@@ -6697,13 +6697,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00118769630847341</v>
+        <v>0.00118679336985931</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00156378953998741</v>
+        <v>0.00124412109096161</v>
       </c>
       <c r="F22" t="n">
-        <v>24.050118119925</v>
+        <v>4.60788917724988</v>
       </c>
     </row>
     <row r="23">
@@ -6717,13 +6717,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000371852766098416</v>
+        <v>0.000371233227697845</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000375026378079024</v>
+        <v>0.000371485663883202</v>
       </c>
       <c r="F23" t="n">
-        <v>3.28283109252127</v>
+        <v>0.228221721524294</v>
       </c>
     </row>
     <row r="24">
@@ -6740,7 +6740,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000389398938105376</v>
+        <v>0.000372818077709026</v>
       </c>
       <c r="F24" t="e">
         <v>#NUM!</v>
@@ -6757,13 +6757,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000372621760988242</v>
+        <v>0.000372570541763392</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000415888520011253</v>
+        <v>0.000375177590486782</v>
       </c>
       <c r="F25" t="n">
-        <v>10.1114786274451</v>
+        <v>0.627828011031176</v>
       </c>
     </row>
     <row r="26">
@@ -6777,13 +6777,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0011976841131088</v>
+        <v>0.00119569414050085</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00152762709141913</v>
+        <v>0.00124047862842381</v>
       </c>
       <c r="F26" t="n">
-        <v>21.5983979443454</v>
+        <v>3.61025872568759</v>
       </c>
     </row>
     <row r="27">
@@ -6797,13 +6797,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000373062825142665</v>
+        <v>0.000371932948989793</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000375835930464556</v>
+        <v>0.000372410419002003</v>
       </c>
       <c r="F27" t="n">
-        <v>2.44825473162359</v>
+        <v>0.398536328797233</v>
       </c>
     </row>
     <row r="28">
@@ -6820,7 +6820,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000393984358615533</v>
+        <v>0.000374531893225373</v>
       </c>
       <c r="F28" t="e">
         <v>#NUM!</v>

--- a/results/chronological/consolidated/Stress_Testing.xlsx
+++ b/results/chronological/consolidated/Stress_Testing.xlsx
@@ -2201,10 +2201,10 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.000168012848226876</v>
+        <v>0.000168686737569334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00973553854254884</v>
+        <v>0.00970426437855947</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
@@ -2225,19 +2225,19 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000166562801048128</v>
+        <v>0.000166772861483521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00968450603949255</v>
+        <v>0.00969435537694422</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000166381990293448</v>
+        <v>0.000166933948048452</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00976701803883266</v>
+        <v>0.00975576335324238</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.108672071034827</v>
+        <v>0.0964971875490472</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -2257,19 +2257,19 @@
         <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000167472880396247</v>
+        <v>0.000167096003851232</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00972364448675293</v>
+        <v>0.00972274631263412</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001669427015022</v>
+        <v>0.000165178898405155</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00965139999178962</v>
+        <v>0.00970365898523208</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.317581355325513</v>
+        <v>-1.16062370229288</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -2291,10 +2291,10 @@
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.0000394838595218529</v>
+        <v>0.0000403045023125828</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00479387637026704</v>
+        <v>0.00476314150753557</v>
       </c>
       <c r="I5"/>
       <c r="J5" t="n">
@@ -2317,10 +2317,10 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000389778236759456</v>
+        <v>0.0000395518045107587</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00477347833269457</v>
+        <v>0.00476641051967204</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2341,19 +2341,19 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000388303679581553</v>
+        <v>0.0000388022922564971</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00474517618359948</v>
+        <v>0.00475143871554619</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0000399185335244449</v>
+        <v>0.0000404785367305131</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0048028757742464</v>
+        <v>0.00474907146904838</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72596578635137</v>
+        <v>4.14106983455374</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -2373,19 +2373,19 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000385844270637529</v>
+        <v>0.0000388145457237465</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00475809503347129</v>
+        <v>0.0047681507479245</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000396218173989364</v>
+        <v>0.0000385790261641135</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00485875183121341</v>
+        <v>0.00472193740859721</v>
       </c>
       <c r="I8" t="n">
-        <v>2.61823006435671</v>
+        <v>-0.610486015461072</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -2407,10 +2407,10 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9" t="n">
-        <v>0.0000909163197171449</v>
+        <v>0.0000918003257372773</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00367913244714291</v>
+        <v>0.00380444242200878</v>
       </c>
       <c r="I9"/>
       <c r="J9" t="n">
@@ -2431,19 +2431,19 @@
         <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000908374727731589</v>
+        <v>0.0000911493049180099</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00366289628874536</v>
+        <v>0.00366323865001799</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0000909780585583841</v>
+        <v>0.0000929522746724327</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00368940049730537</v>
+        <v>0.00385189594458073</v>
       </c>
       <c r="I10" t="n">
-        <v>0.154527132643754</v>
+        <v>1.93967254784948</v>
       </c>
       <c r="J10" t="n">
         <v>1356</v>
@@ -2463,19 +2463,19 @@
         <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000909839146952137</v>
+        <v>0.0000908376325719033</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00367050050416535</v>
+        <v>0.00366562613093932</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0000909876459286935</v>
+        <v>0.0000921365923869022</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00367675730170656</v>
+        <v>0.00375542558706764</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00410081329360218</v>
+        <v>1.409819683307</v>
       </c>
       <c r="J11" t="n">
         <v>1356</v>
@@ -2497,10 +2497,10 @@
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12" t="n">
-        <v>0.000210879445356703</v>
+        <v>0.000211271169167175</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00384133893310973</v>
+        <v>0.00394047465043569</v>
       </c>
       <c r="I12"/>
       <c r="J12" t="n">
@@ -2521,19 +2521,19 @@
         <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000210491823218152</v>
+        <v>0.000210547816315018</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00381030342674765</v>
+        <v>0.00381018002783672</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000210763566417222</v>
+        <v>0.000211828777632523</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00382248703932163</v>
+        <v>0.00402128409505302</v>
       </c>
       <c r="I13" t="n">
-        <v>0.128932720056797</v>
+        <v>0.604715436599983</v>
       </c>
       <c r="J13" t="n">
         <v>1356</v>
@@ -2553,19 +2553,19 @@
         <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00021060201633372</v>
+        <v>0.000210378191550601</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00381036124671783</v>
+        <v>0.00381736819816612</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000210894180591132</v>
+        <v>0.000211458084191767</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00384833573944941</v>
+        <v>0.00391205503433991</v>
       </c>
       <c r="I14" t="n">
-        <v>0.138535950396102</v>
+        <v>0.510688747272816</v>
       </c>
       <c r="J14" t="n">
         <v>1356</v>
@@ -2587,10 +2587,10 @@
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15" t="n">
-        <v>0.0000223524231367376</v>
+        <v>0.0000231252424750306</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00347565341858694</v>
+        <v>0.00357374310745804</v>
       </c>
       <c r="I15"/>
       <c r="J15" t="n">
@@ -2611,19 +2611,19 @@
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000220775924997776</v>
+        <v>0.0000220849957085853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00344472098097703</v>
+        <v>0.00344595974925313</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000226853640530436</v>
+        <v>0.0000236840696878705</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00349702121223252</v>
+        <v>0.00360067817396231</v>
       </c>
       <c r="I16" t="n">
-        <v>2.67913511039511</v>
+        <v>6.75168583929685</v>
       </c>
       <c r="J16" t="n">
         <v>1356</v>
@@ -2643,19 +2643,19 @@
         <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000220933183744288</v>
+        <v>0.000022146378611691</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00344561254483767</v>
+        <v>0.00344248352074403</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000221917077748464</v>
+        <v>0.0000233025181730723</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00345762203315949</v>
+        <v>0.00354350609513691</v>
       </c>
       <c r="I17" t="n">
-        <v>0.443361103236576</v>
+        <v>4.96143615378562</v>
       </c>
       <c r="J17" t="n">
         <v>1356</v>
@@ -2677,10 +2677,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000224495910178183</v>
+        <v>0.0000236095266963912</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00348469207961156</v>
+        <v>0.0036147337275737</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2701,19 +2701,19 @@
         <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000022192621335879</v>
+        <v>0.0000221960581697615</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00344902075624517</v>
+        <v>0.00344889088653652</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000022618362592109</v>
+        <v>0.0000238584347403858</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00349553787471214</v>
+        <v>0.00360282203305426</v>
       </c>
       <c r="I19" t="n">
-        <v>1.88228150687865</v>
+        <v>6.96766820084118</v>
       </c>
       <c r="J19" t="n">
         <v>1356</v>
@@ -2733,19 +2733,19 @@
         <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000221862920587954</v>
+        <v>0.0000222694955558963</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00344777439975394</v>
+        <v>0.00346231355143266</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0000222949695610232</v>
+        <v>0.000022862143760953</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00346402184601575</v>
+        <v>0.00355165781513772</v>
       </c>
       <c r="I20" t="n">
-        <v>0.487453019078507</v>
+        <v>2.59226873583442</v>
       </c>
       <c r="J20" t="n">
         <v>1356</v>
@@ -2767,10 +2767,10 @@
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21" t="n">
-        <v>0.000118104628623601</v>
+        <v>0.000120478191653158</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00996703116283773</v>
+        <v>0.0100333112875579</v>
       </c>
       <c r="I21"/>
       <c r="J21" t="n">
@@ -2791,19 +2791,19 @@
         <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000116096883877524</v>
+        <v>0.00011608477197814</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00987541333067351</v>
+        <v>0.00987458470430241</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00011779484283482</v>
+        <v>0.000119792761538019</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00994643555308831</v>
+        <v>0.00998113227333425</v>
       </c>
       <c r="I22" t="n">
-        <v>1.44145441042515</v>
+        <v>3.09533690706548</v>
       </c>
       <c r="J22" t="n">
         <v>904</v>
@@ -2823,19 +2823,19 @@
         <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000117863898597105</v>
+        <v>0.000118014635242703</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00996194855665492</v>
+        <v>0.00996397339898721</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000117576650393178</v>
+        <v>0.000118082523651514</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00994260516877633</v>
+        <v>0.00988880625534562</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.244307184263673</v>
+        <v>0.0574923423990511</v>
       </c>
       <c r="J23" t="n">
         <v>904</v>
@@ -2857,10 +2857,10 @@
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24" t="n">
-        <v>0.000237924019937213</v>
+        <v>0.000241314086461098</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0117325121427731</v>
+        <v>0.0117724167845115</v>
       </c>
       <c r="I24"/>
       <c r="J24" t="n">
@@ -2881,19 +2881,19 @@
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000240027542340218</v>
+        <v>0.000240254897910958</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0117413709217668</v>
+        <v>0.0117491839519689</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000234691761195535</v>
+        <v>0.000236887716973761</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0115964821194843</v>
+        <v>0.0116185256841245</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.27352725016914</v>
+        <v>-1.4214248759761</v>
       </c>
       <c r="J25" t="n">
         <v>143</v>
@@ -2913,19 +2913,19 @@
         <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000237576440500113</v>
+        <v>0.00023749979494174</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0116666923026084</v>
+        <v>0.0116736994474247</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000238722857025175</v>
+        <v>0.000238100068376096</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0117013659047123</v>
+        <v>0.0116744775589956</v>
       </c>
       <c r="I26" t="n">
-        <v>0.480229056969</v>
+        <v>0.25210972783456</v>
       </c>
       <c r="J26" t="n">
         <v>143</v>
@@ -2947,10 +2947,10 @@
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27" t="n">
-        <v>0.0000995129810803254</v>
+        <v>0.0000976494445238349</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00755756152295052</v>
+        <v>0.00744735465114372</v>
       </c>
       <c r="I27"/>
       <c r="J27" t="n">
@@ -2973,10 +2973,10 @@
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28" t="n">
-        <v>0.292582175522293</v>
+        <v>0.830685797285985</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0833950533585992</v>
+        <v>0.149385629663156</v>
       </c>
       <c r="I28"/>
       <c r="J28" t="n">
@@ -2997,19 +2997,19 @@
         <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0000969830334655324</v>
+        <v>0.000096903548145345</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00737682990190657</v>
+        <v>0.00738222689257791</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0000948206981424455</v>
+        <v>0.0000974007116774414</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00730920197224464</v>
+        <v>0.00749900633507157</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.28044653271638</v>
+        <v>0.510431108288857</v>
       </c>
       <c r="J29" t="n">
         <v>59</v>
@@ -3029,19 +3029,19 @@
         <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0000962990727686393</v>
+        <v>0.0000965134272049953</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00735211799936693</v>
+        <v>0.00737884943851464</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0000955396205013617</v>
+        <v>0.0000977110084807977</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00735827515496806</v>
+        <v>0.00733247315940514</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.794908189180898</v>
+        <v>1.22563597942776</v>
       </c>
       <c r="J30" t="n">
         <v>59</v>
@@ -3063,10 +3063,10 @@
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31" t="n">
-        <v>0.000103469299681138</v>
+        <v>0.000105138890137807</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00456600302431706</v>
+        <v>0.00463390394844477</v>
       </c>
       <c r="I31"/>
       <c r="J31" t="n">
@@ -3087,19 +3087,19 @@
         <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00010358484523185</v>
+        <v>0.000103500206962902</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0045488013143906</v>
+        <v>0.00454816758471772</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000103780232663501</v>
+        <v>0.000105057636617128</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00456031986314871</v>
+        <v>0.00474218482024222</v>
       </c>
       <c r="I32" t="n">
-        <v>0.188270373495941</v>
+        <v>1.48245258924101</v>
       </c>
       <c r="J32" t="n">
         <v>1356</v>
@@ -3119,19 +3119,19 @@
         <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000103479301034791</v>
+        <v>0.000103042316098792</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00455198431025287</v>
+        <v>0.00455396567523226</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000103467514539824</v>
+        <v>0.000103716125508746</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00455643765317813</v>
+        <v>0.00461844024646972</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0113914932811296</v>
+        <v>0.649666969961517</v>
       </c>
       <c r="J33" t="n">
         <v>1356</v>
@@ -3153,10 +3153,10 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.000222689674794028</v>
+        <v>0.0002232359749759</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00470639606659162</v>
+        <v>0.004779176257381</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
@@ -3177,19 +3177,19 @@
         <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000222899865221556</v>
+        <v>0.000222736870573489</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0046950535944229</v>
+        <v>0.00469571713525595</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00022233574224847</v>
+        <v>0.000225822947087929</v>
       </c>
       <c r="H35" t="n">
-        <v>0.004715386664599</v>
+        <v>0.00487692343074086</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.253725724609545</v>
+        <v>1.36659119643778</v>
       </c>
       <c r="J35" t="n">
         <v>1356</v>
@@ -3209,19 +3209,19 @@
         <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.000222657099915918</v>
+        <v>0.00022254082437536</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0046971628550312</v>
+        <v>0.00471338265169423</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00022289278399334</v>
+        <v>0.000223697588902695</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00469636719445802</v>
+        <v>0.00477900913009476</v>
       </c>
       <c r="I36" t="n">
-        <v>0.105738765158737</v>
+        <v>0.517110860697776</v>
       </c>
       <c r="J36" t="n">
         <v>1356</v>
@@ -3243,10 +3243,10 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37" t="n">
-        <v>0.0000354850101297475</v>
+        <v>0.0000360613514685076</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00434752632850846</v>
+        <v>0.00441149099105941</v>
       </c>
       <c r="I37"/>
       <c r="J37" t="n">
@@ -3267,19 +3267,19 @@
         <v>46</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0000352632451049437</v>
+        <v>0.0000352893534349984</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00432952817316515</v>
+        <v>0.00433173896860628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0000360503228540325</v>
+        <v>0.0000375781701462824</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00439270892941174</v>
+        <v>0.00454250508978385</v>
       </c>
       <c r="I38" t="n">
-        <v>2.18327517419379</v>
+        <v>6.09081470006166</v>
       </c>
       <c r="J38" t="n">
         <v>1356</v>
@@ -3299,19 +3299,19 @@
         <v>47</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0000352584464270468</v>
+        <v>0.0000352535610816748</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00432944210135638</v>
+        <v>0.00433620863786005</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000352804169931256</v>
+        <v>0.0000358948522048799</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00434821739079862</v>
+        <v>0.00438510914715597</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0622741111112526</v>
+        <v>1.78658243122098</v>
       </c>
       <c r="J39" t="n">
         <v>1356</v>
@@ -3333,10 +3333,10 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40" t="n">
-        <v>0.0000352589255565391</v>
+        <v>0.000037075527171547</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00434582816655067</v>
+        <v>0.00445335648233131</v>
       </c>
       <c r="I40"/>
       <c r="J40" t="n">
@@ -3357,19 +3357,19 @@
         <v>46</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0000353359900355605</v>
+        <v>0.000035341952461012</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00433337932653729</v>
+        <v>0.0043333460246805</v>
       </c>
       <c r="G41" t="n">
-        <v>0.000035523145871124</v>
+        <v>0.0000377757810605194</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00437914514010886</v>
+        <v>0.00454948527139777</v>
       </c>
       <c r="I41" t="n">
-        <v>0.526856028580774</v>
+        <v>6.44282800032192</v>
       </c>
       <c r="J41" t="n">
         <v>1356</v>
@@ -3389,19 +3389,19 @@
         <v>47</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0000352993334686903</v>
+        <v>0.0000352174686628394</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00433590492373329</v>
+        <v>0.00433039996899882</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0000354714422896823</v>
+        <v>0.0000362553165181104</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00435047976478737</v>
+        <v>0.00439740927962886</v>
       </c>
       <c r="I42" t="n">
-        <v>0.485203898918008</v>
+        <v>2.86260872871605</v>
       </c>
       <c r="J42" t="n">
         <v>1356</v>
@@ -3423,10 +3423,10 @@
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43" t="n">
-        <v>0.000131827964784891</v>
+        <v>0.000133468961478627</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0101806329983924</v>
+        <v>0.0102222094776653</v>
       </c>
       <c r="I43"/>
       <c r="J43" t="n">
@@ -3449,10 +3449,10 @@
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44" t="n">
-        <v>0.000118803372758431</v>
+        <v>0.000120581276377261</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00954154013277616</v>
+        <v>0.00957882634204162</v>
       </c>
       <c r="I44"/>
       <c r="J44" t="n">
@@ -3473,19 +3473,19 @@
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001414857018751</v>
+        <v>0.000141508269708647</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0106222637269262</v>
+        <v>0.0106227898698546</v>
       </c>
       <c r="G45" t="n">
-        <v>0.000126356938748648</v>
+        <v>0.000127515913326502</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00989127942739404</v>
+        <v>0.00991303286838473</v>
       </c>
       <c r="I45" t="n">
-        <v>-11.9730370775652</v>
+        <v>-10.9730276144572</v>
       </c>
       <c r="J45" t="n">
         <v>904</v>
@@ -3505,19 +3505,19 @@
         <v>47</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000133570781644775</v>
+        <v>0.000133785593225993</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0102577867023216</v>
+        <v>0.0102667448135987</v>
       </c>
       <c r="G46" t="n">
-        <v>0.000130276196310112</v>
+        <v>0.000130497832556177</v>
       </c>
       <c r="H46" t="n">
-        <v>0.010102478483756</v>
+        <v>0.0101008922858352</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.52892349329941</v>
+        <v>-2.51939867920835</v>
       </c>
       <c r="J46" t="n">
         <v>904</v>
@@ -3539,10 +3539,10 @@
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47" t="n">
-        <v>0.000516616822406843</v>
+        <v>0.00051640075999157</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0165168297565646</v>
+        <v>0.0164958855706283</v>
       </c>
       <c r="I47"/>
       <c r="J47" t="n">
@@ -3563,19 +3563,19 @@
         <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000512806842840657</v>
+        <v>0.000512579964774807</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0165127970776505</v>
+        <v>0.0165058165355639</v>
       </c>
       <c r="G48" t="n">
-        <v>0.000517788662744236</v>
+        <v>0.000513517743105937</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0164971593411957</v>
+        <v>0.0165473064586123</v>
       </c>
       <c r="I48" t="n">
-        <v>0.962133832203817</v>
+        <v>0.182618486648236</v>
       </c>
       <c r="J48" t="n">
         <v>143</v>
@@ -3595,19 +3595,19 @@
         <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000514185326971938</v>
+        <v>0.000519431667521127</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0164066911021035</v>
+        <v>0.0164993944488472</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000513591561800653</v>
+        <v>0.000513036856868621</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0164713489784217</v>
+        <v>0.0165274761435378</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.115610382928344</v>
+        <v>-1.24646223110316</v>
       </c>
       <c r="J49" t="n">
         <v>143</v>
@@ -3629,10 +3629,10 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.00025887137451676</v>
+        <v>0.000260418757469357</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0121919229021894</v>
+        <v>0.0122640000949425</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
@@ -3653,19 +3653,19 @@
         <v>46</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000256458779390605</v>
+        <v>0.000256674386722905</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0120478853153263</v>
+        <v>0.0120328290801632</v>
       </c>
       <c r="G51" t="n">
-        <v>0.00025262803724549</v>
+        <v>0.000252769102373959</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0119162024329556</v>
+        <v>0.0120126046785228</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.51635669060443</v>
+        <v>-1.54500067938191</v>
       </c>
       <c r="J51" t="n">
         <v>59</v>
@@ -3685,19 +3685,19 @@
         <v>47</v>
       </c>
       <c r="E52" t="n">
-        <v>0.000258105524459544</v>
+        <v>0.000260683997833854</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0120810685791986</v>
+        <v>0.012215472669499</v>
       </c>
       <c r="G52" t="n">
-        <v>0.000259288302320898</v>
+        <v>0.000261747631599948</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0120670563421511</v>
+        <v>0.0121573146188589</v>
       </c>
       <c r="I52" t="n">
-        <v>0.456163217070273</v>
+        <v>0.406358506318553</v>
       </c>
       <c r="J52" t="n">
         <v>59</v>
@@ -3719,10 +3719,10 @@
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53" t="n">
-        <v>0.000162906224822172</v>
+        <v>0.000163912916132638</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0077507945516883</v>
+        <v>0.00777158051656032</v>
       </c>
       <c r="I53"/>
       <c r="J53" t="n">
@@ -3743,19 +3743,19 @@
         <v>46</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000163444483383347</v>
+        <v>0.000163199612143657</v>
       </c>
       <c r="F54" t="n">
-        <v>0.00777072663832541</v>
+        <v>0.00777429899374019</v>
       </c>
       <c r="G54" t="n">
-        <v>0.000162666790246751</v>
+        <v>0.000164144129669294</v>
       </c>
       <c r="H54" t="n">
-        <v>0.00775820310463819</v>
+        <v>0.00778668254139907</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.478089679778036</v>
+        <v>0.575419619050758</v>
       </c>
       <c r="J54" t="n">
         <v>1356</v>
@@ -3775,19 +3775,19 @@
         <v>47</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000162344675989324</v>
+        <v>0.000162869542806892</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00771087495893431</v>
+        <v>0.00772508980534471</v>
       </c>
       <c r="G55" t="n">
-        <v>0.00016255809225367</v>
+        <v>0.000163423638235491</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00773755598539883</v>
+        <v>0.00775183501599565</v>
       </c>
       <c r="I55" t="n">
-        <v>0.131286152160834</v>
+        <v>0.339054640186476</v>
       </c>
       <c r="J55" t="n">
         <v>1356</v>
@@ -3809,10 +3809,10 @@
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56" t="n">
-        <v>0.000283212431303479</v>
+        <v>0.000284022983668778</v>
       </c>
       <c r="H56" t="n">
-        <v>0.00787760802375231</v>
+        <v>0.00792201268064297</v>
       </c>
       <c r="I56"/>
       <c r="J56" t="n">
@@ -3833,19 +3833,19 @@
         <v>46</v>
       </c>
       <c r="E57" t="n">
-        <v>0.000282815668879992</v>
+        <v>0.000282339956097267</v>
       </c>
       <c r="F57" t="n">
-        <v>0.00792005079901508</v>
+        <v>0.00791829105903136</v>
       </c>
       <c r="G57" t="n">
-        <v>0.000282196361704233</v>
+        <v>0.000284477931643895</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00791488543901683</v>
+        <v>0.00793269269042557</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.219459659939844</v>
+        <v>0.751543550064957</v>
       </c>
       <c r="J57" t="n">
         <v>1356</v>
@@ -3865,19 +3865,19 @@
         <v>47</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000281480184614982</v>
+        <v>0.000281679695387752</v>
       </c>
       <c r="F58" t="n">
-        <v>0.00784388874615388</v>
+        <v>0.00787518484721763</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000283006146848539</v>
+        <v>0.000286120212369316</v>
       </c>
       <c r="H58" t="n">
-        <v>0.00789952222352718</v>
+        <v>0.00796346392707323</v>
       </c>
       <c r="I58" t="n">
-        <v>0.539197558268408</v>
+        <v>1.55197598407767</v>
       </c>
       <c r="J58" t="n">
         <v>1356</v>
@@ -3899,10 +3899,10 @@
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.0000940229083161743</v>
+        <v>0.0000953941486679623</v>
       </c>
       <c r="H59" t="n">
-        <v>0.00752134277093106</v>
+        <v>0.00758759018338344</v>
       </c>
       <c r="I59"/>
       <c r="J59" t="n">
@@ -3923,19 +3923,19 @@
         <v>46</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000094142197351141</v>
+        <v>0.000094115806746459</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00755450300734596</v>
+        <v>0.0075551441247932</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0000934753542243088</v>
+        <v>0.0000946623485766923</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00750695747425842</v>
+        <v>0.00754332421676345</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.71338924828459</v>
+        <v>0.577359254709895</v>
       </c>
       <c r="J60" t="n">
         <v>1356</v>
@@ -3955,19 +3955,19 @@
         <v>47</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0000936171558442319</v>
+        <v>0.0000940865136941432</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00749339743158192</v>
+        <v>0.00751423157600635</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0000942811552980978</v>
+        <v>0.0000959647742698298</v>
       </c>
       <c r="H61" t="n">
-        <v>0.00753898218570277</v>
+        <v>0.00760899578196267</v>
       </c>
       <c r="I61" t="n">
-        <v>0.704275898790669</v>
+        <v>1.95723961211583</v>
       </c>
       <c r="J61" t="n">
         <v>1356</v>
@@ -3989,10 +3989,10 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.0000947962811010623</v>
+        <v>0.0000949337910695293</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00755875345228711</v>
+        <v>0.00753839939038186</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -4013,19 +4013,19 @@
         <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0000941958059141655</v>
+        <v>0.0000942717789076125</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00755668532245322</v>
+        <v>0.00756051290685797</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0000938142965855758</v>
+        <v>0.0000966093641318648</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0075175861579488</v>
+        <v>0.00764764298794843</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.406664381096431</v>
+        <v>2.41962592887133</v>
       </c>
       <c r="J63" t="n">
         <v>1356</v>
@@ -4045,19 +4045,19 @@
         <v>47</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0000935772020226656</v>
+        <v>0.0000935958250157173</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00749055676435012</v>
+        <v>0.00750519647103852</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0000942778270800512</v>
+        <v>0.0000957695508813098</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0075251859606301</v>
+        <v>0.0075787979562898</v>
       </c>
       <c r="I64" t="n">
-        <v>0.74314934813958</v>
+        <v>2.26974632917146</v>
       </c>
       <c r="J64" t="n">
         <v>1356</v>
@@ -4079,10 +4079,10 @@
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000217078768001028</v>
+        <v>0.000219074500375511</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0123170236265169</v>
+        <v>0.0123435687331036</v>
       </c>
       <c r="I65"/>
       <c r="J65" t="n">
@@ -4103,19 +4103,19 @@
         <v>46</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000226774658862064</v>
+        <v>0.000226753925554217</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0126567294583957</v>
+        <v>0.0126561827699229</v>
       </c>
       <c r="G66" t="n">
-        <v>0.000215394276598182</v>
+        <v>0.000216397716693238</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0122400174835535</v>
+        <v>0.0122215291273252</v>
       </c>
       <c r="I66" t="n">
-        <v>-5.28351191295214</v>
+        <v>-4.78572926703244</v>
       </c>
       <c r="J66" t="n">
         <v>904</v>
@@ -4135,19 +4135,19 @@
         <v>47</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000210230636751771</v>
+        <v>0.000210732340051025</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0120586133573266</v>
+        <v>0.0120781025365511</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000218369603078567</v>
+        <v>0.000219100145523878</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0123428273035239</v>
+        <v>0.0123936081674398</v>
       </c>
       <c r="I67" t="n">
-        <v>3.72715167864653</v>
+        <v>3.81916929030111</v>
       </c>
       <c r="J67" t="n">
         <v>904</v>
@@ -4169,10 +4169,10 @@
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.00356738074628703</v>
+        <v>0.00359361205954346</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0491665162131087</v>
+        <v>0.0489229727884067</v>
       </c>
       <c r="I68"/>
       <c r="J68" t="n">
@@ -4193,19 +4193,19 @@
         <v>46</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00359417098707252</v>
+        <v>0.00359485200917855</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0493769851300678</v>
+        <v>0.0493321758124025</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00356547121089913</v>
+        <v>0.00354137926118332</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0493410102398191</v>
+        <v>0.0494420366478078</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.804936415855917</v>
+        <v>-1.50994129833364</v>
       </c>
       <c r="J69" t="n">
         <v>143</v>
@@ -4225,19 +4225,19 @@
         <v>47</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00357142072037244</v>
+        <v>0.00361763266038078</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0493017215544986</v>
+        <v>0.0496083913704915</v>
       </c>
       <c r="G70" t="n">
-        <v>0.00358463161868233</v>
+        <v>0.00361156619525572</v>
       </c>
       <c r="H70" t="n">
-        <v>0.049377752825185</v>
+        <v>0.0495940543522813</v>
       </c>
       <c r="I70" t="n">
-        <v>0.368542704389443</v>
+        <v>-0.167973250304351</v>
       </c>
       <c r="J70" t="n">
         <v>143</v>
@@ -4259,10 +4259,10 @@
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71" t="n">
-        <v>0.00341654496767278</v>
+        <v>0.00353394491403295</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0450729748215993</v>
+        <v>0.0466505137776462</v>
       </c>
       <c r="I71"/>
       <c r="J71" t="n">
@@ -4283,19 +4283,19 @@
         <v>48</v>
       </c>
       <c r="E72" t="n">
-        <v>4.41781437905188</v>
+        <v>4.41926393746313</v>
       </c>
       <c r="F72" t="n">
-        <v>2.10103526254686</v>
+        <v>2.1013802532007</v>
       </c>
       <c r="G72" t="n">
-        <v>3.63959608111757</v>
+        <v>3.58789325409697</v>
       </c>
       <c r="H72" t="n">
-        <v>1.90398638880817</v>
+        <v>1.8894545761062</v>
       </c>
       <c r="I72" t="n">
-        <v>-21.3819962597432</v>
+        <v>-23.1715556870826</v>
       </c>
       <c r="J72" t="n">
         <v>59</v>
@@ -4315,19 +4315,19 @@
         <v>46</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00346597714960312</v>
+        <v>0.00347412929413676</v>
       </c>
       <c r="F73" t="n">
-        <v>0.045441537595296</v>
+        <v>0.0455671619890465</v>
       </c>
       <c r="G73" t="n">
-        <v>0.00346035435447877</v>
+        <v>0.00336908984281903</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0453335981152301</v>
+        <v>0.0450204435591811</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.162491888065416</v>
+        <v>-3.11773969286127</v>
       </c>
       <c r="J73" t="n">
         <v>59</v>
@@ -4347,19 +4347,19 @@
         <v>47</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0034721922497019</v>
+        <v>0.00346827427474752</v>
       </c>
       <c r="F74" t="n">
-        <v>0.045571673780738</v>
+        <v>0.0454349590163139</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00349527415221793</v>
+        <v>0.00344640958199682</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0457786519248969</v>
+        <v>0.0451644394227361</v>
       </c>
       <c r="I74" t="n">
-        <v>0.66037459469045</v>
+        <v>-0.634419451040232</v>
       </c>
       <c r="J74" t="n">
         <v>59</v>
@@ -4381,10 +4381,10 @@
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75" t="n">
-        <v>0.00126949174070929</v>
+        <v>0.00129939543247604</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0253883913569005</v>
+        <v>0.0257297258080896</v>
       </c>
       <c r="I75"/>
       <c r="J75" t="n">
@@ -4405,19 +4405,19 @@
         <v>48</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00126830026415411</v>
+        <v>0.00127368533224027</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0253599391870407</v>
+        <v>0.0253733320670219</v>
       </c>
       <c r="G76" t="n">
-        <v>0.00129977802592766</v>
+        <v>0.00141346108785193</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0258020806307223</v>
+        <v>0.0274994639637762</v>
       </c>
       <c r="I76" t="n">
-        <v>2.42177980744703</v>
+        <v>9.88890014822223</v>
       </c>
       <c r="J76" t="n">
         <v>1356</v>
@@ -4437,19 +4437,19 @@
         <v>46</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00126859220588297</v>
+        <v>0.00126832649343184</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0252680416011099</v>
+        <v>0.0252649741570728</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00128442262970654</v>
+        <v>0.00132899081410772</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0256080947054334</v>
+        <v>0.0261532079692212</v>
       </c>
       <c r="I77" t="n">
-        <v>1.23249337542304</v>
+        <v>4.56469074367629</v>
       </c>
       <c r="J77" t="n">
         <v>1356</v>
@@ -4469,19 +4469,19 @@
         <v>47</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00126995970422846</v>
+        <v>0.00127321893707097</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0253760635545864</v>
+        <v>0.0254167540510852</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00127101209670812</v>
+        <v>0.00128233567278445</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0253582808200466</v>
+        <v>0.0255147342653038</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0827995644088251</v>
+        <v>0.710947679844543</v>
       </c>
       <c r="J78" t="n">
         <v>1356</v>
@@ -4503,10 +4503,10 @@
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79" t="n">
-        <v>0.00140419518819495</v>
+        <v>0.00142018970248723</v>
       </c>
       <c r="H79" t="n">
-        <v>0.025481153790619</v>
+        <v>0.0260228734433242</v>
       </c>
       <c r="I79"/>
       <c r="J79" t="n">
@@ -4527,19 +4527,19 @@
         <v>48</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00139712173476602</v>
+        <v>0.00140403196291606</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0254733982020694</v>
+        <v>0.0255066194328175</v>
       </c>
       <c r="G80" t="n">
-        <v>0.001425484568641</v>
+        <v>0.00158125397994027</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0258826651453883</v>
+        <v>0.0278299692907715</v>
       </c>
       <c r="I80" t="n">
-        <v>1.98969771395195</v>
+        <v>11.2076882823658</v>
       </c>
       <c r="J80" t="n">
         <v>1356</v>
@@ -4559,19 +4559,19 @@
         <v>46</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00139813813367398</v>
+        <v>0.00139811432927473</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0254133277403025</v>
+        <v>0.0254180627369097</v>
       </c>
       <c r="G81" t="n">
-        <v>0.00141856559100391</v>
+        <v>0.00144230396013013</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0258847669183924</v>
+        <v>0.026216388356017</v>
       </c>
       <c r="I81" t="n">
-        <v>1.44000795306687</v>
+        <v>3.06382233405254</v>
       </c>
       <c r="J81" t="n">
         <v>1356</v>
@@ -4591,19 +4591,19 @@
         <v>47</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00139945268126122</v>
+        <v>0.00139787310550105</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0255091669592029</v>
+        <v>0.025542366020423</v>
       </c>
       <c r="G82" t="n">
-        <v>0.00139967000198347</v>
+        <v>0.00141021011183999</v>
       </c>
       <c r="H82" t="n">
-        <v>0.025516387553182</v>
+        <v>0.0256728421723744</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0155265685440839</v>
+        <v>0.87483462466706</v>
       </c>
       <c r="J82" t="n">
         <v>1356</v>
@@ -4625,10 +4625,10 @@
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.00119422204118529</v>
+        <v>0.00120657733759437</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0252613519128394</v>
+        <v>0.0254382396213519</v>
       </c>
       <c r="I83"/>
       <c r="J83" t="n">
@@ -4649,19 +4649,19 @@
         <v>48</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00118679336985931</v>
+        <v>0.00119191264969172</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0251152137543551</v>
+        <v>0.0252710339242026</v>
       </c>
       <c r="G84" t="n">
-        <v>0.00124412109096161</v>
+        <v>0.00133931606282742</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0259156960012802</v>
+        <v>0.0271453538137612</v>
       </c>
       <c r="I84" t="n">
-        <v>4.60788917724988</v>
+        <v>11.005872118379</v>
       </c>
       <c r="J84" t="n">
         <v>1356</v>
@@ -4681,19 +4681,19 @@
         <v>46</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00118778533927516</v>
+        <v>0.00118728364286866</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0250749117734855</v>
+        <v>0.0250730012699673</v>
       </c>
       <c r="G85" t="n">
-        <v>0.00120601175593113</v>
+        <v>0.0012653455231335</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0254706531847801</v>
+        <v>0.0260776128088539</v>
       </c>
       <c r="I85" t="n">
-        <v>1.51129676525456</v>
+        <v>6.16921456137385</v>
       </c>
       <c r="J85" t="n">
         <v>1356</v>
@@ -4713,19 +4713,19 @@
         <v>47</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00118902653318703</v>
+        <v>0.00119280862763669</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0251750857397259</v>
+        <v>0.0252323313056193</v>
       </c>
       <c r="G86" t="n">
-        <v>0.00118943823214851</v>
+        <v>0.00120366796734008</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0251594834864654</v>
+        <v>0.0252634378524213</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0346128912248868</v>
+        <v>0.902187313947106</v>
       </c>
       <c r="J86" t="n">
         <v>1356</v>
@@ -4747,10 +4747,10 @@
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.00119969768924166</v>
+        <v>0.00122029760265053</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0252553485936688</v>
+        <v>0.0257213535607059</v>
       </c>
       <c r="I87"/>
       <c r="J87" t="n">
@@ -4771,19 +4771,19 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00119569414050085</v>
+        <v>0.00119681005362634</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0252105032247734</v>
+        <v>0.0252182665668578</v>
       </c>
       <c r="G88" t="n">
-        <v>0.00124047862842381</v>
+        <v>0.00134656770183042</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0258516978783029</v>
+        <v>0.0273573758161006</v>
       </c>
       <c r="I88" t="n">
-        <v>3.61025872568759</v>
+        <v>11.1214347411203</v>
       </c>
       <c r="J88" t="n">
         <v>1356</v>
@@ -4803,19 +4803,19 @@
         <v>46</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00119317092850798</v>
+        <v>0.00119262458285996</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0251027954498308</v>
+        <v>0.0250957861042803</v>
       </c>
       <c r="G89" t="n">
-        <v>0.00120390651881475</v>
+        <v>0.00125141730232595</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0253751563985663</v>
+        <v>0.0261721107435556</v>
       </c>
       <c r="I89" t="n">
-        <v>0.891729560309629</v>
+        <v>4.6980906654166</v>
       </c>
       <c r="J89" t="n">
         <v>1356</v>
@@ -4835,19 +4835,19 @@
         <v>47</v>
       </c>
       <c r="E90" t="n">
-        <v>0.00119417568972794</v>
+        <v>0.0011925892466452</v>
       </c>
       <c r="F90" t="n">
-        <v>0.025188313775438</v>
+        <v>0.0252024743848921</v>
       </c>
       <c r="G90" t="n">
-        <v>0.00119257133030756</v>
+        <v>0.00120132534186739</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0251337000886586</v>
+        <v>0.0252970633990847</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.134529430618063</v>
+        <v>0.727204772739514</v>
       </c>
       <c r="J90" t="n">
         <v>1356</v>
@@ -4869,10 +4869,10 @@
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.00107171596067512</v>
+        <v>0.00107709167434717</v>
       </c>
       <c r="H91" t="n">
-        <v>0.022935504523937</v>
+        <v>0.0231683950008167</v>
       </c>
       <c r="I91"/>
       <c r="J91" t="n">
@@ -4893,19 +4893,19 @@
         <v>46</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0010755597003059</v>
+        <v>0.00107579040585935</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0230195832292353</v>
+        <v>0.0230264904002747</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00106160866552392</v>
+        <v>0.00109508474380975</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0227152253529482</v>
+        <v>0.0234971599887171</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.31414100459448</v>
+        <v>1.76190363891582</v>
       </c>
       <c r="J92" t="n">
         <v>904</v>
@@ -4925,19 +4925,19 @@
         <v>47</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00105006788309468</v>
+        <v>0.00104800916598896</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0226109310151397</v>
+        <v>0.0225697680372925</v>
       </c>
       <c r="G93" t="n">
-        <v>0.00105559105450692</v>
+        <v>0.00105684006373575</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0227205444155499</v>
+        <v>0.0227145537684215</v>
       </c>
       <c r="I93" t="n">
-        <v>0.523230221463248</v>
+        <v>0.835594528426302</v>
       </c>
       <c r="J93" t="n">
         <v>904</v>
@@ -4959,10 +4959,10 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.0016629924424144</v>
+        <v>0.00165801205264355</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0305983889368759</v>
+        <v>0.0306393865520959</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -4983,19 +4983,19 @@
         <v>46</v>
       </c>
       <c r="E95" t="n">
-        <v>0.00167503372265746</v>
+        <v>0.00167767137845497</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0308214105538606</v>
+        <v>0.0308535525403695</v>
       </c>
       <c r="G95" t="n">
-        <v>0.00165700077894368</v>
+        <v>0.0016754592482692</v>
       </c>
       <c r="H95" t="n">
-        <v>0.03054740541421</v>
+        <v>0.0307275709575662</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.08828818567431</v>
+        <v>-0.132031273697815</v>
       </c>
       <c r="J95" t="n">
         <v>143</v>
@@ -5015,19 +5015,19 @@
         <v>47</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0016625104376959</v>
+        <v>0.00165933224312697</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0306435767036062</v>
+        <v>0.0306410646750981</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00166535765885425</v>
+        <v>0.00166767405914687</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0306967340726227</v>
+        <v>0.0307704067464129</v>
       </c>
       <c r="I96" t="n">
-        <v>0.170967548214427</v>
+        <v>0.50020661856264</v>
       </c>
       <c r="J96" t="n">
         <v>143</v>
@@ -5049,10 +5049,10 @@
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00222235977088024</v>
+        <v>0.00219397279986159</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0352393461219392</v>
+        <v>0.0348184667053898</v>
       </c>
       <c r="I97"/>
       <c r="J97" t="n">
@@ -5073,19 +5073,19 @@
         <v>46</v>
       </c>
       <c r="E98" t="n">
-        <v>0.00221471440718524</v>
+        <v>0.00221171365255538</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0350340858182158</v>
+        <v>0.0349917490732939</v>
       </c>
       <c r="G98" t="n">
-        <v>0.00222317765715165</v>
+        <v>0.00219531889035867</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0350007528363568</v>
+        <v>0.0348039822241817</v>
       </c>
       <c r="I98" t="n">
-        <v>0.380682575645363</v>
+        <v>-0.746805499132938</v>
       </c>
       <c r="J98" t="n">
         <v>59</v>
@@ -5105,19 +5105,19 @@
         <v>47</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00221741788104407</v>
+        <v>0.00222425899670776</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0351100416011255</v>
+        <v>0.0349666048167687</v>
       </c>
       <c r="G99" t="n">
-        <v>0.00221121439533158</v>
+        <v>0.00223423375933978</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0350610154199865</v>
+        <v>0.0351989436854309</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.280546550600572</v>
+        <v>0.446451164311883</v>
       </c>
       <c r="J99" t="n">
         <v>59</v>
@@ -5139,10 +5139,10 @@
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.00044093681053862</v>
+        <v>0.00044388554500548</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0138513787439611</v>
+        <v>0.0139170029038713</v>
       </c>
       <c r="I100"/>
       <c r="J100" t="n">
@@ -5163,19 +5163,19 @@
         <v>46</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000439311628114974</v>
+        <v>0.000439974285919277</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0138107058102261</v>
+        <v>0.0138159439735513</v>
       </c>
       <c r="G101" t="n">
-        <v>0.000440783986579755</v>
+        <v>0.000440961902269623</v>
       </c>
       <c r="H101" t="n">
-        <v>0.013852439801653</v>
+        <v>0.0138507046608504</v>
       </c>
       <c r="I101" t="n">
-        <v>0.334031750156272</v>
+        <v>0.223968634311138</v>
       </c>
       <c r="J101" t="n">
         <v>1356</v>
@@ -5195,19 +5195,19 @@
         <v>47</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000439496550493423</v>
+        <v>0.000439845086265423</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0138350546445429</v>
+        <v>0.0138525399354658</v>
       </c>
       <c r="G102" t="n">
-        <v>0.000440834250232135</v>
+        <v>0.000440624382932558</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0138370229172925</v>
+        <v>0.0138788724566194</v>
       </c>
       <c r="I102" t="n">
-        <v>0.303447324704921</v>
+        <v>0.176861902636555</v>
       </c>
       <c r="J102" t="n">
         <v>1356</v>
@@ -5229,10 +5229,10 @@
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.000559468640765309</v>
+        <v>0.000564040080425826</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0139976827511502</v>
+        <v>0.0140496933121928</v>
       </c>
       <c r="I103"/>
       <c r="J103" t="n">
@@ -5253,19 +5253,19 @@
         <v>46</v>
       </c>
       <c r="E104" t="n">
-        <v>0.000558226037271329</v>
+        <v>0.000560769395159396</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0139596113089262</v>
+        <v>0.0139627289503163</v>
       </c>
       <c r="G104" t="n">
-        <v>0.000559754006059833</v>
+        <v>0.000565120901327657</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0140653818557902</v>
+        <v>0.0141382598390514</v>
       </c>
       <c r="I104" t="n">
-        <v>0.272971478892965</v>
+        <v>0.770013311848341</v>
       </c>
       <c r="J104" t="n">
         <v>1356</v>
@@ -5285,19 +5285,19 @@
         <v>47</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000558433917692732</v>
+        <v>0.000558017658895458</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0139808410180449</v>
+        <v>0.0139846989880688</v>
       </c>
       <c r="G105" t="n">
-        <v>0.000558647688288992</v>
+        <v>0.000561189824155014</v>
       </c>
       <c r="H105" t="n">
-        <v>0.013969263166289</v>
+        <v>0.0140593369457126</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0382657264571899</v>
+        <v>0.565257088246883</v>
       </c>
       <c r="J105" t="n">
         <v>1356</v>
@@ -5319,10 +5319,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.00037099982872742</v>
+        <v>0.000375867714693547</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0135891021428979</v>
+        <v>0.0137004109084272</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -5343,19 +5343,19 @@
         <v>46</v>
       </c>
       <c r="E107" t="n">
-        <v>0.000372200312311268</v>
+        <v>0.000372032169871245</v>
       </c>
       <c r="F107" t="n">
-        <v>0.013593885199505</v>
+        <v>0.0135919185493906</v>
       </c>
       <c r="G107" t="n">
-        <v>0.000372359424094623</v>
+        <v>0.000372903627829227</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0136147701958315</v>
+        <v>0.013676742553819</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0427306986366075</v>
+        <v>0.233695221216993</v>
       </c>
       <c r="J107" t="n">
         <v>1356</v>
@@ -5375,19 +5375,19 @@
         <v>47</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000372538656917855</v>
+        <v>0.000372069421134595</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0136226666468386</v>
+        <v>0.0136056373613499</v>
       </c>
       <c r="G108" t="n">
-        <v>0.000373395376005613</v>
+        <v>0.000373256752247392</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0136398574458481</v>
+        <v>0.0136237415927978</v>
       </c>
       <c r="I108" t="n">
-        <v>0.229440197391443</v>
+        <v>0.318100370762827</v>
       </c>
       <c r="J108" t="n">
         <v>1356</v>
@@ -5409,10 +5409,10 @@
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.000372306715581013</v>
+        <v>0.00037219150633222</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0136329797466528</v>
+        <v>0.0136546082963883</v>
       </c>
       <c r="I109"/>
       <c r="J109" t="n">
@@ -5433,19 +5433,19 @@
         <v>46</v>
       </c>
       <c r="E110" t="n">
-        <v>0.000372186054354876</v>
+        <v>0.000372027483026352</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0135936079494866</v>
+        <v>0.0135887949508507</v>
       </c>
       <c r="G110" t="n">
-        <v>0.000371919996639911</v>
+        <v>0.000376853132503008</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0135997143779944</v>
+        <v>0.0137365987375999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0715362759112003</v>
+        <v>1.28051197149539</v>
       </c>
       <c r="J110" t="n">
         <v>1356</v>
@@ -5465,19 +5465,19 @@
         <v>47</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000372210902709852</v>
+        <v>0.000372920913495732</v>
       </c>
       <c r="F111" t="n">
-        <v>0.013619147429444</v>
+        <v>0.0136139282162822</v>
       </c>
       <c r="G111" t="n">
-        <v>0.000374031234839224</v>
+        <v>0.000372463059217537</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0136501264448723</v>
+        <v>0.0136262096082293</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4866791753783</v>
+        <v>-0.122926090752899</v>
       </c>
       <c r="J111" t="n">
         <v>1356</v>
@@ -5499,10 +5499,10 @@
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.000429655701055872</v>
+        <v>0.000428033006907758</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0144611958542264</v>
+        <v>0.0143965718712105</v>
       </c>
       <c r="I112"/>
       <c r="J112" t="n">
@@ -5525,10 +5525,10 @@
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.329150150998404</v>
+        <v>0.327818819777481</v>
       </c>
       <c r="H113" t="n">
-        <v>0.573271859594898</v>
+        <v>0.571753276009051</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5549,19 +5549,19 @@
         <v>46</v>
       </c>
       <c r="E114" t="n">
-        <v>0.00047475521125153</v>
+        <v>0.000474916022319012</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0158016264005254</v>
+        <v>0.0158049825668476</v>
       </c>
       <c r="G114" t="n">
-        <v>0.000432182878986002</v>
+        <v>0.00043758361088985</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0145789638922094</v>
+        <v>0.0147229983823517</v>
       </c>
       <c r="I114" t="n">
-        <v>-9.85053650561368</v>
+        <v>-8.53149215374969</v>
       </c>
       <c r="J114" t="n">
         <v>904</v>
@@ -5581,19 +5581,19 @@
         <v>47</v>
       </c>
       <c r="E115" t="n">
-        <v>0.000426179164350369</v>
+        <v>0.000425515296006831</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0143833648165557</v>
+        <v>0.0143672464520354</v>
       </c>
       <c r="G115" t="n">
-        <v>0.000427008189826589</v>
+        <v>0.000428750687598975</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0144123676336341</v>
+        <v>0.014452985972911</v>
       </c>
       <c r="I115" t="n">
-        <v>0.194147441658177</v>
+        <v>0.754609073693322</v>
       </c>
       <c r="J115" t="n">
         <v>904</v>
@@ -5615,10 +5615,10 @@
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.00264745262372193</v>
+        <v>0.00268815282645594</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0396499856306016</v>
+        <v>0.0397139063005678</v>
       </c>
       <c r="I116"/>
       <c r="J116" t="n">
@@ -5639,19 +5639,19 @@
         <v>46</v>
       </c>
       <c r="E117" t="n">
-        <v>0.00265653562230783</v>
+        <v>0.00265406788311174</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0397869536390067</v>
+        <v>0.0397281039170092</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00268704149904935</v>
+        <v>0.00263230119537899</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0397417273526017</v>
+        <v>0.0391034281942115</v>
       </c>
       <c r="I117" t="n">
-        <v>1.135296077575</v>
+        <v>-0.826907185658203</v>
       </c>
       <c r="J117" t="n">
         <v>143</v>
@@ -5671,19 +5671,19 @@
         <v>47</v>
       </c>
       <c r="E118" t="n">
-        <v>0.00263903803503108</v>
+        <v>0.002631692108181</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0395032577301121</v>
+        <v>0.0394235433463223</v>
       </c>
       <c r="G118" t="n">
-        <v>0.00265474186475337</v>
+        <v>0.00266166067175063</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0396722225635807</v>
+        <v>0.0396589737538678</v>
       </c>
       <c r="I118" t="n">
-        <v>0.591538858477626</v>
+        <v>1.12593479280457</v>
       </c>
       <c r="J118" t="n">
         <v>143</v>
@@ -5705,10 +5705,10 @@
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00111524711761984</v>
+        <v>0.00113457545034649</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0252367693964405</v>
+        <v>0.0257435351200147</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5731,10 +5731,10 @@
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>1061400423109867481920204606040400802462086840</v>
+        <v>34764983312067686094800642000668806826040826064</v>
       </c>
       <c r="H120" t="n">
-        <v>15215459857134428094424</v>
+        <v>35594942945077449720428</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5755,19 +5755,19 @@
         <v>46</v>
       </c>
       <c r="E121" t="n">
-        <v>0.00109416670218656</v>
+        <v>0.00109058322274795</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0250529562835777</v>
+        <v>0.0250212587860377</v>
       </c>
       <c r="G121" t="n">
-        <v>0.00119594310269944</v>
+        <v>0.00122927328076133</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0260970928929715</v>
+        <v>0.0272304903618475</v>
       </c>
       <c r="I121" t="n">
-        <v>8.51013733706484</v>
+        <v>11.2822803671036</v>
       </c>
       <c r="J121" t="n">
         <v>59</v>
@@ -5787,19 +5787,19 @@
         <v>47</v>
       </c>
       <c r="E122" t="n">
-        <v>0.00109437617745845</v>
+        <v>0.00108781475944967</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0251561893670149</v>
+        <v>0.0250089723720988</v>
       </c>
       <c r="G122" t="n">
-        <v>0.00108928546754795</v>
+        <v>0.00112181867464217</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0250610931299064</v>
+        <v>0.0255617793524954</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.467343966495385</v>
+        <v>3.03114183790421</v>
       </c>
       <c r="J122" t="n">
         <v>59</v>
@@ -5821,10 +5821,10 @@
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000586995491744777</v>
+        <v>0.0006013383804105</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0164017351130259</v>
+        <v>0.0167163375747326</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5845,19 +5845,19 @@
         <v>46</v>
       </c>
       <c r="E124" t="n">
-        <v>0.000585466945058359</v>
+        <v>0.000585347938179291</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0164453706189652</v>
+        <v>0.0164485025863485</v>
       </c>
       <c r="G124" t="n">
-        <v>0.000586413707104618</v>
+        <v>0.000657777629776339</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0166235280978523</v>
+        <v>0.0180145301302652</v>
       </c>
       <c r="I124" t="n">
-        <v>0.161449508220675</v>
+        <v>11.0112731595443</v>
       </c>
       <c r="J124" t="n">
         <v>1356</v>
@@ -5877,19 +5877,19 @@
         <v>47</v>
       </c>
       <c r="E125" t="n">
-        <v>0.000580142073780285</v>
+        <v>0.00058180775759088</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0163515627437534</v>
+        <v>0.0164088578937446</v>
       </c>
       <c r="G125" t="n">
-        <v>0.000584767352877175</v>
+        <v>0.000583251128564573</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0164377105200668</v>
+        <v>0.0165201244729046</v>
       </c>
       <c r="I125" t="n">
-        <v>0.790960554506467</v>
+        <v>0.247469898128661</v>
       </c>
       <c r="J125" t="n">
         <v>1356</v>
@@ -5911,10 +5911,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000707910633596739</v>
+        <v>0.00071160326161031</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0166493072121474</v>
+        <v>0.0167996248627374</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5935,19 +5935,19 @@
         <v>46</v>
       </c>
       <c r="E127" t="n">
-        <v>0.00070442559884505</v>
+        <v>0.000707558822284473</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0165962765560253</v>
+        <v>0.0166011919235433</v>
       </c>
       <c r="G127" t="n">
-        <v>0.000707833401836747</v>
+        <v>0.000771405337108256</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0167588100816374</v>
+        <v>0.017759199987949</v>
       </c>
       <c r="I127" t="n">
-        <v>0.481441393250684</v>
+        <v>8.27664935053763</v>
       </c>
       <c r="J127" t="n">
         <v>1356</v>
@@ -5967,19 +5967,19 @@
         <v>47</v>
       </c>
       <c r="E128" t="n">
-        <v>0.000698774432717714</v>
+        <v>0.000702587964204197</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0165251785149179</v>
+        <v>0.0166020031036067</v>
       </c>
       <c r="G128" t="n">
-        <v>0.000700737274871891</v>
+        <v>0.000701531193601345</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0165204560081845</v>
+        <v>0.0165425523387417</v>
       </c>
       <c r="I128" t="n">
-        <v>0.28011099517084</v>
+        <v>-0.150637721100813</v>
       </c>
       <c r="J128" t="n">
         <v>1356</v>
@@ -6001,10 +6001,10 @@
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.000519826254758784</v>
+        <v>0.000540542085230146</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0163068180535817</v>
+        <v>0.0167542833634366</v>
       </c>
       <c r="I129"/>
       <c r="J129" t="n">
@@ -6025,19 +6025,19 @@
         <v>46</v>
       </c>
       <c r="E130" t="n">
-        <v>0.00051822502876104</v>
+        <v>0.000517910021047639</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0162266448161833</v>
+        <v>0.0162205018347943</v>
       </c>
       <c r="G130" t="n">
-        <v>0.000522915259878459</v>
+        <v>0.000567151651688081</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0163527723336984</v>
+        <v>0.0173297985015766</v>
       </c>
       <c r="I130" t="n">
-        <v>0.896939041042455</v>
+        <v>8.68226875367076</v>
       </c>
       <c r="J130" t="n">
         <v>1356</v>
@@ -6057,19 +6057,19 @@
         <v>47</v>
       </c>
       <c r="E131" t="n">
-        <v>0.000514865255436474</v>
+        <v>0.000516148701510878</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0161710972725239</v>
+        <v>0.0161730966745508</v>
       </c>
       <c r="G131" t="n">
-        <v>0.000514327095079015</v>
+        <v>0.000517504467143139</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0161431967780579</v>
+        <v>0.016251397069094</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.104633872609065</v>
+        <v>0.261981435589282</v>
       </c>
       <c r="J131" t="n">
         <v>1356</v>
@@ -6091,10 +6091,10 @@
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000522682156854144</v>
+        <v>0.000541107000709345</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0163710524446327</v>
+        <v>0.0169139969570544</v>
       </c>
       <c r="I132"/>
       <c r="J132" t="n">
@@ -6115,19 +6115,19 @@
         <v>46</v>
       </c>
       <c r="E133" t="n">
-        <v>0.000518341850431891</v>
+        <v>0.000517812358050164</v>
       </c>
       <c r="F133" t="n">
-        <v>0.016231461766293</v>
+        <v>0.0162251408840576</v>
       </c>
       <c r="G133" t="n">
-        <v>0.000523283222417222</v>
+        <v>0.000572225127040427</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0163859860336213</v>
+        <v>0.0174510264386328</v>
       </c>
       <c r="I133" t="n">
-        <v>0.94430162742564</v>
+        <v>9.50897931932617</v>
       </c>
       <c r="J133" t="n">
         <v>1356</v>
@@ -6147,19 +6147,19 @@
         <v>47</v>
       </c>
       <c r="E134" t="n">
-        <v>0.000514148273950815</v>
+        <v>0.000515384050890979</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0161594361819877</v>
+        <v>0.0161680643942117</v>
       </c>
       <c r="G134" t="n">
-        <v>0.000515815709934471</v>
+        <v>0.000517210017034205</v>
       </c>
       <c r="H134" t="n">
-        <v>0.016184711931186</v>
+        <v>0.0162054641686816</v>
       </c>
       <c r="I134" t="n">
-        <v>0.323261961887067</v>
+        <v>0.353041527249634</v>
       </c>
       <c r="J134" t="n">
         <v>1356</v>
@@ -6181,10 +6181,10 @@
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000490130995429692</v>
+        <v>0.000501608467794939</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0163429665557648</v>
+        <v>0.0165772519514686</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
@@ -6205,19 +6205,19 @@
         <v>46</v>
       </c>
       <c r="E136" t="n">
-        <v>0.000490908252541121</v>
+        <v>0.000491075252473478</v>
       </c>
       <c r="F136" t="n">
-        <v>0.016355628970026</v>
+        <v>0.0163591959415439</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000497600435591791</v>
+        <v>0.000561833316357502</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0165690221960083</v>
+        <v>0.0176341159725294</v>
       </c>
       <c r="I136" t="n">
-        <v>1.34489091487844</v>
+        <v>12.5941381231653</v>
       </c>
       <c r="J136" t="n">
         <v>904</v>
@@ -6237,19 +6237,19 @@
         <v>47</v>
       </c>
       <c r="E137" t="n">
-        <v>0.000479845638706473</v>
+        <v>0.000481764806560618</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0160787606248338</v>
+        <v>0.0161001781311565</v>
       </c>
       <c r="G137" t="n">
-        <v>0.000489341235945051</v>
+        <v>0.000497075916031759</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0163074426162949</v>
+        <v>0.0165023076245274</v>
       </c>
       <c r="I137" t="n">
-        <v>1.94048580848501</v>
+        <v>3.08023562947338</v>
       </c>
       <c r="J137" t="n">
         <v>904</v>
@@ -6297,13 +6297,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00119452173996487</v>
+        <v>0.00119480106609414</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00121114039720704</v>
+        <v>0.00119738839412016</v>
       </c>
       <c r="F2" t="n">
-        <v>1.27624843127922</v>
+        <v>1.75403923976168</v>
       </c>
     </row>
     <row r="3">
@@ -6317,13 +6317,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.41781437905188</v>
+        <v>4.41926393746313</v>
       </c>
       <c r="E3" t="n">
-        <v>265350105777466870480806404060600208648024260</v>
+        <v>8691245828016921523200468000442204284060284046</v>
       </c>
       <c r="F3" t="n">
-        <v>-21.3819962597432</v>
+        <v>-23.1715556870826</v>
       </c>
     </row>
     <row r="4">
@@ -6337,13 +6337,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00119616255541606</v>
+        <v>0.00119606000027793</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00119837062588644</v>
+        <v>0.00120008328037061</v>
       </c>
       <c r="F4" t="n">
-        <v>0.36532819497343</v>
+        <v>0.644113670243516</v>
       </c>
     </row>
     <row r="5">
@@ -6360,7 +6360,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0011920033452153</v>
+        <v>0.00121014431142447</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -6377,13 +6377,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0014741895863778</v>
+        <v>0.00147436649915243</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00147139598385423</v>
+        <v>0.00146107985215994</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.36299900215923</v>
+        <v>-0.601864826578078</v>
       </c>
     </row>
     <row r="7">
@@ -6397,13 +6397,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00146536730682795</v>
+        <v>0.00147211407966714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00147066471043633</v>
+        <v>0.00147620279163385</v>
       </c>
       <c r="F7" t="n">
-        <v>0.19634773829944</v>
+        <v>-0.116134674083102</v>
       </c>
     </row>
     <row r="8">
@@ -6420,7 +6420,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00146672991716572</v>
+        <v>0.00147769642044416</v>
       </c>
       <c r="F8" t="e">
         <v>#NUM!</v>
@@ -6437,13 +6437,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000420930068118874</v>
+        <v>0.000421021441315474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000408489673047228</v>
+        <v>0.00042636801043581</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.27248019590366</v>
+        <v>-1.13981172768212</v>
       </c>
     </row>
     <row r="10">
@@ -6460,7 +6460,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.164634477185581</v>
+        <v>0.163969700526929</v>
       </c>
       <c r="F10" t="e">
         <v>#NUM!</v>
@@ -6477,13 +6477,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000402959667190862</v>
+        <v>0.000402970306179354</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000406360488343403</v>
+        <v>0.000408391194849675</v>
       </c>
       <c r="F11" t="n">
-        <v>0.601964078781648</v>
+        <v>1.00461703084747</v>
       </c>
     </row>
     <row r="12">
@@ -6500,7 +6500,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000409752336428368</v>
+        <v>0.000413292467092861</v>
       </c>
       <c r="F12" t="e">
         <v>#NUM!</v>
@@ -6517,13 +6517,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00044187293007411</v>
+        <v>0.000441916306925829</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000444840900809925</v>
+        <v>0.000464980731185423</v>
       </c>
       <c r="F13" t="n">
-        <v>0.265447076693608</v>
+        <v>3.29957954894549</v>
       </c>
     </row>
     <row r="14">
@@ -6537,13 +6537,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00126830026415411</v>
+        <v>0.00127368533224027</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00129977802592766</v>
+        <v>0.00141346108785193</v>
       </c>
       <c r="F14" t="n">
-        <v>2.42177980744703</v>
+        <v>9.88890014822223</v>
       </c>
     </row>
     <row r="15">
@@ -6557,13 +6557,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00044106770337025</v>
+        <v>0.000441936878734143</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000442271158756603</v>
+        <v>0.000444247923402119</v>
       </c>
       <c r="F15" t="n">
-        <v>0.216867152632253</v>
+        <v>0.588970129010791</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000442452647868856</v>
+        <v>0.00045091191498329</v>
       </c>
       <c r="F16" t="e">
         <v>#NUM!</v>
@@ -6597,13 +6597,13 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000562832854518344</v>
+        <v>0.00056367786495073</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000566908111545069</v>
+        <v>0.000583493309155064</v>
       </c>
       <c r="F17" t="n">
-        <v>0.308361360119654</v>
+        <v>2.47222252992354</v>
       </c>
     </row>
     <row r="18">
@@ -6617,13 +6617,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00139712173476602</v>
+        <v>0.00140403196291606</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001425484568641</v>
+        <v>0.00158125397994027</v>
       </c>
       <c r="F18" t="n">
-        <v>1.98969771395195</v>
+        <v>11.2076882823658</v>
       </c>
     </row>
     <row r="19">
@@ -6637,13 +6637,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000561900055422715</v>
+        <v>0.00056217957331907</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000562641346096227</v>
+        <v>0.000565701169176687</v>
       </c>
       <c r="F19" t="n">
-        <v>0.186229260665894</v>
+        <v>0.644871597310232</v>
       </c>
     </row>
     <row r="20">
@@ -6660,7 +6660,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000564726002335202</v>
+        <v>0.000569060528722536</v>
       </c>
       <c r="F20" t="e">
         <v>#NUM!</v>
@@ -6677,13 +6677,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000371615619217221</v>
+        <v>0.000371452664946264</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000375582913505933</v>
+        <v>0.000393554231843609</v>
       </c>
       <c r="F21" t="n">
-        <v>1.09999792353966</v>
+        <v>4.75083972172167</v>
       </c>
     </row>
     <row r="22">
@@ -6697,13 +6697,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00118679336985931</v>
+        <v>0.00119191264969172</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00124412109096161</v>
+        <v>0.00133931606282742</v>
       </c>
       <c r="F22" t="n">
-        <v>4.60788917724988</v>
+        <v>11.005872118379</v>
       </c>
     </row>
     <row r="23">
@@ -6717,13 +6717,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000371233227697845</v>
+        <v>0.000372085533944945</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000371485663883202</v>
+        <v>0.000374931888563065</v>
       </c>
       <c r="F23" t="n">
-        <v>0.228221721524294</v>
+        <v>1.69792121957027</v>
       </c>
     </row>
     <row r="24">
@@ -6740,7 +6740,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000372818077709026</v>
+        <v>0.000379594646688261</v>
       </c>
       <c r="F24" t="e">
         <v>#NUM!</v>
@@ -6757,13 +6757,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000372570541763392</v>
+        <v>0.000372379035579144</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000375177590486782</v>
+        <v>0.000393123190300359</v>
       </c>
       <c r="F25" t="n">
-        <v>0.627828011031176</v>
+        <v>5.2196173477121</v>
       </c>
     </row>
     <row r="26">
@@ -6777,13 +6777,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00119569414050085</v>
+        <v>0.00119681005362634</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00124047862842381</v>
+        <v>0.00134656770183042</v>
       </c>
       <c r="F26" t="n">
-        <v>3.61025872568759</v>
+        <v>11.1214347411203</v>
       </c>
     </row>
     <row r="27">
@@ -6797,13 +6797,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000371932948989793</v>
+        <v>0.00037199616671106</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000372410419002003</v>
+        <v>0.00037431423821325</v>
       </c>
       <c r="F27" t="n">
-        <v>0.398536328797233</v>
+        <v>1.4469906671597</v>
       </c>
     </row>
     <row r="28">
@@ -6820,7 +6820,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000374531893225373</v>
+        <v>0.000381535825771593</v>
       </c>
       <c r="F28" t="e">
         <v>#NUM!</v>

--- a/results/chronological/consolidated/Stress_Testing.xlsx
+++ b/results/chronological/consolidated/Stress_Testing.xlsx
@@ -155,13 +155,13 @@
     <t xml:space="preserve">sGARCH</t>
   </si>
   <si>
+    <t xml:space="preserve">eGARCH</t>
+  </si>
+  <si>
     <t xml:space="preserve">TGARCH</t>
   </si>
   <si>
     <t xml:space="preserve">gjrGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eGARCH</t>
   </si>
   <si>
     <t xml:space="preserve">mean_NF_GARCH_MSE</t>
@@ -2225,19 +2225,19 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000166772861483521</v>
+        <v>0.000167390769583144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00969435537694422</v>
+        <v>0.00974045974012153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000166933948048452</v>
+        <v>0.00016372650862773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00975576335324238</v>
+        <v>0.00961013285454498</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0964971875490472</v>
+        <v>-2.23803768010831</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -2257,19 +2257,19 @@
         <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000167096003851232</v>
+        <v>0.000167850774117696</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00972274631263412</v>
+        <v>0.0097640934864094</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000165178898405155</v>
+        <v>0.000166847493402141</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00970365898523208</v>
+        <v>0.00973457659125091</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.16062370229288</v>
+        <v>-0.60131602525049</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -2283,22 +2283,28 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5"/>
-      <c r="F5"/>
+        <v>48</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.000167137451846857</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.00972844644050327</v>
+      </c>
       <c r="G5" t="n">
-        <v>0.0000403045023125828</v>
+        <v>0.000170783013894062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00476314150753557</v>
-      </c>
-      <c r="I5"/>
+        <v>0.0098253300770865</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.13461629706705</v>
+      </c>
       <c r="J5" t="n">
-        <v>59</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
@@ -2312,15 +2318,15 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000395518045107587</v>
+        <v>0.0000383758005516446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00476641051967204</v>
+        <v>0.00475854037000235</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2341,19 +2347,19 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000388022922564971</v>
+        <v>0.0000387970650100645</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00475143871554619</v>
+        <v>0.00480853491760829</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0000404785367305131</v>
+        <v>0.0000378174276516739</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00474907146904838</v>
+        <v>0.00467961022608443</v>
       </c>
       <c r="I7" t="n">
-        <v>4.14106983455374</v>
+        <v>-2.59043890402536</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -2373,19 +2379,19 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000388145457237465</v>
+        <v>0.0000388787292366403</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0047681507479245</v>
+        <v>0.00476880980827408</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000385790261641135</v>
+        <v>0.0000392318124851237</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00472193740859721</v>
+        <v>0.00483188635763098</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.610486015461072</v>
+        <v>0.899992190310669</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -2396,25 +2402,31 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9"/>
+        <v>48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0000383111734548554</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00474862661305495</v>
+      </c>
       <c r="G9" t="n">
-        <v>0.0000918003257372773</v>
+        <v>0.0000415062588425139</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00380444242200878</v>
-      </c>
-      <c r="I9"/>
+        <v>0.00499701353633637</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7.69783998066787</v>
+      </c>
       <c r="J9" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -2428,23 +2440,17 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0000911493049180099</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.00366323865001799</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
       <c r="G10" t="n">
-        <v>0.0000929522746724327</v>
+        <v>0.0000919954176231408</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00385189594458073</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.93967254784948</v>
-      </c>
+        <v>0.0037891615776163</v>
+      </c>
+      <c r="I10"/>
       <c r="J10" t="n">
         <v>1356</v>
       </c>
@@ -2460,22 +2466,22 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000908376325719033</v>
+        <v>0.0000911438050313301</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00366562613093932</v>
+        <v>0.00366548984427773</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0000921365923869022</v>
+        <v>0.0000912058248203277</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00375542558706764</v>
+        <v>0.00368557176461186</v>
       </c>
       <c r="I11" t="n">
-        <v>1.409819683307</v>
+        <v>0.0679998115469423</v>
       </c>
       <c r="J11" t="n">
         <v>1356</v>
@@ -2489,20 +2495,26 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12"/>
+        <v>47</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0000907412069112315</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.00366857318202165</v>
+      </c>
       <c r="G12" t="n">
-        <v>0.000211271169167175</v>
+        <v>0.0000913618269711371</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00394047465043569</v>
-      </c>
-      <c r="I12"/>
+        <v>0.00373114346469385</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.679299090747991</v>
+      </c>
       <c r="J12" t="n">
         <v>1356</v>
       </c>
@@ -2515,25 +2527,25 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000210547816315018</v>
+        <v>0.0000908730375540498</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00381018002783672</v>
+        <v>0.00367947127946332</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000211828777632523</v>
+        <v>0.0000914215294691344</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00402128409505302</v>
+        <v>0.00374015885338721</v>
       </c>
       <c r="I13" t="n">
-        <v>0.604715436599983</v>
+        <v>0.599959241843324</v>
       </c>
       <c r="J13" t="n">
         <v>1356</v>
@@ -2550,23 +2562,17 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.000210378191550601</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.00381736819816612</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
       <c r="G14" t="n">
-        <v>0.000211458084191767</v>
+        <v>0.000212624154643448</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00391205503433991</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.510688747272816</v>
-      </c>
+        <v>0.0039682070509222</v>
+      </c>
+      <c r="I14"/>
       <c r="J14" t="n">
         <v>1356</v>
       </c>
@@ -2579,20 +2585,26 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15"/>
-      <c r="F15"/>
+        <v>46</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.000210678901021354</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.00381761361143642</v>
+      </c>
       <c r="G15" t="n">
-        <v>0.0000231252424750306</v>
+        <v>0.000210478634131197</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00357374310745804</v>
-      </c>
-      <c r="I15"/>
+        <v>0.00383983704543749</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.09514832276639</v>
+      </c>
       <c r="J15" t="n">
         <v>1356</v>
       </c>
@@ -2605,25 +2617,25 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000220849957085853</v>
+        <v>0.000210700505187153</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00344595974925313</v>
+        <v>0.00382819813454769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000236840696878705</v>
+        <v>0.000211295321399885</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00360067817396231</v>
+        <v>0.00387011538513842</v>
       </c>
       <c r="I16" t="n">
-        <v>6.75168583929685</v>
+        <v>0.281509410048078</v>
       </c>
       <c r="J16" t="n">
         <v>1356</v>
@@ -2637,25 +2649,25 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000022146378611691</v>
+        <v>0.000210572594374674</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00344248352074403</v>
+        <v>0.00382068948337397</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000233025181730723</v>
+        <v>0.000210699992424365</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00354350609513691</v>
+        <v>0.00387564847369017</v>
       </c>
       <c r="I17" t="n">
-        <v>4.96143615378562</v>
+        <v>0.0604641928200469</v>
       </c>
       <c r="J17" t="n">
         <v>1356</v>
@@ -2669,7 +2681,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
@@ -2677,10 +2689,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000236095266963912</v>
+        <v>0.0000238690994494394</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0036147337275737</v>
+        <v>0.00359832122415118</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2695,25 +2707,25 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0000221960581697615</v>
+        <v>0.0000221891593871965</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00344889088653652</v>
+        <v>0.00345737058058294</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0000238584347403858</v>
+        <v>0.0000222166281663315</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00360282203305426</v>
+        <v>0.00346214461682645</v>
       </c>
       <c r="I19" t="n">
-        <v>6.96766820084118</v>
+        <v>0.123640630474047</v>
       </c>
       <c r="J19" t="n">
         <v>1356</v>
@@ -2727,25 +2739,25 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
         <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000222694955558963</v>
+        <v>0.0000221051813738323</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00346231355143266</v>
+        <v>0.00344846314933526</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000022862143760953</v>
+        <v>0.0000226695565639773</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00355165781513772</v>
+        <v>0.00350589061423782</v>
       </c>
       <c r="I20" t="n">
-        <v>2.59226873583442</v>
+        <v>2.48957313546119</v>
       </c>
       <c r="J20" t="n">
         <v>1356</v>
@@ -2759,22 +2771,28 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21"/>
-      <c r="F21"/>
+        <v>48</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0000222430861946734</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.00345561740124356</v>
+      </c>
       <c r="G21" t="n">
-        <v>0.000120478191653158</v>
+        <v>0.0000228213826452332</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0100333112875579</v>
-      </c>
-      <c r="I21"/>
+        <v>0.00351530195519723</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.53401145561403</v>
+      </c>
       <c r="J21" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="22">
@@ -2785,28 +2803,22 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.00011608477197814</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.00987458470430241</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E22"/>
+      <c r="F22"/>
       <c r="G22" t="n">
-        <v>0.000119792761538019</v>
+        <v>0.0000239436374210842</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00998113227333425</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.09533690706548</v>
-      </c>
+        <v>0.00360039788898703</v>
+      </c>
+      <c r="I22"/>
       <c r="J22" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="23">
@@ -2817,202 +2829,214 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000118014635242703</v>
+        <v>0.0000223220232706449</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00996397339898721</v>
+        <v>0.00344949482479674</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000118082523651514</v>
+        <v>0.0000223818901589383</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00988880625534562</v>
+        <v>0.00346201332680005</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0574923423990511</v>
+        <v>0.267479144381026</v>
       </c>
       <c r="J23" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24"/>
-      <c r="F24"/>
+        <v>47</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.000022320159558227</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.00346668144845584</v>
+      </c>
       <c r="G24" t="n">
-        <v>0.000241314086461098</v>
+        <v>0.0000227555990269618</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0117724167845115</v>
-      </c>
-      <c r="I24"/>
+        <v>0.00352960424438782</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.91354869726283</v>
+      </c>
       <c r="J24" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000240254897910958</v>
+        <v>0.0000222957051309558</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0117491839519689</v>
+        <v>0.00345771608220651</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000236887716973761</v>
+        <v>0.0000231131686764108</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0116185256841245</v>
+        <v>0.00353415999539343</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4214248759761</v>
+        <v>3.53678700181551</v>
       </c>
       <c r="J25" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.00023749979494174</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0116736994474247</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
       <c r="G26" t="n">
-        <v>0.000238100068376096</v>
+        <v>0.000120017100028126</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0116744775589956</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.25210972783456</v>
-      </c>
+        <v>0.0100115488357566</v>
+      </c>
+      <c r="I26"/>
       <c r="J26" t="n">
-        <v>143</v>
+        <v>904</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27"/>
-      <c r="F27"/>
+        <v>46</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.000147204556239559</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0112782823754828</v>
+      </c>
       <c r="G27" t="n">
-        <v>0.0000976494445238349</v>
+        <v>0.000106670499260581</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00744735465114372</v>
-      </c>
-      <c r="I27"/>
+        <v>0.00937461069068446</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-37.9993130808916</v>
+      </c>
       <c r="J27" t="n">
-        <v>59</v>
+        <v>904</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28"/>
-      <c r="F28"/>
+        <v>47</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000119584764091518</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0100387759894535</v>
+      </c>
       <c r="G28" t="n">
-        <v>0.830685797285985</v>
+        <v>0.000117027185832018</v>
       </c>
       <c r="H28" t="n">
-        <v>0.149385629663156</v>
-      </c>
-      <c r="I28"/>
+        <v>0.00991440281856469</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-2.18545651706177</v>
+      </c>
       <c r="J28" t="n">
-        <v>59</v>
+        <v>904</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000096903548145345</v>
+        <v>0.00011792721863554</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00738222689257791</v>
+        <v>0.00996631076000351</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0000974007116774414</v>
+        <v>0.000118793552389528</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00749900633507157</v>
+        <v>0.00995709170409208</v>
       </c>
       <c r="I29" t="n">
-        <v>0.510431108288857</v>
+        <v>0.729276746558553</v>
       </c>
       <c r="J29" t="n">
-        <v>59</v>
+        <v>904</v>
       </c>
     </row>
     <row r="30">
@@ -3023,28 +3047,22 @@
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.0000965134272049953</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.00737884943851464</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30"/>
       <c r="G30" t="n">
-        <v>0.0000977110084807977</v>
+        <v>0.000240409228876508</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00733247315940514</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.22563597942776</v>
-      </c>
+        <v>0.0117910181351902</v>
+      </c>
+      <c r="I30"/>
       <c r="J30" t="n">
-        <v>59</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31">
@@ -3052,25 +3070,31 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31"/>
-      <c r="F31"/>
+        <v>46</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.000238191325640674</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0116669377619493</v>
+      </c>
       <c r="G31" t="n">
-        <v>0.000105138890137807</v>
+        <v>0.000238477232100878</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00463390394844477</v>
-      </c>
-      <c r="I31"/>
+        <v>0.0117100594735287</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.119888367407202</v>
+      </c>
       <c r="J31" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32">
@@ -3078,31 +3102,31 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000103500206962902</v>
+        <v>0.000239498244305225</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00454816758471772</v>
+        <v>0.0117331851034052</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000105057636617128</v>
+        <v>0.000236848469434413</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00474218482024222</v>
+        <v>0.0116740063207011</v>
       </c>
       <c r="I32" t="n">
-        <v>1.48245258924101</v>
+        <v>-1.11876377210286</v>
       </c>
       <c r="J32" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33">
@@ -3110,31 +3134,31 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000103042316098792</v>
+        <v>0.000237297279806234</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00455396567523226</v>
+        <v>0.0116384046798125</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000103716125508746</v>
+        <v>0.000237829636887</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00461844024646972</v>
+        <v>0.0116404453902345</v>
       </c>
       <c r="I33" t="n">
-        <v>0.649666969961517</v>
+        <v>0.223839672689488</v>
       </c>
       <c r="J33" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34">
@@ -3142,10 +3166,10 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
         <v>45</v>
@@ -3153,14 +3177,14 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.0002232359749759</v>
+        <v>0.000100435736413944</v>
       </c>
       <c r="H34" t="n">
-        <v>0.004779176257381</v>
+        <v>0.00737480853548937</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
@@ -3168,31 +3192,31 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
         <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000222736870573489</v>
+        <v>0.0000968840321836063</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00469571713525595</v>
+        <v>0.00738820035024361</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000225822947087929</v>
+        <v>0.0000960030801995614</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00487692343074086</v>
+        <v>0.00734600686134965</v>
       </c>
       <c r="I35" t="n">
-        <v>1.36659119643778</v>
+        <v>-0.917628874212873</v>
       </c>
       <c r="J35" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36">
@@ -3200,31 +3224,31 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
         <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00022254082437536</v>
+        <v>0.0000972761676027537</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00471338265169423</v>
+        <v>0.00741070991236692</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000223697588902695</v>
+        <v>0.0000969058390597625</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00477900913009476</v>
+        <v>0.00739420630223323</v>
       </c>
       <c r="I36" t="n">
-        <v>0.517110860697776</v>
+        <v>-0.382152970950334</v>
       </c>
       <c r="J36" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
@@ -3232,25 +3256,31 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37"/>
-      <c r="F37"/>
+        <v>48</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0000969714682154979</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.00739887187023373</v>
+      </c>
       <c r="G37" t="n">
-        <v>0.0000360613514685076</v>
+        <v>0.000100299649098669</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00441149099105941</v>
-      </c>
-      <c r="I37"/>
+        <v>0.0075342177947084</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.31823781347146</v>
+      </c>
       <c r="J37" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38">
@@ -3261,26 +3291,20 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.0000352893534349984</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.00433173896860628</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
       <c r="G38" t="n">
-        <v>0.0000375781701462824</v>
+        <v>0.000104877900909667</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00454250508978385</v>
-      </c>
-      <c r="I38" t="n">
-        <v>6.09081470006166</v>
-      </c>
+        <v>0.00464118971782387</v>
+      </c>
+      <c r="I38"/>
       <c r="J38" t="n">
         <v>1356</v>
       </c>
@@ -3293,25 +3317,25 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0000352535610816748</v>
+        <v>0.000103680993400411</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00433620863786005</v>
+        <v>0.0045710177165076</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000358948522048799</v>
+        <v>0.000103531840220819</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00438510914715597</v>
+        <v>0.00458451275752314</v>
       </c>
       <c r="I39" t="n">
-        <v>1.78658243122098</v>
+        <v>-0.144065032819417</v>
       </c>
       <c r="J39" t="n">
         <v>1356</v>
@@ -3325,20 +3349,26 @@
         <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40"/>
-      <c r="F40"/>
+        <v>47</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000103536518424468</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.00455690367897501</v>
+      </c>
       <c r="G40" t="n">
-        <v>0.000037075527171547</v>
+        <v>0.000104160985220688</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00445335648233131</v>
-      </c>
-      <c r="I40"/>
+        <v>0.0046220091431613</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.599520823364534</v>
+      </c>
       <c r="J40" t="n">
         <v>1356</v>
       </c>
@@ -3351,25 +3381,25 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E41" t="n">
-        <v>0.000035341952461012</v>
+        <v>0.00010361737980067</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0043333460246805</v>
+        <v>0.00454986113295566</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0000377757810605194</v>
+        <v>0.000103674298990429</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00454948527139777</v>
+        <v>0.00460886685209101</v>
       </c>
       <c r="I41" t="n">
-        <v>6.44282800032192</v>
+        <v>0.0549019287453466</v>
       </c>
       <c r="J41" t="n">
         <v>1356</v>
@@ -3383,26 +3413,20 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.0000352174686628394</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.00433039996899882</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E42"/>
+      <c r="F42"/>
       <c r="G42" t="n">
-        <v>0.0000362553165181104</v>
+        <v>0.00022295225482055</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00439740927962886</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.86260872871605</v>
-      </c>
+        <v>0.0047466622445616</v>
+      </c>
+      <c r="I42"/>
       <c r="J42" t="n">
         <v>1356</v>
       </c>
@@ -3415,22 +3439,28 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43"/>
-      <c r="F43"/>
+        <v>46</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.000222908271412988</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.00471136680376117</v>
+      </c>
       <c r="G43" t="n">
-        <v>0.000133468961478627</v>
+        <v>0.000222148253539582</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0102222094776653</v>
-      </c>
-      <c r="I43"/>
+        <v>0.00469744398732774</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-0.342121921417959</v>
+      </c>
       <c r="J43" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="44">
@@ -3441,22 +3471,28 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
-      </c>
-      <c r="E44"/>
-      <c r="F44"/>
+        <v>47</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.00022299486383428</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.00470368105570547</v>
+      </c>
       <c r="G44" t="n">
-        <v>0.000120581276377261</v>
+        <v>0.000223088525672698</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00957882634204162</v>
-      </c>
-      <c r="I44"/>
+        <v>0.00473424162894216</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0419841576952139</v>
+      </c>
       <c r="J44" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="45">
@@ -3467,28 +3503,28 @@
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E45" t="n">
-        <v>0.000141508269708647</v>
+        <v>0.00022281837487585</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0106227898698546</v>
+        <v>0.00469875582190401</v>
       </c>
       <c r="G45" t="n">
-        <v>0.000127515913326502</v>
+        <v>0.000223248196899965</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00991303286838473</v>
+        <v>0.00474699281270626</v>
       </c>
       <c r="I45" t="n">
-        <v>-10.9730276144572</v>
+        <v>0.192531017084864</v>
       </c>
       <c r="J45" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="46">
@@ -3499,129 +3535,129 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.000133785593225993</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.0102667448135987</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
       <c r="G46" t="n">
-        <v>0.000130497832556177</v>
+        <v>0.0000361023100106164</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0101008922858352</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-2.51939867920835</v>
-      </c>
+        <v>0.00437981741054315</v>
+      </c>
+      <c r="I46"/>
       <c r="J46" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47"/>
-      <c r="F47"/>
+        <v>46</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0000353971748680677</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.00434239219078202</v>
+      </c>
       <c r="G47" t="n">
-        <v>0.00051640075999157</v>
+        <v>0.0000353944635728929</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0164958855706283</v>
-      </c>
-      <c r="I47"/>
+        <v>0.00435278527628025</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.00766022394775305</v>
+      </c>
       <c r="J47" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000512579964774807</v>
+        <v>0.0000352252546988029</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0165058165355639</v>
+        <v>0.00433420586697496</v>
       </c>
       <c r="G48" t="n">
-        <v>0.000513517743105937</v>
+        <v>0.0000357883408157283</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0165473064586123</v>
+        <v>0.00436793725689673</v>
       </c>
       <c r="I48" t="n">
-        <v>0.182618486648236</v>
+        <v>1.57337865933677</v>
       </c>
       <c r="J48" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000519431667521127</v>
+        <v>0.0000353221063200369</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0164993944488472</v>
+        <v>0.00433316953740108</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000513036856868621</v>
+        <v>0.0000359543638833064</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0165274761435378</v>
+        <v>0.00438121507681389</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.24646223110316</v>
+        <v>1.75850020687772</v>
       </c>
       <c r="J49" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
         <v>45</v>
@@ -3629,226 +3665,232 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.000260418757469357</v>
+        <v>0.0000366751183215674</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0122640000949425</v>
+        <v>0.0044192686297208</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
         <v>46</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000256674386722905</v>
+        <v>0.0000354097202656811</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0120328290801632</v>
+        <v>0.00433825615711742</v>
       </c>
       <c r="G51" t="n">
-        <v>0.000252769102373959</v>
+        <v>0.0000352522765945581</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0120126046785228</v>
+        <v>0.00433127981133599</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.54500067938191</v>
+        <v>-0.4466198677996</v>
       </c>
       <c r="J51" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
         <v>47</v>
       </c>
       <c r="E52" t="n">
-        <v>0.000260683997833854</v>
+        <v>0.0000353585136956152</v>
       </c>
       <c r="F52" t="n">
-        <v>0.012215472669499</v>
+        <v>0.00434265007823211</v>
       </c>
       <c r="G52" t="n">
-        <v>0.000261747631599948</v>
+        <v>0.00003585892882906</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0121573146188589</v>
+        <v>0.00436782600333632</v>
       </c>
       <c r="I52" t="n">
-        <v>0.406358506318553</v>
+        <v>1.39551054586782</v>
       </c>
       <c r="J52" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53"/>
-      <c r="F53"/>
+        <v>48</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0000354378727125389</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.00435033738714455</v>
+      </c>
       <c r="G53" t="n">
-        <v>0.000163912916132638</v>
+        <v>0.0000361587874056296</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00777158051656032</v>
-      </c>
-      <c r="I53"/>
+        <v>0.00438186484996242</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.99374687265773</v>
+      </c>
       <c r="J53" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.000163199612143657</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.00777429899374019</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E54"/>
+      <c r="F54"/>
       <c r="G54" t="n">
-        <v>0.000164144129669294</v>
+        <v>0.000132224829945565</v>
       </c>
       <c r="H54" t="n">
-        <v>0.00778668254139907</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.575419619050758</v>
-      </c>
+        <v>0.0101568711984453</v>
+      </c>
+      <c r="I54"/>
       <c r="J54" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000162869542806892</v>
+        <v>0.000154725243034373</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00772508980534471</v>
+        <v>0.0111895378356009</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000163423638235491</v>
+        <v>0.000120818238968247</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00775183501599565</v>
+        <v>0.00963902875001785</v>
       </c>
       <c r="I55" t="n">
-        <v>0.339054640186476</v>
+        <v>-28.0644746651516</v>
       </c>
       <c r="J55" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
-      </c>
-      <c r="E56"/>
-      <c r="F56"/>
+        <v>47</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.000133341318669117</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0102436055767891</v>
+      </c>
       <c r="G56" t="n">
-        <v>0.000284022983668778</v>
+        <v>0.000130356337988292</v>
       </c>
       <c r="H56" t="n">
-        <v>0.00792201268064297</v>
-      </c>
-      <c r="I56"/>
+        <v>0.0100959133463467</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-2.28986233188992</v>
+      </c>
       <c r="J56" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>0.000282339956097267</v>
+        <v>0.00013353712390326</v>
       </c>
       <c r="F57" t="n">
-        <v>0.00791829105903136</v>
+        <v>0.0102543735711536</v>
       </c>
       <c r="G57" t="n">
-        <v>0.000284477931643895</v>
+        <v>0.000130605044765472</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00793269269042557</v>
+        <v>0.0101169377002651</v>
       </c>
       <c r="I57" t="n">
-        <v>0.751543550064957</v>
+        <v>-2.24499684759748</v>
       </c>
       <c r="J57" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="58">
@@ -3856,31 +3898,25 @@
         <v>30</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.000281679695387752</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.00787518484721763</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E58"/>
+      <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000286120212369316</v>
+        <v>0.000509593372187773</v>
       </c>
       <c r="H58" t="n">
-        <v>0.00796346392707323</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1.55197598407767</v>
-      </c>
+        <v>0.0163047301690871</v>
+      </c>
+      <c r="I58"/>
       <c r="J58" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59">
@@ -3888,25 +3924,31 @@
         <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59"/>
-      <c r="F59"/>
+        <v>46</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.000516025348960836</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0164057668533221</v>
+      </c>
       <c r="G59" t="n">
-        <v>0.0000953941486679623</v>
+        <v>0.000513604511694003</v>
       </c>
       <c r="H59" t="n">
-        <v>0.00758759018338344</v>
-      </c>
-      <c r="I59"/>
+        <v>0.0164301601039204</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-0.471342679379501</v>
+      </c>
       <c r="J59" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60">
@@ -3914,31 +3956,31 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000094115806746459</v>
+        <v>0.000517635924727256</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0075551441247932</v>
+        <v>0.0164538747346341</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0000946623485766923</v>
+        <v>0.000513100205737699</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00754332421676345</v>
+        <v>0.0163980589166189</v>
       </c>
       <c r="I60" t="n">
-        <v>0.577359254709895</v>
+        <v>-0.883983077542493</v>
       </c>
       <c r="J60" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61">
@@ -3946,31 +3988,31 @@
         <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0000940865136941432</v>
+        <v>0.000512738875788594</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00751423157600635</v>
+        <v>0.0164255410635976</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0000959647742698298</v>
+        <v>0.000510589300252105</v>
       </c>
       <c r="H61" t="n">
-        <v>0.00760899578196267</v>
+        <v>0.0163944134853723</v>
       </c>
       <c r="I61" t="n">
-        <v>1.95723961211583</v>
+        <v>-0.420998938956898</v>
       </c>
       <c r="J61" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62">
@@ -3978,10 +4020,10 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
         <v>45</v>
@@ -3989,14 +4031,14 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.0000949337910695293</v>
+        <v>0.000256461740788886</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00753839939038186</v>
+        <v>0.012073981454637</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -4004,31 +4046,31 @@
         <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D63" t="s">
         <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0000942717789076125</v>
+        <v>0.00025898280141391</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00756051290685797</v>
+        <v>0.0120157800871535</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0000966093641318648</v>
+        <v>0.00025326068627261</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00764764298794843</v>
+        <v>0.0120363378621733</v>
       </c>
       <c r="I63" t="n">
-        <v>2.41962592887133</v>
+        <v>-2.25937757080082</v>
       </c>
       <c r="J63" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
@@ -4036,31 +4078,31 @@
         <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D64" t="s">
         <v>47</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0000935958250157173</v>
+        <v>0.00025742929216685</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00750519647103852</v>
+        <v>0.0120442691808859</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0000957695508813098</v>
+        <v>0.000255761518076394</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0075787979562898</v>
+        <v>0.0119909485230251</v>
       </c>
       <c r="I64" t="n">
-        <v>2.26974632917146</v>
+        <v>-0.652081713855661</v>
       </c>
       <c r="J64" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65">
@@ -4068,25 +4110,31 @@
         <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D65" t="s">
-        <v>45</v>
-      </c>
-      <c r="E65"/>
-      <c r="F65"/>
+        <v>48</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.00025833660557955</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.0120578372413049</v>
+      </c>
       <c r="G65" t="n">
-        <v>0.000219074500375511</v>
+        <v>0.000256551627309593</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0123435687331036</v>
-      </c>
-      <c r="I65"/>
+        <v>0.0119712794957244</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-0.695757921583275</v>
+      </c>
       <c r="J65" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66">
@@ -4097,28 +4145,22 @@
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.000226753925554217</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.0126561827699229</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E66"/>
+      <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.000216397716693238</v>
+        <v>0.000165815958335335</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0122215291273252</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-4.78572926703244</v>
-      </c>
+        <v>0.00786228187051452</v>
+      </c>
+      <c r="I66"/>
       <c r="J66" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="67">
@@ -4129,295 +4171,301 @@
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000210732340051025</v>
+        <v>0.000168632370621721</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0120781025365511</v>
+        <v>0.00794048453287123</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000219100145523878</v>
+        <v>1606.07772349607</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0123936081674398</v>
+        <v>12.5251882107183</v>
       </c>
       <c r="I67" t="n">
-        <v>3.81916929030111</v>
+        <v>99.9999895003605</v>
       </c>
       <c r="J67" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D68" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68"/>
-      <c r="F68"/>
+        <v>47</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.000162785932689634</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.00771187099999145</v>
+      </c>
       <c r="G68" t="n">
-        <v>0.00359361205954346</v>
+        <v>0.000162066477685287</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0489229727884067</v>
-      </c>
-      <c r="I68"/>
+        <v>0.00774757434318174</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-0.443925859698309</v>
+      </c>
       <c r="J68" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00359485200917855</v>
+        <v>0.000162043713034707</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0493321758124025</v>
+        <v>0.00770566903897201</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00354137926118332</v>
+        <v>0.000164734717010711</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0494420366478078</v>
+        <v>0.00785961488916734</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.50994129833364</v>
+        <v>1.63353786307737</v>
       </c>
       <c r="J69" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>47</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.00361763266038078</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.0496083913704915</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E70"/>
+      <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.00361156619525572</v>
+        <v>0.0002833163035876</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0495940543522813</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-0.167973250304351</v>
-      </c>
+        <v>0.00796890206023885</v>
+      </c>
+      <c r="I70"/>
       <c r="J70" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>45</v>
-      </c>
-      <c r="E71"/>
-      <c r="F71"/>
+        <v>46</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.00028734448295794</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.00808775990715803</v>
+      </c>
       <c r="G71" t="n">
-        <v>0.00353394491403295</v>
+        <v>1784.31569451374</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0466505137776462</v>
-      </c>
-      <c r="I71"/>
+        <v>13.3680483107481</v>
+      </c>
+      <c r="I71" t="n">
+        <v>99.9999838960962</v>
+      </c>
       <c r="J71" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E72" t="n">
-        <v>4.41926393746313</v>
+        <v>0.000282030585080843</v>
       </c>
       <c r="F72" t="n">
-        <v>2.1013802532007</v>
+        <v>0.00786050475239171</v>
       </c>
       <c r="G72" t="n">
-        <v>3.58789325409697</v>
+        <v>0.000282938874566499</v>
       </c>
       <c r="H72" t="n">
-        <v>1.8894545761062</v>
+        <v>0.00791072778257996</v>
       </c>
       <c r="I72" t="n">
-        <v>-23.1715556870826</v>
+        <v>0.321019685629283</v>
       </c>
       <c r="J72" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00347412929413676</v>
+        <v>0.000281720781021467</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0455671619890465</v>
+        <v>0.00786382465019119</v>
       </c>
       <c r="G73" t="n">
-        <v>0.00336908984281903</v>
+        <v>0.00028385443137022</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0450204435591811</v>
+        <v>0.00792797046037918</v>
       </c>
       <c r="I73" t="n">
-        <v>-3.11773969286127</v>
+        <v>0.751670614565956</v>
       </c>
       <c r="J73" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>47</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.00346827427474752</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.0454349590163139</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E74"/>
+      <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.00344640958199682</v>
+        <v>0.0000958874139316355</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0451644394227361</v>
-      </c>
-      <c r="I74" t="n">
-        <v>-0.634419451040232</v>
-      </c>
+        <v>0.00759530703158959</v>
+      </c>
+      <c r="I74"/>
       <c r="J74" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B75" t="s">
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>45</v>
-      </c>
-      <c r="E75"/>
-      <c r="F75"/>
+        <v>46</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.000101212777507098</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.00772256896917212</v>
+      </c>
       <c r="G75" t="n">
-        <v>0.00129939543247604</v>
+        <v>1893.22553371356</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0257297258080896</v>
-      </c>
-      <c r="I75"/>
+        <v>13.6943596668656</v>
+      </c>
+      <c r="I75" t="n">
+        <v>99.9999946539503</v>
+      </c>
       <c r="J75" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00127368533224027</v>
+        <v>0.0000944000428344622</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0253733320670219</v>
+        <v>0.00753228035996503</v>
       </c>
       <c r="G76" t="n">
-        <v>0.00141346108785193</v>
+        <v>0.0000950145981632541</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0274994639637762</v>
+        <v>0.0075397181759165</v>
       </c>
       <c r="I76" t="n">
-        <v>9.88890014822223</v>
+        <v>0.646800955507888</v>
       </c>
       <c r="J76" t="n">
         <v>1356</v>
@@ -4425,31 +4473,31 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B77" t="s">
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00126832649343184</v>
+        <v>0.0000938908490588591</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0252649741570728</v>
+        <v>0.00750244594215055</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00132899081410772</v>
+        <v>0.0000951410240036972</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0261532079692212</v>
+        <v>0.00757812484437359</v>
       </c>
       <c r="I77" t="n">
-        <v>4.56469074367629</v>
+        <v>1.31402300735113</v>
       </c>
       <c r="J77" t="n">
         <v>1356</v>
@@ -4457,89 +4505,89 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>47</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.00127321893707097</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.0254167540510852</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E78"/>
+      <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.00128233567278445</v>
+        <v>0.00009514606259915</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0255147342653038</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.710947679844543</v>
-      </c>
+        <v>0.00755718384344694</v>
+      </c>
+      <c r="I78"/>
       <c r="J78" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79"/>
-      <c r="F79"/>
+        <v>46</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.000101285365743898</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.00772643559911495</v>
+      </c>
       <c r="G79" t="n">
-        <v>0.00142018970248723</v>
+        <v>1792.80816800499</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0260228734433242</v>
-      </c>
-      <c r="I79"/>
+        <v>12.6341673432909</v>
+      </c>
+      <c r="I79" t="n">
+        <v>99.9999943504627</v>
+      </c>
       <c r="J79" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00140403196291606</v>
+        <v>0.0000939478611045351</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0255066194328175</v>
+        <v>0.00750435767309101</v>
       </c>
       <c r="G80" t="n">
-        <v>0.00158125397994027</v>
+        <v>0.0000943880570403498</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0278299692907715</v>
+        <v>0.00752401112050828</v>
       </c>
       <c r="I80" t="n">
-        <v>11.2076882823658</v>
+        <v>0.466368256342583</v>
       </c>
       <c r="J80" t="n">
         <v>1356</v>
@@ -4547,31 +4595,31 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B81" t="s">
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00139811432927473</v>
+        <v>0.0000938302713916549</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0254180627369097</v>
+        <v>0.00749133546172005</v>
       </c>
       <c r="G81" t="n">
-        <v>0.00144230396013013</v>
+        <v>0.0000952479785922654</v>
       </c>
       <c r="H81" t="n">
-        <v>0.026216388356017</v>
+        <v>0.00759305381098087</v>
       </c>
       <c r="I81" t="n">
-        <v>3.06382233405254</v>
+        <v>1.48843809765177</v>
       </c>
       <c r="J81" t="n">
         <v>1356</v>
@@ -4579,124 +4627,124 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>47</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.00139787310550105</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.025542366020423</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E82"/>
+      <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.00141021011183999</v>
+        <v>0.000221592644343359</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0256728421723744</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.87483462466706</v>
-      </c>
+        <v>0.012451624232008</v>
+      </c>
+      <c r="I82"/>
       <c r="J82" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s">
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>45</v>
-      </c>
-      <c r="E83"/>
-      <c r="F83"/>
+        <v>46</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.000207252758704122</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.0119352179681168</v>
+      </c>
       <c r="G83" t="n">
-        <v>0.00120657733759437</v>
+        <v>0.000214277606989952</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0254382396213519</v>
-      </c>
-      <c r="I83"/>
+        <v>0.0121820482464378</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3.27838656801834</v>
+      </c>
       <c r="J83" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B84" t="s">
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00119191264969172</v>
+        <v>0.000209881181466135</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0252710339242026</v>
+        <v>0.0120475983421917</v>
       </c>
       <c r="G84" t="n">
-        <v>0.00133931606282742</v>
+        <v>0.000214126473871428</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0271453538137612</v>
+        <v>0.0121910054273889</v>
       </c>
       <c r="I84" t="n">
-        <v>11.005872118379</v>
+        <v>1.98260977661366</v>
       </c>
       <c r="J84" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00118728364286866</v>
+        <v>0.000211300731242513</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0250730012699673</v>
+        <v>0.0120787786232535</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0012653455231335</v>
+        <v>0.00021958209006681</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0260776128088539</v>
+        <v>0.0123827539471938</v>
       </c>
       <c r="I85" t="n">
-        <v>6.16921456137385</v>
+        <v>3.77141816155308</v>
       </c>
       <c r="J85" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="86">
@@ -4704,31 +4752,25 @@
         <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>47</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0.00119280862763669</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.0252323313056193</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E86"/>
+      <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.00120366796734008</v>
+        <v>0.0036894350235934</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0252634378524213</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.902187313947106</v>
-      </c>
+        <v>0.0498344561779589</v>
+      </c>
+      <c r="I86"/>
       <c r="J86" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87">
@@ -4736,25 +4778,31 @@
         <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>45</v>
-      </c>
-      <c r="E87"/>
-      <c r="F87"/>
+        <v>46</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.00359877018624284</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.049400760864911</v>
+      </c>
       <c r="G87" t="n">
-        <v>0.00122029760265053</v>
+        <v>0.00359638190728069</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0257213535607059</v>
-      </c>
-      <c r="I87"/>
+        <v>0.0494185626785117</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-0.0664078238552078</v>
+      </c>
       <c r="J87" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88">
@@ -4762,31 +4810,31 @@
         <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00119681005362634</v>
+        <v>0.00356809488401079</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0252182665668578</v>
+        <v>0.0492785940261417</v>
       </c>
       <c r="G88" t="n">
-        <v>0.00134656770183042</v>
+        <v>0.00358749160132498</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0273573758161006</v>
+        <v>0.0494035345381209</v>
       </c>
       <c r="I88" t="n">
-        <v>11.1214347411203</v>
+        <v>0.54067631285967</v>
       </c>
       <c r="J88" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89">
@@ -4794,31 +4842,31 @@
         <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00119262458285996</v>
+        <v>0.00354681580225372</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0250957861042803</v>
+        <v>0.0491321965268284</v>
       </c>
       <c r="G89" t="n">
-        <v>0.00125141730232595</v>
+        <v>0.00360369875039564</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0261721107435556</v>
+        <v>0.0495188121412551</v>
       </c>
       <c r="I89" t="n">
-        <v>4.6980906654166</v>
+        <v>1.57846013448468</v>
       </c>
       <c r="J89" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90">
@@ -4826,31 +4874,25 @@
         <v>31</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>47</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.0011925892466452</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.0252024743848921</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E90"/>
+      <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00120132534186739</v>
+        <v>0.00367285350058195</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0252970633990847</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0.727204772739514</v>
-      </c>
+        <v>0.0473897330050055</v>
+      </c>
+      <c r="I90"/>
       <c r="J90" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91">
@@ -4858,25 +4900,31 @@
         <v>31</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>45</v>
-      </c>
-      <c r="E91"/>
-      <c r="F91"/>
+        <v>46</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.00347976402188034</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.0455231176018629</v>
+      </c>
       <c r="G91" t="n">
-        <v>0.00107709167434717</v>
+        <v>0.0034847403871761</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0231683950008167</v>
-      </c>
-      <c r="I91"/>
+        <v>0.0457987302637745</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.142804477316954</v>
+      </c>
       <c r="J91" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92">
@@ -4884,31 +4932,31 @@
         <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E92" t="n">
-        <v>0.00107579040585935</v>
+        <v>0.00347789416951809</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0230264904002747</v>
+        <v>0.0454952200681589</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00109508474380975</v>
+        <v>0.00348560216955811</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0234971599887171</v>
+        <v>0.0457454428487404</v>
       </c>
       <c r="I92" t="n">
-        <v>1.76190363891582</v>
+        <v>0.221138261484305</v>
       </c>
       <c r="J92" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">
@@ -4916,42 +4964,42 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00104800916598896</v>
+        <v>0.00346500087238016</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0225697680372925</v>
+        <v>0.0454134587017214</v>
       </c>
       <c r="G93" t="n">
-        <v>0.00105684006373575</v>
+        <v>0.0034862189222032</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0227145537684215</v>
+        <v>0.0453399347875267</v>
       </c>
       <c r="I93" t="n">
-        <v>0.835594528426302</v>
+        <v>0.608626431573235</v>
       </c>
       <c r="J93" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D94" t="s">
         <v>45</v>
@@ -4959,223 +5007,229 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.00165801205264355</v>
+        <v>0.00129009219262651</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0306393865520959</v>
+        <v>0.0255720143607566</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D95" t="s">
         <v>46</v>
       </c>
       <c r="E95" t="n">
-        <v>0.00167767137845497</v>
+        <v>0.00126824238880099</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0308535525403695</v>
+        <v>0.0253323572808158</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0016754592482692</v>
+        <v>0.0012714645170265</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0307275709575662</v>
+        <v>0.0253941466388331</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.132031273697815</v>
+        <v>0.253418650883599</v>
       </c>
       <c r="J95" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D96" t="s">
         <v>47</v>
       </c>
       <c r="E96" t="n">
-        <v>0.00165933224312697</v>
+        <v>0.00126858722756147</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0306410646750981</v>
+        <v>0.0253735347377748</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00166767405914687</v>
+        <v>0.00127195335724615</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0307704067464129</v>
+        <v>0.0254486085569248</v>
       </c>
       <c r="I96" t="n">
-        <v>0.50020661856264</v>
+        <v>0.264642540978639</v>
       </c>
       <c r="J96" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>45</v>
-      </c>
-      <c r="E97"/>
-      <c r="F97"/>
+        <v>48</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.00127206474590307</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.0253870455119289</v>
+      </c>
       <c r="G97" t="n">
-        <v>0.00219397279986159</v>
+        <v>0.00127646735485478</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0348184667053898</v>
-      </c>
-      <c r="I97"/>
+        <v>0.0254947938057283</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.344905722419878</v>
+      </c>
       <c r="J97" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>46</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.00221171365255538</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.0349917490732939</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E98"/>
+      <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00219531889035867</v>
+        <v>0.00142505175858711</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0348039822241817</v>
-      </c>
-      <c r="I98" t="n">
-        <v>-0.746805499132938</v>
-      </c>
+        <v>0.0258486596295141</v>
+      </c>
+      <c r="I98"/>
       <c r="J98" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00222425899670776</v>
+        <v>0.00139588955623743</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0349666048167687</v>
+        <v>0.0254449636524747</v>
       </c>
       <c r="G99" t="n">
-        <v>0.00223423375933978</v>
+        <v>0.0014046815217409</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0351989436854309</v>
+        <v>0.0255324360702824</v>
       </c>
       <c r="I99" t="n">
-        <v>0.446451164311883</v>
+        <v>0.625904546147141</v>
       </c>
       <c r="J99" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B100" t="s">
         <v>18</v>
       </c>
       <c r="C100" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
-      </c>
-      <c r="E100"/>
-      <c r="F100"/>
+        <v>47</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.001399013692437</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.0255301578255073</v>
+      </c>
       <c r="G100" t="n">
-        <v>0.00044388554500548</v>
+        <v>0.00140710106616449</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0139170029038713</v>
-      </c>
-      <c r="I100"/>
+        <v>0.025629530201547</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.574754288939357</v>
+      </c>
       <c r="J100" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B101" t="s">
         <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000439974285919277</v>
+        <v>0.00140201625958041</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0138159439735513</v>
+        <v>0.025535899271791</v>
       </c>
       <c r="G101" t="n">
-        <v>0.000440961902269623</v>
+        <v>0.00140603418103231</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0138507046608504</v>
+        <v>0.0255487790348562</v>
       </c>
       <c r="I101" t="n">
-        <v>0.223968634311138</v>
+        <v>0.285762715167538</v>
       </c>
       <c r="J101" t="n">
         <v>1356</v>
@@ -5183,89 +5237,89 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B102" t="s">
         <v>18</v>
       </c>
       <c r="C102" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>47</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0.000439845086265423</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.0138525399354658</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E102"/>
+      <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.000440624382932558</v>
+        <v>0.00119244579546568</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0138788724566194</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0.176861902636555</v>
-      </c>
+        <v>0.0251643833711406</v>
+      </c>
+      <c r="I102"/>
       <c r="J102" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B103" t="s">
         <v>18</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>45</v>
-      </c>
-      <c r="E103"/>
-      <c r="F103"/>
+        <v>46</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.00119457648815891</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.0252214708666564</v>
+      </c>
       <c r="G103" t="n">
-        <v>0.000564040080425826</v>
+        <v>0.00119610768031777</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0140496933121928</v>
-      </c>
-      <c r="I103"/>
+        <v>0.0252560367096212</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.128014574612191</v>
+      </c>
       <c r="J103" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B104" t="s">
         <v>18</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D104" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E104" t="n">
-        <v>0.000560769395159396</v>
+        <v>0.00118973844791006</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0139627289503163</v>
+        <v>0.0251653836699592</v>
       </c>
       <c r="G104" t="n">
-        <v>0.000565120901327657</v>
+        <v>0.00119252399300116</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0141382598390514</v>
+        <v>0.025173157789918</v>
       </c>
       <c r="I104" t="n">
-        <v>0.770013311848341</v>
+        <v>0.233583987194362</v>
       </c>
       <c r="J104" t="n">
         <v>1356</v>
@@ -5273,31 +5327,31 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B105" t="s">
         <v>18</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000558017658895458</v>
+        <v>0.00118991315860311</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0139846989880688</v>
+        <v>0.0251834767319172</v>
       </c>
       <c r="G105" t="n">
-        <v>0.000561189824155014</v>
+        <v>0.00119466071725694</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0140593369457126</v>
+        <v>0.0253136050428243</v>
       </c>
       <c r="I105" t="n">
-        <v>0.565257088246883</v>
+        <v>0.397398071707525</v>
       </c>
       <c r="J105" t="n">
         <v>1356</v>
@@ -5305,13 +5359,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B106" t="s">
         <v>18</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s">
         <v>45</v>
@@ -5319,10 +5373,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.000375867714693547</v>
+        <v>0.00120296347530362</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0137004109084272</v>
+        <v>0.0252346187819973</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -5331,31 +5385,31 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B107" t="s">
         <v>18</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
         <v>46</v>
       </c>
       <c r="E107" t="n">
-        <v>0.000372032169871245</v>
+        <v>0.00119471390482805</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0135919185493906</v>
+        <v>0.0252108714059851</v>
       </c>
       <c r="G107" t="n">
-        <v>0.000372903627829227</v>
+        <v>0.00120261336570215</v>
       </c>
       <c r="H107" t="n">
-        <v>0.013676742553819</v>
+        <v>0.0252495216273366</v>
       </c>
       <c r="I107" t="n">
-        <v>0.233695221216993</v>
+        <v>0.656857897923809</v>
       </c>
       <c r="J107" t="n">
         <v>1356</v>
@@ -5363,31 +5417,31 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B108" t="s">
         <v>18</v>
       </c>
       <c r="C108" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D108" t="s">
         <v>47</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000372069421134595</v>
+        <v>0.00119431599904316</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0136056373613499</v>
+        <v>0.0251998011855152</v>
       </c>
       <c r="G108" t="n">
-        <v>0.000373256752247392</v>
+        <v>0.00120248868424409</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0136237415927978</v>
+        <v>0.0252562825324428</v>
       </c>
       <c r="I108" t="n">
-        <v>0.318100370762827</v>
+        <v>0.679647576564828</v>
       </c>
       <c r="J108" t="n">
         <v>1356</v>
@@ -5395,7 +5449,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B109" t="s">
         <v>18</v>
@@ -5404,88 +5458,88 @@
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>45</v>
-      </c>
-      <c r="E109"/>
-      <c r="F109"/>
+        <v>48</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.0011911593977007</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.0251924647014567</v>
+      </c>
       <c r="G109" t="n">
-        <v>0.00037219150633222</v>
+        <v>0.00121280768205429</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0136546082963883</v>
-      </c>
-      <c r="I109"/>
+        <v>0.0253514297729635</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.78497256192499</v>
+      </c>
       <c r="J109" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B110" t="s">
         <v>18</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D110" t="s">
-        <v>46</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0.000372027483026352</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0.0135887949508507</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E110"/>
+      <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.000376853132503008</v>
+        <v>0.00107996704992498</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0137365987375999</v>
-      </c>
-      <c r="I110" t="n">
-        <v>1.28051197149539</v>
-      </c>
+        <v>0.0230866330867458</v>
+      </c>
+      <c r="I110"/>
       <c r="J110" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B111" t="s">
         <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000372920913495732</v>
+        <v>0.00105829575197546</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0136139282162822</v>
+        <v>0.0227090399390152</v>
       </c>
       <c r="G111" t="n">
-        <v>0.000372463059217537</v>
+        <v>0.00105666916432244</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0136262096082293</v>
+        <v>0.0226552023906844</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.122926090752899</v>
+        <v>-0.153935376175228</v>
       </c>
       <c r="J111" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B112" t="s">
         <v>18</v>
@@ -5494,24 +5548,30 @@
         <v>27</v>
       </c>
       <c r="D112" t="s">
-        <v>45</v>
-      </c>
-      <c r="E112"/>
-      <c r="F112"/>
+        <v>47</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.00104684932491007</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.0225191897277554</v>
+      </c>
       <c r="G112" t="n">
-        <v>0.000428033006907758</v>
+        <v>0.00106107008706408</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0143965718712105</v>
-      </c>
-      <c r="I112"/>
+        <v>0.0227148044229999</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1.34022835318609</v>
+      </c>
       <c r="J112" t="n">
         <v>904</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B113" t="s">
         <v>18</v>
@@ -5522,15 +5582,21 @@
       <c r="D113" t="s">
         <v>48</v>
       </c>
-      <c r="E113"/>
-      <c r="F113"/>
+      <c r="E113" t="n">
+        <v>0.00105231392678582</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.0226346451964706</v>
+      </c>
       <c r="G113" t="n">
-        <v>0.327818819777481</v>
+        <v>0.00106804464192645</v>
       </c>
       <c r="H113" t="n">
-        <v>0.571753276009051</v>
-      </c>
-      <c r="I113"/>
+        <v>0.0228864365463717</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1.47285183812652</v>
+      </c>
       <c r="J113" t="n">
         <v>904</v>
       </c>
@@ -5540,31 +5606,25 @@
         <v>32</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>46</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0.000474916022319012</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0.0158049825668476</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E114"/>
+      <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.00043758361088985</v>
+        <v>0.00165341602227451</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0147229983823517</v>
-      </c>
-      <c r="I114" t="n">
-        <v>-8.53149215374969</v>
-      </c>
+        <v>0.0305620148491919</v>
+      </c>
+      <c r="I114"/>
       <c r="J114" t="n">
-        <v>904</v>
+        <v>143</v>
       </c>
     </row>
     <row r="115">
@@ -5572,36 +5632,30 @@
         <v>32</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>47</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0.000425515296006831</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0.0143672464520354</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E115"/>
+      <c r="F115"/>
       <c r="G115" t="n">
-        <v>0.000428750687598975</v>
+        <v>0.0016703779813622</v>
       </c>
       <c r="H115" t="n">
-        <v>0.014452985972911</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0.754609073693322</v>
-      </c>
+        <v>0.030702625550758</v>
+      </c>
+      <c r="I115"/>
       <c r="J115" t="n">
-        <v>904</v>
+        <v>143</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
@@ -5610,24 +5664,30 @@
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>45</v>
-      </c>
-      <c r="E116"/>
-      <c r="F116"/>
+        <v>47</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.00165820182232547</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.0306129502577943</v>
+      </c>
       <c r="G116" t="n">
-        <v>0.00268815282645594</v>
+        <v>0.00166777604435993</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0397139063005678</v>
-      </c>
-      <c r="I116"/>
+        <v>0.0308048534766547</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.574071204993794</v>
+      </c>
       <c r="J116" t="n">
         <v>143</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
@@ -5636,22 +5696,22 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E117" t="n">
-        <v>0.00265406788311174</v>
+        <v>0.00166341268735721</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0397281039170092</v>
+        <v>0.0306182825762281</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00263230119537899</v>
+        <v>0.00165499021296652</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0391034281942115</v>
+        <v>0.0306163541241423</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.826907185658203</v>
+        <v>-0.508913848837206</v>
       </c>
       <c r="J117" t="n">
         <v>143</v>
@@ -5659,39 +5719,33 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>47</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0.002631692108181</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0.0394235433463223</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E118"/>
+      <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.00266166067175063</v>
+        <v>0.00223129197341069</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0396589737538678</v>
-      </c>
-      <c r="I118" t="n">
-        <v>1.12593479280457</v>
-      </c>
+        <v>0.0353374772554385</v>
+      </c>
+      <c r="I118"/>
       <c r="J118" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
@@ -5700,15 +5754,15 @@
         <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00113457545034649</v>
+        <v>0.00219393284869236</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0257435351200147</v>
+        <v>0.0348129447068459</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5717,7 +5771,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -5726,24 +5780,30 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>48</v>
-      </c>
-      <c r="E120"/>
-      <c r="F120"/>
+        <v>47</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.00220916868978119</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.0350001958743357</v>
+      </c>
       <c r="G120" t="n">
-        <v>34764983312067686094800642000668806826040826064</v>
+        <v>0.00219266203757769</v>
       </c>
       <c r="H120" t="n">
-        <v>35594942945077449720428</v>
-      </c>
-      <c r="I120"/>
+        <v>0.0349430169207912</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-0.752813334686707</v>
+      </c>
       <c r="J120" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -5752,22 +5812,22 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E121" t="n">
-        <v>0.00109058322274795</v>
+        <v>0.00222409037143345</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0250212587860377</v>
+        <v>0.0351450092539544</v>
       </c>
       <c r="G121" t="n">
-        <v>0.00122927328076133</v>
+        <v>0.00221562078910958</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0272304903618475</v>
+        <v>0.0351863839878927</v>
       </c>
       <c r="I121" t="n">
-        <v>11.2822803671036</v>
+        <v>-0.382266783445026</v>
       </c>
       <c r="J121" t="n">
         <v>59</v>
@@ -5775,39 +5835,33 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C122" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>47</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0.00108781475944967</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0.0250089723720988</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E122"/>
+      <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.00112181867464217</v>
+        <v>0.000441445975702941</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0255617793524954</v>
-      </c>
-      <c r="I122" t="n">
-        <v>3.03114183790421</v>
-      </c>
+        <v>0.0139629771530332</v>
+      </c>
+      <c r="I122"/>
       <c r="J122" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B123" t="s">
         <v>18</v>
@@ -5816,15 +5870,15 @@
         <v>19</v>
       </c>
       <c r="D123" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.0006013383804105</v>
+        <v>0.000439898102676739</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0167163375747326</v>
+        <v>0.0138506499225828</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5833,7 +5887,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B124" t="s">
         <v>18</v>
@@ -5842,22 +5896,22 @@
         <v>19</v>
       </c>
       <c r="D124" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E124" t="n">
-        <v>0.000585347938179291</v>
+        <v>0.000439600805870272</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0164485025863485</v>
+        <v>0.0138250283730559</v>
       </c>
       <c r="G124" t="n">
-        <v>0.000657777629776339</v>
+        <v>0.000440323315365035</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0180145301302652</v>
+        <v>0.0138882694653945</v>
       </c>
       <c r="I124" t="n">
-        <v>11.0112731595443</v>
+        <v>0.164086131610805</v>
       </c>
       <c r="J124" t="n">
         <v>1356</v>
@@ -5865,7 +5919,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B125" t="s">
         <v>18</v>
@@ -5874,22 +5928,22 @@
         <v>19</v>
       </c>
       <c r="D125" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E125" t="n">
-        <v>0.00058180775759088</v>
+        <v>0.000440359756604141</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0164088578937446</v>
+        <v>0.0138657022872707</v>
       </c>
       <c r="G125" t="n">
-        <v>0.000583251128564573</v>
+        <v>0.000440216743149556</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0165201244729046</v>
+        <v>0.0138521416952495</v>
       </c>
       <c r="I125" t="n">
-        <v>0.247469898128661</v>
+        <v>-0.0324870547997314</v>
       </c>
       <c r="J125" t="n">
         <v>1356</v>
@@ -5897,7 +5951,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B126" t="s">
         <v>18</v>
@@ -5911,10 +5965,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.00071160326161031</v>
+        <v>0.000554718563543539</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0167996248627374</v>
+        <v>0.0139818992045249</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5923,7 +5977,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B127" t="s">
         <v>18</v>
@@ -5934,28 +5988,22 @@
       <c r="D127" t="s">
         <v>46</v>
       </c>
-      <c r="E127" t="n">
-        <v>0.000707558822284473</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0.0166011919235433</v>
-      </c>
+      <c r="E127"/>
+      <c r="F127"/>
       <c r="G127" t="n">
-        <v>0.000771405337108256</v>
+        <v>0.000557482992075759</v>
       </c>
       <c r="H127" t="n">
-        <v>0.017759199987949</v>
-      </c>
-      <c r="I127" t="n">
-        <v>8.27664935053763</v>
-      </c>
+        <v>0.0139670855227749</v>
+      </c>
+      <c r="I127"/>
       <c r="J127" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B128" t="s">
         <v>18</v>
@@ -5967,19 +6015,19 @@
         <v>47</v>
       </c>
       <c r="E128" t="n">
-        <v>0.000702587964204197</v>
+        <v>0.000558765283081715</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0166020031036067</v>
+        <v>0.0139936678336691</v>
       </c>
       <c r="G128" t="n">
-        <v>0.000701531193601345</v>
+        <v>0.000561788182131778</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0165425523387417</v>
+        <v>0.0140382793639325</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.150637721100813</v>
+        <v>0.538085197626103</v>
       </c>
       <c r="J128" t="n">
         <v>1356</v>
@@ -5987,33 +6035,39 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B129" t="s">
         <v>18</v>
       </c>
       <c r="C129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>45</v>
-      </c>
-      <c r="E129"/>
-      <c r="F129"/>
+        <v>48</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.000559928786407684</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.0139943377463331</v>
+      </c>
       <c r="G129" t="n">
-        <v>0.000540542085230146</v>
+        <v>0.000561874820747092</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0167542833634366</v>
-      </c>
-      <c r="I129"/>
+        <v>0.0140236172915855</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.346346600265922</v>
+      </c>
       <c r="J129" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B130" t="s">
         <v>18</v>
@@ -6022,30 +6076,24 @@
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>46</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0.000517910021047639</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.0162205018347943</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E130"/>
+      <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.000567151651688081</v>
+        <v>0.000371710913738308</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0173297985015766</v>
-      </c>
-      <c r="I130" t="n">
-        <v>8.68226875367076</v>
-      </c>
+        <v>0.0136612221293268</v>
+      </c>
+      <c r="I130"/>
       <c r="J130" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B131" t="s">
         <v>18</v>
@@ -6054,80 +6102,80 @@
         <v>23</v>
       </c>
       <c r="D131" t="s">
-        <v>47</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0.000516148701510878</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0.0161730966745508</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E131"/>
+      <c r="F131"/>
       <c r="G131" t="n">
-        <v>0.000517504467143139</v>
+        <v>0.000374330689349969</v>
       </c>
       <c r="H131" t="n">
-        <v>0.016251397069094</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.261981435589282</v>
-      </c>
+        <v>0.0136723065389618</v>
+      </c>
+      <c r="I131"/>
       <c r="J131" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B132" t="s">
         <v>18</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D132" t="s">
-        <v>45</v>
-      </c>
-      <c r="E132"/>
-      <c r="F132"/>
+        <v>47</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.000372392817057295</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.0136223862866359</v>
+      </c>
       <c r="G132" t="n">
-        <v>0.000541107000709345</v>
+        <v>0.000376085983657055</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0169139969570544</v>
-      </c>
-      <c r="I132"/>
+        <v>0.0136782237306819</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.982000595674347</v>
+      </c>
       <c r="J132" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B133" t="s">
         <v>18</v>
       </c>
       <c r="C133" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D133" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E133" t="n">
-        <v>0.000517812358050164</v>
+        <v>0.000373614377012493</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0162251408840576</v>
+        <v>0.0136434024631597</v>
       </c>
       <c r="G133" t="n">
-        <v>0.000572225127040427</v>
+        <v>0.000374536466952402</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0174510264386328</v>
+        <v>0.0136642073033251</v>
       </c>
       <c r="I133" t="n">
-        <v>9.50897931932617</v>
+        <v>0.246194969320778</v>
       </c>
       <c r="J133" t="n">
         <v>1356</v>
@@ -6135,7 +6183,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B134" t="s">
         <v>18</v>
@@ -6144,114 +6192,1078 @@
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>47</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0.000515384050890979</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0.0161680643942117</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E134"/>
+      <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.000517210017034205</v>
+        <v>0.000369323544634441</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0162054641686816</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0.353041527249634</v>
-      </c>
+        <v>0.0136169985205166</v>
+      </c>
+      <c r="I134"/>
       <c r="J134" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B135" t="s">
         <v>18</v>
       </c>
       <c r="C135" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000501608467794939</v>
+        <v>0.000374086546685996</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0165772519514686</v>
+        <v>0.0136505957718665</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B136" t="s">
         <v>18</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E136" t="n">
-        <v>0.000491075252473478</v>
+        <v>0.000372173566245856</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0163591959415439</v>
+        <v>0.0136059733207704</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000561833316357502</v>
+        <v>0.000373773943852681</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0176341159725294</v>
+        <v>0.0136458717780032</v>
       </c>
       <c r="I136" t="n">
-        <v>12.5941381231653</v>
+        <v>0.428167247381803</v>
       </c>
       <c r="J136" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>32</v>
+      </c>
+      <c r="B137" t="s">
+        <v>18</v>
+      </c>
+      <c r="C137" t="s">
+        <v>25</v>
+      </c>
+      <c r="D137" t="s">
+        <v>48</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.000371827736288835</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.0136090330158051</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.000372967634167825</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.0136355504376896</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.305629168475566</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>32</v>
+      </c>
+      <c r="B138" t="s">
+        <v>18</v>
+      </c>
+      <c r="C138" t="s">
+        <v>27</v>
+      </c>
+      <c r="D138" t="s">
+        <v>45</v>
+      </c>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138" t="n">
+        <v>0.00043081320244971</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.0144607767761894</v>
+      </c>
+      <c r="I138"/>
+      <c r="J138" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>32</v>
+      </c>
+      <c r="B139" t="s">
+        <v>18</v>
+      </c>
+      <c r="C139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D139" t="s">
+        <v>46</v>
+      </c>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139" t="n">
+        <v>0.000430623780748095</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.0144855076209628</v>
+      </c>
+      <c r="I139"/>
+      <c r="J139" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>32</v>
+      </c>
+      <c r="B140" t="s">
+        <v>18</v>
+      </c>
+      <c r="C140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D140" t="s">
+        <v>47</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.000425760087117938</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.0143894536228639</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.000430152341215417</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.014507762637408</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.02109268662076</v>
+      </c>
+      <c r="J140" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>32</v>
+      </c>
+      <c r="B141" t="s">
+        <v>18</v>
+      </c>
+      <c r="C141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" t="s">
+        <v>48</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.000425834334838184</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.0143824042304185</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.00042675870973324</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.0143555637166811</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.216603639005718</v>
+      </c>
+      <c r="J141" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
         <v>33</v>
       </c>
-      <c r="B137" t="s">
-        <v>18</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="B142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" t="s">
+        <v>45</v>
+      </c>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142" t="n">
+        <v>0.00268968781552142</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.040233569810268</v>
+      </c>
+      <c r="I142"/>
+      <c r="J142" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>33</v>
+      </c>
+      <c r="B143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" t="s">
+        <v>14</v>
+      </c>
+      <c r="D143" t="s">
+        <v>46</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.00261895164248887</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.0393001944768515</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.00262201152404863</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.0393063290198784</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.116699775408867</v>
+      </c>
+      <c r="J143" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>33</v>
+      </c>
+      <c r="B144" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" t="s">
+        <v>47</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.00264197102372509</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.0395554223013669</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.00264274496640274</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.0396931544687569</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.0292855605625911</v>
+      </c>
+      <c r="J144" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>33</v>
+      </c>
+      <c r="B145" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" t="s">
+        <v>48</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.00265892751213425</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.0396512072522042</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.00265301936198677</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.0395290933786506</v>
+      </c>
+      <c r="I145" t="n">
+        <v>-0.222695327148181</v>
+      </c>
+      <c r="J145" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>33</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
+        <v>16</v>
+      </c>
+      <c r="D146" t="s">
+        <v>45</v>
+      </c>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146" t="n">
+        <v>0.00116447693609324</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.0264840745678379</v>
+      </c>
+      <c r="I146"/>
+      <c r="J146" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>33</v>
+      </c>
+      <c r="B147" t="s">
+        <v>13</v>
+      </c>
+      <c r="C147" t="s">
+        <v>16</v>
+      </c>
+      <c r="D147" t="s">
+        <v>46</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.00112704262855789</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.0254223354178506</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.00112399005786281</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.0255669895810273</v>
+      </c>
+      <c r="I147" t="n">
+        <v>-0.271583424936371</v>
+      </c>
+      <c r="J147" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>33</v>
+      </c>
+      <c r="B148" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" t="s">
+        <v>16</v>
+      </c>
+      <c r="D148" t="s">
+        <v>47</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.00109868565386831</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.0251939102600145</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.00111247877387397</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.0254932361761065</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1.23985466775485</v>
+      </c>
+      <c r="J148" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>33</v>
+      </c>
+      <c r="B149" t="s">
+        <v>13</v>
+      </c>
+      <c r="C149" t="s">
+        <v>16</v>
+      </c>
+      <c r="D149" t="s">
+        <v>48</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.00109798601208766</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.0250937480338882</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.00110202816137862</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.0255787317785432</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.366791832788591</v>
+      </c>
+      <c r="J149" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>33</v>
+      </c>
+      <c r="B150" t="s">
+        <v>18</v>
+      </c>
+      <c r="C150" t="s">
+        <v>19</v>
+      </c>
+      <c r="D150" t="s">
+        <v>45</v>
+      </c>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150" t="n">
+        <v>0.000599747962336917</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.0168557467742565</v>
+      </c>
+      <c r="I150"/>
+      <c r="J150" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>33</v>
+      </c>
+      <c r="B151" t="s">
+        <v>18</v>
+      </c>
+      <c r="C151" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" t="s">
+        <v>46</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.000583467966436226</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.0164228594251004</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.000581560265235879</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.0163717888303528</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-0.32803155827244</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>33</v>
+      </c>
+      <c r="B152" t="s">
+        <v>18</v>
+      </c>
+      <c r="C152" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" t="s">
+        <v>47</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.000580665349151087</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.0163858610904858</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.000580333349800885</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.0163918885077154</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-0.0572083872684009</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>33</v>
+      </c>
+      <c r="B153" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153" t="s">
+        <v>19</v>
+      </c>
+      <c r="D153" t="s">
+        <v>48</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.000583287964039877</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.0164058243930587</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.000581043398396412</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.0164467979029068</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-0.386299138697611</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>33</v>
+      </c>
+      <c r="B154" t="s">
+        <v>18</v>
+      </c>
+      <c r="C154" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154" t="s">
+        <v>45</v>
+      </c>
+      <c r="E154"/>
+      <c r="F154"/>
+      <c r="G154" t="n">
+        <v>0.000733442147241684</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0171016330092669</v>
+      </c>
+      <c r="I154"/>
+      <c r="J154" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>33</v>
+      </c>
+      <c r="B155" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.000698539780076497</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0165357238916385</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.000700884543485353</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0165305769891701</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.334543460923791</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>33</v>
+      </c>
+      <c r="B156" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" t="s">
+        <v>47</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.000699007310220551</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.0165217794806285</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.000707261834780408</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0165475795656655</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1.16711013572786</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>33</v>
+      </c>
+      <c r="B157" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157" t="s">
+        <v>21</v>
+      </c>
+      <c r="D157" t="s">
+        <v>48</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.000702740521396811</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.0165495231400744</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.000701470541414973</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.0165730148039869</v>
+      </c>
+      <c r="I157" t="n">
+        <v>-0.181045376371209</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>33</v>
+      </c>
+      <c r="B158" t="s">
+        <v>18</v>
+      </c>
+      <c r="C158" t="s">
+        <v>23</v>
+      </c>
+      <c r="D158" t="s">
+        <v>45</v>
+      </c>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158" t="n">
+        <v>0.000533181627325904</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.0166465368560204</v>
+      </c>
+      <c r="I158"/>
+      <c r="J158" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>33</v>
+      </c>
+      <c r="B159" t="s">
+        <v>18</v>
+      </c>
+      <c r="C159" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" t="s">
+        <v>46</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.000516437004313829</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.0161924004291914</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.000515135469779379</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.0162296906740466</v>
+      </c>
+      <c r="I159" t="n">
+        <v>-0.25265869092778</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>33</v>
+      </c>
+      <c r="B160" t="s">
+        <v>18</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+      <c r="D160" t="s">
+        <v>47</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.000514629831776683</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.0161873360129158</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.000522178065542295</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.0162948523274425</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1.44552869293211</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>33</v>
+      </c>
+      <c r="B161" t="s">
+        <v>18</v>
+      </c>
+      <c r="C161" t="s">
+        <v>23</v>
+      </c>
+      <c r="D161" t="s">
+        <v>48</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.000514907592634405</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.0161918112171043</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.000518422754932936</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.0162462825593094</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.67804938442294</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>33</v>
+      </c>
+      <c r="B162" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" t="s">
+        <v>25</v>
+      </c>
+      <c r="D162" t="s">
+        <v>45</v>
+      </c>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162" t="n">
+        <v>0.000540311872704341</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.0168103013403629</v>
+      </c>
+      <c r="I162"/>
+      <c r="J162" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>33</v>
+      </c>
+      <c r="B163" t="s">
+        <v>18</v>
+      </c>
+      <c r="C163" t="s">
+        <v>25</v>
+      </c>
+      <c r="D163" t="s">
+        <v>46</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.000515832650532893</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.0161900700128506</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.00051743920899692</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.0161651553305949</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.310482552557568</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>33</v>
+      </c>
+      <c r="B164" t="s">
+        <v>18</v>
+      </c>
+      <c r="C164" t="s">
+        <v>25</v>
+      </c>
+      <c r="D164" t="s">
+        <v>47</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.000513468431727726</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.0161455092047277</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.000516928249509697</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.0162622745887077</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.669303290205565</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>33</v>
+      </c>
+      <c r="B165" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" t="s">
+        <v>25</v>
+      </c>
+      <c r="D165" t="s">
+        <v>48</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.000515401163955399</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.016189165944605</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.000518152384373022</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.016284561087362</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.530967433634873</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>33</v>
+      </c>
+      <c r="B166" t="s">
+        <v>18</v>
+      </c>
+      <c r="C166" t="s">
         <v>27</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D166" t="s">
+        <v>45</v>
+      </c>
+      <c r="E166"/>
+      <c r="F166"/>
+      <c r="G166" t="n">
+        <v>0.000513214768192043</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.0166982710796898</v>
+      </c>
+      <c r="I166"/>
+      <c r="J166" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>33</v>
+      </c>
+      <c r="B167" t="s">
+        <v>18</v>
+      </c>
+      <c r="C167" t="s">
+        <v>27</v>
+      </c>
+      <c r="D167" t="s">
+        <v>46</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.000463431238055903</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.0156660956000309</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.000480770340358602</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.016078089874649</v>
+      </c>
+      <c r="I167" t="n">
+        <v>3.60652495529679</v>
+      </c>
+      <c r="J167" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>33</v>
+      </c>
+      <c r="B168" t="s">
+        <v>18</v>
+      </c>
+      <c r="C168" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168" t="s">
         <v>47</v>
       </c>
-      <c r="E137" t="n">
-        <v>0.000481764806560618</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.0161001781311565</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0.000497075916031759</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0.0165023076245274</v>
-      </c>
-      <c r="I137" t="n">
-        <v>3.08023562947338</v>
-      </c>
-      <c r="J137" t="n">
+      <c r="E168" t="n">
+        <v>0.000467473423972771</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.0157542551139309</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.000482379343376721</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.0161371076345837</v>
+      </c>
+      <c r="I168" t="n">
+        <v>3.09008244416233</v>
+      </c>
+      <c r="J168" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>33</v>
+      </c>
+      <c r="B169" t="s">
+        <v>18</v>
+      </c>
+      <c r="C169" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169" t="s">
+        <v>48</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.000476758676422462</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.0160465401543294</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.000501189023645224</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.016603213630096</v>
+      </c>
+      <c r="I169" t="n">
+        <v>4.87447770605102</v>
+      </c>
+      <c r="J169" t="n">
         <v>904</v>
       </c>
     </row>
@@ -6291,19 +7303,19 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00119480106609414</v>
+        <v>0.00119655545036231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00119738839412016</v>
+        <v>0.00119710702510518</v>
       </c>
       <c r="F2" t="n">
-        <v>1.75403923976168</v>
+        <v>0.0956561833428542</v>
       </c>
     </row>
     <row r="3">
@@ -6311,19 +7323,19 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.41926393746313</v>
+        <v>0.00100029410980916</v>
       </c>
       <c r="E3" t="n">
-        <v>8691245828016921523200468000442204284060284046</v>
+        <v>0.00119829074797585</v>
       </c>
       <c r="F3" t="n">
-        <v>-23.1715556870826</v>
+        <v>-1.1792448593317</v>
       </c>
     </row>
     <row r="4">
@@ -6331,19 +7343,19 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00119606000027793</v>
+        <v>0.0011967827505252</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00120008328037061</v>
+        <v>0.0012003709013237</v>
       </c>
       <c r="F4" t="n">
-        <v>0.644113670243516</v>
+        <v>1.81891189224548</v>
       </c>
     </row>
     <row r="5">
@@ -6360,7 +7372,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00121014431142447</v>
+        <v>0.00124398261464006</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -6371,19 +7383,19 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00147436649915243</v>
+        <v>0.00146554211220192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00146107985215994</v>
+        <v>0.00146913479677698</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.601864826578078</v>
+        <v>-0.243338299413299</v>
       </c>
     </row>
     <row r="7">
@@ -6391,19 +7403,19 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00147211407966714</v>
+        <v>0.00142786585458327</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00147620279163385</v>
+        <v>0.00146742994418569</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.116134674083102</v>
+        <v>-0.50784000810539</v>
       </c>
     </row>
     <row r="8">
@@ -6411,39 +7423,39 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="e">
-        <v>#NUM!</v>
+      <c r="D8" t="n">
+        <v>0.00146438826819781</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00147769642044416</v>
-      </c>
-      <c r="F8" t="e">
-        <v>#NUM!</v>
+        <v>0.00147181837939702</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.464051331549821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.000421021441315474</v>
+      <c r="D9" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00042636801043581</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1.13981172768212</v>
+        <v>0.00149187136667049</v>
+      </c>
+      <c r="F9" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="10">
@@ -6451,19 +7463,19 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="e">
-        <v>#NUM!</v>
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.000400481683371258</v>
       </c>
       <c r="E10" t="n">
-        <v>0.163969700526929</v>
-      </c>
-      <c r="F10" t="e">
-        <v>#NUM!</v>
+        <v>0.000405851961557992</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.493115735271858</v>
       </c>
     </row>
     <row r="11">
@@ -6471,19 +7483,19 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000402970306179354</v>
+        <v>0.000406181909601884</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000408391194849675</v>
+        <v>0.000401638271774652</v>
       </c>
       <c r="F11" t="n">
-        <v>1.00461703084747</v>
+        <v>-11.8665623197807</v>
       </c>
     </row>
     <row r="12">
@@ -6491,39 +7503,39 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="e">
-        <v>#NUM!</v>
+      <c r="D12" t="n">
+        <v>0.000402945335304631</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000413292467092861</v>
-      </c>
-      <c r="F12" t="e">
-        <v>#NUM!</v>
+        <v>0.000410828843754454</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.46993854061624</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.000441916306925829</v>
+      <c r="D13" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000464980731185423</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3.29957954894549</v>
+        <v>0.00041630493248063</v>
+      </c>
+      <c r="F13" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="14">
@@ -6531,19 +7543,19 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00127368533224027</v>
+        <v>0.000440986173434694</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00141346108785193</v>
+        <v>0.000441699885381531</v>
       </c>
       <c r="F14" t="n">
-        <v>9.88890014822223</v>
+        <v>0.201069056622543</v>
       </c>
     </row>
     <row r="15">
@@ -6551,19 +7563,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000441936878734143</v>
+        <v>0.000443033504858136</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000444247923402119</v>
+        <v>267.68003519277</v>
       </c>
       <c r="F15" t="n">
-        <v>0.588970129010791</v>
+        <v>19.9698622743398</v>
       </c>
     </row>
     <row r="16">
@@ -6571,39 +7583,39 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="e">
-        <v>#NUM!</v>
+      <c r="D16" t="n">
+        <v>0.000442041099489419</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00045091191498329</v>
-      </c>
-      <c r="F16" t="e">
-        <v>#NUM!</v>
+        <v>0.000442926340311838</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.369086427098096</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.00056367786495073</v>
+      <c r="D17" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000583493309155064</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.47222252992354</v>
+        <v>0.000448995901255752</v>
+      </c>
+      <c r="F17" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="18">
@@ -6611,19 +7623,19 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00140403196291606</v>
+        <v>0.000562085373306923</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00158125397994027</v>
+        <v>0.000565578967452626</v>
       </c>
       <c r="F18" t="n">
-        <v>11.2076882823658</v>
+        <v>0.48741047927765</v>
       </c>
     </row>
     <row r="19">
@@ -6631,19 +7643,19 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00056217957331907</v>
+        <v>0.000563072198341242</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000565701169176687</v>
+        <v>297.386465031614</v>
       </c>
       <c r="F19" t="n">
-        <v>0.644871597310232</v>
+        <v>20.1046323317966</v>
       </c>
     </row>
     <row r="20">
@@ -6651,39 +7663,39 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
-      <c r="D20" t="e">
-        <v>#NUM!</v>
+      <c r="D20" t="n">
+        <v>0.000563299552942815</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000569060528722536</v>
-      </c>
-      <c r="F20" t="e">
-        <v>#NUM!</v>
+        <v>0.000564530360648154</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.24262162725552</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.000371452664946264</v>
+      <c r="D21" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000393554231843609</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4.75083972172167</v>
+        <v>0.000572017530403988</v>
+      </c>
+      <c r="F21" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="22">
@@ -6691,19 +7703,19 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00119191264969172</v>
+        <v>0.000371415262608523</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00133931606282742</v>
+        <v>0.000374043422957246</v>
       </c>
       <c r="F22" t="n">
-        <v>11.005872118379</v>
+        <v>1.22847767101778</v>
       </c>
     </row>
     <row r="23">
@@ -6711,19 +7723,19 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000372085533944945</v>
+        <v>0.00037396252084702</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000374931888563065</v>
+        <v>315.537946149748</v>
       </c>
       <c r="F23" t="n">
-        <v>1.69792121957027</v>
+        <v>19.9982661888322</v>
       </c>
     </row>
     <row r="24">
@@ -6731,39 +7743,39 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="D24" t="e">
-        <v>#NUM!</v>
+      <c r="D24" t="n">
+        <v>0.00037164852830393</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000379594646688261</v>
-      </c>
-      <c r="F24" t="e">
-        <v>#NUM!</v>
+        <v>0.000373589451612419</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.15469618254902</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="n">
         <v>6</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.000372379035579144</v>
+      <c r="D25" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000393123190300359</v>
-      </c>
-      <c r="F25" t="n">
-        <v>5.2196173477121</v>
+        <v>0.00037553285998693</v>
+      </c>
+      <c r="F25" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="26">
@@ -6771,19 +7783,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00119681005362634</v>
+        <v>0.000371930755229186</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00134656770183042</v>
+        <v>0.000374365577083806</v>
       </c>
       <c r="F26" t="n">
-        <v>11.1214347411203</v>
+        <v>0.925424268937572</v>
       </c>
     </row>
     <row r="27">
@@ -6791,19 +7803,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00037199616671106</v>
+        <v>0.000373912732928233</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00037431423821325</v>
+        <v>298.801719963046</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4469906671597</v>
+        <v>20.1576388155051</v>
       </c>
     </row>
     <row r="28">
@@ -6811,18 +7823,38 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C28" t="n">
         <v>6</v>
       </c>
-      <c r="D28" t="e">
+      <c r="D28" t="n">
+        <v>0.00037165869119668</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000376407939211573</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.60675685602674</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="E28" t="n">
-        <v>0.000381535825771593</v>
-      </c>
-      <c r="F28" t="e">
+      <c r="E29" t="n">
+        <v>0.000378060618497367</v>
+      </c>
+      <c r="F29" t="e">
         <v>#NUM!</v>
       </c>
     </row>

--- a/results/chronological/consolidated/Stress_Testing.xlsx
+++ b/results/chronological/consolidated/Stress_Testing.xlsx
@@ -2201,10 +2201,10 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.000168686737569334</v>
+        <v>0.000166951352009226</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00970426437855947</v>
+        <v>0.00970468066990117</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
@@ -2323,10 +2323,10 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000383758005516446</v>
+        <v>0.0000389439834297262</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00475854037000235</v>
+        <v>0.00477169304922805</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2445,10 +2445,10 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10" t="n">
-        <v>0.0000919954176231408</v>
+        <v>0.0000910022935740849</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0037891615776163</v>
+        <v>0.00367083436958826</v>
       </c>
       <c r="I10"/>
       <c r="J10" t="n">
@@ -2567,10 +2567,10 @@
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14" t="n">
-        <v>0.000212624154643448</v>
+        <v>0.000211069332287431</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0039682070509222</v>
+        <v>0.00382465460406651</v>
       </c>
       <c r="I14"/>
       <c r="J14" t="n">
@@ -2689,10 +2689,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000238690994494394</v>
+        <v>0.0000225783042244154</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00359832122415118</v>
+        <v>0.00347357615032662</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2811,10 +2811,10 @@
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22" t="n">
-        <v>0.0000239436374210842</v>
+        <v>0.0000225218283341104</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00360039788898703</v>
+        <v>0.00346672521481672</v>
       </c>
       <c r="I22"/>
       <c r="J22" t="n">
@@ -2933,10 +2933,10 @@
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26" t="n">
-        <v>0.000120017100028126</v>
+        <v>0.000118162887999717</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0100115488357566</v>
+        <v>0.00996640043893173</v>
       </c>
       <c r="I26"/>
       <c r="J26" t="n">
@@ -3055,10 +3055,10 @@
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30" t="n">
-        <v>0.000240409228876508</v>
+        <v>0.00023832954051971</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0117910181351902</v>
+        <v>0.0116870267057331</v>
       </c>
       <c r="I30"/>
       <c r="J30" t="n">
@@ -3177,10 +3177,10 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.000100435736413944</v>
+        <v>0.0000976968062414234</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00737480853548937</v>
+        <v>0.00734187982457743</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
@@ -3299,10 +3299,10 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38" t="n">
-        <v>0.000104877900909667</v>
+        <v>0.000103727608124984</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00464118971782387</v>
+        <v>0.00455564789974985</v>
       </c>
       <c r="I38"/>
       <c r="J38" t="n">
@@ -3421,10 +3421,10 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42" t="n">
-        <v>0.00022295225482055</v>
+        <v>0.000222375374752585</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0047466622445616</v>
+        <v>0.00470330026920116</v>
       </c>
       <c r="I42"/>
       <c r="J42" t="n">
@@ -3543,10 +3543,10 @@
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46" t="n">
-        <v>0.0000361023100106164</v>
+        <v>0.0000354501843301481</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00437981741054315</v>
+        <v>0.00434374097915329</v>
       </c>
       <c r="I46"/>
       <c r="J46" t="n">
@@ -3665,10 +3665,10 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.0000366751183215674</v>
+        <v>0.0000355776895936481</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0044192686297208</v>
+        <v>0.00433599898517031</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
@@ -3787,10 +3787,10 @@
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54" t="n">
-        <v>0.000132224829945565</v>
+        <v>0.000130659464947865</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0101568711984453</v>
+        <v>0.0101081778445376</v>
       </c>
       <c r="I54"/>
       <c r="J54" t="n">
@@ -3909,10 +3909,10 @@
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000509593372187773</v>
+        <v>0.000514077013255524</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0163047301690871</v>
+        <v>0.016413932506955</v>
       </c>
       <c r="I58"/>
       <c r="J58" t="n">
@@ -4031,10 +4031,10 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.000256461740788886</v>
+        <v>0.000255628278480086</v>
       </c>
       <c r="H62" t="n">
-        <v>0.012073981454637</v>
+        <v>0.0120463189912403</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -4153,10 +4153,10 @@
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.000165815958335335</v>
+        <v>0.000163941763014223</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00786228187051452</v>
+        <v>0.00778046952207918</v>
       </c>
       <c r="I66"/>
       <c r="J66" t="n">
@@ -4275,10 +4275,10 @@
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.0002833163035876</v>
+        <v>0.000282133888118239</v>
       </c>
       <c r="H70" t="n">
-        <v>0.00796890206023885</v>
+        <v>0.00787918931130336</v>
       </c>
       <c r="I70"/>
       <c r="J70" t="n">
@@ -4397,10 +4397,10 @@
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.0000958874139316355</v>
+        <v>0.0000945377175719618</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00759530703158959</v>
+        <v>0.00753901453921994</v>
       </c>
       <c r="I74"/>
       <c r="J74" t="n">
@@ -4519,10 +4519,10 @@
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.00009514606259915</v>
+        <v>0.0000941458902904498</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00755718384344694</v>
+        <v>0.00751890765003684</v>
       </c>
       <c r="I78"/>
       <c r="J78" t="n">
@@ -4641,10 +4641,10 @@
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.000221592644343359</v>
+        <v>0.000215692929484584</v>
       </c>
       <c r="H82" t="n">
-        <v>0.012451624232008</v>
+        <v>0.0122567740825998</v>
       </c>
       <c r="I82"/>
       <c r="J82" t="n">
@@ -4763,10 +4763,10 @@
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.0036894350235934</v>
+        <v>0.00358565786388399</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0498344561779589</v>
+        <v>0.0493874740165199</v>
       </c>
       <c r="I86"/>
       <c r="J86" t="n">
@@ -4885,10 +4885,10 @@
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00367285350058195</v>
+        <v>0.00349386299399352</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0473897330050055</v>
+        <v>0.0459747385242672</v>
       </c>
       <c r="I90"/>
       <c r="J90" t="n">
@@ -5007,10 +5007,10 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.00129009219262651</v>
+        <v>0.0012781130895058</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0255720143607566</v>
+        <v>0.0254647142158253</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -5129,10 +5129,10 @@
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00142505175858711</v>
+        <v>0.00141992526724589</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0258486596295141</v>
+        <v>0.0256755420060456</v>
       </c>
       <c r="I98"/>
       <c r="J98" t="n">
@@ -5251,10 +5251,10 @@
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.00119244579546568</v>
+        <v>0.00119899462861565</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0251643833711406</v>
+        <v>0.0252687461648014</v>
       </c>
       <c r="I102"/>
       <c r="J102" t="n">
@@ -5373,10 +5373,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.00120296347530362</v>
+        <v>0.00120168990212095</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0252346187819973</v>
+        <v>0.0251622208356207</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -5495,10 +5495,10 @@
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.00107996704992498</v>
+        <v>0.0010617363059797</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0230866330867458</v>
+        <v>0.0228232465978768</v>
       </c>
       <c r="I110"/>
       <c r="J110" t="n">
@@ -5617,10 +5617,10 @@
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.00165341602227451</v>
+        <v>0.00166078224759289</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0305620148491919</v>
+        <v>0.0305842263140882</v>
       </c>
       <c r="I114"/>
       <c r="J114" t="n">
@@ -5733,10 +5733,10 @@
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.00223129197341069</v>
+        <v>0.00223277854413594</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0353374772554385</v>
+        <v>0.0352608912488804</v>
       </c>
       <c r="I118"/>
       <c r="J118" t="n">
@@ -5849,10 +5849,10 @@
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.000441445975702941</v>
+        <v>0.000441846366082811</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0139629771530332</v>
+        <v>0.0139014624498722</v>
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
@@ -5965,10 +5965,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000554718563543539</v>
+        <v>0.000555424518770416</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0139818992045249</v>
+        <v>0.0139814740674101</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -6081,10 +6081,10 @@
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.000371710913738308</v>
+        <v>0.000373540377812871</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0136612221293268</v>
+        <v>0.0136652236531096</v>
       </c>
       <c r="I130"/>
       <c r="J130" t="n">
@@ -6197,10 +6197,10 @@
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.000369323544634441</v>
+        <v>0.000369655887615657</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0136169985205166</v>
+        <v>0.0135913243800647</v>
       </c>
       <c r="I134"/>
       <c r="J134" t="n">
@@ -6313,10 +6313,10 @@
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138" t="n">
-        <v>0.00043081320244971</v>
+        <v>0.00042861553841477</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0144607767761894</v>
+        <v>0.014396097917095</v>
       </c>
       <c r="I138"/>
       <c r="J138" t="n">
@@ -6429,10 +6429,10 @@
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142" t="n">
-        <v>0.00268968781552142</v>
+        <v>0.00261947251925398</v>
       </c>
       <c r="H142" t="n">
-        <v>0.040233569810268</v>
+        <v>0.0395379087269634</v>
       </c>
       <c r="I142"/>
       <c r="J142" t="n">
@@ -6551,10 +6551,10 @@
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146" t="n">
-        <v>0.00116447693609324</v>
+        <v>0.00109865931443775</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0264840745678379</v>
+        <v>0.0252370067191239</v>
       </c>
       <c r="I146"/>
       <c r="J146" t="n">
@@ -6673,10 +6673,10 @@
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150" t="n">
-        <v>0.000599747962336917</v>
+        <v>0.000587270326972051</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0168557467742565</v>
+        <v>0.0165420575351505</v>
       </c>
       <c r="I150"/>
       <c r="J150" t="n">
@@ -6795,10 +6795,10 @@
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154" t="n">
-        <v>0.000733442147241684</v>
+        <v>0.000712145460208505</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0171016330092669</v>
+        <v>0.0166789955728449</v>
       </c>
       <c r="I154"/>
       <c r="J154" t="n">
@@ -6917,10 +6917,10 @@
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158" t="n">
-        <v>0.000533181627325904</v>
+        <v>0.000517399554471212</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0166465368560204</v>
+        <v>0.0162626609232933</v>
       </c>
       <c r="I158"/>
       <c r="J158" t="n">
@@ -7039,10 +7039,10 @@
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162" t="n">
-        <v>0.000540311872704341</v>
+        <v>0.000519209348078926</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0168103013403629</v>
+        <v>0.0163176273811625</v>
       </c>
       <c r="I162"/>
       <c r="J162" t="n">
@@ -7161,10 +7161,10 @@
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166" t="n">
-        <v>0.000513214768192043</v>
+        <v>0.000479404243175749</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0166982710796898</v>
+        <v>0.0160170888969772</v>
       </c>
       <c r="I166"/>
       <c r="J166" t="n">
@@ -7372,7 +7372,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00124398261464006</v>
+        <v>0.00120292832011974</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -7452,7 +7452,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00149187136667049</v>
+        <v>0.00146421175608589</v>
       </c>
       <c r="F9" t="e">
         <v>#NUM!</v>
@@ -7532,7 +7532,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00041630493248063</v>
+        <v>0.000405711895000397</v>
       </c>
       <c r="F13" t="e">
         <v>#NUM!</v>
@@ -7612,7 +7612,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000448995901255752</v>
+        <v>0.000444316907878992</v>
       </c>
       <c r="F17" t="e">
         <v>#NUM!</v>
@@ -7692,7 +7692,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000572017530403988</v>
+        <v>0.000567178973563844</v>
       </c>
       <c r="F21" t="e">
         <v>#NUM!</v>
@@ -7772,7 +7772,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00037553285998693</v>
+        <v>0.00037375012783771</v>
       </c>
       <c r="F25" t="e">
         <v>#NUM!</v>
@@ -7852,7 +7852,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000378060618497367</v>
+        <v>0.000373800091005624</v>
       </c>
       <c r="F29" t="e">
         <v>#NUM!</v>

--- a/results/chronological/consolidated/Stress_Testing.xlsx
+++ b/results/chronological/consolidated/Stress_Testing.xlsx
@@ -2201,10 +2201,10 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.000166951352009226</v>
+        <v>0.000166484270628164</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00970468066990117</v>
+        <v>0.00970310735528819</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
@@ -2224,21 +2224,15 @@
       <c r="D3" t="s">
         <v>46</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.000167390769583144</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.00974045974012153</v>
-      </c>
+      <c r="E3"/>
+      <c r="F3"/>
       <c r="G3" t="n">
-        <v>0.00016372650862773</v>
+        <v>0.000168289500776009</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00961013285454498</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-2.23803768010831</v>
-      </c>
+        <v>0.00972963582566889</v>
+      </c>
+      <c r="I3"/>
       <c r="J3" t="n">
         <v>143</v>
       </c>
@@ -2256,21 +2250,15 @@
       <c r="D4" t="s">
         <v>47</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.000167850774117696</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0097640934864094</v>
-      </c>
+      <c r="E4"/>
+      <c r="F4"/>
       <c r="G4" t="n">
-        <v>0.000166847493402141</v>
+        <v>0.000169297288284172</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00973457659125091</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.60131602525049</v>
-      </c>
+        <v>0.00976754848874467</v>
+      </c>
+      <c r="I4"/>
       <c r="J4" t="n">
         <v>143</v>
       </c>
@@ -2288,21 +2276,15 @@
       <c r="D5" t="s">
         <v>48</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.000167137451846857</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.00972844644050327</v>
-      </c>
+      <c r="E5"/>
+      <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.000170783013894062</v>
+        <v>0.000165511353111637</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0098253300770865</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.13461629706705</v>
-      </c>
+        <v>0.00967456182510069</v>
+      </c>
+      <c r="I5"/>
       <c r="J5" t="n">
         <v>143</v>
       </c>
@@ -2323,10 +2305,10 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000389439834297262</v>
+        <v>0.0000392307905735696</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00477169304922805</v>
+        <v>0.00484471095658396</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2346,21 +2328,15 @@
       <c r="D7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.0000387970650100645</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.00480853491760829</v>
-      </c>
+      <c r="E7"/>
+      <c r="F7"/>
       <c r="G7" t="n">
-        <v>0.0000378174276516739</v>
+        <v>0.0000409331927054679</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00467961022608443</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-2.59043890402536</v>
-      </c>
+        <v>0.00489005908368984</v>
+      </c>
+      <c r="I7"/>
       <c r="J7" t="n">
         <v>59</v>
       </c>
@@ -2378,21 +2354,15 @@
       <c r="D8" t="s">
         <v>47</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.0000388787292366403</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.00476880980827408</v>
-      </c>
+      <c r="E8"/>
+      <c r="F8"/>
       <c r="G8" t="n">
-        <v>0.0000392318124851237</v>
+        <v>0.0000397401120504396</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00483188635763098</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.899992190310669</v>
-      </c>
+        <v>0.00487014817836813</v>
+      </c>
+      <c r="I8"/>
       <c r="J8" t="n">
         <v>59</v>
       </c>
@@ -2410,21 +2380,15 @@
       <c r="D9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.0000383111734548554</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.00474862661305495</v>
-      </c>
+      <c r="E9"/>
+      <c r="F9"/>
       <c r="G9" t="n">
-        <v>0.0000415062588425139</v>
+        <v>0.0000438377093889929</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00499701353633637</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7.69783998066787</v>
-      </c>
+        <v>0.00506435219823743</v>
+      </c>
+      <c r="I9"/>
       <c r="J9" t="n">
         <v>59</v>
       </c>
@@ -2445,10 +2409,10 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10" t="n">
-        <v>0.0000910022935740849</v>
+        <v>0.0000910435252355826</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00367083436958826</v>
+        <v>0.00368569306814232</v>
       </c>
       <c r="I10"/>
       <c r="J10" t="n">
@@ -2468,21 +2432,15 @@
       <c r="D11" t="s">
         <v>46</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.0000911438050313301</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.00366548984427773</v>
-      </c>
+      <c r="E11"/>
+      <c r="F11"/>
       <c r="G11" t="n">
-        <v>0.0000912058248203277</v>
+        <v>0.0000914390867340853</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00368557176461186</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.0679998115469423</v>
-      </c>
+        <v>0.00371627952278092</v>
+      </c>
+      <c r="I11"/>
       <c r="J11" t="n">
         <v>1356</v>
       </c>
@@ -2500,21 +2458,15 @@
       <c r="D12" t="s">
         <v>47</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.0000907412069112315</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.00366857318202165</v>
-      </c>
+      <c r="E12"/>
+      <c r="F12"/>
       <c r="G12" t="n">
-        <v>0.0000913618269711371</v>
+        <v>0.000091416751422101</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00373114346469385</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.679299090747991</v>
-      </c>
+        <v>0.0037393464914384</v>
+      </c>
+      <c r="I12"/>
       <c r="J12" t="n">
         <v>1356</v>
       </c>
@@ -2532,21 +2484,15 @@
       <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.0000908730375540498</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.00367947127946332</v>
-      </c>
+      <c r="E13"/>
+      <c r="F13"/>
       <c r="G13" t="n">
-        <v>0.0000914215294691344</v>
+        <v>0.0000919308706440001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00374015885338721</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.599959241843324</v>
-      </c>
+        <v>0.00380818062097797</v>
+      </c>
+      <c r="I13"/>
       <c r="J13" t="n">
         <v>1356</v>
       </c>
@@ -2567,10 +2513,10 @@
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14" t="n">
-        <v>0.000211069332287431</v>
+        <v>0.000210491733674835</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00382465460406651</v>
+        <v>0.00385700157071754</v>
       </c>
       <c r="I14"/>
       <c r="J14" t="n">
@@ -2590,21 +2536,15 @@
       <c r="D15" t="s">
         <v>46</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.000210678901021354</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.00381761361143642</v>
-      </c>
+      <c r="E15"/>
+      <c r="F15"/>
       <c r="G15" t="n">
-        <v>0.000210478634131197</v>
+        <v>0.000211970528435656</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00383983704543749</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.09514832276639</v>
-      </c>
+        <v>0.00385010794736463</v>
+      </c>
+      <c r="I15"/>
       <c r="J15" t="n">
         <v>1356</v>
       </c>
@@ -2622,21 +2562,15 @@
       <c r="D16" t="s">
         <v>47</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.000210700505187153</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.00382819813454769</v>
-      </c>
+      <c r="E16"/>
+      <c r="F16"/>
       <c r="G16" t="n">
-        <v>0.000211295321399885</v>
+        <v>0.000211650722581567</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00387011538513842</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.281509410048078</v>
-      </c>
+        <v>0.00385732399535418</v>
+      </c>
+      <c r="I16"/>
       <c r="J16" t="n">
         <v>1356</v>
       </c>
@@ -2654,21 +2588,15 @@
       <c r="D17" t="s">
         <v>48</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.000210572594374674</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.00382068948337397</v>
-      </c>
+      <c r="E17"/>
+      <c r="F17"/>
       <c r="G17" t="n">
-        <v>0.000210699992424365</v>
+        <v>0.000211221276859103</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00387564847369017</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.0604641928200469</v>
-      </c>
+        <v>0.00393208422166285</v>
+      </c>
+      <c r="I17"/>
       <c r="J17" t="n">
         <v>1356</v>
       </c>
@@ -2689,10 +2617,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000225783042244154</v>
+        <v>0.0000222186552830504</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00347357615032662</v>
+        <v>0.00347492879441313</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2712,21 +2640,15 @@
       <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.0000221891593871965</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.00345737058058294</v>
-      </c>
+      <c r="E19"/>
+      <c r="F19"/>
       <c r="G19" t="n">
-        <v>0.0000222166281663315</v>
+        <v>0.0000224149052033806</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00346214461682645</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.123640630474047</v>
-      </c>
+        <v>0.003470703398814</v>
+      </c>
+      <c r="I19"/>
       <c r="J19" t="n">
         <v>1356</v>
       </c>
@@ -2744,21 +2666,15 @@
       <c r="D20" t="s">
         <v>47</v>
       </c>
-      <c r="E20" t="n">
-        <v>0.0000221051813738323</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.00344846314933526</v>
-      </c>
+      <c r="E20"/>
+      <c r="F20"/>
       <c r="G20" t="n">
-        <v>0.0000226695565639773</v>
+        <v>0.0000230475573548821</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00350589061423782</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.48957313546119</v>
-      </c>
+        <v>0.00353935463444195</v>
+      </c>
+      <c r="I20"/>
       <c r="J20" t="n">
         <v>1356</v>
       </c>
@@ -2776,21 +2692,15 @@
       <c r="D21" t="s">
         <v>48</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.0000222430861946734</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.00345561740124356</v>
-      </c>
+      <c r="E21"/>
+      <c r="F21"/>
       <c r="G21" t="n">
-        <v>0.0000228213826452332</v>
+        <v>0.0000237799490195526</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00351530195519723</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.53401145561403</v>
-      </c>
+        <v>0.00362245920045411</v>
+      </c>
+      <c r="I21"/>
       <c r="J21" t="n">
         <v>1356</v>
       </c>
@@ -2811,10 +2721,10 @@
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22" t="n">
-        <v>0.0000225218283341104</v>
+        <v>0.0000224296933499698</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00346672521481672</v>
+        <v>0.00345338181246906</v>
       </c>
       <c r="I22"/>
       <c r="J22" t="n">
@@ -2834,21 +2744,15 @@
       <c r="D23" t="s">
         <v>46</v>
       </c>
-      <c r="E23" t="n">
-        <v>0.0000223220232706449</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.00344949482479674</v>
-      </c>
+      <c r="E23"/>
+      <c r="F23"/>
       <c r="G23" t="n">
-        <v>0.0000223818901589383</v>
+        <v>0.0000226077640735609</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00346201332680005</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.267479144381026</v>
-      </c>
+        <v>0.00350072653022918</v>
+      </c>
+      <c r="I23"/>
       <c r="J23" t="n">
         <v>1356</v>
       </c>
@@ -2866,21 +2770,15 @@
       <c r="D24" t="s">
         <v>47</v>
       </c>
-      <c r="E24" t="n">
-        <v>0.000022320159558227</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.00346668144845584</v>
-      </c>
+      <c r="E24"/>
+      <c r="F24"/>
       <c r="G24" t="n">
-        <v>0.0000227555990269618</v>
+        <v>0.0000225650498261076</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00352960424438782</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.91354869726283</v>
-      </c>
+        <v>0.00349202517186894</v>
+      </c>
+      <c r="I24"/>
       <c r="J24" t="n">
         <v>1356</v>
       </c>
@@ -2898,21 +2796,15 @@
       <c r="D25" t="s">
         <v>48</v>
       </c>
-      <c r="E25" t="n">
-        <v>0.0000222957051309558</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.00345771608220651</v>
-      </c>
+      <c r="E25"/>
+      <c r="F25"/>
       <c r="G25" t="n">
-        <v>0.0000231131686764108</v>
+        <v>0.0000240961031372539</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00353415999539343</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.53678700181551</v>
-      </c>
+        <v>0.00365446957456209</v>
+      </c>
+      <c r="I25"/>
       <c r="J25" t="n">
         <v>1356</v>
       </c>
@@ -2933,10 +2825,10 @@
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26" t="n">
-        <v>0.000118162887999717</v>
+        <v>0.000118327367256644</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00996640043893173</v>
+        <v>0.00996001591083214</v>
       </c>
       <c r="I26"/>
       <c r="J26" t="n">
@@ -2956,21 +2848,15 @@
       <c r="D27" t="s">
         <v>46</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.000147204556239559</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0112782823754828</v>
-      </c>
+      <c r="E27"/>
+      <c r="F27"/>
       <c r="G27" t="n">
-        <v>0.000106670499260581</v>
+        <v>0.000107656534332223</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00937461069068446</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-37.9993130808916</v>
-      </c>
+        <v>0.00941187355406007</v>
+      </c>
+      <c r="I27"/>
       <c r="J27" t="n">
         <v>904</v>
       </c>
@@ -2988,21 +2874,15 @@
       <c r="D28" t="s">
         <v>47</v>
       </c>
-      <c r="E28" t="n">
-        <v>0.000119584764091518</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.0100387759894535</v>
-      </c>
+      <c r="E28"/>
+      <c r="F28"/>
       <c r="G28" t="n">
-        <v>0.000117027185832018</v>
+        <v>0.000116531984775962</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00991440281856469</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-2.18545651706177</v>
-      </c>
+        <v>0.00988232404996959</v>
+      </c>
+      <c r="I28"/>
       <c r="J28" t="n">
         <v>904</v>
       </c>
@@ -3020,21 +2900,15 @@
       <c r="D29" t="s">
         <v>48</v>
       </c>
-      <c r="E29" t="n">
-        <v>0.00011792721863554</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.00996631076000351</v>
-      </c>
+      <c r="E29"/>
+      <c r="F29"/>
       <c r="G29" t="n">
-        <v>0.000118793552389528</v>
+        <v>0.000121095198094957</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00995709170409208</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.729276746558553</v>
-      </c>
+        <v>0.0100491563276939</v>
+      </c>
+      <c r="I29"/>
       <c r="J29" t="n">
         <v>904</v>
       </c>
@@ -3055,10 +2929,10 @@
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30" t="n">
-        <v>0.00023832954051971</v>
+        <v>0.000236053686397006</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0116870267057331</v>
+        <v>0.0115928485674324</v>
       </c>
       <c r="I30"/>
       <c r="J30" t="n">
@@ -3078,21 +2952,15 @@
       <c r="D31" t="s">
         <v>46</v>
       </c>
-      <c r="E31" t="n">
-        <v>0.000238191325640674</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0116669377619493</v>
-      </c>
+      <c r="E31"/>
+      <c r="F31"/>
       <c r="G31" t="n">
-        <v>0.000238477232100878</v>
+        <v>0.000239482805165124</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0117100594735287</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.119888367407202</v>
-      </c>
+        <v>0.0117605962562826</v>
+      </c>
+      <c r="I31"/>
       <c r="J31" t="n">
         <v>143</v>
       </c>
@@ -3110,21 +2978,15 @@
       <c r="D32" t="s">
         <v>47</v>
       </c>
-      <c r="E32" t="n">
-        <v>0.000239498244305225</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.0117331851034052</v>
-      </c>
+      <c r="E32"/>
+      <c r="F32"/>
       <c r="G32" t="n">
-        <v>0.000236848469434413</v>
+        <v>0.000237488920794175</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0116740063207011</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-1.11876377210286</v>
-      </c>
+        <v>0.0116789752103996</v>
+      </c>
+      <c r="I32"/>
       <c r="J32" t="n">
         <v>143</v>
       </c>
@@ -3142,21 +3004,15 @@
       <c r="D33" t="s">
         <v>48</v>
       </c>
-      <c r="E33" t="n">
-        <v>0.000237297279806234</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.0116384046798125</v>
-      </c>
+      <c r="E33"/>
+      <c r="F33"/>
       <c r="G33" t="n">
-        <v>0.000237829636887</v>
+        <v>0.00023883205285248</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0116404453902345</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.223839672689488</v>
-      </c>
+        <v>0.0116754397530211</v>
+      </c>
+      <c r="I33"/>
       <c r="J33" t="n">
         <v>143</v>
       </c>
@@ -3177,10 +3033,10 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.0000976968062414234</v>
+        <v>0.0000973661859329106</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00734187982457743</v>
+        <v>0.00739296675780731</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
@@ -3200,21 +3056,15 @@
       <c r="D35" t="s">
         <v>46</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.0000968840321836063</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.00738820035024361</v>
-      </c>
+      <c r="E35"/>
+      <c r="F35"/>
       <c r="G35" t="n">
-        <v>0.0000960030801995614</v>
+        <v>0.0000953822627784744</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00734600686134965</v>
-      </c>
-      <c r="I35" t="n">
-        <v>-0.917628874212873</v>
-      </c>
+        <v>0.0073744492549293</v>
+      </c>
+      <c r="I35"/>
       <c r="J35" t="n">
         <v>59</v>
       </c>
@@ -3232,21 +3082,15 @@
       <c r="D36" t="s">
         <v>47</v>
       </c>
-      <c r="E36" t="n">
-        <v>0.0000972761676027537</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.00741070991236692</v>
-      </c>
+      <c r="E36"/>
+      <c r="F36"/>
       <c r="G36" t="n">
-        <v>0.0000969058390597625</v>
+        <v>0.0000946116483417459</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00739420630223323</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-0.382152970950334</v>
-      </c>
+        <v>0.00724964722353417</v>
+      </c>
+      <c r="I36"/>
       <c r="J36" t="n">
         <v>59</v>
       </c>
@@ -3264,21 +3108,15 @@
       <c r="D37" t="s">
         <v>48</v>
       </c>
-      <c r="E37" t="n">
-        <v>0.0000969714682154979</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.00739887187023373</v>
-      </c>
+      <c r="E37"/>
+      <c r="F37"/>
       <c r="G37" t="n">
-        <v>0.000100299649098669</v>
+        <v>0.000096209422431322</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0075342177947084</v>
-      </c>
-      <c r="I37" t="n">
-        <v>3.31823781347146</v>
-      </c>
+        <v>0.00758701501489448</v>
+      </c>
+      <c r="I37"/>
       <c r="J37" t="n">
         <v>59</v>
       </c>
@@ -3299,10 +3137,10 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38" t="n">
-        <v>0.000103727608124984</v>
+        <v>0.000104035175877921</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00455564789974985</v>
+        <v>0.00459165630850136</v>
       </c>
       <c r="I38"/>
       <c r="J38" t="n">
@@ -3322,21 +3160,15 @@
       <c r="D39" t="s">
         <v>46</v>
       </c>
-      <c r="E39" t="n">
-        <v>0.000103680993400411</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.0045710177165076</v>
-      </c>
+      <c r="E39"/>
+      <c r="F39"/>
       <c r="G39" t="n">
-        <v>0.000103531840220819</v>
+        <v>0.000104059215140179</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00458451275752314</v>
-      </c>
-      <c r="I39" t="n">
-        <v>-0.144065032819417</v>
-      </c>
+        <v>0.00461739816141817</v>
+      </c>
+      <c r="I39"/>
       <c r="J39" t="n">
         <v>1356</v>
       </c>
@@ -3354,21 +3186,15 @@
       <c r="D40" t="s">
         <v>47</v>
       </c>
-      <c r="E40" t="n">
-        <v>0.000103536518424468</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.00455690367897501</v>
-      </c>
+      <c r="E40"/>
+      <c r="F40"/>
       <c r="G40" t="n">
-        <v>0.000104160985220688</v>
+        <v>0.000104150338931593</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0046220091431613</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.599520823364534</v>
-      </c>
+        <v>0.00461835867010007</v>
+      </c>
+      <c r="I40"/>
       <c r="J40" t="n">
         <v>1356</v>
       </c>
@@ -3386,21 +3212,15 @@
       <c r="D41" t="s">
         <v>48</v>
       </c>
-      <c r="E41" t="n">
-        <v>0.00010361737980067</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.00454986113295566</v>
-      </c>
+      <c r="E41"/>
+      <c r="F41"/>
       <c r="G41" t="n">
-        <v>0.000103674298990429</v>
+        <v>0.000105323406256092</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00460886685209101</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.0549019287453466</v>
-      </c>
+        <v>0.00468709361530862</v>
+      </c>
+      <c r="I41"/>
       <c r="J41" t="n">
         <v>1356</v>
       </c>
@@ -3421,10 +3241,10 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42" t="n">
-        <v>0.000222375374752585</v>
+        <v>0.000223696012654615</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00470330026920116</v>
+        <v>0.00477056655491325</v>
       </c>
       <c r="I42"/>
       <c r="J42" t="n">
@@ -3444,21 +3264,15 @@
       <c r="D43" t="s">
         <v>46</v>
       </c>
-      <c r="E43" t="n">
-        <v>0.000222908271412988</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.00471136680376117</v>
-      </c>
+      <c r="E43"/>
+      <c r="F43"/>
       <c r="G43" t="n">
-        <v>0.000222148253539582</v>
+        <v>0.000223115439459715</v>
       </c>
       <c r="H43" t="n">
-        <v>0.00469744398732774</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-0.342121921417959</v>
-      </c>
+        <v>0.00473645769321433</v>
+      </c>
+      <c r="I43"/>
       <c r="J43" t="n">
         <v>1356</v>
       </c>
@@ -3476,21 +3290,15 @@
       <c r="D44" t="s">
         <v>47</v>
       </c>
-      <c r="E44" t="n">
-        <v>0.00022299486383428</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.00470368105570547</v>
-      </c>
+      <c r="E44"/>
+      <c r="F44"/>
       <c r="G44" t="n">
-        <v>0.000223088525672698</v>
+        <v>0.000223794522495776</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00473424162894216</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.0419841576952139</v>
-      </c>
+        <v>0.00477468499764365</v>
+      </c>
+      <c r="I44"/>
       <c r="J44" t="n">
         <v>1356</v>
       </c>
@@ -3508,21 +3316,15 @@
       <c r="D45" t="s">
         <v>48</v>
       </c>
-      <c r="E45" t="n">
-        <v>0.00022281837487585</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.00469875582190401</v>
-      </c>
+      <c r="E45"/>
+      <c r="F45"/>
       <c r="G45" t="n">
-        <v>0.000223248196899965</v>
+        <v>0.000224529084627498</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00474699281270626</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.192531017084864</v>
-      </c>
+        <v>0.00485204551059975</v>
+      </c>
+      <c r="I45"/>
       <c r="J45" t="n">
         <v>1356</v>
       </c>
@@ -3543,10 +3345,10 @@
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46" t="n">
-        <v>0.0000354501843301481</v>
+        <v>0.0000354283376961201</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00434374097915329</v>
+        <v>0.00435277066986542</v>
       </c>
       <c r="I46"/>
       <c r="J46" t="n">
@@ -3566,21 +3368,15 @@
       <c r="D47" t="s">
         <v>46</v>
       </c>
-      <c r="E47" t="n">
-        <v>0.0000353971748680677</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.00434239219078202</v>
-      </c>
+      <c r="E47"/>
+      <c r="F47"/>
       <c r="G47" t="n">
-        <v>0.0000353944635728929</v>
+        <v>0.000035855592008376</v>
       </c>
       <c r="H47" t="n">
-        <v>0.00435278527628025</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-0.00766022394775305</v>
-      </c>
+        <v>0.00437161739664475</v>
+      </c>
+      <c r="I47"/>
       <c r="J47" t="n">
         <v>1356</v>
       </c>
@@ -3598,21 +3394,15 @@
       <c r="D48" t="s">
         <v>47</v>
       </c>
-      <c r="E48" t="n">
-        <v>0.0000352252546988029</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.00433420586697496</v>
-      </c>
+      <c r="E48"/>
+      <c r="F48"/>
       <c r="G48" t="n">
-        <v>0.0000357883408157283</v>
+        <v>0.0000358221383369487</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00436793725689673</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1.57337865933677</v>
-      </c>
+        <v>0.00440021464323623</v>
+      </c>
+      <c r="I48"/>
       <c r="J48" t="n">
         <v>1356</v>
       </c>
@@ -3630,21 +3420,15 @@
       <c r="D49" t="s">
         <v>48</v>
       </c>
-      <c r="E49" t="n">
-        <v>0.0000353221063200369</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.00433316953740108</v>
-      </c>
+      <c r="E49"/>
+      <c r="F49"/>
       <c r="G49" t="n">
-        <v>0.0000359543638833064</v>
+        <v>0.0000360277606482271</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00438121507681389</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1.75850020687772</v>
-      </c>
+        <v>0.0043906115980566</v>
+      </c>
+      <c r="I49"/>
       <c r="J49" t="n">
         <v>1356</v>
       </c>
@@ -3665,10 +3449,10 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.0000355776895936481</v>
+        <v>0.0000357596782510935</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00433599898517031</v>
+        <v>0.00438446955624749</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
@@ -3688,21 +3472,15 @@
       <c r="D51" t="s">
         <v>46</v>
       </c>
-      <c r="E51" t="n">
-        <v>0.0000354097202656811</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.00433825615711742</v>
-      </c>
+      <c r="E51"/>
+      <c r="F51"/>
       <c r="G51" t="n">
-        <v>0.0000352522765945581</v>
+        <v>0.0000356419678473142</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00433127981133599</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-0.4466198677996</v>
-      </c>
+        <v>0.00438206760429898</v>
+      </c>
+      <c r="I51"/>
       <c r="J51" t="n">
         <v>1356</v>
       </c>
@@ -3720,21 +3498,15 @@
       <c r="D52" t="s">
         <v>47</v>
       </c>
-      <c r="E52" t="n">
-        <v>0.0000353585136956152</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.00434265007823211</v>
-      </c>
+      <c r="E52"/>
+      <c r="F52"/>
       <c r="G52" t="n">
-        <v>0.00003585892882906</v>
+        <v>0.0000361112784607043</v>
       </c>
       <c r="H52" t="n">
-        <v>0.00436782600333632</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1.39551054586782</v>
-      </c>
+        <v>0.00441034534937561</v>
+      </c>
+      <c r="I52"/>
       <c r="J52" t="n">
         <v>1356</v>
       </c>
@@ -3752,21 +3524,15 @@
       <c r="D53" t="s">
         <v>48</v>
       </c>
-      <c r="E53" t="n">
-        <v>0.0000354378727125389</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.00435033738714455</v>
-      </c>
+      <c r="E53"/>
+      <c r="F53"/>
       <c r="G53" t="n">
-        <v>0.0000361587874056296</v>
+        <v>0.0000361663837673313</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00438186484996242</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1.99374687265773</v>
-      </c>
+        <v>0.00444787764257511</v>
+      </c>
+      <c r="I53"/>
       <c r="J53" t="n">
         <v>1356</v>
       </c>
@@ -3787,10 +3553,10 @@
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54" t="n">
-        <v>0.000130659464947865</v>
+        <v>0.000131375628428823</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0101081778445376</v>
+        <v>0.0101394925373157</v>
       </c>
       <c r="I54"/>
       <c r="J54" t="n">
@@ -3810,21 +3576,15 @@
       <c r="D55" t="s">
         <v>46</v>
       </c>
-      <c r="E55" t="n">
-        <v>0.000154725243034373</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.0111895378356009</v>
-      </c>
+      <c r="E55"/>
+      <c r="F55"/>
       <c r="G55" t="n">
-        <v>0.000120818238968247</v>
+        <v>0.00012161121910038</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00963902875001785</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-28.0644746651516</v>
-      </c>
+        <v>0.00968806939379764</v>
+      </c>
+      <c r="I55"/>
       <c r="J55" t="n">
         <v>904</v>
       </c>
@@ -3842,21 +3602,15 @@
       <c r="D56" t="s">
         <v>47</v>
       </c>
-      <c r="E56" t="n">
-        <v>0.000133341318669117</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.0102436055767891</v>
-      </c>
+      <c r="E56"/>
+      <c r="F56"/>
       <c r="G56" t="n">
-        <v>0.000130356337988292</v>
+        <v>0.000129795491402692</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0100959133463467</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-2.28986233188992</v>
-      </c>
+        <v>0.0100539551347552</v>
+      </c>
+      <c r="I56"/>
       <c r="J56" t="n">
         <v>904</v>
       </c>
@@ -3874,21 +3628,15 @@
       <c r="D57" t="s">
         <v>48</v>
       </c>
-      <c r="E57" t="n">
-        <v>0.00013353712390326</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.0102543735711536</v>
-      </c>
+      <c r="E57"/>
+      <c r="F57"/>
       <c r="G57" t="n">
-        <v>0.000130605044765472</v>
+        <v>0.000130804416937181</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0101169377002651</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-2.24499684759748</v>
-      </c>
+        <v>0.0101352145029411</v>
+      </c>
+      <c r="I57"/>
       <c r="J57" t="n">
         <v>904</v>
       </c>
@@ -3909,10 +3657,10 @@
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000514077013255524</v>
+        <v>0.000513891265253846</v>
       </c>
       <c r="H58" t="n">
-        <v>0.016413932506955</v>
+        <v>0.0164214537432564</v>
       </c>
       <c r="I58"/>
       <c r="J58" t="n">
@@ -3932,21 +3680,15 @@
       <c r="D59" t="s">
         <v>46</v>
       </c>
-      <c r="E59" t="n">
-        <v>0.000516025348960836</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.0164057668533221</v>
-      </c>
+      <c r="E59"/>
+      <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.000513604511694003</v>
+        <v>0.000515809009061069</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0164301601039204</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-0.471342679379501</v>
-      </c>
+        <v>0.0162868276640632</v>
+      </c>
+      <c r="I59"/>
       <c r="J59" t="n">
         <v>143</v>
       </c>
@@ -3964,21 +3706,15 @@
       <c r="D60" t="s">
         <v>47</v>
       </c>
-      <c r="E60" t="n">
-        <v>0.000517635924727256</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.0164538747346341</v>
-      </c>
+      <c r="E60"/>
+      <c r="F60"/>
       <c r="G60" t="n">
-        <v>0.000513100205737699</v>
+        <v>0.000508471873658877</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0163980589166189</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-0.883983077542493</v>
-      </c>
+        <v>0.0163825927656844</v>
+      </c>
+      <c r="I60"/>
       <c r="J60" t="n">
         <v>143</v>
       </c>
@@ -3996,21 +3732,15 @@
       <c r="D61" t="s">
         <v>48</v>
       </c>
-      <c r="E61" t="n">
-        <v>0.000512738875788594</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.0164255410635976</v>
-      </c>
+      <c r="E61"/>
+      <c r="F61"/>
       <c r="G61" t="n">
-        <v>0.000510589300252105</v>
+        <v>0.00052116771067046</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0163944134853723</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-0.420998938956898</v>
-      </c>
+        <v>0.016526944273177</v>
+      </c>
+      <c r="I61"/>
       <c r="J61" t="n">
         <v>143</v>
       </c>
@@ -4031,10 +3761,10 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.000255628278480086</v>
+        <v>0.000258671141797781</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0120463189912403</v>
+        <v>0.0121066593043908</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -4054,21 +3784,15 @@
       <c r="D63" t="s">
         <v>46</v>
       </c>
-      <c r="E63" t="n">
-        <v>0.00025898280141391</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.0120157800871535</v>
-      </c>
+      <c r="E63"/>
+      <c r="F63"/>
       <c r="G63" t="n">
-        <v>0.00025326068627261</v>
+        <v>0.00025928217246475</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0120363378621733</v>
-      </c>
-      <c r="I63" t="n">
-        <v>-2.25937757080082</v>
-      </c>
+        <v>0.012140228329092</v>
+      </c>
+      <c r="I63"/>
       <c r="J63" t="n">
         <v>59</v>
       </c>
@@ -4086,21 +3810,15 @@
       <c r="D64" t="s">
         <v>47</v>
       </c>
-      <c r="E64" t="n">
-        <v>0.00025742929216685</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.0120442691808859</v>
-      </c>
+      <c r="E64"/>
+      <c r="F64"/>
       <c r="G64" t="n">
-        <v>0.000255761518076394</v>
+        <v>0.000259673880381271</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0119909485230251</v>
-      </c>
-      <c r="I64" t="n">
-        <v>-0.652081713855661</v>
-      </c>
+        <v>0.0121059145240385</v>
+      </c>
+      <c r="I64"/>
       <c r="J64" t="n">
         <v>59</v>
       </c>
@@ -4118,21 +3836,15 @@
       <c r="D65" t="s">
         <v>48</v>
       </c>
-      <c r="E65" t="n">
-        <v>0.00025833660557955</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.0120578372413049</v>
-      </c>
+      <c r="E65"/>
+      <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000256551627309593</v>
+        <v>0.000257628291703162</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0119712794957244</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-0.695757921583275</v>
-      </c>
+        <v>0.012131012247036</v>
+      </c>
+      <c r="I65"/>
       <c r="J65" t="n">
         <v>59</v>
       </c>
@@ -4153,10 +3865,10 @@
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.000163941763014223</v>
+        <v>0.000164031822677654</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00778046952207918</v>
+        <v>0.00776603538648519</v>
       </c>
       <c r="I66"/>
       <c r="J66" t="n">
@@ -4176,21 +3888,15 @@
       <c r="D67" t="s">
         <v>46</v>
       </c>
-      <c r="E67" t="n">
-        <v>0.000168632370621721</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.00794048453287123</v>
-      </c>
+      <c r="E67"/>
+      <c r="F67"/>
       <c r="G67" t="n">
-        <v>1606.07772349607</v>
+        <v>3641.268396681</v>
       </c>
       <c r="H67" t="n">
-        <v>12.5251882107183</v>
-      </c>
-      <c r="I67" t="n">
-        <v>99.9999895003605</v>
-      </c>
+        <v>13.4428494697121</v>
+      </c>
+      <c r="I67"/>
       <c r="J67" t="n">
         <v>1356</v>
       </c>
@@ -4208,21 +3914,15 @@
       <c r="D68" t="s">
         <v>47</v>
       </c>
-      <c r="E68" t="n">
-        <v>0.000162785932689634</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.00771187099999145</v>
-      </c>
+      <c r="E68"/>
+      <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.000162066477685287</v>
+        <v>0.000163331312256752</v>
       </c>
       <c r="H68" t="n">
-        <v>0.00774757434318174</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-0.443925859698309</v>
-      </c>
+        <v>0.00775969348478108</v>
+      </c>
+      <c r="I68"/>
       <c r="J68" t="n">
         <v>1356</v>
       </c>
@@ -4240,21 +3940,15 @@
       <c r="D69" t="s">
         <v>48</v>
       </c>
-      <c r="E69" t="n">
-        <v>0.000162043713034707</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.00770566903897201</v>
-      </c>
+      <c r="E69"/>
+      <c r="F69"/>
       <c r="G69" t="n">
-        <v>0.000164734717010711</v>
+        <v>0.000167324634048557</v>
       </c>
       <c r="H69" t="n">
-        <v>0.00785961488916734</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1.63353786307737</v>
-      </c>
+        <v>0.00789985210528485</v>
+      </c>
+      <c r="I69"/>
       <c r="J69" t="n">
         <v>1356</v>
       </c>
@@ -4275,10 +3969,10 @@
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.000282133888118239</v>
+        <v>0.000283351406973571</v>
       </c>
       <c r="H70" t="n">
-        <v>0.00787918931130336</v>
+        <v>0.00790124899403807</v>
       </c>
       <c r="I70"/>
       <c r="J70" t="n">
@@ -4298,21 +3992,15 @@
       <c r="D71" t="s">
         <v>46</v>
       </c>
-      <c r="E71" t="n">
-        <v>0.00028734448295794</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0.00808775990715803</v>
-      </c>
+      <c r="E71"/>
+      <c r="F71"/>
       <c r="G71" t="n">
-        <v>1784.31569451374</v>
+        <v>3916.75918161957</v>
       </c>
       <c r="H71" t="n">
-        <v>13.3680483107481</v>
-      </c>
-      <c r="I71" t="n">
-        <v>99.9999838960962</v>
-      </c>
+        <v>14.5828947605775</v>
+      </c>
+      <c r="I71"/>
       <c r="J71" t="n">
         <v>1356</v>
       </c>
@@ -4330,21 +4018,15 @@
       <c r="D72" t="s">
         <v>47</v>
       </c>
-      <c r="E72" t="n">
-        <v>0.000282030585080843</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.00786050475239171</v>
-      </c>
+      <c r="E72"/>
+      <c r="F72"/>
       <c r="G72" t="n">
-        <v>0.000282938874566499</v>
+        <v>0.000283374509906629</v>
       </c>
       <c r="H72" t="n">
-        <v>0.00791072778257996</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.321019685629283</v>
-      </c>
+        <v>0.00791259266787795</v>
+      </c>
+      <c r="I72"/>
       <c r="J72" t="n">
         <v>1356</v>
       </c>
@@ -4362,21 +4044,15 @@
       <c r="D73" t="s">
         <v>48</v>
       </c>
-      <c r="E73" t="n">
-        <v>0.000281720781021467</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.00786382465019119</v>
-      </c>
+      <c r="E73"/>
+      <c r="F73"/>
       <c r="G73" t="n">
-        <v>0.00028385443137022</v>
+        <v>0.000281963316312913</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00792797046037918</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.751670614565956</v>
-      </c>
+        <v>0.00793625174710484</v>
+      </c>
+      <c r="I73"/>
       <c r="J73" t="n">
         <v>1356</v>
       </c>
@@ -4397,10 +4073,10 @@
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.0000945377175719618</v>
+        <v>0.000095454274157071</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00753901453921994</v>
+        <v>0.00760074612715361</v>
       </c>
       <c r="I74"/>
       <c r="J74" t="n">
@@ -4420,21 +4096,15 @@
       <c r="D75" t="s">
         <v>46</v>
       </c>
-      <c r="E75" t="n">
-        <v>0.000101212777507098</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.00772256896917212</v>
-      </c>
+      <c r="E75"/>
+      <c r="F75"/>
       <c r="G75" t="n">
-        <v>1893.22553371356</v>
+        <v>3927.23878656565</v>
       </c>
       <c r="H75" t="n">
-        <v>13.6943596668656</v>
-      </c>
-      <c r="I75" t="n">
-        <v>99.9999946539503</v>
-      </c>
+        <v>14.7310198020601</v>
+      </c>
+      <c r="I75"/>
       <c r="J75" t="n">
         <v>1356</v>
       </c>
@@ -4452,21 +4122,15 @@
       <c r="D76" t="s">
         <v>47</v>
       </c>
-      <c r="E76" t="n">
-        <v>0.0000944000428344622</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.00753228035996503</v>
-      </c>
+      <c r="E76"/>
+      <c r="F76"/>
       <c r="G76" t="n">
-        <v>0.0000950145981632541</v>
+        <v>0.0000943820890119737</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0075397181759165</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.646800955507888</v>
-      </c>
+        <v>0.00754786430188658</v>
+      </c>
+      <c r="I76"/>
       <c r="J76" t="n">
         <v>1356</v>
       </c>
@@ -4484,21 +4148,15 @@
       <c r="D77" t="s">
         <v>48</v>
       </c>
-      <c r="E77" t="n">
-        <v>0.0000938908490588591</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.00750244594215055</v>
-      </c>
+      <c r="E77"/>
+      <c r="F77"/>
       <c r="G77" t="n">
-        <v>0.0000951410240036972</v>
+        <v>0.0000967882000933601</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00757812484437359</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1.31402300735113</v>
-      </c>
+        <v>0.00767199540863344</v>
+      </c>
+      <c r="I77"/>
       <c r="J77" t="n">
         <v>1356</v>
       </c>
@@ -4519,10 +4177,10 @@
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.0000941458902904498</v>
+        <v>0.0000947024962371123</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00751890765003684</v>
+        <v>0.00752717159420323</v>
       </c>
       <c r="I78"/>
       <c r="J78" t="n">
@@ -4542,21 +4200,15 @@
       <c r="D79" t="s">
         <v>46</v>
       </c>
-      <c r="E79" t="n">
-        <v>0.000101285365743898</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.00772643559911495</v>
-      </c>
+      <c r="E79"/>
+      <c r="F79"/>
       <c r="G79" t="n">
-        <v>1792.80816800499</v>
+        <v>2966.40274876976</v>
       </c>
       <c r="H79" t="n">
-        <v>12.6341673432909</v>
-      </c>
-      <c r="I79" t="n">
-        <v>99.9999943504627</v>
-      </c>
+        <v>11.7779169965903</v>
+      </c>
+      <c r="I79"/>
       <c r="J79" t="n">
         <v>1356</v>
       </c>
@@ -4574,21 +4226,15 @@
       <c r="D80" t="s">
         <v>47</v>
       </c>
-      <c r="E80" t="n">
-        <v>0.0000939478611045351</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.00750435767309101</v>
-      </c>
+      <c r="E80"/>
+      <c r="F80"/>
       <c r="G80" t="n">
-        <v>0.0000943880570403498</v>
+        <v>0.0000947667085053843</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00752401112050828</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.466368256342583</v>
-      </c>
+        <v>0.00753321373753232</v>
+      </c>
+      <c r="I80"/>
       <c r="J80" t="n">
         <v>1356</v>
       </c>
@@ -4606,21 +4252,15 @@
       <c r="D81" t="s">
         <v>48</v>
       </c>
-      <c r="E81" t="n">
-        <v>0.0000938302713916549</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.00749133546172005</v>
-      </c>
+      <c r="E81"/>
+      <c r="F81"/>
       <c r="G81" t="n">
-        <v>0.0000952479785922654</v>
+        <v>0.0000968952330080658</v>
       </c>
       <c r="H81" t="n">
-        <v>0.00759305381098087</v>
-      </c>
-      <c r="I81" t="n">
-        <v>1.48843809765177</v>
-      </c>
+        <v>0.00765938366312265</v>
+      </c>
+      <c r="I81"/>
       <c r="J81" t="n">
         <v>1356</v>
       </c>
@@ -4641,10 +4281,10 @@
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.000215692929484584</v>
+        <v>0.000215213144063283</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0122567740825998</v>
+        <v>0.0122635543626808</v>
       </c>
       <c r="I82"/>
       <c r="J82" t="n">
@@ -4664,21 +4304,15 @@
       <c r="D83" t="s">
         <v>46</v>
       </c>
-      <c r="E83" t="n">
-        <v>0.000207252758704122</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.0119352179681168</v>
-      </c>
+      <c r="E83"/>
+      <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.000214277606989952</v>
+        <v>0.000215776919114253</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0121820482464378</v>
-      </c>
-      <c r="I83" t="n">
-        <v>3.27838656801834</v>
-      </c>
+        <v>0.0122625349663978</v>
+      </c>
+      <c r="I83"/>
       <c r="J83" t="n">
         <v>904</v>
       </c>
@@ -4696,21 +4330,15 @@
       <c r="D84" t="s">
         <v>47</v>
       </c>
-      <c r="E84" t="n">
-        <v>0.000209881181466135</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.0120475983421917</v>
-      </c>
+      <c r="E84"/>
+      <c r="F84"/>
       <c r="G84" t="n">
-        <v>0.000214126473871428</v>
+        <v>0.000215189343434735</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0121910054273889</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1.98260977661366</v>
-      </c>
+        <v>0.0121732367471544</v>
+      </c>
+      <c r="I84"/>
       <c r="J84" t="n">
         <v>904</v>
       </c>
@@ -4728,21 +4356,15 @@
       <c r="D85" t="s">
         <v>48</v>
       </c>
-      <c r="E85" t="n">
-        <v>0.000211300731242513</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.0120787786232535</v>
-      </c>
+      <c r="E85"/>
+      <c r="F85"/>
       <c r="G85" t="n">
-        <v>0.00021958209006681</v>
+        <v>0.000222816099380324</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0123827539471938</v>
-      </c>
-      <c r="I85" t="n">
-        <v>3.77141816155308</v>
-      </c>
+        <v>0.0124931074264007</v>
+      </c>
+      <c r="I85"/>
       <c r="J85" t="n">
         <v>904</v>
       </c>
@@ -4763,10 +4385,10 @@
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.00358565786388399</v>
+        <v>0.00355333880973882</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0493874740165199</v>
+        <v>0.0490502654152361</v>
       </c>
       <c r="I86"/>
       <c r="J86" t="n">
@@ -4786,21 +4408,15 @@
       <c r="D87" t="s">
         <v>46</v>
       </c>
-      <c r="E87" t="n">
-        <v>0.00359877018624284</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.049400760864911</v>
-      </c>
+      <c r="E87"/>
+      <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.00359638190728069</v>
+        <v>0.0036326256891661</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0494185626785117</v>
-      </c>
-      <c r="I87" t="n">
-        <v>-0.0664078238552078</v>
-      </c>
+        <v>0.0498238256356843</v>
+      </c>
+      <c r="I87"/>
       <c r="J87" t="n">
         <v>143</v>
       </c>
@@ -4818,21 +4434,15 @@
       <c r="D88" t="s">
         <v>47</v>
       </c>
-      <c r="E88" t="n">
-        <v>0.00356809488401079</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.0492785940261417</v>
-      </c>
+      <c r="E88"/>
+      <c r="F88"/>
       <c r="G88" t="n">
-        <v>0.00358749160132498</v>
+        <v>0.00359856325615095</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0494035345381209</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0.54067631285967</v>
-      </c>
+        <v>0.048998618294352</v>
+      </c>
+      <c r="I88"/>
       <c r="J88" t="n">
         <v>143</v>
       </c>
@@ -4850,21 +4460,15 @@
       <c r="D89" t="s">
         <v>48</v>
       </c>
-      <c r="E89" t="n">
-        <v>0.00354681580225372</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.0491321965268284</v>
-      </c>
+      <c r="E89"/>
+      <c r="F89"/>
       <c r="G89" t="n">
-        <v>0.00360369875039564</v>
+        <v>0.00357147069230454</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0495188121412551</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1.57846013448468</v>
-      </c>
+        <v>0.0495086761623069</v>
+      </c>
+      <c r="I89"/>
       <c r="J89" t="n">
         <v>143</v>
       </c>
@@ -4885,10 +4489,10 @@
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00349386299399352</v>
+        <v>0.00351002813413657</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0459747385242672</v>
+        <v>0.0457862725121527</v>
       </c>
       <c r="I90"/>
       <c r="J90" t="n">
@@ -4908,21 +4512,15 @@
       <c r="D91" t="s">
         <v>46</v>
       </c>
-      <c r="E91" t="n">
-        <v>0.00347976402188034</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.0455231176018629</v>
-      </c>
+      <c r="E91"/>
+      <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.0034847403871761</v>
+        <v>0.00350206977748975</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0457987302637745</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0.142804477316954</v>
-      </c>
+        <v>0.0456053441023868</v>
+      </c>
+      <c r="I91"/>
       <c r="J91" t="n">
         <v>59</v>
       </c>
@@ -4940,21 +4538,15 @@
       <c r="D92" t="s">
         <v>47</v>
       </c>
-      <c r="E92" t="n">
-        <v>0.00347789416951809</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.0454952200681589</v>
-      </c>
+      <c r="E92"/>
+      <c r="F92"/>
       <c r="G92" t="n">
-        <v>0.00348560216955811</v>
+        <v>0.00344622358389272</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0457454428487404</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0.221138261484305</v>
-      </c>
+        <v>0.0449376122465321</v>
+      </c>
+      <c r="I92"/>
       <c r="J92" t="n">
         <v>59</v>
       </c>
@@ -4972,21 +4564,15 @@
       <c r="D93" t="s">
         <v>48</v>
       </c>
-      <c r="E93" t="n">
-        <v>0.00346500087238016</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.0454134587017214</v>
-      </c>
+      <c r="E93"/>
+      <c r="F93"/>
       <c r="G93" t="n">
-        <v>0.0034862189222032</v>
+        <v>0.00353214647848182</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0453399347875267</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.608626431573235</v>
-      </c>
+        <v>0.0454523882347959</v>
+      </c>
+      <c r="I93"/>
       <c r="J93" t="n">
         <v>59</v>
       </c>
@@ -5007,10 +4593,10 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.0012781130895058</v>
+        <v>0.001268876203963</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0254647142158253</v>
+        <v>0.0254921997525729</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -5030,21 +4616,15 @@
       <c r="D95" t="s">
         <v>46</v>
       </c>
-      <c r="E95" t="n">
-        <v>0.00126824238880099</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.0253323572808158</v>
-      </c>
+      <c r="E95"/>
+      <c r="F95"/>
       <c r="G95" t="n">
-        <v>0.0012714645170265</v>
+        <v>0.00128674883540449</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0253941466388331</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0.253418650883599</v>
-      </c>
+        <v>0.0256251225406456</v>
+      </c>
+      <c r="I95"/>
       <c r="J95" t="n">
         <v>1356</v>
       </c>
@@ -5062,21 +4642,15 @@
       <c r="D96" t="s">
         <v>47</v>
       </c>
-      <c r="E96" t="n">
-        <v>0.00126858722756147</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.0253735347377748</v>
-      </c>
+      <c r="E96"/>
+      <c r="F96"/>
       <c r="G96" t="n">
-        <v>0.00127195335724615</v>
+        <v>0.00127848349183079</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0254486085569248</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0.264642540978639</v>
-      </c>
+        <v>0.0254672602398019</v>
+      </c>
+      <c r="I96"/>
       <c r="J96" t="n">
         <v>1356</v>
       </c>
@@ -5094,21 +4668,15 @@
       <c r="D97" t="s">
         <v>48</v>
       </c>
-      <c r="E97" t="n">
-        <v>0.00127206474590307</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0.0253870455119289</v>
-      </c>
+      <c r="E97"/>
+      <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00127646735485478</v>
+        <v>0.00127627829485169</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0254947938057283</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0.344905722419878</v>
-      </c>
+        <v>0.0255048263898938</v>
+      </c>
+      <c r="I97"/>
       <c r="J97" t="n">
         <v>1356</v>
       </c>
@@ -5129,10 +4697,10 @@
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00141992526724589</v>
+        <v>0.00142343424309353</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0256755420060456</v>
+        <v>0.0260283153464511</v>
       </c>
       <c r="I98"/>
       <c r="J98" t="n">
@@ -5152,21 +4720,15 @@
       <c r="D99" t="s">
         <v>46</v>
       </c>
-      <c r="E99" t="n">
-        <v>0.00139588955623743</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0.0254449636524747</v>
-      </c>
+      <c r="E99"/>
+      <c r="F99"/>
       <c r="G99" t="n">
-        <v>0.0014046815217409</v>
+        <v>0.00140183713206107</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0255324360702824</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0.625904546147141</v>
-      </c>
+        <v>0.0255803532216804</v>
+      </c>
+      <c r="I99"/>
       <c r="J99" t="n">
         <v>1356</v>
       </c>
@@ -5184,21 +4746,15 @@
       <c r="D100" t="s">
         <v>47</v>
       </c>
-      <c r="E100" t="n">
-        <v>0.001399013692437</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.0255301578255073</v>
-      </c>
+      <c r="E100"/>
+      <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.00140710106616449</v>
+        <v>0.00140800188381269</v>
       </c>
       <c r="H100" t="n">
-        <v>0.025629530201547</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0.574754288939357</v>
-      </c>
+        <v>0.0256471092403121</v>
+      </c>
+      <c r="I100"/>
       <c r="J100" t="n">
         <v>1356</v>
       </c>
@@ -5216,21 +4772,15 @@
       <c r="D101" t="s">
         <v>48</v>
       </c>
-      <c r="E101" t="n">
-        <v>0.00140201625958041</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.025535899271791</v>
-      </c>
+      <c r="E101"/>
+      <c r="F101"/>
       <c r="G101" t="n">
-        <v>0.00140603418103231</v>
+        <v>0.00140396794078537</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0255487790348562</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0.285762715167538</v>
-      </c>
+        <v>0.0254890404413901</v>
+      </c>
+      <c r="I101"/>
       <c r="J101" t="n">
         <v>1356</v>
       </c>
@@ -5251,10 +4801,10 @@
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.00119899462861565</v>
+        <v>0.00120512778618731</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0252687461648014</v>
+        <v>0.0253515510624697</v>
       </c>
       <c r="I102"/>
       <c r="J102" t="n">
@@ -5274,21 +4824,15 @@
       <c r="D103" t="s">
         <v>46</v>
       </c>
-      <c r="E103" t="n">
-        <v>0.00119457648815891</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.0252214708666564</v>
-      </c>
+      <c r="E103"/>
+      <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.00119610768031777</v>
+        <v>0.00119864227673681</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0252560367096212</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0.128014574612191</v>
-      </c>
+        <v>0.025308447452098</v>
+      </c>
+      <c r="I103"/>
       <c r="J103" t="n">
         <v>1356</v>
       </c>
@@ -5306,21 +4850,15 @@
       <c r="D104" t="s">
         <v>47</v>
       </c>
-      <c r="E104" t="n">
-        <v>0.00118973844791006</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0.0251653836699592</v>
-      </c>
+      <c r="E104"/>
+      <c r="F104"/>
       <c r="G104" t="n">
-        <v>0.00119252399300116</v>
+        <v>0.00120392844915105</v>
       </c>
       <c r="H104" t="n">
-        <v>0.025173157789918</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0.233583987194362</v>
-      </c>
+        <v>0.0252439516559322</v>
+      </c>
+      <c r="I104"/>
       <c r="J104" t="n">
         <v>1356</v>
       </c>
@@ -5338,21 +4876,15 @@
       <c r="D105" t="s">
         <v>48</v>
       </c>
-      <c r="E105" t="n">
-        <v>0.00118991315860311</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.0251834767319172</v>
-      </c>
+      <c r="E105"/>
+      <c r="F105"/>
       <c r="G105" t="n">
-        <v>0.00119466071725694</v>
+        <v>0.0012096688164163</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0253136050428243</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0.397398071707525</v>
-      </c>
+        <v>0.0254208570953128</v>
+      </c>
+      <c r="I105"/>
       <c r="J105" t="n">
         <v>1356</v>
       </c>
@@ -5373,10 +4905,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.00120168990212095</v>
+        <v>0.00120474120348163</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0251622208356207</v>
+        <v>0.0254779531089513</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -5396,21 +4928,15 @@
       <c r="D107" t="s">
         <v>46</v>
       </c>
-      <c r="E107" t="n">
-        <v>0.00119471390482805</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0.0252108714059851</v>
-      </c>
+      <c r="E107"/>
+      <c r="F107"/>
       <c r="G107" t="n">
-        <v>0.00120261336570215</v>
+        <v>0.00120637412162947</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0252495216273366</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0.656857897923809</v>
-      </c>
+        <v>0.0253746506974337</v>
+      </c>
+      <c r="I107"/>
       <c r="J107" t="n">
         <v>1356</v>
       </c>
@@ -5428,21 +4954,15 @@
       <c r="D108" t="s">
         <v>47</v>
       </c>
-      <c r="E108" t="n">
-        <v>0.00119431599904316</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.0251998011855152</v>
-      </c>
+      <c r="E108"/>
+      <c r="F108"/>
       <c r="G108" t="n">
-        <v>0.00120248868424409</v>
+        <v>0.00119841846512677</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0252562825324428</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0.679647576564828</v>
-      </c>
+        <v>0.0251989531920394</v>
+      </c>
+      <c r="I108"/>
       <c r="J108" t="n">
         <v>1356</v>
       </c>
@@ -5460,21 +4980,15 @@
       <c r="D109" t="s">
         <v>48</v>
       </c>
-      <c r="E109" t="n">
-        <v>0.0011911593977007</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.0251924647014567</v>
-      </c>
+      <c r="E109"/>
+      <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.00121280768205429</v>
+        <v>0.00119513113049113</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0253514297729635</v>
-      </c>
-      <c r="I109" t="n">
-        <v>1.78497256192499</v>
-      </c>
+        <v>0.0253350339873985</v>
+      </c>
+      <c r="I109"/>
       <c r="J109" t="n">
         <v>1356</v>
       </c>
@@ -5495,10 +5009,10 @@
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.0010617363059797</v>
+        <v>0.00106375242667207</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0228232465978768</v>
+        <v>0.0228340268892552</v>
       </c>
       <c r="I110"/>
       <c r="J110" t="n">
@@ -5518,21 +5032,15 @@
       <c r="D111" t="s">
         <v>46</v>
       </c>
-      <c r="E111" t="n">
-        <v>0.00105829575197546</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0.0227090399390152</v>
-      </c>
+      <c r="E111"/>
+      <c r="F111"/>
       <c r="G111" t="n">
-        <v>0.00105666916432244</v>
+        <v>0.00105103955356946</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0226552023906844</v>
-      </c>
-      <c r="I111" t="n">
-        <v>-0.153935376175228</v>
-      </c>
+        <v>0.0225654393514319</v>
+      </c>
+      <c r="I111"/>
       <c r="J111" t="n">
         <v>904</v>
       </c>
@@ -5550,21 +5058,15 @@
       <c r="D112" t="s">
         <v>47</v>
       </c>
-      <c r="E112" t="n">
-        <v>0.00104684932491007</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.0225191897277554</v>
-      </c>
+      <c r="E112"/>
+      <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.00106107008706408</v>
+        <v>0.00106439030684942</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0227148044229999</v>
-      </c>
-      <c r="I112" t="n">
-        <v>1.34022835318609</v>
-      </c>
+        <v>0.0228415947807389</v>
+      </c>
+      <c r="I112"/>
       <c r="J112" t="n">
         <v>904</v>
       </c>
@@ -5582,21 +5084,15 @@
       <c r="D113" t="s">
         <v>48</v>
       </c>
-      <c r="E113" t="n">
-        <v>0.00105231392678582</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0.0226346451964706</v>
-      </c>
+      <c r="E113"/>
+      <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.00106804464192645</v>
+        <v>0.0010847173552226</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0228864365463717</v>
-      </c>
-      <c r="I113" t="n">
-        <v>1.47285183812652</v>
-      </c>
+        <v>0.0231120090588809</v>
+      </c>
+      <c r="I113"/>
       <c r="J113" t="n">
         <v>904</v>
       </c>
@@ -5617,10 +5113,10 @@
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.00166078224759289</v>
+        <v>0.00168237934474001</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0305842263140882</v>
+        <v>0.0309047033061323</v>
       </c>
       <c r="I114"/>
       <c r="J114" t="n">
@@ -5643,10 +5139,10 @@
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115" t="n">
-        <v>0.0016703779813622</v>
+        <v>0.0016828843805046</v>
       </c>
       <c r="H115" t="n">
-        <v>0.030702625550758</v>
+        <v>0.030929933453631</v>
       </c>
       <c r="I115"/>
       <c r="J115" t="n">
@@ -5666,21 +5162,15 @@
       <c r="D116" t="s">
         <v>47</v>
       </c>
-      <c r="E116" t="n">
-        <v>0.00165820182232547</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0.0306129502577943</v>
-      </c>
+      <c r="E116"/>
+      <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.00166777604435993</v>
+        <v>0.00167372980681774</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0308048534766547</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0.574071204993794</v>
-      </c>
+        <v>0.0306830489549518</v>
+      </c>
+      <c r="I116"/>
       <c r="J116" t="n">
         <v>143</v>
       </c>
@@ -5698,21 +5188,15 @@
       <c r="D117" t="s">
         <v>48</v>
       </c>
-      <c r="E117" t="n">
-        <v>0.00166341268735721</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.0306182825762281</v>
-      </c>
+      <c r="E117"/>
+      <c r="F117"/>
       <c r="G117" t="n">
-        <v>0.00165499021296652</v>
+        <v>0.0016659878623652</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0306163541241423</v>
-      </c>
-      <c r="I117" t="n">
-        <v>-0.508913848837206</v>
-      </c>
+        <v>0.030621867569401</v>
+      </c>
+      <c r="I117"/>
       <c r="J117" t="n">
         <v>143</v>
       </c>
@@ -5733,10 +5217,10 @@
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.00223277854413594</v>
+        <v>0.0021931884067139</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0352608912488804</v>
+        <v>0.0349113861158832</v>
       </c>
       <c r="I118"/>
       <c r="J118" t="n">
@@ -5759,10 +5243,10 @@
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00219393284869236</v>
+        <v>0.00221774653023235</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0348129447068459</v>
+        <v>0.0351438426701978</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5782,21 +5266,15 @@
       <c r="D120" t="s">
         <v>47</v>
       </c>
-      <c r="E120" t="n">
-        <v>0.00220916868978119</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0.0350001958743357</v>
-      </c>
+      <c r="E120"/>
+      <c r="F120"/>
       <c r="G120" t="n">
-        <v>0.00219266203757769</v>
+        <v>0.00225225656568711</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0349430169207912</v>
-      </c>
-      <c r="I120" t="n">
-        <v>-0.752813334686707</v>
-      </c>
+        <v>0.0354031100924943</v>
+      </c>
+      <c r="I120"/>
       <c r="J120" t="n">
         <v>59</v>
       </c>
@@ -5814,21 +5292,15 @@
       <c r="D121" t="s">
         <v>48</v>
       </c>
-      <c r="E121" t="n">
-        <v>0.00222409037143345</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0.0351450092539544</v>
-      </c>
+      <c r="E121"/>
+      <c r="F121"/>
       <c r="G121" t="n">
-        <v>0.00221562078910958</v>
+        <v>0.00219449851988753</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0351863839878927</v>
-      </c>
-      <c r="I121" t="n">
-        <v>-0.382266783445026</v>
-      </c>
+        <v>0.0349219330899769</v>
+      </c>
+      <c r="I121"/>
       <c r="J121" t="n">
         <v>59</v>
       </c>
@@ -5849,10 +5321,10 @@
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.000441846366082811</v>
+        <v>0.000442204818182434</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0139014624498722</v>
+        <v>0.0138844903141728</v>
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
@@ -5875,10 +5347,10 @@
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000439898102676739</v>
+        <v>0.000441198311985781</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0138506499225828</v>
+        <v>0.0139425845415084</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5898,21 +5370,15 @@
       <c r="D124" t="s">
         <v>47</v>
       </c>
-      <c r="E124" t="n">
-        <v>0.000439600805870272</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.0138250283730559</v>
-      </c>
+      <c r="E124"/>
+      <c r="F124"/>
       <c r="G124" t="n">
-        <v>0.000440323315365035</v>
+        <v>0.000443221877780747</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0138882694653945</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0.164086131610805</v>
-      </c>
+        <v>0.0139163799674648</v>
+      </c>
+      <c r="I124"/>
       <c r="J124" t="n">
         <v>1356</v>
       </c>
@@ -5930,21 +5396,15 @@
       <c r="D125" t="s">
         <v>48</v>
       </c>
-      <c r="E125" t="n">
-        <v>0.000440359756604141</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.0138657022872707</v>
-      </c>
+      <c r="E125"/>
+      <c r="F125"/>
       <c r="G125" t="n">
-        <v>0.000440216743149556</v>
+        <v>0.000439126525731664</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0138521416952495</v>
-      </c>
-      <c r="I125" t="n">
-        <v>-0.0324870547997314</v>
-      </c>
+        <v>0.013802860323273</v>
+      </c>
+      <c r="I125"/>
       <c r="J125" t="n">
         <v>1356</v>
       </c>
@@ -5965,10 +5425,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000555424518770416</v>
+        <v>0.00056588793156236</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0139814740674101</v>
+        <v>0.0141206707519765</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5991,10 +5451,10 @@
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127" t="n">
-        <v>0.000557482992075759</v>
+        <v>0.000564501728290724</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0139670855227749</v>
+        <v>0.0140885573093786</v>
       </c>
       <c r="I127"/>
       <c r="J127" t="n">
@@ -6014,21 +5474,15 @@
       <c r="D128" t="s">
         <v>47</v>
       </c>
-      <c r="E128" t="n">
-        <v>0.000558765283081715</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0.0139936678336691</v>
-      </c>
+      <c r="E128"/>
+      <c r="F128"/>
       <c r="G128" t="n">
-        <v>0.000561788182131778</v>
+        <v>0.000559889349455259</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0140382793639325</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0.538085197626103</v>
-      </c>
+        <v>0.0140126471544071</v>
+      </c>
+      <c r="I128"/>
       <c r="J128" t="n">
         <v>1356</v>
       </c>
@@ -6046,21 +5500,15 @@
       <c r="D129" t="s">
         <v>48</v>
       </c>
-      <c r="E129" t="n">
-        <v>0.000559928786407684</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0.0139943377463331</v>
-      </c>
+      <c r="E129"/>
+      <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.000561874820747092</v>
+        <v>0.000557315045636113</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0140236172915855</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0.346346600265922</v>
-      </c>
+        <v>0.0140478434611803</v>
+      </c>
+      <c r="I129"/>
       <c r="J129" t="n">
         <v>1356</v>
       </c>
@@ -6081,10 +5529,10 @@
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.000373540377812871</v>
+        <v>0.00037570798509782</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0136652236531096</v>
+        <v>0.0137769551008594</v>
       </c>
       <c r="I130"/>
       <c r="J130" t="n">
@@ -6107,10 +5555,10 @@
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131" t="n">
-        <v>0.000374330689349969</v>
+        <v>0.000374501770330167</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0136723065389618</v>
+        <v>0.0136719564122313</v>
       </c>
       <c r="I131"/>
       <c r="J131" t="n">
@@ -6130,21 +5578,15 @@
       <c r="D132" t="s">
         <v>47</v>
       </c>
-      <c r="E132" t="n">
-        <v>0.000372392817057295</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.0136223862866359</v>
-      </c>
+      <c r="E132"/>
+      <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000376085983657055</v>
+        <v>0.000376540978136047</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0136782237306819</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0.982000595674347</v>
-      </c>
+        <v>0.0136731017353717</v>
+      </c>
+      <c r="I132"/>
       <c r="J132" t="n">
         <v>1356</v>
       </c>
@@ -6162,21 +5604,15 @@
       <c r="D133" t="s">
         <v>48</v>
       </c>
-      <c r="E133" t="n">
-        <v>0.000373614377012493</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0.0136434024631597</v>
-      </c>
+      <c r="E133"/>
+      <c r="F133"/>
       <c r="G133" t="n">
-        <v>0.000374536466952402</v>
+        <v>0.000375418732465198</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0136642073033251</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0.246194969320778</v>
-      </c>
+        <v>0.0136815436822647</v>
+      </c>
+      <c r="I133"/>
       <c r="J133" t="n">
         <v>1356</v>
       </c>
@@ -6197,10 +5633,10 @@
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.000369655887615657</v>
+        <v>0.000376544975245059</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0135913243800647</v>
+        <v>0.0136760526163706</v>
       </c>
       <c r="I134"/>
       <c r="J134" t="n">
@@ -6223,10 +5659,10 @@
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000374086546685996</v>
+        <v>0.000379160724282207</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0136505957718665</v>
+        <v>0.0137105584613234</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
@@ -6246,21 +5682,15 @@
       <c r="D136" t="s">
         <v>47</v>
       </c>
-      <c r="E136" t="n">
-        <v>0.000372173566245856</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0.0136059733207704</v>
-      </c>
+      <c r="E136"/>
+      <c r="F136"/>
       <c r="G136" t="n">
-        <v>0.000373773943852681</v>
+        <v>0.000372891378291104</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0136458717780032</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0.428167247381803</v>
-      </c>
+        <v>0.0137115917182896</v>
+      </c>
+      <c r="I136"/>
       <c r="J136" t="n">
         <v>1356</v>
       </c>
@@ -6278,21 +5708,15 @@
       <c r="D137" t="s">
         <v>48</v>
       </c>
-      <c r="E137" t="n">
-        <v>0.000371827736288835</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.0136090330158051</v>
-      </c>
+      <c r="E137"/>
+      <c r="F137"/>
       <c r="G137" t="n">
-        <v>0.000372967634167825</v>
+        <v>0.000375203785674494</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0136355504376896</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0.305629168475566</v>
-      </c>
+        <v>0.0136965521693395</v>
+      </c>
+      <c r="I137"/>
       <c r="J137" t="n">
         <v>1356</v>
       </c>
@@ -6313,10 +5737,10 @@
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138" t="n">
-        <v>0.00042861553841477</v>
+        <v>0.000428261207343361</v>
       </c>
       <c r="H138" t="n">
-        <v>0.014396097917095</v>
+        <v>0.0144552944390549</v>
       </c>
       <c r="I138"/>
       <c r="J138" t="n">
@@ -6339,10 +5763,10 @@
       <c r="E139"/>
       <c r="F139"/>
       <c r="G139" t="n">
-        <v>0.000430623780748095</v>
+        <v>0.000430146913970015</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0144855076209628</v>
+        <v>0.0145454240249258</v>
       </c>
       <c r="I139"/>
       <c r="J139" t="n">
@@ -6362,21 +5786,15 @@
       <c r="D140" t="s">
         <v>47</v>
       </c>
-      <c r="E140" t="n">
-        <v>0.000425760087117938</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0.0143894536228639</v>
-      </c>
+      <c r="E140"/>
+      <c r="F140"/>
       <c r="G140" t="n">
-        <v>0.000430152341215417</v>
+        <v>0.000428161676723352</v>
       </c>
       <c r="H140" t="n">
-        <v>0.014507762637408</v>
-      </c>
-      <c r="I140" t="n">
-        <v>1.02109268662076</v>
-      </c>
+        <v>0.0144861949155819</v>
+      </c>
+      <c r="I140"/>
       <c r="J140" t="n">
         <v>904</v>
       </c>
@@ -6394,21 +5812,15 @@
       <c r="D141" t="s">
         <v>48</v>
       </c>
-      <c r="E141" t="n">
-        <v>0.000425834334838184</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0.0143824042304185</v>
-      </c>
+      <c r="E141"/>
+      <c r="F141"/>
       <c r="G141" t="n">
-        <v>0.00042675870973324</v>
+        <v>0.000428434834322226</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0143555637166811</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0.216603639005718</v>
-      </c>
+        <v>0.0144624277251371</v>
+      </c>
+      <c r="I141"/>
       <c r="J141" t="n">
         <v>904</v>
       </c>
@@ -6429,10 +5841,10 @@
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142" t="n">
-        <v>0.00261947251925398</v>
+        <v>0.00269327101544228</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0395379087269634</v>
+        <v>0.0395890514698644</v>
       </c>
       <c r="I142"/>
       <c r="J142" t="n">
@@ -6452,21 +5864,15 @@
       <c r="D143" t="s">
         <v>46</v>
       </c>
-      <c r="E143" t="n">
-        <v>0.00261895164248887</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0.0393001944768515</v>
-      </c>
+      <c r="E143"/>
+      <c r="F143"/>
       <c r="G143" t="n">
-        <v>0.00262201152404863</v>
+        <v>0.00264517170430861</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0393063290198784</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0.116699775408867</v>
-      </c>
+        <v>0.0395602202298087</v>
+      </c>
+      <c r="I143"/>
       <c r="J143" t="n">
         <v>143</v>
       </c>
@@ -6484,21 +5890,15 @@
       <c r="D144" t="s">
         <v>47</v>
       </c>
-      <c r="E144" t="n">
-        <v>0.00264197102372509</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0.0395554223013669</v>
-      </c>
+      <c r="E144"/>
+      <c r="F144"/>
       <c r="G144" t="n">
-        <v>0.00264274496640274</v>
+        <v>0.00263577327697478</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0396931544687569</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0.0292855605625911</v>
-      </c>
+        <v>0.0395022019424421</v>
+      </c>
+      <c r="I144"/>
       <c r="J144" t="n">
         <v>143</v>
       </c>
@@ -6516,21 +5916,15 @@
       <c r="D145" t="s">
         <v>48</v>
       </c>
-      <c r="E145" t="n">
-        <v>0.00265892751213425</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.0396512072522042</v>
-      </c>
+      <c r="E145"/>
+      <c r="F145"/>
       <c r="G145" t="n">
-        <v>0.00265301936198677</v>
+        <v>0.00265436017671846</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0395290933786506</v>
-      </c>
-      <c r="I145" t="n">
-        <v>-0.222695327148181</v>
-      </c>
+        <v>0.0398647492300283</v>
+      </c>
+      <c r="I145"/>
       <c r="J145" t="n">
         <v>143</v>
       </c>
@@ -6551,10 +5945,10 @@
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146" t="n">
-        <v>0.00109865931443775</v>
+        <v>0.00110502542008869</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0252370067191239</v>
+        <v>0.0248905137807538</v>
       </c>
       <c r="I146"/>
       <c r="J146" t="n">
@@ -6574,21 +5968,15 @@
       <c r="D147" t="s">
         <v>46</v>
       </c>
-      <c r="E147" t="n">
-        <v>0.00112704262855789</v>
-      </c>
-      <c r="F147" t="n">
-        <v>0.0254223354178506</v>
-      </c>
+      <c r="E147"/>
+      <c r="F147"/>
       <c r="G147" t="n">
-        <v>0.00112399005786281</v>
+        <v>0.00109140662737337</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0255669895810273</v>
-      </c>
-      <c r="I147" t="n">
-        <v>-0.271583424936371</v>
-      </c>
+        <v>0.0252103636419588</v>
+      </c>
+      <c r="I147"/>
       <c r="J147" t="n">
         <v>59</v>
       </c>
@@ -6606,21 +5994,15 @@
       <c r="D148" t="s">
         <v>47</v>
       </c>
-      <c r="E148" t="n">
-        <v>0.00109868565386831</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0.0251939102600145</v>
-      </c>
+      <c r="E148"/>
+      <c r="F148"/>
       <c r="G148" t="n">
-        <v>0.00111247877387397</v>
+        <v>0.00112225056637693</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0254932361761065</v>
-      </c>
-      <c r="I148" t="n">
-        <v>1.23985466775485</v>
-      </c>
+        <v>0.0253354614189151</v>
+      </c>
+      <c r="I148"/>
       <c r="J148" t="n">
         <v>59</v>
       </c>
@@ -6638,21 +6020,15 @@
       <c r="D149" t="s">
         <v>48</v>
       </c>
-      <c r="E149" t="n">
-        <v>0.00109798601208766</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0.0250937480338882</v>
-      </c>
+      <c r="E149"/>
+      <c r="F149"/>
       <c r="G149" t="n">
-        <v>0.00110202816137862</v>
+        <v>0.00108554652467177</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0255787317785432</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0.366791832788591</v>
-      </c>
+        <v>0.024954477939671</v>
+      </c>
+      <c r="I149"/>
       <c r="J149" t="n">
         <v>59</v>
       </c>
@@ -6673,10 +6049,10 @@
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150" t="n">
-        <v>0.000587270326972051</v>
+        <v>0.000590162052551526</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0165420575351505</v>
+        <v>0.0167012462256698</v>
       </c>
       <c r="I150"/>
       <c r="J150" t="n">
@@ -6696,21 +6072,15 @@
       <c r="D151" t="s">
         <v>46</v>
       </c>
-      <c r="E151" t="n">
-        <v>0.000583467966436226</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0.0164228594251004</v>
-      </c>
+      <c r="E151"/>
+      <c r="F151"/>
       <c r="G151" t="n">
-        <v>0.000581560265235879</v>
+        <v>0.000585679687226191</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0163717888303528</v>
-      </c>
-      <c r="I151" t="n">
-        <v>-0.32803155827244</v>
-      </c>
+        <v>0.0164924991748802</v>
+      </c>
+      <c r="I151"/>
       <c r="J151" t="n">
         <v>1356</v>
       </c>
@@ -6728,21 +6098,15 @@
       <c r="D152" t="s">
         <v>47</v>
       </c>
-      <c r="E152" t="n">
-        <v>0.000580665349151087</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.0163858610904858</v>
-      </c>
+      <c r="E152"/>
+      <c r="F152"/>
       <c r="G152" t="n">
-        <v>0.000580333349800885</v>
+        <v>0.000593375413158922</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0163918885077154</v>
-      </c>
-      <c r="I152" t="n">
-        <v>-0.0572083872684009</v>
-      </c>
+        <v>0.0165050313918445</v>
+      </c>
+      <c r="I152"/>
       <c r="J152" t="n">
         <v>1356</v>
       </c>
@@ -6760,21 +6124,15 @@
       <c r="D153" t="s">
         <v>48</v>
       </c>
-      <c r="E153" t="n">
-        <v>0.000583287964039877</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.0164058243930587</v>
-      </c>
+      <c r="E153"/>
+      <c r="F153"/>
       <c r="G153" t="n">
-        <v>0.000581043398396412</v>
+        <v>0.000587886560348952</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0164467979029068</v>
-      </c>
-      <c r="I153" t="n">
-        <v>-0.386299138697611</v>
-      </c>
+        <v>0.0165764469856095</v>
+      </c>
+      <c r="I153"/>
       <c r="J153" t="n">
         <v>1356</v>
       </c>
@@ -6795,10 +6153,10 @@
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154" t="n">
-        <v>0.000712145460208505</v>
+        <v>0.00071806909945495</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0166789955728449</v>
+        <v>0.016816689102073</v>
       </c>
       <c r="I154"/>
       <c r="J154" t="n">
@@ -6818,21 +6176,15 @@
       <c r="D155" t="s">
         <v>46</v>
       </c>
-      <c r="E155" t="n">
-        <v>0.000698539780076497</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0.0165357238916385</v>
-      </c>
+      <c r="E155"/>
+      <c r="F155"/>
       <c r="G155" t="n">
-        <v>0.000700884543485353</v>
+        <v>0.00070474717611004</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0165305769891701</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0.334543460923791</v>
-      </c>
+        <v>0.0165941330286568</v>
+      </c>
+      <c r="I155"/>
       <c r="J155" t="n">
         <v>1356</v>
       </c>
@@ -6850,21 +6202,15 @@
       <c r="D156" t="s">
         <v>47</v>
       </c>
-      <c r="E156" t="n">
-        <v>0.000699007310220551</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.0165217794806285</v>
-      </c>
+      <c r="E156"/>
+      <c r="F156"/>
       <c r="G156" t="n">
-        <v>0.000707261834780408</v>
+        <v>0.000710943499766929</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0165475795656655</v>
-      </c>
-      <c r="I156" t="n">
-        <v>1.16711013572786</v>
-      </c>
+        <v>0.0166384316338683</v>
+      </c>
+      <c r="I156"/>
       <c r="J156" t="n">
         <v>1356</v>
       </c>
@@ -6882,21 +6228,15 @@
       <c r="D157" t="s">
         <v>48</v>
       </c>
-      <c r="E157" t="n">
-        <v>0.000702740521396811</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.0165495231400744</v>
-      </c>
+      <c r="E157"/>
+      <c r="F157"/>
       <c r="G157" t="n">
-        <v>0.000701470541414973</v>
+        <v>0.000713633652667348</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0165730148039869</v>
-      </c>
-      <c r="I157" t="n">
-        <v>-0.181045376371209</v>
-      </c>
+        <v>0.0166118443532897</v>
+      </c>
+      <c r="I157"/>
       <c r="J157" t="n">
         <v>1356</v>
       </c>
@@ -6917,10 +6257,10 @@
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158" t="n">
-        <v>0.000517399554471212</v>
+        <v>0.000522885073455123</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0162626609232933</v>
+        <v>0.0163866432140927</v>
       </c>
       <c r="I158"/>
       <c r="J158" t="n">
@@ -6940,21 +6280,15 @@
       <c r="D159" t="s">
         <v>46</v>
       </c>
-      <c r="E159" t="n">
-        <v>0.000516437004313829</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.0161924004291914</v>
-      </c>
+      <c r="E159"/>
+      <c r="F159"/>
       <c r="G159" t="n">
-        <v>0.000515135469779379</v>
+        <v>0.000523336973189577</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0162296906740466</v>
-      </c>
-      <c r="I159" t="n">
-        <v>-0.25265869092778</v>
-      </c>
+        <v>0.0163046106258134</v>
+      </c>
+      <c r="I159"/>
       <c r="J159" t="n">
         <v>1356</v>
       </c>
@@ -6972,21 +6306,15 @@
       <c r="D160" t="s">
         <v>47</v>
       </c>
-      <c r="E160" t="n">
-        <v>0.000514629831776683</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.0161873360129158</v>
-      </c>
+      <c r="E160"/>
+      <c r="F160"/>
       <c r="G160" t="n">
-        <v>0.000522178065542295</v>
+        <v>0.000520409368057618</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0162948523274425</v>
-      </c>
-      <c r="I160" t="n">
-        <v>1.44552869293211</v>
-      </c>
+        <v>0.0162894454532659</v>
+      </c>
+      <c r="I160"/>
       <c r="J160" t="n">
         <v>1356</v>
       </c>
@@ -7004,21 +6332,15 @@
       <c r="D161" t="s">
         <v>48</v>
       </c>
-      <c r="E161" t="n">
-        <v>0.000514907592634405</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.0161918112171043</v>
-      </c>
+      <c r="E161"/>
+      <c r="F161"/>
       <c r="G161" t="n">
-        <v>0.000518422754932936</v>
+        <v>0.000524545154866656</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0162462825593094</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0.67804938442294</v>
-      </c>
+        <v>0.0164268455881536</v>
+      </c>
+      <c r="I161"/>
       <c r="J161" t="n">
         <v>1356</v>
       </c>
@@ -7039,10 +6361,10 @@
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162" t="n">
-        <v>0.000519209348078926</v>
+        <v>0.000529009605686526</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0163176273811625</v>
+        <v>0.0165621642674863</v>
       </c>
       <c r="I162"/>
       <c r="J162" t="n">
@@ -7062,21 +6384,15 @@
       <c r="D163" t="s">
         <v>46</v>
       </c>
-      <c r="E163" t="n">
-        <v>0.000515832650532893</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0.0161900700128506</v>
-      </c>
+      <c r="E163"/>
+      <c r="F163"/>
       <c r="G163" t="n">
-        <v>0.00051743920899692</v>
+        <v>0.000519401035452289</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0161651553305949</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0.310482552557568</v>
-      </c>
+        <v>0.0162834954876742</v>
+      </c>
+      <c r="I163"/>
       <c r="J163" t="n">
         <v>1356</v>
       </c>
@@ -7094,21 +6410,15 @@
       <c r="D164" t="s">
         <v>47</v>
       </c>
-      <c r="E164" t="n">
-        <v>0.000513468431727726</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.0161455092047277</v>
-      </c>
+      <c r="E164"/>
+      <c r="F164"/>
       <c r="G164" t="n">
-        <v>0.000516928249509697</v>
+        <v>0.000526390407050498</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0162622745887077</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0.669303290205565</v>
-      </c>
+        <v>0.0164709546815536</v>
+      </c>
+      <c r="I164"/>
       <c r="J164" t="n">
         <v>1356</v>
       </c>
@@ -7126,21 +6436,15 @@
       <c r="D165" t="s">
         <v>48</v>
       </c>
-      <c r="E165" t="n">
-        <v>0.000515401163955399</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0.016189165944605</v>
-      </c>
+      <c r="E165"/>
+      <c r="F165"/>
       <c r="G165" t="n">
-        <v>0.000518152384373022</v>
+        <v>0.000522307774557241</v>
       </c>
       <c r="H165" t="n">
-        <v>0.016284561087362</v>
-      </c>
-      <c r="I165" t="n">
-        <v>0.530967433634873</v>
-      </c>
+        <v>0.0163211730449248</v>
+      </c>
+      <c r="I165"/>
       <c r="J165" t="n">
         <v>1356</v>
       </c>
@@ -7161,10 +6465,10 @@
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166" t="n">
-        <v>0.000479404243175749</v>
+        <v>0.000484383547652276</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0160170888969772</v>
+        <v>0.0161376467990644</v>
       </c>
       <c r="I166"/>
       <c r="J166" t="n">
@@ -7184,21 +6488,15 @@
       <c r="D167" t="s">
         <v>46</v>
       </c>
-      <c r="E167" t="n">
-        <v>0.000463431238055903</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0.0156660956000309</v>
-      </c>
+      <c r="E167"/>
+      <c r="F167"/>
       <c r="G167" t="n">
-        <v>0.000480770340358602</v>
+        <v>0.000484190546227605</v>
       </c>
       <c r="H167" t="n">
-        <v>0.016078089874649</v>
-      </c>
-      <c r="I167" t="n">
-        <v>3.60652495529679</v>
-      </c>
+        <v>0.0161419199853566</v>
+      </c>
+      <c r="I167"/>
       <c r="J167" t="n">
         <v>904</v>
       </c>
@@ -7216,21 +6514,15 @@
       <c r="D168" t="s">
         <v>47</v>
       </c>
-      <c r="E168" t="n">
-        <v>0.000467473423972771</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0.0157542551139309</v>
-      </c>
+      <c r="E168"/>
+      <c r="F168"/>
       <c r="G168" t="n">
-        <v>0.000482379343376721</v>
+        <v>0.000487098319254647</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0161371076345837</v>
-      </c>
-      <c r="I168" t="n">
-        <v>3.09008244416233</v>
-      </c>
+        <v>0.0161812580899703</v>
+      </c>
+      <c r="I168"/>
       <c r="J168" t="n">
         <v>904</v>
       </c>
@@ -7248,21 +6540,15 @@
       <c r="D169" t="s">
         <v>48</v>
       </c>
-      <c r="E169" t="n">
-        <v>0.000476758676422462</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.0160465401543294</v>
-      </c>
+      <c r="E169"/>
+      <c r="F169"/>
       <c r="G169" t="n">
-        <v>0.000501189023645224</v>
+        <v>0.00052394728522948</v>
       </c>
       <c r="H169" t="n">
-        <v>0.016603213630096</v>
-      </c>
-      <c r="I169" t="n">
-        <v>4.87447770605102</v>
-      </c>
+        <v>0.01685309614394</v>
+      </c>
+      <c r="I169"/>
       <c r="J169" t="n">
         <v>904</v>
       </c>
@@ -7308,14 +6594,14 @@
       <c r="C2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.00119655545036231</v>
+      <c r="D2" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00119710702510518</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0956561833428542</v>
+        <v>0.00120245939278837</v>
+      </c>
+      <c r="F2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="3">
@@ -7328,14 +6614,14 @@
       <c r="C3" t="n">
         <v>6</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.00100029410980916</v>
+      <c r="D3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00119829074797585</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-1.1792448593317</v>
+        <v>0.00120113676050736</v>
+      </c>
+      <c r="F3" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="4">
@@ -7348,14 +6634,14 @@
       <c r="C4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.0011967827505252</v>
+      <c r="D4" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0012003709013237</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.81891189224548</v>
+        <v>0.0012016444910941</v>
+      </c>
+      <c r="F4" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="5">
@@ -7372,7 +6658,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00120292832011974</v>
+        <v>0.00120058501320724</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -7388,14 +6674,14 @@
       <c r="C6" t="n">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.00146554211220192</v>
+      <c r="D6" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00146913479677698</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.243338299413299</v>
+        <v>0.00147055407044678</v>
+      </c>
+      <c r="F6" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="7">
@@ -7408,14 +6694,14 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.00142786585458327</v>
+      <c r="D7" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00146742994418569</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.50784000810539</v>
+        <v>0.00148071051483025</v>
+      </c>
+      <c r="F7" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="8">
@@ -7428,14 +6714,14 @@
       <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.00146438826819781</v>
+      <c r="D8" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00147181837939702</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.464051331549821</v>
+        <v>0.00146955497467046</v>
+      </c>
+      <c r="F8" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="9">
@@ -7452,7 +6738,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00146421175608589</v>
+        <v>0.00147423639870002</v>
       </c>
       <c r="F9" t="e">
         <v>#NUM!</v>
@@ -7468,14 +6754,14 @@
       <c r="C10" t="n">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.000400481683371258</v>
+      <c r="D10" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000405851961557992</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.493115735271858</v>
+        <v>0.000406861187073468</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="11">
@@ -7488,14 +6774,14 @@
       <c r="C11" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.000406181909601884</v>
+      <c r="D11" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000401638271774652</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-11.8665623197807</v>
+        <v>0.00040173694771899</v>
+      </c>
+      <c r="F11" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="12">
@@ -7508,14 +6794,14 @@
       <c r="C12" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.000402945335304631</v>
+      <c r="D12" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000410828843754454</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.46993854061624</v>
+        <v>0.000418635864864461</v>
+      </c>
+      <c r="F12" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="13">
@@ -7532,7 +6818,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000405711895000397</v>
+        <v>0.000406885553569409</v>
       </c>
       <c r="F13" t="e">
         <v>#NUM!</v>
@@ -7548,14 +6834,14 @@
       <c r="C14" t="n">
         <v>6</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.000440986173434694</v>
+      <c r="D14" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000441699885381531</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.201069056622543</v>
+        <v>0.000445663197563484</v>
+      </c>
+      <c r="F14" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="15">
@@ -7568,14 +6854,14 @@
       <c r="C15" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.000443033504858136</v>
+      <c r="D15" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E15" t="n">
-        <v>267.68003519277</v>
-      </c>
-      <c r="F15" t="n">
-        <v>19.9698622743398</v>
+        <v>606.878484301023</v>
+      </c>
+      <c r="F15" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="16">
@@ -7588,14 +6874,14 @@
       <c r="C16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.000442041099489419</v>
+      <c r="D16" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000442926340311838</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.369086427098096</v>
+        <v>0.000444645048646826</v>
+      </c>
+      <c r="F16" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="17">
@@ -7612,7 +6898,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000444316907878992</v>
+        <v>0.000443392266414686</v>
       </c>
       <c r="F17" t="e">
         <v>#NUM!</v>
@@ -7628,14 +6914,14 @@
       <c r="C18" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.000562085373306923</v>
+      <c r="D18" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000565578967452626</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.48741047927765</v>
+        <v>0.000566275748003142</v>
+      </c>
+      <c r="F18" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="19">
@@ -7648,14 +6934,14 @@
       <c r="C19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.000563072198341242</v>
+      <c r="D19" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E19" t="n">
-        <v>297.386465031614</v>
-      </c>
-      <c r="F19" t="n">
-        <v>20.1046323317966</v>
+        <v>652.793714631928</v>
+      </c>
+      <c r="F19" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="20">
@@ -7668,14 +6954,14 @@
       <c r="C20" t="n">
         <v>6</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.000563299552942815</v>
+      <c r="D20" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000564530360648154</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.24262162725552</v>
+        <v>0.000565438386148057</v>
+      </c>
+      <c r="F20" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="21">
@@ -7692,7 +6978,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000567178973563844</v>
+        <v>0.000570821737902311</v>
       </c>
       <c r="F21" t="e">
         <v>#NUM!</v>
@@ -7708,14 +6994,14 @@
       <c r="C22" t="n">
         <v>6</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.000371415262608523</v>
+      <c r="D22" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000374043422957246</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.22847767101778</v>
+        <v>0.000375688430008086</v>
+      </c>
+      <c r="F22" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="23">
@@ -7728,14 +7014,14 @@
       <c r="C23" t="n">
         <v>6</v>
       </c>
-      <c r="D23" t="n">
-        <v>0.00037396252084702</v>
+      <c r="D23" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E23" t="n">
-        <v>315.537946149748</v>
-      </c>
-      <c r="F23" t="n">
-        <v>19.9982661888322</v>
+        <v>654.540156886194</v>
+      </c>
+      <c r="F23" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="24">
@@ -7748,14 +7034,14 @@
       <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.00037164852830393</v>
+      <c r="D24" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000373589451612419</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.15469618254902</v>
+        <v>0.000377704768918216</v>
+      </c>
+      <c r="F24" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="25">
@@ -7772,7 +7058,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00037375012783771</v>
+        <v>0.000376137018646083</v>
       </c>
       <c r="F25" t="e">
         <v>#NUM!</v>
@@ -7788,14 +7074,14 @@
       <c r="C26" t="n">
         <v>6</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.000371930755229186</v>
+      <c r="D26" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000374365577083806</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.925424268937572</v>
+        <v>0.000375190547876761</v>
+      </c>
+      <c r="F26" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="27">
@@ -7808,14 +7094,14 @@
       <c r="C27" t="n">
         <v>6</v>
       </c>
-      <c r="D27" t="n">
-        <v>0.000373912732928233</v>
+      <c r="D27" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E27" t="n">
-        <v>298.801719963046</v>
-      </c>
-      <c r="F27" t="n">
-        <v>20.1576388155051</v>
+        <v>494.400818659229</v>
+      </c>
+      <c r="F27" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="28">
@@ -7828,14 +7114,14 @@
       <c r="C28" t="n">
         <v>6</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.00037165869119668</v>
+      <c r="D28" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000376407939211573</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.60675685602674</v>
+        <v>0.000374966735105919</v>
+      </c>
+      <c r="F28" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="29">
@@ -7852,7 +7138,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000373800091005624</v>
+        <v>0.000377197942041899</v>
       </c>
       <c r="F29" t="e">
         <v>#NUM!</v>

--- a/results/chronological/consolidated/Stress_Testing.xlsx
+++ b/results/chronological/consolidated/Stress_Testing.xlsx
@@ -2201,10 +2201,10 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.000166484270628164</v>
+        <v>0.000166739674733316</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00970310735528819</v>
+        <v>0.00971732808060449</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
@@ -2227,10 +2227,10 @@
       <c r="E3"/>
       <c r="F3"/>
       <c r="G3" t="n">
-        <v>0.000168289500776009</v>
+        <v>0.000167175330738123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00972963582566889</v>
+        <v>0.00969679997595236</v>
       </c>
       <c r="I3"/>
       <c r="J3" t="n">
@@ -2253,10 +2253,10 @@
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4" t="n">
-        <v>0.000169297288284172</v>
+        <v>0.000168581205434697</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00976754848874467</v>
+        <v>0.00975243476012632</v>
       </c>
       <c r="I4"/>
       <c r="J4" t="n">
@@ -2279,10 +2279,10 @@
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.000165511353111637</v>
+        <v>0.000165946196747117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00967456182510069</v>
+        <v>0.00968779503037587</v>
       </c>
       <c r="I5"/>
       <c r="J5" t="n">
@@ -2305,10 +2305,10 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000392307905735696</v>
+        <v>0.0000389508304105256</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00484471095658396</v>
+        <v>0.00479221654974713</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2331,10 +2331,10 @@
       <c r="E7"/>
       <c r="F7"/>
       <c r="G7" t="n">
-        <v>0.0000409331927054679</v>
+        <v>0.0000400318637141898</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00489005908368984</v>
+        <v>0.00483614225363564</v>
       </c>
       <c r="I7"/>
       <c r="J7" t="n">
@@ -2357,10 +2357,10 @@
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8" t="n">
-        <v>0.0000397401120504396</v>
+        <v>0.000039395853483857</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00487014817836813</v>
+        <v>0.00482974473923613</v>
       </c>
       <c r="I8"/>
       <c r="J8" t="n">
@@ -2383,10 +2383,10 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9" t="n">
-        <v>0.0000438377093889929</v>
+        <v>0.0000409458523869202</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00506435219823743</v>
+        <v>0.00487411691263711</v>
       </c>
       <c r="I9"/>
       <c r="J9" t="n">
@@ -2409,10 +2409,10 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10" t="n">
-        <v>0.0000910435252355826</v>
+        <v>0.0000908171867866898</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00368569306814232</v>
+        <v>0.00366519621067291</v>
       </c>
       <c r="I10"/>
       <c r="J10" t="n">
@@ -2435,10 +2435,10 @@
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11" t="n">
-        <v>0.0000914390867340853</v>
+        <v>0.0000911173378568578</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00371627952278092</v>
+        <v>0.00368329611257963</v>
       </c>
       <c r="I11"/>
       <c r="J11" t="n">
@@ -2461,10 +2461,10 @@
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12" t="n">
-        <v>0.000091416751422101</v>
+        <v>0.0000905535712653308</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0037393464914384</v>
+        <v>0.00366131247505962</v>
       </c>
       <c r="I12"/>
       <c r="J12" t="n">
@@ -2487,10 +2487,10 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13" t="n">
-        <v>0.0000919308706440001</v>
+        <v>0.0000909296862838701</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00380818062097797</v>
+        <v>0.00369546173378378</v>
       </c>
       <c r="I13"/>
       <c r="J13" t="n">
@@ -2513,10 +2513,10 @@
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14" t="n">
-        <v>0.000210491733674835</v>
+        <v>0.000210323748351391</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00385700157071754</v>
+        <v>0.00381801617738811</v>
       </c>
       <c r="I14"/>
       <c r="J14" t="n">
@@ -2539,10 +2539,10 @@
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15" t="n">
-        <v>0.000211970528435656</v>
+        <v>0.00021131422926976</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00385010794736463</v>
+        <v>0.0038231289768156</v>
       </c>
       <c r="I15"/>
       <c r="J15" t="n">
@@ -2565,10 +2565,10 @@
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16" t="n">
-        <v>0.000211650722581567</v>
+        <v>0.000210821777926766</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00385732399535418</v>
+        <v>0.00379901350243081</v>
       </c>
       <c r="I16"/>
       <c r="J16" t="n">
@@ -2591,10 +2591,10 @@
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17" t="n">
-        <v>0.000211221276859103</v>
+        <v>0.000210327126665955</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00393208422166285</v>
+        <v>0.00384210305857647</v>
       </c>
       <c r="I17"/>
       <c r="J17" t="n">
@@ -2617,10 +2617,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000222186552830504</v>
+        <v>0.0000220711242461332</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00347492879441313</v>
+        <v>0.00344949018560108</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2643,10 +2643,10 @@
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19" t="n">
-        <v>0.0000224149052033806</v>
+        <v>0.000022179574728979</v>
       </c>
       <c r="H19" t="n">
-        <v>0.003470703398814</v>
+        <v>0.00344940609590205</v>
       </c>
       <c r="I19"/>
       <c r="J19" t="n">
@@ -2669,10 +2669,10 @@
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20" t="n">
-        <v>0.0000230475573548821</v>
+        <v>0.0000221576876840921</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00353935463444195</v>
+        <v>0.00344994502646059</v>
       </c>
       <c r="I20"/>
       <c r="J20" t="n">
@@ -2695,10 +2695,10 @@
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21" t="n">
-        <v>0.0000237799490195526</v>
+        <v>0.0000227032859694928</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00362245920045411</v>
+        <v>0.00350208639245075</v>
       </c>
       <c r="I21"/>
       <c r="J21" t="n">
@@ -2721,10 +2721,10 @@
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22" t="n">
-        <v>0.0000224296933499698</v>
+        <v>0.0000221932204066097</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00345338181246906</v>
+        <v>0.00344464200490092</v>
       </c>
       <c r="I22"/>
       <c r="J22" t="n">
@@ -2747,10 +2747,10 @@
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23" t="n">
-        <v>0.0000226077640735609</v>
+        <v>0.0000223488776437385</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00350072653022918</v>
+        <v>0.00346957300140853</v>
       </c>
       <c r="I23"/>
       <c r="J23" t="n">
@@ -2773,10 +2773,10 @@
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24" t="n">
-        <v>0.0000225650498261076</v>
+        <v>0.0000221176829550244</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00349202517186894</v>
+        <v>0.00343953476475697</v>
       </c>
       <c r="I24"/>
       <c r="J24" t="n">
@@ -2799,10 +2799,10 @@
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25" t="n">
-        <v>0.0000240961031372539</v>
+        <v>0.0000228410825216375</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00365446957456209</v>
+        <v>0.0035227248423214</v>
       </c>
       <c r="I25"/>
       <c r="J25" t="n">
@@ -2825,10 +2825,10 @@
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26" t="n">
-        <v>0.000118327367256644</v>
+        <v>0.000119559917594589</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00996001591083214</v>
+        <v>0.0100392337062433</v>
       </c>
       <c r="I26"/>
       <c r="J26" t="n">
@@ -2851,10 +2851,10 @@
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27" t="n">
-        <v>0.000107656534332223</v>
+        <v>0.000126102572491251</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00941187355406007</v>
+        <v>0.0103505519399723</v>
       </c>
       <c r="I27"/>
       <c r="J27" t="n">
@@ -2877,10 +2877,10 @@
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28" t="n">
-        <v>0.000116531984775962</v>
+        <v>0.000118149298394823</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00988232404996959</v>
+        <v>0.00998068235862</v>
       </c>
       <c r="I28"/>
       <c r="J28" t="n">
@@ -2903,10 +2903,10 @@
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29" t="n">
-        <v>0.000121095198094957</v>
+        <v>0.000119268811863974</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0100491563276939</v>
+        <v>0.0100062668000053</v>
       </c>
       <c r="I29"/>
       <c r="J29" t="n">
@@ -2929,10 +2929,10 @@
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30" t="n">
-        <v>0.000236053686397006</v>
+        <v>0.000237024151559849</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0115928485674324</v>
+        <v>0.0116382393245931</v>
       </c>
       <c r="I30"/>
       <c r="J30" t="n">
@@ -2955,10 +2955,10 @@
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31" t="n">
-        <v>0.000239482805165124</v>
+        <v>0.00023852208040406</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0117605962562826</v>
+        <v>0.0117123382470976</v>
       </c>
       <c r="I31"/>
       <c r="J31" t="n">
@@ -2981,10 +2981,10 @@
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32" t="n">
-        <v>0.000237488920794175</v>
+        <v>0.000237499926222673</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0116789752103996</v>
+        <v>0.011678521418508</v>
       </c>
       <c r="I32"/>
       <c r="J32" t="n">
@@ -3007,10 +3007,10 @@
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33" t="n">
-        <v>0.00023883205285248</v>
+        <v>0.00023873183209257</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0116754397530211</v>
+        <v>0.011675248076978</v>
       </c>
       <c r="I33"/>
       <c r="J33" t="n">
@@ -3033,10 +3033,10 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.0000973661859329106</v>
+        <v>0.0000968264802807851</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00739296675780731</v>
+        <v>0.00737437235015226</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
@@ -3059,10 +3059,10 @@
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35" t="n">
-        <v>0.0000953822627784744</v>
+        <v>0.0000956232853216208</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0073744492549293</v>
+        <v>0.00737383150229211</v>
       </c>
       <c r="I35"/>
       <c r="J35" t="n">
@@ -3085,10 +3085,10 @@
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36" t="n">
-        <v>0.0000946116483417459</v>
+        <v>0.0000951271634404866</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00724964722353417</v>
+        <v>0.0072793287018844</v>
       </c>
       <c r="I36"/>
       <c r="J36" t="n">
@@ -3111,10 +3111,10 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37" t="n">
-        <v>0.000096209422431322</v>
+        <v>0.0000962687695955398</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00758701501489448</v>
+        <v>0.00745593004436244</v>
       </c>
       <c r="I37"/>
       <c r="J37" t="n">
@@ -3137,10 +3137,10 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38" t="n">
-        <v>0.000104035175877921</v>
+        <v>0.000103575565856709</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00459165630850136</v>
+        <v>0.004551842318293</v>
       </c>
       <c r="I38"/>
       <c r="J38" t="n">
@@ -3163,10 +3163,10 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39" t="n">
-        <v>0.000104059215140179</v>
+        <v>0.000103719350853209</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00461739816141817</v>
+        <v>0.00458193897051283</v>
       </c>
       <c r="I39"/>
       <c r="J39" t="n">
@@ -3189,10 +3189,10 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40" t="n">
-        <v>0.000104150338931593</v>
+        <v>0.000103265523226432</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00461835867010007</v>
+        <v>0.00455632580972199</v>
       </c>
       <c r="I40"/>
       <c r="J40" t="n">
@@ -3215,10 +3215,10 @@
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41" t="n">
-        <v>0.000105323406256092</v>
+        <v>0.000104232883771404</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00468709361530862</v>
+        <v>0.00460177075401775</v>
       </c>
       <c r="I41"/>
       <c r="J41" t="n">
@@ -3241,10 +3241,10 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42" t="n">
-        <v>0.000223696012654615</v>
+        <v>0.000222942591649192</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00477056655491325</v>
+        <v>0.00471176308168258</v>
       </c>
       <c r="I42"/>
       <c r="J42" t="n">
@@ -3267,10 +3267,10 @@
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43" t="n">
-        <v>0.000223115439459715</v>
+        <v>0.000222865076190597</v>
       </c>
       <c r="H43" t="n">
-        <v>0.00473645769321433</v>
+        <v>0.00471187698067763</v>
       </c>
       <c r="I43"/>
       <c r="J43" t="n">
@@ -3293,10 +3293,10 @@
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44" t="n">
-        <v>0.000223794522495776</v>
+        <v>0.000222898724811435</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00477468499764365</v>
+        <v>0.00469845482594636</v>
       </c>
       <c r="I44"/>
       <c r="J44" t="n">
@@ -3319,10 +3319,10 @@
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45" t="n">
-        <v>0.000224529084627498</v>
+        <v>0.00022348319959687</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00485204551059975</v>
+        <v>0.00476126434005401</v>
       </c>
       <c r="I45"/>
       <c r="J45" t="n">
@@ -3345,10 +3345,10 @@
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46" t="n">
-        <v>0.0000354283376961201</v>
+        <v>0.0000351995643943563</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00435277066986542</v>
+        <v>0.00432602359521006</v>
       </c>
       <c r="I46"/>
       <c r="J46" t="n">
@@ -3371,10 +3371,10 @@
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47" t="n">
-        <v>0.000035855592008376</v>
+        <v>0.0000354932123842432</v>
       </c>
       <c r="H47" t="n">
-        <v>0.00437161739664475</v>
+        <v>0.0043457973205701</v>
       </c>
       <c r="I47"/>
       <c r="J47" t="n">
@@ -3397,10 +3397,10 @@
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48" t="n">
-        <v>0.0000358221383369487</v>
+        <v>0.0000352290908133938</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00440021464323623</v>
+        <v>0.00433441473027599</v>
       </c>
       <c r="I48"/>
       <c r="J48" t="n">
@@ -3423,10 +3423,10 @@
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49" t="n">
-        <v>0.0000360277606482271</v>
+        <v>0.0000353256814976408</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0043906115980566</v>
+        <v>0.00433976327562276</v>
       </c>
       <c r="I49"/>
       <c r="J49" t="n">
@@ -3449,10 +3449,10 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.0000357596782510935</v>
+        <v>0.0000353661460515132</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00438446955624749</v>
+        <v>0.00434047603229454</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
@@ -3475,10 +3475,10 @@
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51" t="n">
-        <v>0.0000356419678473142</v>
+        <v>0.0000353996572259399</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00438206760429898</v>
+        <v>0.00435014343138524</v>
       </c>
       <c r="I51"/>
       <c r="J51" t="n">
@@ -3501,10 +3501,10 @@
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52" t="n">
-        <v>0.0000361112784607043</v>
+        <v>0.0000354204932749904</v>
       </c>
       <c r="H52" t="n">
-        <v>0.00441034534937561</v>
+        <v>0.00434479800363271</v>
       </c>
       <c r="I52"/>
       <c r="J52" t="n">
@@ -3527,10 +3527,10 @@
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53" t="n">
-        <v>0.0000361663837673313</v>
+        <v>0.0000354165973363969</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00444787764257511</v>
+        <v>0.0043683154994951</v>
       </c>
       <c r="I53"/>
       <c r="J53" t="n">
@@ -3553,10 +3553,10 @@
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54" t="n">
-        <v>0.000131375628428823</v>
+        <v>0.00013173125919463</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0101394925373157</v>
+        <v>0.0101683370068564</v>
       </c>
       <c r="I54"/>
       <c r="J54" t="n">
@@ -3579,10 +3579,10 @@
       <c r="E55"/>
       <c r="F55"/>
       <c r="G55" t="n">
-        <v>0.00012161121910038</v>
+        <v>0.00013721539361702</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00968806939379764</v>
+        <v>0.0104372712014222</v>
       </c>
       <c r="I55"/>
       <c r="J55" t="n">
@@ -3605,10 +3605,10 @@
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56" t="n">
-        <v>0.000129795491402692</v>
+        <v>0.000131895909839568</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0100539551347552</v>
+        <v>0.0101787870098288</v>
       </c>
       <c r="I56"/>
       <c r="J56" t="n">
@@ -3631,10 +3631,10 @@
       <c r="E57"/>
       <c r="F57"/>
       <c r="G57" t="n">
-        <v>0.000130804416937181</v>
+        <v>0.000131999591766133</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0101352145029411</v>
+        <v>0.010191526874584</v>
       </c>
       <c r="I57"/>
       <c r="J57" t="n">
@@ -3657,10 +3657,10 @@
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000513891265253846</v>
+        <v>0.000514871623255834</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0164214537432564</v>
+        <v>0.0163596111610899</v>
       </c>
       <c r="I58"/>
       <c r="J58" t="n">
@@ -3683,10 +3683,10 @@
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.000515809009061069</v>
+        <v>0.000515581267172311</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0162868276640632</v>
+        <v>0.0162963363513796</v>
       </c>
       <c r="I59"/>
       <c r="J59" t="n">
@@ -3709,10 +3709,10 @@
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60" t="n">
-        <v>0.000508471873658877</v>
+        <v>0.000510962126007053</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0163825927656844</v>
+        <v>0.0163684629636016</v>
       </c>
       <c r="I60"/>
       <c r="J60" t="n">
@@ -3735,10 +3735,10 @@
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61" t="n">
-        <v>0.00052116771067046</v>
+        <v>0.000518031264874855</v>
       </c>
       <c r="H61" t="n">
-        <v>0.016526944273177</v>
+        <v>0.0164481290485706</v>
       </c>
       <c r="I61"/>
       <c r="J61" t="n">
@@ -3761,10 +3761,10 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.000258671141797781</v>
+        <v>0.000260188711618463</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0121066593043908</v>
+        <v>0.0121258593927602</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -3787,10 +3787,10 @@
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63" t="n">
-        <v>0.00025928217246475</v>
+        <v>0.000259065133200994</v>
       </c>
       <c r="H63" t="n">
-        <v>0.012140228329092</v>
+        <v>0.0121220291895014</v>
       </c>
       <c r="I63"/>
       <c r="J63" t="n">
@@ -3813,10 +3813,10 @@
       <c r="E64"/>
       <c r="F64"/>
       <c r="G64" t="n">
-        <v>0.000259673880381271</v>
+        <v>0.000259318123429544</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0121059145240385</v>
+        <v>0.0121009912602446</v>
       </c>
       <c r="I64"/>
       <c r="J64" t="n">
@@ -3839,10 +3839,10 @@
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000257628291703162</v>
+        <v>0.000256894238556425</v>
       </c>
       <c r="H65" t="n">
-        <v>0.012131012247036</v>
+        <v>0.0120941920059368</v>
       </c>
       <c r="I65"/>
       <c r="J65" t="n">
@@ -3865,10 +3865,10 @@
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.000164031822677654</v>
+        <v>0.000162586279202364</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00776603538648519</v>
+        <v>0.00770558800555955</v>
       </c>
       <c r="I66"/>
       <c r="J66" t="n">
@@ -3891,10 +3891,10 @@
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67" t="n">
-        <v>3641.268396681</v>
+        <v>1213.74285915808</v>
       </c>
       <c r="H67" t="n">
-        <v>13.4428494697121</v>
+        <v>7.76426077312173</v>
       </c>
       <c r="I67"/>
       <c r="J67" t="n">
@@ -3917,10 +3917,10 @@
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.000163331312256752</v>
+        <v>0.000162611247765157</v>
       </c>
       <c r="H68" t="n">
-        <v>0.00775969348478108</v>
+        <v>0.00772844257661858</v>
       </c>
       <c r="I68"/>
       <c r="J68" t="n">
@@ -3943,10 +3943,10 @@
       <c r="E69"/>
       <c r="F69"/>
       <c r="G69" t="n">
-        <v>0.000167324634048557</v>
+        <v>0.000164737133869094</v>
       </c>
       <c r="H69" t="n">
-        <v>0.00789985210528485</v>
+        <v>0.00778915638572289</v>
       </c>
       <c r="I69"/>
       <c r="J69" t="n">
@@ -3969,10 +3969,10 @@
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.000283351406973571</v>
+        <v>0.000281960284267101</v>
       </c>
       <c r="H70" t="n">
-        <v>0.00790124899403807</v>
+        <v>0.00783862267199919</v>
       </c>
       <c r="I70"/>
       <c r="J70" t="n">
@@ -3995,10 +3995,10 @@
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71" t="n">
-        <v>3916.75918161957</v>
+        <v>1305.59381848702</v>
       </c>
       <c r="H71" t="n">
-        <v>14.5828947605775</v>
+        <v>8.42261251279047</v>
       </c>
       <c r="I71"/>
       <c r="J71" t="n">
@@ -4021,10 +4021,10 @@
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72" t="n">
-        <v>0.000283374509906629</v>
+        <v>0.000282410295172309</v>
       </c>
       <c r="H72" t="n">
-        <v>0.00791259266787795</v>
+        <v>0.0078770578332271</v>
       </c>
       <c r="I72"/>
       <c r="J72" t="n">
@@ -4047,10 +4047,10 @@
       <c r="E73"/>
       <c r="F73"/>
       <c r="G73" t="n">
-        <v>0.000281963316312913</v>
+        <v>0.000280795607591805</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00793625174710484</v>
+        <v>0.00787537753172</v>
       </c>
       <c r="I73"/>
       <c r="J73" t="n">
@@ -4073,10 +4073,10 @@
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.000095454274157071</v>
+        <v>0.0000940433060653965</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00760074612715361</v>
+        <v>0.00750967045408458</v>
       </c>
       <c r="I74"/>
       <c r="J74" t="n">
@@ -4099,10 +4099,10 @@
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75" t="n">
-        <v>3927.23878656565</v>
+        <v>1309.0573790592</v>
       </c>
       <c r="H75" t="n">
-        <v>14.7310198020601</v>
+        <v>8.50789169517494</v>
       </c>
       <c r="I75"/>
       <c r="J75" t="n">
@@ -4125,10 +4125,10 @@
       <c r="E76"/>
       <c r="F76"/>
       <c r="G76" t="n">
-        <v>0.0000943820890119737</v>
+        <v>0.0000938119979712337</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00754786430188658</v>
+        <v>0.00752160542967396</v>
       </c>
       <c r="I76"/>
       <c r="J76" t="n">
@@ -4151,10 +4151,10 @@
       <c r="E77"/>
       <c r="F77"/>
       <c r="G77" t="n">
-        <v>0.0000967882000933601</v>
+        <v>0.0000948789136557377</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00767199540863344</v>
+        <v>0.00758009648366493</v>
       </c>
       <c r="I77"/>
       <c r="J77" t="n">
@@ -4177,10 +4177,10 @@
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.0000947024962371123</v>
+        <v>0.0000937679823806852</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00752717159420323</v>
+        <v>0.00748359730946349</v>
       </c>
       <c r="I78"/>
       <c r="J78" t="n">
@@ -4203,10 +4203,10 @@
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79" t="n">
-        <v>2966.40274876976</v>
+        <v>988.789718931182</v>
       </c>
       <c r="H79" t="n">
-        <v>11.7779169965903</v>
+        <v>6.80298988814467</v>
       </c>
       <c r="I79"/>
       <c r="J79" t="n">
@@ -4229,10 +4229,10 @@
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80" t="n">
-        <v>0.0000947667085053843</v>
+        <v>0.0000940730250249333</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00753321373753232</v>
+        <v>0.00750398603015387</v>
       </c>
       <c r="I80"/>
       <c r="J80" t="n">
@@ -4255,10 +4255,10 @@
       <c r="E81"/>
       <c r="F81"/>
       <c r="G81" t="n">
-        <v>0.0000968952330080658</v>
+        <v>0.0000950396415045482</v>
       </c>
       <c r="H81" t="n">
-        <v>0.00765938366312265</v>
+        <v>0.00757004383527859</v>
       </c>
       <c r="I81"/>
       <c r="J81" t="n">
@@ -4281,10 +4281,10 @@
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.000215213144063283</v>
+        <v>0.000206902778904061</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0122635543626808</v>
+        <v>0.0119538641845173</v>
       </c>
       <c r="I82"/>
       <c r="J82" t="n">
@@ -4307,10 +4307,10 @@
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.000215776919114253</v>
+        <v>0.000213787473182652</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0122625349663978</v>
+        <v>0.0121913586574552</v>
       </c>
       <c r="I83"/>
       <c r="J83" t="n">
@@ -4333,10 +4333,10 @@
       <c r="E84"/>
       <c r="F84"/>
       <c r="G84" t="n">
-        <v>0.000215189343434735</v>
+        <v>0.000213071141908161</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0121732367471544</v>
+        <v>0.0121255161008157</v>
       </c>
       <c r="I84"/>
       <c r="J84" t="n">
@@ -4359,10 +4359,10 @@
       <c r="E85"/>
       <c r="F85"/>
       <c r="G85" t="n">
-        <v>0.000222816099380324</v>
+        <v>0.000216909117864017</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0124931074264007</v>
+        <v>0.0123069544453788</v>
       </c>
       <c r="I85"/>
       <c r="J85" t="n">
@@ -4385,10 +4385,10 @@
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.00355333880973882</v>
+        <v>0.00356709287518203</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0490502654152361</v>
+        <v>0.0492007849855877</v>
       </c>
       <c r="I86"/>
       <c r="J86" t="n">
@@ -4411,10 +4411,10 @@
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.0036326256891661</v>
+        <v>0.00361467683447758</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0498238256356843</v>
+        <v>0.0496728683521829</v>
       </c>
       <c r="I87"/>
       <c r="J87" t="n">
@@ -4437,10 +4437,10 @@
       <c r="E88"/>
       <c r="F88"/>
       <c r="G88" t="n">
-        <v>0.00359856325615095</v>
+        <v>0.00359154994380956</v>
       </c>
       <c r="H88" t="n">
-        <v>0.048998618294352</v>
+        <v>0.0491321379267671</v>
       </c>
       <c r="I88"/>
       <c r="J88" t="n">
@@ -4463,10 +4463,10 @@
       <c r="E89"/>
       <c r="F89"/>
       <c r="G89" t="n">
-        <v>0.00357147069230454</v>
+        <v>0.00357367400960657</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0495086761623069</v>
+        <v>0.0494550331160037</v>
       </c>
       <c r="I89"/>
       <c r="J89" t="n">
@@ -4489,10 +4489,10 @@
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00351002813413657</v>
+        <v>0.00347343413176563</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0457862725121527</v>
+        <v>0.0455677016188068</v>
       </c>
       <c r="I90"/>
       <c r="J90" t="n">
@@ -4515,10 +4515,10 @@
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.00350206977748975</v>
+        <v>0.00349043678651564</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0456053441023868</v>
+        <v>0.0456121639974128</v>
       </c>
       <c r="I91"/>
       <c r="J91" t="n">
@@ -4541,10 +4541,10 @@
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92" t="n">
-        <v>0.00344622358389272</v>
+        <v>0.0034556929213981</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0449376122465321</v>
+        <v>0.0452045464056649</v>
       </c>
       <c r="I92"/>
       <c r="J92" t="n">
@@ -4567,10 +4567,10 @@
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93" t="n">
-        <v>0.00353214647848182</v>
+        <v>0.00350824349449575</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0454523882347959</v>
+        <v>0.0455409538236593</v>
       </c>
       <c r="I93"/>
       <c r="J93" t="n">
@@ -4593,10 +4593,10 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.001268876203963</v>
+        <v>0.00126524291543443</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0254921997525729</v>
+        <v>0.0253375134652221</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -4619,10 +4619,10 @@
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95" t="n">
-        <v>0.00128674883540449</v>
+        <v>0.00127711952409654</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0256251225406456</v>
+        <v>0.0254814280930115</v>
       </c>
       <c r="I95"/>
       <c r="J95" t="n">
@@ -4645,10 +4645,10 @@
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96" t="n">
-        <v>0.00127848349183079</v>
+        <v>0.00126738530947306</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0254672602398019</v>
+        <v>0.0253654245953917</v>
       </c>
       <c r="I96"/>
       <c r="J96" t="n">
@@ -4671,10 +4671,10 @@
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00127627829485169</v>
+        <v>0.00126866914403079</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0255048263898938</v>
+        <v>0.0253719531646511</v>
       </c>
       <c r="I97"/>
       <c r="J97" t="n">
@@ -4697,10 +4697,10 @@
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00142343424309353</v>
+        <v>0.00139699309507506</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0260283153464511</v>
+        <v>0.0255469344955213</v>
       </c>
       <c r="I98"/>
       <c r="J98" t="n">
@@ -4723,10 +4723,10 @@
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99" t="n">
-        <v>0.00140183713206107</v>
+        <v>0.00139789893744094</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0255803532216804</v>
+        <v>0.0255180572916646</v>
       </c>
       <c r="I99"/>
       <c r="J99" t="n">
@@ -4749,10 +4749,10 @@
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.00140800188381269</v>
+        <v>0.00139856072290935</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0256471092403121</v>
+        <v>0.0255102068619735</v>
       </c>
       <c r="I100"/>
       <c r="J100" t="n">
@@ -4775,10 +4775,10 @@
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101" t="n">
-        <v>0.00140396794078537</v>
+        <v>0.0013970158963728</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0254890404413901</v>
+        <v>0.0254483740475441</v>
       </c>
       <c r="I101"/>
       <c r="J101" t="n">
@@ -4801,10 +4801,10 @@
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.00120512778618731</v>
+        <v>0.00118888995517411</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0253515510624697</v>
+        <v>0.0251469497211458</v>
       </c>
       <c r="I102"/>
       <c r="J102" t="n">
@@ -4827,10 +4827,10 @@
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.00119864227673681</v>
+        <v>0.0011922663691207</v>
       </c>
       <c r="H103" t="n">
-        <v>0.025308447452098</v>
+        <v>0.0252102347187435</v>
       </c>
       <c r="I103"/>
       <c r="J103" t="n">
@@ -4853,10 +4853,10 @@
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104" t="n">
-        <v>0.00120392844915105</v>
+        <v>0.00119073380143728</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0252439516559322</v>
+        <v>0.0251662408435151</v>
       </c>
       <c r="I104"/>
       <c r="J104" t="n">
@@ -4879,10 +4879,10 @@
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105" t="n">
-        <v>0.0012096688164163</v>
+        <v>0.00119554228152484</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0254208570953128</v>
+        <v>0.0252196956628167</v>
       </c>
       <c r="I105"/>
       <c r="J105" t="n">
@@ -4905,10 +4905,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.00120474120348163</v>
+        <v>0.00119266728566019</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0254779531089513</v>
+        <v>0.0251880273764967</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -4931,10 +4931,10 @@
       <c r="E107"/>
       <c r="F107"/>
       <c r="G107" t="n">
-        <v>0.00120637412162947</v>
+        <v>0.00119907927963404</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0253746506974337</v>
+        <v>0.0252650970235112</v>
       </c>
       <c r="I107"/>
       <c r="J107" t="n">
@@ -4957,10 +4957,10 @@
       <c r="E108"/>
       <c r="F108"/>
       <c r="G108" t="n">
-        <v>0.00119841846512677</v>
+        <v>0.00119286974617785</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0251989531920394</v>
+        <v>0.0251750369276858</v>
       </c>
       <c r="I108"/>
       <c r="J108" t="n">
@@ -4983,10 +4983,10 @@
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.00119513113049113</v>
+        <v>0.00119224520621769</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0253350339873985</v>
+        <v>0.0251990886329344</v>
       </c>
       <c r="I109"/>
       <c r="J109" t="n">
@@ -5009,10 +5009,10 @@
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.00106375242667207</v>
+        <v>0.00105190919406783</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0228340268892552</v>
+        <v>0.0226437487805914</v>
       </c>
       <c r="I110"/>
       <c r="J110" t="n">
@@ -5035,10 +5035,10 @@
       <c r="E111"/>
       <c r="F111"/>
       <c r="G111" t="n">
-        <v>0.00105103955356946</v>
+        <v>0.00104880333000164</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0225654393514319</v>
+        <v>0.0225643052973476</v>
       </c>
       <c r="I111"/>
       <c r="J111" t="n">
@@ -5061,10 +5061,10 @@
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.00106439030684942</v>
+        <v>0.00105118426391401</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0228415947807389</v>
+        <v>0.0226355189916163</v>
       </c>
       <c r="I112"/>
       <c r="J112" t="n">
@@ -5087,10 +5087,10 @@
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.0010847173552226</v>
+        <v>0.00105929170646389</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0231120090588809</v>
+        <v>0.0227374738466541</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5113,10 +5113,10 @@
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.00168237934474001</v>
+        <v>0.00166657826440175</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0309047033061323</v>
+        <v>0.0306961695852543</v>
       </c>
       <c r="I114"/>
       <c r="J114" t="n">
@@ -5139,10 +5139,10 @@
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115" t="n">
-        <v>0.0016828843805046</v>
+        <v>0.00167355487426778</v>
       </c>
       <c r="H115" t="n">
-        <v>0.030929933453631</v>
+        <v>0.0308007466693071</v>
       </c>
       <c r="I115"/>
       <c r="J115" t="n">
@@ -5165,10 +5165,10 @@
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.00167372980681774</v>
+        <v>0.0016679229279071</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0306830489549518</v>
+        <v>0.0306488592878618</v>
       </c>
       <c r="I116"/>
       <c r="J116" t="n">
@@ -5191,10 +5191,10 @@
       <c r="E117"/>
       <c r="F117"/>
       <c r="G117" t="n">
-        <v>0.0016659878623652</v>
+        <v>0.00166336609497293</v>
       </c>
       <c r="H117" t="n">
-        <v>0.030621867569401</v>
+        <v>0.0306152304432491</v>
       </c>
       <c r="I117"/>
       <c r="J117" t="n">
@@ -5217,10 +5217,10 @@
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.0021931884067139</v>
+        <v>0.0022097436548237</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0349113861158832</v>
+        <v>0.035050748939306</v>
       </c>
       <c r="I118"/>
       <c r="J118" t="n">
@@ -5243,10 +5243,10 @@
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00221774653023235</v>
+        <v>0.00221710847752892</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0351438426701978</v>
+        <v>0.0350879420045787</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5269,10 +5269,10 @@
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>0.00225225656568711</v>
+        <v>0.00223248760201288</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0354031100924943</v>
+        <v>0.0352798684248624</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5295,10 +5295,10 @@
       <c r="E121"/>
       <c r="F121"/>
       <c r="G121" t="n">
-        <v>0.00219449851988753</v>
+        <v>0.00220302886527406</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0349219330899769</v>
+        <v>0.0349619618279106</v>
       </c>
       <c r="I121"/>
       <c r="J121" t="n">
@@ -5321,10 +5321,10 @@
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.000442204818182434</v>
+        <v>0.00044022273608923</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0138844903141728</v>
+        <v>0.0138252451802776</v>
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
@@ -5347,10 +5347,10 @@
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000441198311985781</v>
+        <v>0.000439897445163341</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0139425845415084</v>
+        <v>0.0138770372669694</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5373,10 +5373,10 @@
       <c r="E124"/>
       <c r="F124"/>
       <c r="G124" t="n">
-        <v>0.000443221877780747</v>
+        <v>0.000440413564673099</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0139163799674648</v>
+        <v>0.0138447314947511</v>
       </c>
       <c r="I124"/>
       <c r="J124" t="n">
@@ -5399,10 +5399,10 @@
       <c r="E125"/>
       <c r="F125"/>
       <c r="G125" t="n">
-        <v>0.000439126525731664</v>
+        <v>0.000438793509147836</v>
       </c>
       <c r="H125" t="n">
-        <v>0.013802860323273</v>
+        <v>0.0138041252317179</v>
       </c>
       <c r="I125"/>
       <c r="J125" t="n">
@@ -5425,10 +5425,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.00056588793156236</v>
+        <v>0.000561507988559075</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0141206707519765</v>
+        <v>0.0140052168487452</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5451,10 +5451,10 @@
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127" t="n">
-        <v>0.000564501728290724</v>
+        <v>0.000561454361354745</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0140885573093786</v>
+        <v>0.014025753891243</v>
       </c>
       <c r="I127"/>
       <c r="J127" t="n">
@@ -5477,10 +5477,10 @@
       <c r="E128"/>
       <c r="F128"/>
       <c r="G128" t="n">
-        <v>0.000559889349455259</v>
+        <v>0.000557896256776269</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0140126471544071</v>
+        <v>0.0139729587331149</v>
       </c>
       <c r="I128"/>
       <c r="J128" t="n">
@@ -5503,10 +5503,10 @@
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.000557315045636113</v>
+        <v>0.000556402491690548</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0140478434611803</v>
+        <v>0.013994148780252</v>
       </c>
       <c r="I129"/>
       <c r="J129" t="n">
@@ -5529,10 +5529,10 @@
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.00037570798509782</v>
+        <v>0.000372328070510838</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0137769551008594</v>
+        <v>0.013628839874028</v>
       </c>
       <c r="I130"/>
       <c r="J130" t="n">
@@ -5555,10 +5555,10 @@
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131" t="n">
-        <v>0.000374501770330167</v>
+        <v>0.000372776889516162</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0136719564122313</v>
+        <v>0.0136249609336273</v>
       </c>
       <c r="I131"/>
       <c r="J131" t="n">
@@ -5581,10 +5581,10 @@
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000376540978136047</v>
+        <v>0.000373195497273434</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0136731017353717</v>
+        <v>0.0136120071781038</v>
       </c>
       <c r="I132"/>
       <c r="J132" t="n">
@@ -5607,10 +5607,10 @@
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133" t="n">
-        <v>0.000375418732465198</v>
+        <v>0.000373069837619335</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0136815436822647</v>
+        <v>0.0136225126161665</v>
       </c>
       <c r="I133"/>
       <c r="J133" t="n">
@@ -5633,10 +5633,10 @@
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.000376544975245059</v>
+        <v>0.000372794714475328</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0136760526163706</v>
+        <v>0.0136085662090615</v>
       </c>
       <c r="I134"/>
       <c r="J134" t="n">
@@ -5659,10 +5659,10 @@
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000379160724282207</v>
+        <v>0.000375706967440677</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0137105584613234</v>
+        <v>0.0136523246886673</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
@@ -5685,10 +5685,10 @@
       <c r="E136"/>
       <c r="F136"/>
       <c r="G136" t="n">
-        <v>0.000372891378291104</v>
+        <v>0.000371812999795075</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0137115917182896</v>
+        <v>0.0136239618090333</v>
       </c>
       <c r="I136"/>
       <c r="J136" t="n">
@@ -5711,10 +5711,10 @@
       <c r="E137"/>
       <c r="F137"/>
       <c r="G137" t="n">
-        <v>0.000375203785674494</v>
+        <v>0.000373071949175921</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0136965521693395</v>
+        <v>0.013642436151581</v>
       </c>
       <c r="I137"/>
       <c r="J137" t="n">
@@ -5737,10 +5737,10 @@
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138" t="n">
-        <v>0.000428261207343361</v>
+        <v>0.000426298441099335</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0144552944390549</v>
+        <v>0.0143954509505574</v>
       </c>
       <c r="I138"/>
       <c r="J138" t="n">
@@ -5763,10 +5763,10 @@
       <c r="E139"/>
       <c r="F139"/>
       <c r="G139" t="n">
-        <v>0.000430146913970015</v>
+        <v>0.000426961747789713</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0145454240249258</v>
+        <v>0.0144382224623116</v>
       </c>
       <c r="I139"/>
       <c r="J139" t="n">
@@ -5789,10 +5789,10 @@
       <c r="E140"/>
       <c r="F140"/>
       <c r="G140" t="n">
-        <v>0.000428161676723352</v>
+        <v>0.00042556844247673</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0144861949155819</v>
+        <v>0.0143859614426913</v>
       </c>
       <c r="I140"/>
       <c r="J140" t="n">
@@ -5815,10 +5815,10 @@
       <c r="E141"/>
       <c r="F141"/>
       <c r="G141" t="n">
-        <v>0.000428434834322226</v>
+        <v>0.000426453714080303</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0144624277251371</v>
+        <v>0.0143987429518154</v>
       </c>
       <c r="I141"/>
       <c r="J141" t="n">
@@ -5841,10 +5841,10 @@
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142" t="n">
-        <v>0.00269327101544228</v>
+        <v>0.00266189274448004</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0395890514698644</v>
+        <v>0.0395332494639327</v>
       </c>
       <c r="I142"/>
       <c r="J142" t="n">
@@ -5867,10 +5867,10 @@
       <c r="E143"/>
       <c r="F143"/>
       <c r="G143" t="n">
-        <v>0.00264517170430861</v>
+        <v>0.00264407450488645</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0395602202298087</v>
+        <v>0.0395308620255686</v>
       </c>
       <c r="I143"/>
       <c r="J143" t="n">
@@ -5893,10 +5893,10 @@
       <c r="E144"/>
       <c r="F144"/>
       <c r="G144" t="n">
-        <v>0.00263577327697478</v>
+        <v>0.00264094073260641</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0395022019424421</v>
+        <v>0.0395708532395442</v>
       </c>
       <c r="I144"/>
       <c r="J144" t="n">
@@ -5919,10 +5919,10 @@
       <c r="E145"/>
       <c r="F145"/>
       <c r="G145" t="n">
-        <v>0.00265436017671846</v>
+        <v>0.00264900354608587</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0398647492300283</v>
+        <v>0.0397517171495199</v>
       </c>
       <c r="I145"/>
       <c r="J145" t="n">
@@ -5945,10 +5945,10 @@
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146" t="n">
-        <v>0.00110502542008869</v>
+        <v>0.00109660996556027</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0248905137807538</v>
+        <v>0.0250020115801956</v>
       </c>
       <c r="I146"/>
       <c r="J146" t="n">
@@ -5971,10 +5971,10 @@
       <c r="E147"/>
       <c r="F147"/>
       <c r="G147" t="n">
-        <v>0.00109140662737337</v>
+        <v>0.00109240580509464</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0252103636419588</v>
+        <v>0.0251838339596461</v>
       </c>
       <c r="I147"/>
       <c r="J147" t="n">
@@ -5997,10 +5997,10 @@
       <c r="E148"/>
       <c r="F148"/>
       <c r="G148" t="n">
-        <v>0.00112225056637693</v>
+        <v>0.00110657037146525</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0253354614189151</v>
+        <v>0.025247114266781</v>
       </c>
       <c r="I148"/>
       <c r="J148" t="n">
@@ -6023,10 +6023,10 @@
       <c r="E149"/>
       <c r="F149"/>
       <c r="G149" t="n">
-        <v>0.00108554652467177</v>
+        <v>0.00109186411368117</v>
       </c>
       <c r="H149" t="n">
-        <v>0.024954477939671</v>
+        <v>0.0250789892918997</v>
       </c>
       <c r="I149"/>
       <c r="J149" t="n">
@@ -6049,10 +6049,10 @@
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150" t="n">
-        <v>0.000590162052551526</v>
+        <v>0.00058163298147872</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0167012462256698</v>
+        <v>0.016436389149377</v>
       </c>
       <c r="I150"/>
       <c r="J150" t="n">
@@ -6075,10 +6075,10 @@
       <c r="E151"/>
       <c r="F151"/>
       <c r="G151" t="n">
-        <v>0.000585679687226191</v>
+        <v>0.000581864447813023</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0164924991748802</v>
+        <v>0.016404261896359</v>
       </c>
       <c r="I151"/>
       <c r="J151" t="n">
@@ -6101,10 +6101,10 @@
       <c r="E152"/>
       <c r="F152"/>
       <c r="G152" t="n">
-        <v>0.000593375413158922</v>
+        <v>0.000584543883198312</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0165050313918445</v>
+        <v>0.0163803862295117</v>
       </c>
       <c r="I152"/>
       <c r="J152" t="n">
@@ -6127,10 +6127,10 @@
       <c r="E153"/>
       <c r="F153"/>
       <c r="G153" t="n">
-        <v>0.000587886560348952</v>
+        <v>0.000581818645006164</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0165764469856095</v>
+        <v>0.0164240756376304</v>
       </c>
       <c r="I153"/>
       <c r="J153" t="n">
@@ -6153,10 +6153,10 @@
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154" t="n">
-        <v>0.00071806909945495</v>
+        <v>0.000704502166220318</v>
       </c>
       <c r="H154" t="n">
-        <v>0.016816689102073</v>
+        <v>0.0165653600492239</v>
       </c>
       <c r="I154"/>
       <c r="J154" t="n">
@@ -6179,10 +6179,10 @@
       <c r="E155"/>
       <c r="F155"/>
       <c r="G155" t="n">
-        <v>0.00070474717611004</v>
+        <v>0.000700754734122636</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0165941330286568</v>
+        <v>0.0165200377477486</v>
       </c>
       <c r="I155"/>
       <c r="J155" t="n">
@@ -6205,10 +6205,10 @@
       <c r="E156"/>
       <c r="F156"/>
       <c r="G156" t="n">
-        <v>0.000710943499766929</v>
+        <v>0.000702709578892673</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0166384316338683</v>
+        <v>0.0165307045727206</v>
       </c>
       <c r="I156"/>
       <c r="J156" t="n">
@@ -6231,10 +6231,10 @@
       <c r="E157"/>
       <c r="F157"/>
       <c r="G157" t="n">
-        <v>0.000713633652667348</v>
+        <v>0.000704768889545307</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0166118443532897</v>
+        <v>0.0165235072709543</v>
       </c>
       <c r="I157"/>
       <c r="J157" t="n">
@@ -6257,10 +6257,10 @@
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158" t="n">
-        <v>0.000522885073455123</v>
+        <v>0.000514879860652079</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0163866432140927</v>
+        <v>0.016186575928726</v>
       </c>
       <c r="I158"/>
       <c r="J158" t="n">
@@ -6283,10 +6283,10 @@
       <c r="E159"/>
       <c r="F159"/>
       <c r="G159" t="n">
-        <v>0.000523336973189577</v>
+        <v>0.0005174780349884</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0163046106258134</v>
+        <v>0.0161996287580614</v>
       </c>
       <c r="I159"/>
       <c r="J159" t="n">
@@ -6309,10 +6309,10 @@
       <c r="E160"/>
       <c r="F160"/>
       <c r="G160" t="n">
-        <v>0.000520409368057618</v>
+        <v>0.000515251300566603</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0162894454532659</v>
+        <v>0.0161738179102516</v>
       </c>
       <c r="I160"/>
       <c r="J160" t="n">
@@ -6335,10 +6335,10 @@
       <c r="E161"/>
       <c r="F161"/>
       <c r="G161" t="n">
-        <v>0.000524545154866656</v>
+        <v>0.00051515569079851</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0164268455881536</v>
+        <v>0.0162050688203587</v>
       </c>
       <c r="I161"/>
       <c r="J161" t="n">
@@ -6361,10 +6361,10 @@
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162" t="n">
-        <v>0.000529009605686526</v>
+        <v>0.000515975483538925</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0165621642674863</v>
+        <v>0.0162143467350227</v>
       </c>
       <c r="I162"/>
       <c r="J162" t="n">
@@ -6387,10 +6387,10 @@
       <c r="E163"/>
       <c r="F163"/>
       <c r="G163" t="n">
-        <v>0.000519401035452289</v>
+        <v>0.000515249399204647</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0162834954876742</v>
+        <v>0.0161837631667627</v>
       </c>
       <c r="I163"/>
       <c r="J163" t="n">
@@ -6413,10 +6413,10 @@
       <c r="E164"/>
       <c r="F164"/>
       <c r="G164" t="n">
-        <v>0.000526390407050498</v>
+        <v>0.000517974044082233</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0164709546815536</v>
+        <v>0.0162550329107774</v>
       </c>
       <c r="I164"/>
       <c r="J164" t="n">
@@ -6439,10 +6439,10 @@
       <c r="E165"/>
       <c r="F165"/>
       <c r="G165" t="n">
-        <v>0.000522307774557241</v>
+        <v>0.000514517663048894</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0163211730449248</v>
+        <v>0.0161573997755607</v>
       </c>
       <c r="I165"/>
       <c r="J165" t="n">
@@ -6465,10 +6465,10 @@
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166" t="n">
-        <v>0.000484383547652276</v>
+        <v>0.000472414088593065</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0161376467990644</v>
+        <v>0.0158472107195783</v>
       </c>
       <c r="I166"/>
       <c r="J166" t="n">
@@ -6491,10 +6491,10 @@
       <c r="E167"/>
       <c r="F167"/>
       <c r="G167" t="n">
-        <v>0.000484190546227605</v>
+        <v>0.000474557244125652</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0161419199853566</v>
+        <v>0.0159164374511597</v>
       </c>
       <c r="I167"/>
       <c r="J167" t="n">
@@ -6517,10 +6517,10 @@
       <c r="E168"/>
       <c r="F168"/>
       <c r="G168" t="n">
-        <v>0.000487098319254647</v>
+        <v>0.000473096321388058</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0161812580899703</v>
+        <v>0.0158568789536106</v>
       </c>
       <c r="I168"/>
       <c r="J168" t="n">
@@ -6543,10 +6543,10 @@
       <c r="E169"/>
       <c r="F169"/>
       <c r="G169" t="n">
-        <v>0.00052394728522948</v>
+        <v>0.000498501614556952</v>
       </c>
       <c r="H169" t="n">
-        <v>0.01685309614394</v>
+        <v>0.0163844868958091</v>
       </c>
       <c r="I169"/>
       <c r="J169" t="n">
@@ -6598,7 +6598,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00120245939278837</v>
+        <v>0.00119809867253835</v>
       </c>
       <c r="F2" t="e">
         <v>#NUM!</v>
@@ -6618,7 +6618,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00120113676050736</v>
+        <v>0.001199111891896</v>
       </c>
       <c r="F3" t="e">
         <v>#NUM!</v>
@@ -6638,7 +6638,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0012016444910941</v>
+        <v>0.00119954088899831</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -6658,7 +6658,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00120058501320724</v>
+        <v>0.0011959589624099</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -6678,7 +6678,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00147055407044678</v>
+        <v>0.00146957614366458</v>
       </c>
       <c r="F6" t="e">
         <v>#NUM!</v>
@@ -6698,7 +6698,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00148071051483025</v>
+        <v>0.00147559748199105</v>
       </c>
       <c r="F7" t="e">
         <v>#NUM!</v>
@@ -6718,7 +6718,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00146955497467046</v>
+        <v>0.00146812549072999</v>
       </c>
       <c r="F8" t="e">
         <v>#NUM!</v>
@@ -6738,7 +6738,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00147423639870002</v>
+        <v>0.0014690332222688</v>
       </c>
       <c r="F9" t="e">
         <v>#NUM!</v>
@@ -6758,7 +6758,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000406861187073468</v>
+        <v>0.000402160896320226</v>
       </c>
       <c r="F10" t="e">
         <v>#NUM!</v>
@@ -6778,7 +6778,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00040173694771899</v>
+        <v>0.000404571293534656</v>
       </c>
       <c r="F11" t="e">
         <v>#NUM!</v>
@@ -6798,7 +6798,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000418635864864461</v>
+        <v>0.000408737426099211</v>
       </c>
       <c r="F12" t="e">
         <v>#NUM!</v>
@@ -6818,7 +6818,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000406885553569409</v>
+        <v>0.000401469279908919</v>
       </c>
       <c r="F13" t="e">
         <v>#NUM!</v>
@@ -6838,7 +6838,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000445663197563484</v>
+        <v>0.000441462183266898</v>
       </c>
       <c r="F14" t="e">
         <v>#NUM!</v>
@@ -6858,7 +6858,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E15" t="n">
-        <v>606.878484301023</v>
+        <v>202.290892146031</v>
       </c>
       <c r="F15" t="e">
         <v>#NUM!</v>
@@ -6878,7 +6878,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000444645048646826</v>
+        <v>0.000441530167018193</v>
       </c>
       <c r="F16" t="e">
         <v>#NUM!</v>
@@ -6898,7 +6898,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000443392266414686</v>
+        <v>0.000440679610808023</v>
       </c>
       <c r="F17" t="e">
         <v>#NUM!</v>
@@ -6918,7 +6918,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000566275748003142</v>
+        <v>0.0005625495594148</v>
       </c>
       <c r="F18" t="e">
         <v>#NUM!</v>
@@ -6938,7 +6938,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E19" t="n">
-        <v>652.793714631928</v>
+        <v>217.599485462393</v>
       </c>
       <c r="F19" t="e">
         <v>#NUM!</v>
@@ -6958,7 +6958,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000565438386148057</v>
+        <v>0.000562132201910548</v>
       </c>
       <c r="F20" t="e">
         <v>#NUM!</v>
@@ -6978,7 +6978,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000570821737902311</v>
+        <v>0.000563038312353689</v>
       </c>
       <c r="F21" t="e">
         <v>#NUM!</v>
@@ -6998,7 +6998,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000375688430008086</v>
+        <v>0.000371729895957673</v>
       </c>
       <c r="F22" t="e">
         <v>#NUM!</v>
@@ -7018,7 +7018,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E23" t="n">
-        <v>654.540156886194</v>
+        <v>218.176586542214</v>
       </c>
       <c r="F23" t="e">
         <v>#NUM!</v>
@@ -7038,7 +7038,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000377704768918216</v>
+        <v>0.00037277928184426</v>
       </c>
       <c r="F24" t="e">
         <v>#NUM!</v>
@@ -7058,7 +7058,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000376137018646083</v>
+        <v>0.000371235313507152</v>
       </c>
       <c r="F25" t="e">
         <v>#NUM!</v>
@@ -7078,7 +7078,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000375190547876761</v>
+        <v>0.000372377998551685</v>
       </c>
       <c r="F26" t="e">
         <v>#NUM!</v>
@@ -7098,7 +7098,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E27" t="n">
-        <v>494.400818659229</v>
+        <v>164.798644452561</v>
       </c>
       <c r="F27" t="e">
         <v>#NUM!</v>
@@ -7118,7 +7118,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000374966735105919</v>
+        <v>0.000372188689967515</v>
       </c>
       <c r="F28" t="e">
         <v>#NUM!</v>
@@ -7138,7 +7138,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000377197942041899</v>
+        <v>0.000372127472085542</v>
       </c>
       <c r="F29" t="e">
         <v>#NUM!</v>

--- a/results/chronological/consolidated/Stress_Testing.xlsx
+++ b/results/chronological/consolidated/Stress_Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">Asset</t>
   </si>
@@ -107,13 +107,31 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
   </si>
   <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
     <t xml:space="preserve">MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
   </si>
   <si>
     <t xml:space="preserve">AMZN</t>
@@ -1036,13 +1054,13 @@
         <v>143</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0015892701912177</v>
+        <v>-0.00168768228375898</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0227080418990508</v>
+        <v>0.0142640687995322</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0171284654480273</v>
+        <v>-0.287783695478577</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>39692</v>
@@ -1070,13 +1088,13 @@
         <v>59</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00332104828859296</v>
+        <v>-0.000449403652009031</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0158928496727706</v>
+        <v>0.00939792799821303</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00551177711009121</v>
+        <v>-0.115076533623953</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>43862</v>
@@ -1104,21 +1122,21 @@
         <v>4515</v>
       </c>
       <c r="F18" t="n">
-        <v>0.000156399423326306</v>
+        <v>-0.000163252538452272</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0117581471857289</v>
+        <v>0.00760528643800944</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-0.928245353333001</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L18" t="n">
-        <v>8.41718729183222</v>
+        <v>23.1703189354394</v>
       </c>
     </row>
     <row r="19">
@@ -1138,21 +1156,21 @@
         <v>4515</v>
       </c>
       <c r="F19" t="n">
-        <v>0.000112102634843471</v>
+        <v>-0.000207549326935107</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0131969077962237</v>
+        <v>0.00965048327462749</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-1.128245353333</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L19" t="n">
-        <v>21.6834252553647</v>
+        <v>56.293009146425</v>
       </c>
     </row>
     <row r="20">
@@ -1172,21 +1190,21 @@
         <v>4515</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00022172692270406</v>
+        <v>-0.0000964639149448077</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0108460828307998</v>
+        <v>0.00617474445800522</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-0.626694718196798</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00740551000706102</v>
+        <v>0.00218274966114383</v>
       </c>
     </row>
     <row r="21">
@@ -1206,21 +1224,21 @@
         <v>4515</v>
       </c>
       <c r="F21" t="n">
-        <v>0.000220609239357562</v>
+        <v>-0.0000961204741615955</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0108474058914536</v>
+        <v>0.00617496547555279</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-0.625144083060595</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0196049247992935</v>
+        <v>0.00576220745622006</v>
       </c>
     </row>
     <row r="22">
@@ -1240,21 +1258,21 @@
         <v>4515</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.00177937023337358</v>
+        <v>-0.00209902219515216</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0115666353334669</v>
+        <v>0.00732567829467671</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.30653212324354</v>
+        <v>-9.668245353333</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L22" t="n">
-        <v>6.65133285683264</v>
+        <v>18.6419656022739</v>
       </c>
     </row>
     <row r="23">
@@ -1274,13 +1292,13 @@
         <v>143</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.00173692405004033</v>
+        <v>0.0015892701912177</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0600037655773047</v>
+        <v>0.0227080418990508</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.761914216320698</v>
+        <v>0.0171284654480273</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>39692</v>
@@ -1308,13 +1326,13 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00360437391869047</v>
+        <v>0.00332104828859296</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0593766543117209</v>
+        <v>0.0158928496727706</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.184901076210231</v>
+        <v>-0.00551177711009121</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>43862</v>
@@ -1342,21 +1360,21 @@
         <v>4515</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00131551872274189</v>
+        <v>0.000156399423326306</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0319688553700037</v>
+        <v>0.0117581471857289</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24890533785161</v>
+        <v>8.41718729183222</v>
       </c>
     </row>
     <row r="26">
@@ -1376,21 +1394,21 @@
         <v>4515</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00127122193425906</v>
+        <v>0.000112102634843471</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0325708621645964</v>
+        <v>0.0131969077962237</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L26" t="n">
-        <v>3.15552752538385</v>
+        <v>21.6834252553647</v>
       </c>
     </row>
     <row r="27">
@@ -1410,21 +1428,21 @@
         <v>4515</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00137373208548086</v>
+        <v>0.00022172692270406</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0315894131475975</v>
+        <v>0.0108460828307998</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0471697982790727</v>
+        <v>0.00740551000706102</v>
       </c>
     </row>
     <row r="28">
@@ -1444,21 +1462,21 @@
         <v>4515</v>
       </c>
       <c r="F28" t="n">
-        <v>0.00136550026549557</v>
+        <v>0.000220609239357562</v>
       </c>
       <c r="G28" t="n">
-        <v>0.031613978907004</v>
+        <v>0.0108474058914536</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L28" t="n">
-        <v>0.124972278846902</v>
+        <v>0.0196049247992935</v>
       </c>
     </row>
     <row r="29">
@@ -1478,21 +1496,21 @@
         <v>4515</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000620250933957998</v>
+        <v>-0.00177937023337358</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0317960636689187</v>
+        <v>0.0115666353334669</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.15014392888351</v>
+        <v>-8.30653212324354</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L29" t="n">
-        <v>0.701654884751606</v>
+        <v>6.65133285683264</v>
       </c>
     </row>
     <row r="30">
@@ -1512,13 +1530,13 @@
         <v>143</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00267284478763177</v>
+        <v>-0.000145880188868083</v>
       </c>
       <c r="G30" t="n">
-        <v>0.040824434557733</v>
+        <v>0.0203172529977707</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.574935410071788</v>
+        <v>-0.0423297413962951</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>39692</v>
@@ -1546,13 +1564,13 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>0.000917551723869295</v>
+        <v>0.00243810149932368</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0474722084419535</v>
+        <v>0.0153982668526188</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.226041856388705</v>
+        <v>-0.0184549942125036</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>43862</v>
@@ -1580,21 +1598,21 @@
         <v>4515</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000614706511249609</v>
+        <v>0.0000885072892771528</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0183313329363614</v>
+        <v>0.0108917430605193</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L32" t="n">
-        <v>3.1603110105459</v>
+        <v>10.0541731254635</v>
       </c>
     </row>
     <row r="33">
@@ -1614,21 +1632,21 @@
         <v>4515</v>
       </c>
       <c r="F33" t="n">
-        <v>0.000570409722766774</v>
+        <v>0.0000442105007943178</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0192795724598222</v>
+        <v>0.0124325614718848</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L33" t="n">
-        <v>8.49656694415932</v>
+        <v>25.6231683962021</v>
       </c>
     </row>
     <row r="34">
@@ -1648,21 +1666,21 @@
         <v>4515</v>
       </c>
       <c r="F34" t="n">
-        <v>0.000680735893112593</v>
+        <v>0.000153734351268748</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0177698353056321</v>
+        <v>0.00989774521518639</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L34" t="n">
-        <v>0.000460582930751</v>
+        <v>0.0104537364947315</v>
       </c>
     </row>
     <row r="35">
@@ -1682,21 +1700,21 @@
         <v>4515</v>
       </c>
       <c r="F35" t="n">
-        <v>0.000680320092251323</v>
+        <v>0.00015251623053609</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0177699610778231</v>
+        <v>0.00989945645438926</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L35" t="n">
-        <v>0.00116837097772216</v>
+        <v>0.0277447260494053</v>
       </c>
     </row>
     <row r="36">
@@ -1716,21 +1734,21 @@
         <v>4515</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.00132106314545028</v>
+        <v>-0.00184726236742274</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0181294029721542</v>
+        <v>0.0106584328003218</v>
       </c>
       <c r="H36" t="n">
-        <v>-6.71300507381684</v>
+        <v>-8.55755385140675</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L36" t="n">
-        <v>2.02394204150917</v>
+        <v>7.69672054647357</v>
       </c>
     </row>
     <row r="37">
@@ -1750,13 +1768,13 @@
         <v>143</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.000668755477129844</v>
+        <v>0.000855059820899094</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0516086445981722</v>
+        <v>0.0185981575347543</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.835895917643519</v>
+        <v>-0.0116456112114705</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>39692</v>
@@ -1784,13 +1802,13 @@
         <v>59</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00353116230135348</v>
+        <v>0.00309357759226879</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0333217516794831</v>
+        <v>0.016123117157863</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.180723802802995</v>
+        <v>-0.016586722556549</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>43862</v>
@@ -1818,21 +1836,21 @@
         <v>4515</v>
       </c>
       <c r="F39" t="n">
-        <v>0.000906900416826371</v>
+        <v>0.00013473880658215</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0248429145425335</v>
+        <v>0.0106892234803598</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L39" t="n">
-        <v>1.66986953078478</v>
+        <v>10.6617579782835</v>
       </c>
     </row>
     <row r="40">
@@ -1852,21 +1870,21 @@
         <v>4515</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000862603628343536</v>
+        <v>0.0000904420180993153</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0255484513481067</v>
+        <v>0.0122628979548098</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L40" t="n">
-        <v>4.55728577371331</v>
+        <v>26.9534543908585</v>
       </c>
     </row>
     <row r="41">
@@ -1886,21 +1904,21 @@
         <v>4515</v>
       </c>
       <c r="F41" t="n">
-        <v>0.000973272412611131</v>
+        <v>0.000199524583687079</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0244348882628391</v>
+        <v>0.00966133064052844</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0000180103184551862</v>
+        <v>0.0203461977151037</v>
       </c>
     </row>
     <row r="42">
@@ -1920,21 +1938,21 @@
         <v>4515</v>
       </c>
       <c r="F42" t="n">
-        <v>0.000973199225671638</v>
+        <v>0.000197865178067756</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0244348936533635</v>
+        <v>0.00966458205115081</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0000400710923272578</v>
+        <v>0.0540069043175879</v>
       </c>
     </row>
     <row r="43">
@@ -1954,20 +1972,1448 @@
         <v>4515</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.00102886923987352</v>
+        <v>-0.00180103085011774</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0247051764559909</v>
+        <v>0.0104321377356863</v>
       </c>
       <c r="H43" t="n">
-        <v>-5.37325111779614</v>
+        <v>-8.3582040250076</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" t="n">
+        <v>0.00965936532696099</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8.00024000094873</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" t="n">
+        <v>143</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.00173692405004033</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0600037655773047</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.761914216320698</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K44"/>
+      <c r="L44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" t="n">
+        <v>59</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.00360437391869047</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0593766543117209</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.184901076210231</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K45"/>
+      <c r="L45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.00131551872274189</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0319688553700037</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.24890533785161</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.00127122193425906</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0325708621645964</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.15552752538385</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.00137373208548086</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0315894131475975</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0471697982790727</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.00136550026549557</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.031613978907004</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.124972278846902</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.000620250933957998</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0317960636689187</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-5.15014392888351</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.701654884751606</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="n">
+        <v>143</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.00267284478763177</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.040824434557733</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.574935410071788</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" t="n">
+        <v>59</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.000917551723869295</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0474722084419535</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.226041856388705</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.000614706511249609</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0183313329363614</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.1603110105459</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.000570409722766774</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0192795724598222</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L54" t="n">
+        <v>8.49656694415932</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.000680735893112593</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0177698353056321</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.000460582930751</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.000680320092251323</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0177699610778231</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.00116837097772216</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.00132106314545028</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0181294029721542</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-6.71300507381684</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.02394204150917</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" t="n">
+        <v>143</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.00265580653071438</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0258816893587691</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.443569210481156</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K58"/>
+      <c r="L58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" t="n">
+        <v>59</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.000831184477237403</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0386220238465276</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.243367763399513</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K59"/>
+      <c r="L59"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.000300132055082567</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0125883369741618</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6.93230749718272</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.000255835266599732</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.0139236567481399</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L61" t="n">
+        <v>18.2752533502508</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.000366747012457679</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0117722598048185</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.0000959594102858226</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.000366916787108538</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0117722821559868</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.000285822614863924</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.00163563760161732</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.0123771848355655</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-7.80277632641529</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L64" t="n">
+        <v>5.13866426540301</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="n">
+        <v>143</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-0.00634495437900691</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.0468467284865782</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-1.13936337177743</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K65"/>
+      <c r="L65"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" t="n">
+        <v>59</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.00189603239762552</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0437057350558554</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.357708936154046</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J66" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K66"/>
+      <c r="L66"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.000457592631473954</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0212385071530903</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.73586229719154</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.000413295842991119</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0221139210000307</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L68" t="n">
+        <v>6.9704535414842</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.000517870559328579</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0206855391368875</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.0610205318136251</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.000511703304458951</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0207064413049087</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.162129439330862</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-0.00147817702522594</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0210381640802695</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-7.59473794910994</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.76675377213622</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="n">
+        <v>143</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-0.00080850778442218</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0266591556099799</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.236676515342039</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K72"/>
+      <c r="L72"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" t="n">
+        <v>59</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0010890390904826</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.034586899612162</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-0.0956159934404295</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J73" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K73"/>
+      <c r="L73"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.000381042160821637</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0138335058163006</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5.45359157348412</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.000336745372338802</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0150455485323512</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L75" t="n">
+        <v>14.6930612527761</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.000448673172354497</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.013118783917016</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.0052264044052213</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.000449859001163105</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.0131199534103939</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.0141415180904541</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-0.00155472749587825</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.013650802977163</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-7.71426012896369</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L78" t="n">
+        <v>4.06083757217903</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="n">
+        <v>143</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-0.000668755477129844</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.0516086445981722</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.835895917643519</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K79"/>
+      <c r="L79"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" t="n">
+        <v>59</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.00353116230135348</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0333217516794831</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.180723802802995</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K80"/>
+      <c r="L80"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.000906900416826371</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0248429145425335</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" t="n">
         <v>0.0244348838620387</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L81" t="n">
+        <v>1.66986953078478</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.000862603628343536</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0255484513481067</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4.55728577371331</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.000973272412611131</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0244348882628391</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.0000180103184551862</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.000973199225671638</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0244348936533635</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.0000400710923272578</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-0.00102886923987352</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0247051764559909</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-5.37325111779614</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L85" t="n">
         <v>1.1061750711741</v>
       </c>
     </row>
@@ -1990,16 +3436,16 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -2010,13 +3456,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0287032721053359</v>
+        <v>0.0275044669296046</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.126414368878323</v>
+        <v>-0.133774763054744</v>
       </c>
       <c r="F2" t="e">
         <v>#NUM!</v>
@@ -2030,13 +3476,13 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0339078955736443</v>
+        <v>0.0296678688524375</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.436763186145276</v>
+        <v>-0.398495605213219</v>
       </c>
       <c r="F3" t="e">
         <v>#NUM!</v>
@@ -2050,16 +3496,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.016789867869449</v>
+        <v>0.0146851339950314</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.39673848505614</v>
+        <v>-7.83968404538109</v>
       </c>
       <c r="F4" t="n">
-        <v>8.06269664673822</v>
+        <v>7.80678013665365</v>
       </c>
     </row>
     <row r="5">
@@ -2070,16 +3516,16 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0170222126831937</v>
+        <v>0.014914989918467</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.497492666111511</v>
+        <v>-0.429493923980447</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6198221788595</v>
+        <v>10.2272453733501</v>
       </c>
     </row>
     <row r="6">
@@ -2090,16 +3536,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0183291187815318</v>
+        <v>0.0162836484725862</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.564159332778177</v>
+        <v>-0.479493923980447</v>
       </c>
       <c r="F6" t="n">
-        <v>25.8500082410277</v>
+        <v>25.3257041270136</v>
       </c>
     </row>
     <row r="7">
@@ -2110,16 +3556,16 @@
         <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0161457183757358</v>
+        <v>0.0140153927855714</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.399119991836927</v>
+        <v>-0.355178367248472</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0164924466629534</v>
+        <v>0.016523354956486</v>
       </c>
     </row>
     <row r="8">
@@ -2130,16 +3576,16 @@
         <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0161507920007042</v>
+        <v>0.0140202027380506</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.400747317562343</v>
+        <v>-0.355862810516496</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0438298885422007</v>
+        <v>0.0439208290927164</v>
       </c>
     </row>
   </sheetData>
@@ -2164,25 +3610,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -2196,7 +3642,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
@@ -2222,7 +3668,7 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E3"/>
       <c r="F3"/>
@@ -2248,7 +3694,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E4"/>
       <c r="F4"/>
@@ -2274,7 +3720,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
@@ -2300,7 +3746,7 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
@@ -2326,7 +3772,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -2352,7 +3798,7 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8"/>
       <c r="F8"/>
@@ -2378,7 +3824,7 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -2404,7 +3850,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -2430,7 +3876,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -2456,7 +3902,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -2482,7 +3928,7 @@
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -2508,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
@@ -2534,7 +3980,7 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -2560,7 +4006,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -2586,7 +4032,7 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -2612,7 +4058,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -2638,7 +4084,7 @@
         <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E19"/>
       <c r="F19"/>
@@ -2664,7 +4110,7 @@
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -2690,7 +4136,7 @@
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -2716,7 +4162,7 @@
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -2742,7 +4188,7 @@
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
@@ -2768,7 +4214,7 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
@@ -2794,7 +4240,7 @@
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
@@ -2820,7 +4266,7 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
@@ -2846,7 +4292,7 @@
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
@@ -2872,7 +4318,7 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
@@ -2898,7 +4344,7 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
@@ -2924,7 +4370,7 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E30"/>
       <c r="F30"/>
@@ -2950,7 +4396,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E31"/>
       <c r="F31"/>
@@ -2976,7 +4422,7 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E32"/>
       <c r="F32"/>
@@ -3002,7 +4448,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E33"/>
       <c r="F33"/>
@@ -3028,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E34"/>
       <c r="F34"/>
@@ -3054,7 +4500,7 @@
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E35"/>
       <c r="F35"/>
@@ -3080,7 +4526,7 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E36"/>
       <c r="F36"/>
@@ -3106,7 +4552,7 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E37"/>
       <c r="F37"/>
@@ -3132,7 +4578,7 @@
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E38"/>
       <c r="F38"/>
@@ -3158,7 +4604,7 @@
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E39"/>
       <c r="F39"/>
@@ -3184,7 +4630,7 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E40"/>
       <c r="F40"/>
@@ -3210,7 +4656,7 @@
         <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E41"/>
       <c r="F41"/>
@@ -3236,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E42"/>
       <c r="F42"/>
@@ -3262,7 +4708,7 @@
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E43"/>
       <c r="F43"/>
@@ -3288,7 +4734,7 @@
         <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E44"/>
       <c r="F44"/>
@@ -3314,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E45"/>
       <c r="F45"/>
@@ -3340,7 +4786,7 @@
         <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E46"/>
       <c r="F46"/>
@@ -3366,7 +4812,7 @@
         <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E47"/>
       <c r="F47"/>
@@ -3392,7 +4838,7 @@
         <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E48"/>
       <c r="F48"/>
@@ -3418,7 +4864,7 @@
         <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E49"/>
       <c r="F49"/>
@@ -3444,7 +4890,7 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E50"/>
       <c r="F50"/>
@@ -3470,7 +4916,7 @@
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E51"/>
       <c r="F51"/>
@@ -3496,7 +4942,7 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E52"/>
       <c r="F52"/>
@@ -3522,7 +4968,7 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E53"/>
       <c r="F53"/>
@@ -3548,7 +4994,7 @@
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E54"/>
       <c r="F54"/>
@@ -3574,7 +5020,7 @@
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E55"/>
       <c r="F55"/>
@@ -3600,7 +5046,7 @@
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E56"/>
       <c r="F56"/>
@@ -3626,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E57"/>
       <c r="F57"/>
@@ -3652,15 +5098,15 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000514871623255834</v>
+        <v>0.000204477549479361</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0163596111610899</v>
+        <v>0.0107627178522824</v>
       </c>
       <c r="I58"/>
       <c r="J58" t="n">
@@ -3678,15 +5124,15 @@
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.000515581267172311</v>
+        <v>0.000204794760109707</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0162963363513796</v>
+        <v>0.0108327762813775</v>
       </c>
       <c r="I59"/>
       <c r="J59" t="n">
@@ -3704,15 +5150,15 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60" t="n">
-        <v>0.000510962126007053</v>
+        <v>0.000203998056045439</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0163684629636016</v>
+        <v>0.0107727702070823</v>
       </c>
       <c r="I60"/>
       <c r="J60" t="n">
@@ -3730,15 +5176,15 @@
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61" t="n">
-        <v>0.000518031264874855</v>
+        <v>0.000206145114469156</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0164481290485706</v>
+        <v>0.0108343877162128</v>
       </c>
       <c r="I61"/>
       <c r="J61" t="n">
@@ -3756,15 +5202,15 @@
         <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.000260188711618463</v>
+        <v>0.0000853300212224403</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0121258593927602</v>
+        <v>0.00716451993225171</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -3782,15 +5228,15 @@
         <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63" t="n">
-        <v>0.000259065133200994</v>
+        <v>0.0000891594849130703</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0121220291895014</v>
+        <v>0.00725702641978685</v>
       </c>
       <c r="I63"/>
       <c r="J63" t="n">
@@ -3808,15 +5254,15 @@
         <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E64"/>
       <c r="F64"/>
       <c r="G64" t="n">
-        <v>0.000259318123429544</v>
+        <v>0.0000890256594307911</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0121009912602446</v>
+        <v>0.00725832853819443</v>
       </c>
       <c r="I64"/>
       <c r="J64" t="n">
@@ -3834,15 +5280,15 @@
         <v>16</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000256894238556425</v>
+        <v>0.0000877492029714677</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0120941920059368</v>
+        <v>0.00724297882010669</v>
       </c>
       <c r="I65"/>
       <c r="J65" t="n">
@@ -3860,15 +5306,15 @@
         <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.000162586279202364</v>
+        <v>0.0000975295196124737</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00770558800555955</v>
+        <v>0.00438457969549617</v>
       </c>
       <c r="I66"/>
       <c r="J66" t="n">
@@ -3886,15 +5332,15 @@
         <v>19</v>
       </c>
       <c r="D67" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67" t="n">
-        <v>1213.74285915808</v>
+        <v>0.0000978275673492674</v>
       </c>
       <c r="H67" t="n">
-        <v>7.76426077312173</v>
+        <v>0.00440253615086676</v>
       </c>
       <c r="I67"/>
       <c r="J67" t="n">
@@ -3912,15 +5358,15 @@
         <v>19</v>
       </c>
       <c r="D68" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.000162611247765157</v>
+        <v>0.0000974489342915572</v>
       </c>
       <c r="H68" t="n">
-        <v>0.00772844257661858</v>
+        <v>0.0043908045303298</v>
       </c>
       <c r="I68"/>
       <c r="J68" t="n">
@@ -3938,15 +5384,15 @@
         <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E69"/>
       <c r="F69"/>
       <c r="G69" t="n">
-        <v>0.000164737133869094</v>
+        <v>0.0000975890001536484</v>
       </c>
       <c r="H69" t="n">
-        <v>0.00778915638572289</v>
+        <v>0.00438319191959264</v>
       </c>
       <c r="I69"/>
       <c r="J69" t="n">
@@ -3964,15 +5410,15 @@
         <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.000281960284267101</v>
+        <v>0.000215340147769813</v>
       </c>
       <c r="H70" t="n">
-        <v>0.00783862267199919</v>
+        <v>0.00452966053124237</v>
       </c>
       <c r="I70"/>
       <c r="J70" t="n">
@@ -3990,15 +5436,15 @@
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71" t="n">
-        <v>1305.59381848702</v>
+        <v>0.000215556168251757</v>
       </c>
       <c r="H71" t="n">
-        <v>8.42261251279047</v>
+        <v>0.00453570776047664</v>
       </c>
       <c r="I71"/>
       <c r="J71" t="n">
@@ -4016,15 +5462,15 @@
         <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72" t="n">
-        <v>0.000282410295172309</v>
+        <v>0.000215374002673483</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0078770578332271</v>
+        <v>0.00453313031474187</v>
       </c>
       <c r="I72"/>
       <c r="J72" t="n">
@@ -4042,15 +5488,15 @@
         <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E73"/>
       <c r="F73"/>
       <c r="G73" t="n">
-        <v>0.000280795607591805</v>
+        <v>0.000215445593774553</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00787537753172</v>
+        <v>0.00453283735310416</v>
       </c>
       <c r="I73"/>
       <c r="J73" t="n">
@@ -4068,15 +5514,15 @@
         <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.0000940433060653965</v>
+        <v>0.0000318118942234263</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00750967045408458</v>
+        <v>0.00415521407984866</v>
       </c>
       <c r="I74"/>
       <c r="J74" t="n">
@@ -4094,15 +5540,15 @@
         <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75" t="n">
-        <v>1309.0573790592</v>
+        <v>0.0000321306949171509</v>
       </c>
       <c r="H75" t="n">
-        <v>8.50789169517494</v>
+        <v>0.00419317456169534</v>
       </c>
       <c r="I75"/>
       <c r="J75" t="n">
@@ -4120,15 +5566,15 @@
         <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E76"/>
       <c r="F76"/>
       <c r="G76" t="n">
-        <v>0.0000938119979712337</v>
+        <v>0.0000318888667872478</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00752160542967396</v>
+        <v>0.00417427107221481</v>
       </c>
       <c r="I76"/>
       <c r="J76" t="n">
@@ -4146,15 +5592,15 @@
         <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E77"/>
       <c r="F77"/>
       <c r="G77" t="n">
-        <v>0.0000948789136557377</v>
+        <v>0.0000320279226998038</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00758009648366493</v>
+        <v>0.00417352911220678</v>
       </c>
       <c r="I77"/>
       <c r="J77" t="n">
@@ -4172,15 +5618,15 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.0000937679823806852</v>
+        <v>0.0000317811801026438</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00748359730946349</v>
+        <v>0.00415939282327691</v>
       </c>
       <c r="I78"/>
       <c r="J78" t="n">
@@ -4198,15 +5644,15 @@
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79" t="n">
-        <v>988.789718931182</v>
+        <v>0.0000323496780513232</v>
       </c>
       <c r="H79" t="n">
-        <v>6.80298988814467</v>
+        <v>0.00420027660038074</v>
       </c>
       <c r="I79"/>
       <c r="J79" t="n">
@@ -4224,15 +5670,15 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80" t="n">
-        <v>0.0000940730250249333</v>
+        <v>0.0000319862418180184</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00750398603015387</v>
+        <v>0.00416413792655207</v>
       </c>
       <c r="I80"/>
       <c r="J80" t="n">
@@ -4250,15 +5696,15 @@
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E81"/>
       <c r="F81"/>
       <c r="G81" t="n">
-        <v>0.0000950396415045482</v>
+        <v>0.0000319391744816449</v>
       </c>
       <c r="H81" t="n">
-        <v>0.00757004383527859</v>
+        <v>0.00417033730399493</v>
       </c>
       <c r="I81"/>
       <c r="J81" t="n">
@@ -4276,15 +5722,15 @@
         <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.000206902778904061</v>
+        <v>0.000129757594988749</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0119538641845173</v>
+        <v>0.01018812056695</v>
       </c>
       <c r="I82"/>
       <c r="J82" t="n">
@@ -4302,15 +5748,15 @@
         <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.000213787473182652</v>
+        <v>0.000129119339041479</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0121913586574552</v>
+        <v>0.0101499013079248</v>
       </c>
       <c r="I83"/>
       <c r="J83" t="n">
@@ -4328,15 +5774,15 @@
         <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E84"/>
       <c r="F84"/>
       <c r="G84" t="n">
-        <v>0.000213071141908161</v>
+        <v>0.000130272798432306</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0121255161008157</v>
+        <v>0.010201563543119</v>
       </c>
       <c r="I84"/>
       <c r="J84" t="n">
@@ -4354,15 +5800,15 @@
         <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E85"/>
       <c r="F85"/>
       <c r="G85" t="n">
-        <v>0.000216909117864017</v>
+        <v>0.000128318153841272</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0123069544453788</v>
+        <v>0.0101167248579192</v>
       </c>
       <c r="I85"/>
       <c r="J85" t="n">
@@ -4380,15 +5826,15 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.00356709287518203</v>
+        <v>0.000518065622707725</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0492007849855877</v>
+        <v>0.0164423010105302</v>
       </c>
       <c r="I86"/>
       <c r="J86" t="n">
@@ -4406,15 +5852,15 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.00361467683447758</v>
+        <v>0.000518633117452987</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0496728683521829</v>
+        <v>0.0165357997451221</v>
       </c>
       <c r="I87"/>
       <c r="J87" t="n">
@@ -4432,15 +5878,15 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E88"/>
       <c r="F88"/>
       <c r="G88" t="n">
-        <v>0.00359154994380956</v>
+        <v>0.000515766381516243</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0491321379267671</v>
+        <v>0.0163978440251566</v>
       </c>
       <c r="I88"/>
       <c r="J88" t="n">
@@ -4458,15 +5904,15 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E89"/>
       <c r="F89"/>
       <c r="G89" t="n">
-        <v>0.00357367400960657</v>
+        <v>0.000504361550207652</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0494550331160037</v>
+        <v>0.016299066004747</v>
       </c>
       <c r="I89"/>
       <c r="J89" t="n">
@@ -4484,15 +5930,15 @@
         <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00347343413176563</v>
+        <v>0.000258982380856436</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0455677016188068</v>
+        <v>0.0120424019258245</v>
       </c>
       <c r="I90"/>
       <c r="J90" t="n">
@@ -4510,15 +5956,15 @@
         <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.00349043678651564</v>
+        <v>0.000257514705647565</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0456121639974128</v>
+        <v>0.012092621213791</v>
       </c>
       <c r="I91"/>
       <c r="J91" t="n">
@@ -4536,15 +5982,15 @@
         <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92" t="n">
-        <v>0.0034556929213981</v>
+        <v>0.000255740042688118</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0452045464056649</v>
+        <v>0.0121311325837106</v>
       </c>
       <c r="I92"/>
       <c r="J92" t="n">
@@ -4562,15 +6008,15 @@
         <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93" t="n">
-        <v>0.00350824349449575</v>
+        <v>0.000254324321676988</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0455409538236593</v>
+        <v>0.0121304687938613</v>
       </c>
       <c r="I93"/>
       <c r="J93" t="n">
@@ -4588,15 +6034,15 @@
         <v>19</v>
       </c>
       <c r="D94" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.00126524291543443</v>
+        <v>0.000162196838138077</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0253375134652221</v>
+        <v>0.00769909727074466</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -4614,15 +6060,15 @@
         <v>19</v>
       </c>
       <c r="D95" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95" t="n">
-        <v>0.00127711952409654</v>
+        <v>1195.97087214223</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0254814280930115</v>
+        <v>7.67863105524868</v>
       </c>
       <c r="I95"/>
       <c r="J95" t="n">
@@ -4640,15 +6086,15 @@
         <v>19</v>
       </c>
       <c r="D96" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96" t="n">
-        <v>0.00126738530947306</v>
+        <v>0.000162983900177599</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0253654245953917</v>
+        <v>0.00775958032400913</v>
       </c>
       <c r="I96"/>
       <c r="J96" t="n">
@@ -4666,15 +6112,15 @@
         <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00126866914403079</v>
+        <v>0.000162806779451155</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0253719531646511</v>
+        <v>0.007793787550423</v>
       </c>
       <c r="I97"/>
       <c r="J97" t="n">
@@ -4692,15 +6138,15 @@
         <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00139699309507506</v>
+        <v>0.000282111586509824</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0255469344955213</v>
+        <v>0.00786693799790825</v>
       </c>
       <c r="I98"/>
       <c r="J98" t="n">
@@ -4718,15 +6164,15 @@
         <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99" t="n">
-        <v>0.00139789893744094</v>
+        <v>1106.99308339223</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0255180572916646</v>
+        <v>7.49552139523906</v>
       </c>
       <c r="I99"/>
       <c r="J99" t="n">
@@ -4744,15 +6190,15 @@
         <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.00139856072290935</v>
+        <v>0.000280948337007677</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0255102068619735</v>
+        <v>0.00787600991726175</v>
       </c>
       <c r="I100"/>
       <c r="J100" t="n">
@@ -4770,15 +6216,15 @@
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101" t="n">
-        <v>0.0013970158963728</v>
+        <v>0.000285168819193373</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0254483740475441</v>
+        <v>0.0079517220472381</v>
       </c>
       <c r="I101"/>
       <c r="J101" t="n">
@@ -4796,15 +6242,15 @@
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.00118888995517411</v>
+        <v>0.0000936553758320833</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0251469497211458</v>
+        <v>0.00747803777491874</v>
       </c>
       <c r="I102"/>
       <c r="J102" t="n">
@@ -4822,15 +6268,15 @@
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.0011922663691207</v>
+        <v>1189.5793131102</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0252102347187435</v>
+        <v>7.80984690026167</v>
       </c>
       <c r="I103"/>
       <c r="J103" t="n">
@@ -4848,15 +6294,15 @@
         <v>23</v>
       </c>
       <c r="D104" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104" t="n">
-        <v>0.00119073380143728</v>
+        <v>0.0000944596043489018</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0251662408435151</v>
+        <v>0.00755419216415687</v>
       </c>
       <c r="I104"/>
       <c r="J104" t="n">
@@ -4874,15 +6320,15 @@
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105" t="n">
-        <v>0.00119554228152484</v>
+        <v>0.0000951687785575479</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0252196956628167</v>
+        <v>0.00755162652088153</v>
       </c>
       <c r="I105"/>
       <c r="J105" t="n">
@@ -4900,15 +6346,15 @@
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.00119266728566019</v>
+        <v>0.0000940274343706836</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0251880273764967</v>
+        <v>0.00750416366650368</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -4926,15 +6372,15 @@
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E107"/>
       <c r="F107"/>
       <c r="G107" t="n">
-        <v>0.00119907927963404</v>
+        <v>1076.3627939052</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0252650970235112</v>
+        <v>7.32351020769527</v>
       </c>
       <c r="I107"/>
       <c r="J107" t="n">
@@ -4952,15 +6398,15 @@
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E108"/>
       <c r="F108"/>
       <c r="G108" t="n">
-        <v>0.00119286974617785</v>
+        <v>0.0000946782346434687</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0251750369276858</v>
+        <v>0.00755218117541335</v>
       </c>
       <c r="I108"/>
       <c r="J108" t="n">
@@ -4978,15 +6424,15 @@
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.00119224520621769</v>
+        <v>0.0000950628782447814</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0251990886329344</v>
+        <v>0.0075672084287267</v>
       </c>
       <c r="I109"/>
       <c r="J109" t="n">
@@ -5004,15 +6450,15 @@
         <v>27</v>
       </c>
       <c r="D110" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.00105190919406783</v>
+        <v>0.000207193015401097</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0226437487805914</v>
+        <v>0.0119257266313408</v>
       </c>
       <c r="I110"/>
       <c r="J110" t="n">
@@ -5030,15 +6476,15 @@
         <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E111"/>
       <c r="F111"/>
       <c r="G111" t="n">
-        <v>0.00104880333000164</v>
+        <v>0.000212948608541644</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0225643052973476</v>
+        <v>0.0121338185861415</v>
       </c>
       <c r="I111"/>
       <c r="J111" t="n">
@@ -5056,15 +6502,15 @@
         <v>27</v>
       </c>
       <c r="D112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.00105118426391401</v>
+        <v>0.000213542021951181</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0226355189916163</v>
+        <v>0.0121770159417138</v>
       </c>
       <c r="I112"/>
       <c r="J112" t="n">
@@ -5082,15 +6528,15 @@
         <v>27</v>
       </c>
       <c r="D113" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.00105929170646389</v>
+        <v>0.000216089532220706</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0227374738466541</v>
+        <v>0.0122794969145519</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5108,15 +6554,15 @@
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.00166657826440175</v>
+        <v>0.000410879616765388</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0306961695852543</v>
+        <v>0.0149890258624776</v>
       </c>
       <c r="I114"/>
       <c r="J114" t="n">
@@ -5134,15 +6580,15 @@
         <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115" t="n">
-        <v>0.00167355487426778</v>
+        <v>0.000411599072831447</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0308007466693071</v>
+        <v>0.0150412253941229</v>
       </c>
       <c r="I115"/>
       <c r="J115" t="n">
@@ -5160,15 +6606,15 @@
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.0016679229279071</v>
+        <v>0.000415052893191876</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0306488592878618</v>
+        <v>0.0150508867393071</v>
       </c>
       <c r="I116"/>
       <c r="J116" t="n">
@@ -5186,15 +6632,15 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E117"/>
       <c r="F117"/>
       <c r="G117" t="n">
-        <v>0.00166336609497293</v>
+        <v>0.000412926602546874</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0306152304432491</v>
+        <v>0.0150110225971682</v>
       </c>
       <c r="I117"/>
       <c r="J117" t="n">
@@ -5212,15 +6658,15 @@
         <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.0022097436548237</v>
+        <v>0.000237877700866366</v>
       </c>
       <c r="H118" t="n">
-        <v>0.035050748939306</v>
+        <v>0.0110942590815885</v>
       </c>
       <c r="I118"/>
       <c r="J118" t="n">
@@ -5238,15 +6684,15 @@
         <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00221710847752892</v>
+        <v>0.000236789389916103</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0350879420045787</v>
+        <v>0.0109503832765895</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5264,15 +6710,15 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>0.00223248760201288</v>
+        <v>0.000239333093598082</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0352798684248624</v>
+        <v>0.0111351893555681</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5290,15 +6736,15 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E121"/>
       <c r="F121"/>
       <c r="G121" t="n">
-        <v>0.00220302886527406</v>
+        <v>0.000237144251026504</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0349619618279106</v>
+        <v>0.0111387812566376</v>
       </c>
       <c r="I121"/>
       <c r="J121" t="n">
@@ -5316,15 +6762,15 @@
         <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.00044022273608923</v>
+        <v>0.000146565375608219</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0138252451802776</v>
+        <v>0.00690848672760358</v>
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
@@ -5342,15 +6788,15 @@
         <v>19</v>
       </c>
       <c r="D123" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000439897445163341</v>
+        <v>0.000146622517705153</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0138770372669694</v>
+        <v>0.00693661302704114</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5368,15 +6814,15 @@
         <v>19</v>
       </c>
       <c r="D124" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E124"/>
       <c r="F124"/>
       <c r="G124" t="n">
-        <v>0.000440413564673099</v>
+        <v>0.000145971960039479</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0138447314947511</v>
+        <v>0.0069078270849286</v>
       </c>
       <c r="I124"/>
       <c r="J124" t="n">
@@ -5394,15 +6840,15 @@
         <v>19</v>
       </c>
       <c r="D125" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E125"/>
       <c r="F125"/>
       <c r="G125" t="n">
-        <v>0.000438793509147836</v>
+        <v>0.000146680705587266</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0138041252317179</v>
+        <v>0.0069548721591661</v>
       </c>
       <c r="I125"/>
       <c r="J125" t="n">
@@ -5420,15 +6866,15 @@
         <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000561507988559075</v>
+        <v>0.000264993539013037</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0140052168487452</v>
+        <v>0.00704535503251569</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5446,15 +6892,15 @@
         <v>21</v>
       </c>
       <c r="D127" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127" t="n">
-        <v>0.000561454361354745</v>
+        <v>0.000268411179586345</v>
       </c>
       <c r="H127" t="n">
-        <v>0.014025753891243</v>
+        <v>0.00713452803021518</v>
       </c>
       <c r="I127"/>
       <c r="J127" t="n">
@@ -5472,15 +6918,15 @@
         <v>21</v>
       </c>
       <c r="D128" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E128"/>
       <c r="F128"/>
       <c r="G128" t="n">
-        <v>0.000557896256776269</v>
+        <v>0.000265554584344468</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0139729587331149</v>
+        <v>0.00704284804852973</v>
       </c>
       <c r="I128"/>
       <c r="J128" t="n">
@@ -5498,15 +6944,15 @@
         <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.000556402491690548</v>
+        <v>0.000266822304619512</v>
       </c>
       <c r="H129" t="n">
-        <v>0.013994148780252</v>
+        <v>0.00709565252580932</v>
       </c>
       <c r="I129"/>
       <c r="J129" t="n">
@@ -5524,15 +6970,15 @@
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.000372328070510838</v>
+        <v>0.0000774770248919929</v>
       </c>
       <c r="H130" t="n">
-        <v>0.013628839874028</v>
+        <v>0.00668935270351218</v>
       </c>
       <c r="I130"/>
       <c r="J130" t="n">
@@ -5550,15 +6996,15 @@
         <v>23</v>
       </c>
       <c r="D131" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131" t="n">
-        <v>0.000372776889516162</v>
+        <v>0.0000771819862423975</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0136249609336273</v>
+        <v>0.00668262428647748</v>
       </c>
       <c r="I131"/>
       <c r="J131" t="n">
@@ -5576,15 +7022,15 @@
         <v>23</v>
       </c>
       <c r="D132" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000373195497273434</v>
+        <v>0.0000772277795077095</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0136120071781038</v>
+        <v>0.00668506939996752</v>
       </c>
       <c r="I132"/>
       <c r="J132" t="n">
@@ -5602,15 +7048,15 @@
         <v>23</v>
       </c>
       <c r="D133" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133" t="n">
-        <v>0.000373069837619335</v>
+        <v>0.0000792612845702449</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0136225126161665</v>
+        <v>0.00680881716352029</v>
       </c>
       <c r="I133"/>
       <c r="J133" t="n">
@@ -5628,15 +7074,15 @@
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.000372794714475328</v>
+        <v>0.0000771812323997239</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0136085662090615</v>
+        <v>0.00666514081081627</v>
       </c>
       <c r="I134"/>
       <c r="J134" t="n">
@@ -5654,15 +7100,15 @@
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000375706967440677</v>
+        <v>0.0000780816290306126</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0136523246886673</v>
+        <v>0.00672149128104696</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
@@ -5680,15 +7126,15 @@
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E136"/>
       <c r="F136"/>
       <c r="G136" t="n">
-        <v>0.000371812999795075</v>
+        <v>0.0000775542388248838</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0136239618090333</v>
+        <v>0.00671836699459022</v>
       </c>
       <c r="I136"/>
       <c r="J136" t="n">
@@ -5706,15 +7152,15 @@
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E137"/>
       <c r="F137"/>
       <c r="G137" t="n">
-        <v>0.000373071949175921</v>
+        <v>0.0000789809024583931</v>
       </c>
       <c r="H137" t="n">
-        <v>0.013642436151581</v>
+        <v>0.00677917635642502</v>
       </c>
       <c r="I137"/>
       <c r="J137" t="n">
@@ -5732,15 +7178,15 @@
         <v>27</v>
       </c>
       <c r="D138" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138" t="n">
-        <v>0.000426298441099335</v>
+        <v>0.000196817960842603</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0143954509505574</v>
+        <v>0.0117161968411401</v>
       </c>
       <c r="I138"/>
       <c r="J138" t="n">
@@ -5758,15 +7204,15 @@
         <v>27</v>
       </c>
       <c r="D139" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E139"/>
       <c r="F139"/>
       <c r="G139" t="n">
-        <v>0.000426961747789713</v>
+        <v>0.000200140920957103</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0144382224623116</v>
+        <v>0.0118206775293174</v>
       </c>
       <c r="I139"/>
       <c r="J139" t="n">
@@ -5784,15 +7230,15 @@
         <v>27</v>
       </c>
       <c r="D140" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E140"/>
       <c r="F140"/>
       <c r="G140" t="n">
-        <v>0.00042556844247673</v>
+        <v>0.000201710053226512</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0143859614426913</v>
+        <v>0.0118925919330219</v>
       </c>
       <c r="I140"/>
       <c r="J140" t="n">
@@ -5810,15 +7256,15 @@
         <v>27</v>
       </c>
       <c r="D141" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E141"/>
       <c r="F141"/>
       <c r="G141" t="n">
-        <v>0.000426453714080303</v>
+        <v>0.000203509153149215</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0143987429518154</v>
+        <v>0.0119427732974345</v>
       </c>
       <c r="I141"/>
       <c r="J141" t="n">
@@ -5836,15 +7282,15 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142" t="n">
-        <v>0.00266189274448004</v>
+        <v>0.00034497170288116</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0395332494639327</v>
+        <v>0.0134813186192203</v>
       </c>
       <c r="I142"/>
       <c r="J142" t="n">
@@ -5862,15 +7308,15 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E143"/>
       <c r="F143"/>
       <c r="G143" t="n">
-        <v>0.00264407450488645</v>
+        <v>0.000343018680562633</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0395308620255686</v>
+        <v>0.0134510178732504</v>
       </c>
       <c r="I143"/>
       <c r="J143" t="n">
@@ -5888,15 +7334,15 @@
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E144"/>
       <c r="F144"/>
       <c r="G144" t="n">
-        <v>0.00264094073260641</v>
+        <v>0.000343970465595456</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0395708532395442</v>
+        <v>0.013499658571087</v>
       </c>
       <c r="I144"/>
       <c r="J144" t="n">
@@ -5914,15 +7360,15 @@
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E145"/>
       <c r="F145"/>
       <c r="G145" t="n">
-        <v>0.00264900354608587</v>
+        <v>0.000343310658705423</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0397517171495199</v>
+        <v>0.013412627825418</v>
       </c>
       <c r="I145"/>
       <c r="J145" t="n">
@@ -5940,15 +7386,15 @@
         <v>16</v>
       </c>
       <c r="D146" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146" t="n">
-        <v>0.00109660996556027</v>
+        <v>0.000263811707142936</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0250020115801956</v>
+        <v>0.0122601584242954</v>
       </c>
       <c r="I146"/>
       <c r="J146" t="n">
@@ -5966,15 +7412,15 @@
         <v>16</v>
       </c>
       <c r="D147" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E147"/>
       <c r="F147"/>
       <c r="G147" t="n">
-        <v>0.00109240580509464</v>
+        <v>0.00026972161988931</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0251838339596461</v>
+        <v>0.0123442885350847</v>
       </c>
       <c r="I147"/>
       <c r="J147" t="n">
@@ -5992,15 +7438,15 @@
         <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E148"/>
       <c r="F148"/>
       <c r="G148" t="n">
-        <v>0.00110657037146525</v>
+        <v>0.000263347463835664</v>
       </c>
       <c r="H148" t="n">
-        <v>0.025247114266781</v>
+        <v>0.0121160750185186</v>
       </c>
       <c r="I148"/>
       <c r="J148" t="n">
@@ -6018,15 +7464,15 @@
         <v>16</v>
       </c>
       <c r="D149" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E149"/>
       <c r="F149"/>
       <c r="G149" t="n">
-        <v>0.00109186411368117</v>
+        <v>0.000265659920104038</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0250789892918997</v>
+        <v>0.0122712797486374</v>
       </c>
       <c r="I149"/>
       <c r="J149" t="n">
@@ -6044,15 +7490,15 @@
         <v>19</v>
       </c>
       <c r="D150" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150" t="n">
-        <v>0.00058163298147872</v>
+        <v>0.000143157849761406</v>
       </c>
       <c r="H150" t="n">
-        <v>0.016436389149377</v>
+        <v>0.00672001805746283</v>
       </c>
       <c r="I150"/>
       <c r="J150" t="n">
@@ -6070,15 +7516,15 @@
         <v>19</v>
       </c>
       <c r="D151" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E151"/>
       <c r="F151"/>
       <c r="G151" t="n">
-        <v>0.000581864447813023</v>
+        <v>0.000142852599289543</v>
       </c>
       <c r="H151" t="n">
-        <v>0.016404261896359</v>
+        <v>0.0067601891238118</v>
       </c>
       <c r="I151"/>
       <c r="J151" t="n">
@@ -6096,15 +7542,15 @@
         <v>19</v>
       </c>
       <c r="D152" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E152"/>
       <c r="F152"/>
       <c r="G152" t="n">
-        <v>0.000584543883198312</v>
+        <v>0.000142161107529618</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0163803862295117</v>
+        <v>0.00672252165740435</v>
       </c>
       <c r="I152"/>
       <c r="J152" t="n">
@@ -6122,15 +7568,15 @@
         <v>19</v>
       </c>
       <c r="D153" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E153"/>
       <c r="F153"/>
       <c r="G153" t="n">
-        <v>0.000581818645006164</v>
+        <v>0.000143484591449859</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0164240756376304</v>
+        <v>0.00677893871264257</v>
       </c>
       <c r="I153"/>
       <c r="J153" t="n">
@@ -6148,15 +7594,15 @@
         <v>21</v>
       </c>
       <c r="D154" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154" t="n">
-        <v>0.000704502166220318</v>
+        <v>0.00026272403043062</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0165653600492239</v>
+        <v>0.00688869919008294</v>
       </c>
       <c r="I154"/>
       <c r="J154" t="n">
@@ -6174,15 +7620,15 @@
         <v>21</v>
       </c>
       <c r="D155" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E155"/>
       <c r="F155"/>
       <c r="G155" t="n">
-        <v>0.000700754734122636</v>
+        <v>0.000261497324333154</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0165200377477486</v>
+        <v>0.00691872013168776</v>
       </c>
       <c r="I155"/>
       <c r="J155" t="n">
@@ -6200,15 +7646,15 @@
         <v>21</v>
       </c>
       <c r="D156" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E156"/>
       <c r="F156"/>
       <c r="G156" t="n">
-        <v>0.000702709578892673</v>
+        <v>0.000263868327505296</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0165307045727206</v>
+        <v>0.00687864889401414</v>
       </c>
       <c r="I156"/>
       <c r="J156" t="n">
@@ -6226,15 +7672,15 @@
         <v>21</v>
       </c>
       <c r="D157" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E157"/>
       <c r="F157"/>
       <c r="G157" t="n">
-        <v>0.000704768889545307</v>
+        <v>0.000264013140884187</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0165235072709543</v>
+        <v>0.00692848099922221</v>
       </c>
       <c r="I157"/>
       <c r="J157" t="n">
@@ -6252,15 +7698,15 @@
         <v>23</v>
       </c>
       <c r="D158" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158" t="n">
-        <v>0.000514879860652079</v>
+        <v>0.0000734338823940795</v>
       </c>
       <c r="H158" t="n">
-        <v>0.016186575928726</v>
+        <v>0.00653564485904514</v>
       </c>
       <c r="I158"/>
       <c r="J158" t="n">
@@ -6278,15 +7724,15 @@
         <v>23</v>
       </c>
       <c r="D159" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E159"/>
       <c r="F159"/>
       <c r="G159" t="n">
-        <v>0.0005174780349884</v>
+        <v>0.00007391798020678</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0161996287580614</v>
+        <v>0.00655684348846129</v>
       </c>
       <c r="I159"/>
       <c r="J159" t="n">
@@ -6304,15 +7750,15 @@
         <v>23</v>
       </c>
       <c r="D160" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E160"/>
       <c r="F160"/>
       <c r="G160" t="n">
-        <v>0.000515251300566603</v>
+        <v>0.0000732985981708617</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0161738179102516</v>
+        <v>0.00653937536792915</v>
       </c>
       <c r="I160"/>
       <c r="J160" t="n">
@@ -6330,15 +7776,15 @@
         <v>23</v>
       </c>
       <c r="D161" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E161"/>
       <c r="F161"/>
       <c r="G161" t="n">
-        <v>0.00051515569079851</v>
+        <v>0.0000734264303983529</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0162050688203587</v>
+        <v>0.00652336812434081</v>
       </c>
       <c r="I161"/>
       <c r="J161" t="n">
@@ -6356,15 +7802,15 @@
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162" t="n">
-        <v>0.000515975483538925</v>
+        <v>0.0000731819835975405</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0162143467350227</v>
+        <v>0.006509531930357</v>
       </c>
       <c r="I162"/>
       <c r="J162" t="n">
@@ -6382,15 +7828,15 @@
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E163"/>
       <c r="F163"/>
       <c r="G163" t="n">
-        <v>0.000515249399204647</v>
+        <v>0.0000731887357022909</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0161837631667627</v>
+        <v>0.00654187053592133</v>
       </c>
       <c r="I163"/>
       <c r="J163" t="n">
@@ -6408,15 +7854,15 @@
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E164"/>
       <c r="F164"/>
       <c r="G164" t="n">
-        <v>0.000517974044082233</v>
+        <v>0.000072969938697962</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0162550329107774</v>
+        <v>0.00650971844263463</v>
       </c>
       <c r="I164"/>
       <c r="J164" t="n">
@@ -6434,15 +7880,15 @@
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E165"/>
       <c r="F165"/>
       <c r="G165" t="n">
-        <v>0.000514517663048894</v>
+        <v>0.000073378602873691</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0161573997755607</v>
+        <v>0.00652764121502774</v>
       </c>
       <c r="I165"/>
       <c r="J165" t="n">
@@ -6460,15 +7906,15 @@
         <v>27</v>
       </c>
       <c r="D166" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166" t="n">
-        <v>0.000472414088593065</v>
+        <v>0.000188541415835181</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0158472107195783</v>
+        <v>0.0115621741316753</v>
       </c>
       <c r="I166"/>
       <c r="J166" t="n">
@@ -6486,15 +7932,15 @@
         <v>27</v>
       </c>
       <c r="D167" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E167"/>
       <c r="F167"/>
       <c r="G167" t="n">
-        <v>0.000474557244125652</v>
+        <v>0.00019416455185569</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0159164374511597</v>
+        <v>0.0117604717317418</v>
       </c>
       <c r="I167"/>
       <c r="J167" t="n">
@@ -6512,15 +7958,15 @@
         <v>27</v>
       </c>
       <c r="D168" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E168"/>
       <c r="F168"/>
       <c r="G168" t="n">
-        <v>0.000473096321388058</v>
+        <v>0.000192506257707072</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0158568789536106</v>
+        <v>0.011724336473991</v>
       </c>
       <c r="I168"/>
       <c r="J168" t="n">
@@ -6538,18 +7984,4386 @@
         <v>27</v>
       </c>
       <c r="D169" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E169"/>
       <c r="F169"/>
       <c r="G169" t="n">
-        <v>0.000498501614556952</v>
+        <v>0.000193549326953702</v>
       </c>
       <c r="H169" t="n">
-        <v>0.0163844868958091</v>
+        <v>0.0117509450371835</v>
       </c>
       <c r="I169"/>
       <c r="J169" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>34</v>
+      </c>
+      <c r="B170" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" t="s">
+        <v>51</v>
+      </c>
+      <c r="E170"/>
+      <c r="F170"/>
+      <c r="G170" t="n">
+        <v>0.0036381251932954</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.0496627782816975</v>
+      </c>
+      <c r="I170"/>
+      <c r="J170" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>34</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" t="s">
+        <v>52</v>
+      </c>
+      <c r="E171"/>
+      <c r="F171"/>
+      <c r="G171" t="n">
+        <v>0.00359753499313843</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0492627632143011</v>
+      </c>
+      <c r="I171"/>
+      <c r="J171" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>34</v>
+      </c>
+      <c r="B172" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" t="s">
+        <v>53</v>
+      </c>
+      <c r="E172"/>
+      <c r="F172"/>
+      <c r="G172" t="n">
+        <v>0.00356913047144924</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.0491878082832575</v>
+      </c>
+      <c r="I172"/>
+      <c r="J172" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>34</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" t="s">
+        <v>54</v>
+      </c>
+      <c r="E173"/>
+      <c r="F173"/>
+      <c r="G173" t="n">
+        <v>0.00355649884683804</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0492404317010501</v>
+      </c>
+      <c r="I173"/>
+      <c r="J173" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" t="s">
+        <v>16</v>
+      </c>
+      <c r="D174" t="s">
+        <v>51</v>
+      </c>
+      <c r="E174"/>
+      <c r="F174"/>
+      <c r="G174" t="n">
+        <v>0.003484147184224</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.0456744783807424</v>
+      </c>
+      <c r="I174"/>
+      <c r="J174" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>34</v>
+      </c>
+      <c r="B175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" t="s">
+        <v>16</v>
+      </c>
+      <c r="D175" t="s">
+        <v>52</v>
+      </c>
+      <c r="E175"/>
+      <c r="F175"/>
+      <c r="G175" t="n">
+        <v>0.00346671876821047</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.0454312913928589</v>
+      </c>
+      <c r="I175"/>
+      <c r="J175" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>34</v>
+      </c>
+      <c r="B176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" t="s">
+        <v>16</v>
+      </c>
+      <c r="D176" t="s">
+        <v>53</v>
+      </c>
+      <c r="E176"/>
+      <c r="F176"/>
+      <c r="G176" t="n">
+        <v>0.00347494934703716</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.0455330620067754</v>
+      </c>
+      <c r="I176"/>
+      <c r="J176" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>34</v>
+      </c>
+      <c r="B177" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" t="s">
+        <v>16</v>
+      </c>
+      <c r="D177" t="s">
+        <v>54</v>
+      </c>
+      <c r="E177"/>
+      <c r="F177"/>
+      <c r="G177" t="n">
+        <v>0.00343491348207355</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.045148527161354</v>
+      </c>
+      <c r="I177"/>
+      <c r="J177" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>34</v>
+      </c>
+      <c r="B178" t="s">
+        <v>18</v>
+      </c>
+      <c r="C178" t="s">
+        <v>19</v>
+      </c>
+      <c r="D178" t="s">
+        <v>51</v>
+      </c>
+      <c r="E178"/>
+      <c r="F178"/>
+      <c r="G178" t="n">
+        <v>0.00126811630646402</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.0253392636435161</v>
+      </c>
+      <c r="I178"/>
+      <c r="J178" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>34</v>
+      </c>
+      <c r="B179" t="s">
+        <v>18</v>
+      </c>
+      <c r="C179" t="s">
+        <v>19</v>
+      </c>
+      <c r="D179" t="s">
+        <v>52</v>
+      </c>
+      <c r="E179"/>
+      <c r="F179"/>
+      <c r="G179" t="n">
+        <v>0.00126467456649125</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.0252829822768248</v>
+      </c>
+      <c r="I179"/>
+      <c r="J179" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>34</v>
+      </c>
+      <c r="B180" t="s">
+        <v>18</v>
+      </c>
+      <c r="C180" t="s">
+        <v>19</v>
+      </c>
+      <c r="D180" t="s">
+        <v>53</v>
+      </c>
+      <c r="E180"/>
+      <c r="F180"/>
+      <c r="G180" t="n">
+        <v>0.00126652800386674</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.0253548640203161</v>
+      </c>
+      <c r="I180"/>
+      <c r="J180" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>34</v>
+      </c>
+      <c r="B181" t="s">
+        <v>18</v>
+      </c>
+      <c r="C181" t="s">
+        <v>19</v>
+      </c>
+      <c r="D181" t="s">
+        <v>54</v>
+      </c>
+      <c r="E181"/>
+      <c r="F181"/>
+      <c r="G181" t="n">
+        <v>0.00127149271360507</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.0253687821943387</v>
+      </c>
+      <c r="I181"/>
+      <c r="J181" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>34</v>
+      </c>
+      <c r="B182" t="s">
+        <v>18</v>
+      </c>
+      <c r="C182" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" t="s">
+        <v>51</v>
+      </c>
+      <c r="E182"/>
+      <c r="F182"/>
+      <c r="G182" t="n">
+        <v>0.00139008761376244</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.0254564334547203</v>
+      </c>
+      <c r="I182"/>
+      <c r="J182" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>34</v>
+      </c>
+      <c r="B183" t="s">
+        <v>18</v>
+      </c>
+      <c r="C183" t="s">
+        <v>21</v>
+      </c>
+      <c r="D183" t="s">
+        <v>52</v>
+      </c>
+      <c r="E183"/>
+      <c r="F183"/>
+      <c r="G183" t="n">
+        <v>0.00140563663457442</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.0256035458764409</v>
+      </c>
+      <c r="I183"/>
+      <c r="J183" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>34</v>
+      </c>
+      <c r="B184" t="s">
+        <v>18</v>
+      </c>
+      <c r="C184" t="s">
+        <v>21</v>
+      </c>
+      <c r="D184" t="s">
+        <v>53</v>
+      </c>
+      <c r="E184"/>
+      <c r="F184"/>
+      <c r="G184" t="n">
+        <v>0.00140626405337989</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.0255539501141129</v>
+      </c>
+      <c r="I184"/>
+      <c r="J184" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>34</v>
+      </c>
+      <c r="B185" t="s">
+        <v>18</v>
+      </c>
+      <c r="C185" t="s">
+        <v>21</v>
+      </c>
+      <c r="D185" t="s">
+        <v>54</v>
+      </c>
+      <c r="E185"/>
+      <c r="F185"/>
+      <c r="G185" t="n">
+        <v>0.00139952562483402</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.025505927283977</v>
+      </c>
+      <c r="I185"/>
+      <c r="J185" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>34</v>
+      </c>
+      <c r="B186" t="s">
+        <v>18</v>
+      </c>
+      <c r="C186" t="s">
+        <v>23</v>
+      </c>
+      <c r="D186" t="s">
+        <v>51</v>
+      </c>
+      <c r="E186"/>
+      <c r="F186"/>
+      <c r="G186" t="n">
+        <v>0.00118673619053998</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.0251371443190089</v>
+      </c>
+      <c r="I186"/>
+      <c r="J186" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>34</v>
+      </c>
+      <c r="B187" t="s">
+        <v>18</v>
+      </c>
+      <c r="C187" t="s">
+        <v>23</v>
+      </c>
+      <c r="D187" t="s">
+        <v>52</v>
+      </c>
+      <c r="E187"/>
+      <c r="F187"/>
+      <c r="G187" t="n">
+        <v>0.00119518407752138</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.0252434532782093</v>
+      </c>
+      <c r="I187"/>
+      <c r="J187" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>34</v>
+      </c>
+      <c r="B188" t="s">
+        <v>18</v>
+      </c>
+      <c r="C188" t="s">
+        <v>23</v>
+      </c>
+      <c r="D188" t="s">
+        <v>53</v>
+      </c>
+      <c r="E188"/>
+      <c r="F188"/>
+      <c r="G188" t="n">
+        <v>0.00118875819928141</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0251762043851933</v>
+      </c>
+      <c r="I188"/>
+      <c r="J188" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>34</v>
+      </c>
+      <c r="B189" t="s">
+        <v>18</v>
+      </c>
+      <c r="C189" t="s">
+        <v>23</v>
+      </c>
+      <c r="D189" t="s">
+        <v>54</v>
+      </c>
+      <c r="E189"/>
+      <c r="F189"/>
+      <c r="G189" t="n">
+        <v>0.00118893327256391</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.0251902640642417</v>
+      </c>
+      <c r="I189"/>
+      <c r="J189" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>34</v>
+      </c>
+      <c r="B190" t="s">
+        <v>18</v>
+      </c>
+      <c r="C190" t="s">
+        <v>25</v>
+      </c>
+      <c r="D190" t="s">
+        <v>51</v>
+      </c>
+      <c r="E190"/>
+      <c r="F190"/>
+      <c r="G190" t="n">
+        <v>0.00119410125441484</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.0251864726074049</v>
+      </c>
+      <c r="I190"/>
+      <c r="J190" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>34</v>
+      </c>
+      <c r="B191" t="s">
+        <v>18</v>
+      </c>
+      <c r="C191" t="s">
+        <v>25</v>
+      </c>
+      <c r="D191" t="s">
+        <v>52</v>
+      </c>
+      <c r="E191"/>
+      <c r="F191"/>
+      <c r="G191" t="n">
+        <v>0.00119640199819336</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.0252607591360278</v>
+      </c>
+      <c r="I191"/>
+      <c r="J191" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>34</v>
+      </c>
+      <c r="B192" t="s">
+        <v>18</v>
+      </c>
+      <c r="C192" t="s">
+        <v>25</v>
+      </c>
+      <c r="D192" t="s">
+        <v>53</v>
+      </c>
+      <c r="E192"/>
+      <c r="F192"/>
+      <c r="G192" t="n">
+        <v>0.00119618925707479</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.025190633289234</v>
+      </c>
+      <c r="I192"/>
+      <c r="J192" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>34</v>
+      </c>
+      <c r="B193" t="s">
+        <v>18</v>
+      </c>
+      <c r="C193" t="s">
+        <v>25</v>
+      </c>
+      <c r="D193" t="s">
+        <v>54</v>
+      </c>
+      <c r="E193"/>
+      <c r="F193"/>
+      <c r="G193" t="n">
+        <v>0.00119173597115386</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.0252014567648417</v>
+      </c>
+      <c r="I193"/>
+      <c r="J193" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>34</v>
+      </c>
+      <c r="B194" t="s">
+        <v>18</v>
+      </c>
+      <c r="C194" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194" t="s">
+        <v>51</v>
+      </c>
+      <c r="E194"/>
+      <c r="F194"/>
+      <c r="G194" t="n">
+        <v>0.00105300999455119</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.0226724565262974</v>
+      </c>
+      <c r="I194"/>
+      <c r="J194" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>34</v>
+      </c>
+      <c r="B195" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" t="s">
+        <v>27</v>
+      </c>
+      <c r="D195" t="s">
+        <v>52</v>
+      </c>
+      <c r="E195"/>
+      <c r="F195"/>
+      <c r="G195" t="n">
+        <v>0.00105452814360453</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.0227335739794848</v>
+      </c>
+      <c r="I195"/>
+      <c r="J195" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>34</v>
+      </c>
+      <c r="B196" t="s">
+        <v>18</v>
+      </c>
+      <c r="C196" t="s">
+        <v>27</v>
+      </c>
+      <c r="D196" t="s">
+        <v>53</v>
+      </c>
+      <c r="E196"/>
+      <c r="F196"/>
+      <c r="G196" t="n">
+        <v>0.00105572271240952</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.0226091064656082</v>
+      </c>
+      <c r="I196"/>
+      <c r="J196" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>34</v>
+      </c>
+      <c r="B197" t="s">
+        <v>18</v>
+      </c>
+      <c r="C197" t="s">
+        <v>27</v>
+      </c>
+      <c r="D197" t="s">
+        <v>54</v>
+      </c>
+      <c r="E197"/>
+      <c r="F197"/>
+      <c r="G197" t="n">
+        <v>0.00105491878662831</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.0227101736023227</v>
+      </c>
+      <c r="I197"/>
+      <c r="J197" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>35</v>
+      </c>
+      <c r="B198" t="s">
+        <v>13</v>
+      </c>
+      <c r="C198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D198" t="s">
+        <v>51</v>
+      </c>
+      <c r="E198"/>
+      <c r="F198"/>
+      <c r="G198" t="n">
+        <v>0.00166761224042229</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.030724183590473</v>
+      </c>
+      <c r="I198"/>
+      <c r="J198" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>35</v>
+      </c>
+      <c r="B199" t="s">
+        <v>13</v>
+      </c>
+      <c r="C199" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199" t="s">
+        <v>52</v>
+      </c>
+      <c r="E199"/>
+      <c r="F199"/>
+      <c r="G199" t="n">
+        <v>0.00166615778386249</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.0306570479449885</v>
+      </c>
+      <c r="I199"/>
+      <c r="J199" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>35</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
+        <v>14</v>
+      </c>
+      <c r="D200" t="s">
+        <v>53</v>
+      </c>
+      <c r="E200"/>
+      <c r="F200"/>
+      <c r="G200" t="n">
+        <v>0.00166219447105923</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.0306077709655781</v>
+      </c>
+      <c r="I200"/>
+      <c r="J200" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>35</v>
+      </c>
+      <c r="B201" t="s">
+        <v>13</v>
+      </c>
+      <c r="C201" t="s">
+        <v>14</v>
+      </c>
+      <c r="D201" t="s">
+        <v>54</v>
+      </c>
+      <c r="E201"/>
+      <c r="F201"/>
+      <c r="G201" t="n">
+        <v>0.00166821539143441</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.0306519330343691</v>
+      </c>
+      <c r="I201"/>
+      <c r="J201" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>35</v>
+      </c>
+      <c r="B202" t="s">
+        <v>13</v>
+      </c>
+      <c r="C202" t="s">
+        <v>16</v>
+      </c>
+      <c r="D202" t="s">
+        <v>51</v>
+      </c>
+      <c r="E202"/>
+      <c r="F202"/>
+      <c r="G202" t="n">
+        <v>0.00221371667149343</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.0352095752699077</v>
+      </c>
+      <c r="I202"/>
+      <c r="J202" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>35</v>
+      </c>
+      <c r="B203" t="s">
+        <v>13</v>
+      </c>
+      <c r="C203" t="s">
+        <v>16</v>
+      </c>
+      <c r="D203" t="s">
+        <v>52</v>
+      </c>
+      <c r="E203"/>
+      <c r="F203"/>
+      <c r="G203" t="n">
+        <v>0.00219838629557541</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.0349687425776701</v>
+      </c>
+      <c r="I203"/>
+      <c r="J203" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>35</v>
+      </c>
+      <c r="B204" t="s">
+        <v>13</v>
+      </c>
+      <c r="C204" t="s">
+        <v>16</v>
+      </c>
+      <c r="D204" t="s">
+        <v>53</v>
+      </c>
+      <c r="E204"/>
+      <c r="F204"/>
+      <c r="G204" t="n">
+        <v>0.00221137378612753</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.0350618290264087</v>
+      </c>
+      <c r="I204"/>
+      <c r="J204" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>35</v>
+      </c>
+      <c r="B205" t="s">
+        <v>13</v>
+      </c>
+      <c r="C205" t="s">
+        <v>16</v>
+      </c>
+      <c r="D205" t="s">
+        <v>54</v>
+      </c>
+      <c r="E205"/>
+      <c r="F205"/>
+      <c r="G205" t="n">
+        <v>0.00221390122567555</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.0351408377698628</v>
+      </c>
+      <c r="I205"/>
+      <c r="J205" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>35</v>
+      </c>
+      <c r="B206" t="s">
+        <v>18</v>
+      </c>
+      <c r="C206" t="s">
+        <v>19</v>
+      </c>
+      <c r="D206" t="s">
+        <v>51</v>
+      </c>
+      <c r="E206"/>
+      <c r="F206"/>
+      <c r="G206" t="n">
+        <v>0.000440927315547278</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.0138415879749341</v>
+      </c>
+      <c r="I206"/>
+      <c r="J206" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>35</v>
+      </c>
+      <c r="B207" t="s">
+        <v>18</v>
+      </c>
+      <c r="C207" t="s">
+        <v>19</v>
+      </c>
+      <c r="D207" t="s">
+        <v>52</v>
+      </c>
+      <c r="E207"/>
+      <c r="F207"/>
+      <c r="G207" t="n">
+        <v>0.000441080002849877</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.0139009122504683</v>
+      </c>
+      <c r="I207"/>
+      <c r="J207" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>35</v>
+      </c>
+      <c r="B208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C208" t="s">
+        <v>19</v>
+      </c>
+      <c r="D208" t="s">
+        <v>53</v>
+      </c>
+      <c r="E208"/>
+      <c r="F208"/>
+      <c r="G208" t="n">
+        <v>0.000439957125230199</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.0138355216301009</v>
+      </c>
+      <c r="I208"/>
+      <c r="J208" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>35</v>
+      </c>
+      <c r="B209" t="s">
+        <v>18</v>
+      </c>
+      <c r="C209" t="s">
+        <v>19</v>
+      </c>
+      <c r="D209" t="s">
+        <v>54</v>
+      </c>
+      <c r="E209"/>
+      <c r="F209"/>
+      <c r="G209" t="n">
+        <v>0.000440116962759475</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.0138249395722329</v>
+      </c>
+      <c r="I209"/>
+      <c r="J209" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>35</v>
+      </c>
+      <c r="B210" t="s">
+        <v>18</v>
+      </c>
+      <c r="C210" t="s">
+        <v>21</v>
+      </c>
+      <c r="D210" t="s">
+        <v>51</v>
+      </c>
+      <c r="E210"/>
+      <c r="F210"/>
+      <c r="G210" t="n">
+        <v>0.00055798623368306</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.0139583157606297</v>
+      </c>
+      <c r="I210"/>
+      <c r="J210" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>35</v>
+      </c>
+      <c r="B211" t="s">
+        <v>18</v>
+      </c>
+      <c r="C211" t="s">
+        <v>21</v>
+      </c>
+      <c r="D211" t="s">
+        <v>52</v>
+      </c>
+      <c r="E211"/>
+      <c r="F211"/>
+      <c r="G211" t="n">
+        <v>0.000560572567196004</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.0140433847165795</v>
+      </c>
+      <c r="I211"/>
+      <c r="J211" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>35</v>
+      </c>
+      <c r="B212" t="s">
+        <v>18</v>
+      </c>
+      <c r="C212" t="s">
+        <v>21</v>
+      </c>
+      <c r="D212" t="s">
+        <v>53</v>
+      </c>
+      <c r="E212"/>
+      <c r="F212"/>
+      <c r="G212" t="n">
+        <v>0.000558105379367882</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.0139865066720216</v>
+      </c>
+      <c r="I212"/>
+      <c r="J212" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>35</v>
+      </c>
+      <c r="B213" t="s">
+        <v>18</v>
+      </c>
+      <c r="C213" t="s">
+        <v>21</v>
+      </c>
+      <c r="D213" t="s">
+        <v>54</v>
+      </c>
+      <c r="E213"/>
+      <c r="F213"/>
+      <c r="G213" t="n">
+        <v>0.000559993134889333</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.0140057993117563</v>
+      </c>
+      <c r="I213"/>
+      <c r="J213" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>35</v>
+      </c>
+      <c r="B214" t="s">
+        <v>18</v>
+      </c>
+      <c r="C214" t="s">
+        <v>23</v>
+      </c>
+      <c r="D214" t="s">
+        <v>51</v>
+      </c>
+      <c r="E214"/>
+      <c r="F214"/>
+      <c r="G214" t="n">
+        <v>0.000371930517654909</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.0136237968162459</v>
+      </c>
+      <c r="I214"/>
+      <c r="J214" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>35</v>
+      </c>
+      <c r="B215" t="s">
+        <v>18</v>
+      </c>
+      <c r="C215" t="s">
+        <v>23</v>
+      </c>
+      <c r="D215" t="s">
+        <v>52</v>
+      </c>
+      <c r="E215"/>
+      <c r="F215"/>
+      <c r="G215" t="n">
+        <v>0.000371053408017486</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.0136361008685899</v>
+      </c>
+      <c r="I215"/>
+      <c r="J215" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>35</v>
+      </c>
+      <c r="B216" t="s">
+        <v>18</v>
+      </c>
+      <c r="C216" t="s">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>53</v>
+      </c>
+      <c r="E216"/>
+      <c r="F216"/>
+      <c r="G216" t="n">
+        <v>0.0003720898846319</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.0136145728273155</v>
+      </c>
+      <c r="I216"/>
+      <c r="J216" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>35</v>
+      </c>
+      <c r="B217" t="s">
+        <v>18</v>
+      </c>
+      <c r="C217" t="s">
+        <v>23</v>
+      </c>
+      <c r="D217" t="s">
+        <v>54</v>
+      </c>
+      <c r="E217"/>
+      <c r="F217"/>
+      <c r="G217" t="n">
+        <v>0.00037403354880693</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.0136783889142282</v>
+      </c>
+      <c r="I217"/>
+      <c r="J217" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>35</v>
+      </c>
+      <c r="B218" t="s">
+        <v>18</v>
+      </c>
+      <c r="C218" t="s">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>51</v>
+      </c>
+      <c r="E218"/>
+      <c r="F218"/>
+      <c r="G218" t="n">
+        <v>0.000372673174011669</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.0136185851814476</v>
+      </c>
+      <c r="I218"/>
+      <c r="J218" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>35</v>
+      </c>
+      <c r="B219" t="s">
+        <v>18</v>
+      </c>
+      <c r="C219" t="s">
+        <v>25</v>
+      </c>
+      <c r="D219" t="s">
+        <v>52</v>
+      </c>
+      <c r="E219"/>
+      <c r="F219"/>
+      <c r="G219" t="n">
+        <v>0.000371869402349157</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.0136414182944271</v>
+      </c>
+      <c r="I219"/>
+      <c r="J219" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>35</v>
+      </c>
+      <c r="B220" t="s">
+        <v>18</v>
+      </c>
+      <c r="C220" t="s">
+        <v>25</v>
+      </c>
+      <c r="D220" t="s">
+        <v>53</v>
+      </c>
+      <c r="E220"/>
+      <c r="F220"/>
+      <c r="G220" t="n">
+        <v>0.000372621800908681</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.0136283067210671</v>
+      </c>
+      <c r="I220"/>
+      <c r="J220" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>35</v>
+      </c>
+      <c r="B221" t="s">
+        <v>18</v>
+      </c>
+      <c r="C221" t="s">
+        <v>25</v>
+      </c>
+      <c r="D221" t="s">
+        <v>54</v>
+      </c>
+      <c r="E221"/>
+      <c r="F221"/>
+      <c r="G221" t="n">
+        <v>0.000371485561165672</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.0136066516801793</v>
+      </c>
+      <c r="I221"/>
+      <c r="J221" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>35</v>
+      </c>
+      <c r="B222" t="s">
+        <v>18</v>
+      </c>
+      <c r="C222" t="s">
+        <v>27</v>
+      </c>
+      <c r="D222" t="s">
+        <v>51</v>
+      </c>
+      <c r="E222"/>
+      <c r="F222"/>
+      <c r="G222" t="n">
+        <v>0.000426716702573042</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.0144062298899832</v>
+      </c>
+      <c r="I222"/>
+      <c r="J222" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>35</v>
+      </c>
+      <c r="B223" t="s">
+        <v>18</v>
+      </c>
+      <c r="C223" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223" t="s">
+        <v>52</v>
+      </c>
+      <c r="E223"/>
+      <c r="F223"/>
+      <c r="G223" t="n">
+        <v>0.000426270269863009</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.014367787948999</v>
+      </c>
+      <c r="I223"/>
+      <c r="J223" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>35</v>
+      </c>
+      <c r="B224" t="s">
+        <v>18</v>
+      </c>
+      <c r="C224" t="s">
+        <v>27</v>
+      </c>
+      <c r="D224" t="s">
+        <v>53</v>
+      </c>
+      <c r="E224"/>
+      <c r="F224"/>
+      <c r="G224" t="n">
+        <v>0.000426437348226608</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.0143911833197185</v>
+      </c>
+      <c r="I224"/>
+      <c r="J224" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>35</v>
+      </c>
+      <c r="B225" t="s">
+        <v>18</v>
+      </c>
+      <c r="C225" t="s">
+        <v>27</v>
+      </c>
+      <c r="D225" t="s">
+        <v>54</v>
+      </c>
+      <c r="E225"/>
+      <c r="F225"/>
+      <c r="G225" t="n">
+        <v>0.00042725573166905</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.0143829478503235</v>
+      </c>
+      <c r="I225"/>
+      <c r="J225" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>36</v>
+      </c>
+      <c r="B226" t="s">
+        <v>13</v>
+      </c>
+      <c r="C226" t="s">
+        <v>14</v>
+      </c>
+      <c r="D226" t="s">
+        <v>51</v>
+      </c>
+      <c r="E226"/>
+      <c r="F226"/>
+      <c r="G226" t="n">
+        <v>0.000676683744102551</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.0195906323295824</v>
+      </c>
+      <c r="I226"/>
+      <c r="J226" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>36</v>
+      </c>
+      <c r="B227" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227" t="s">
+        <v>14</v>
+      </c>
+      <c r="D227" t="s">
+        <v>52</v>
+      </c>
+      <c r="E227"/>
+      <c r="F227"/>
+      <c r="G227" t="n">
+        <v>0.000672402641346374</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.0195516649985889</v>
+      </c>
+      <c r="I227"/>
+      <c r="J227" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>36</v>
+      </c>
+      <c r="B228" t="s">
+        <v>13</v>
+      </c>
+      <c r="C228" t="s">
+        <v>14</v>
+      </c>
+      <c r="D228" t="s">
+        <v>53</v>
+      </c>
+      <c r="E228"/>
+      <c r="F228"/>
+      <c r="G228" t="n">
+        <v>0.000674521843369174</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.0195509382881051</v>
+      </c>
+      <c r="I228"/>
+      <c r="J228" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>36</v>
+      </c>
+      <c r="B229" t="s">
+        <v>13</v>
+      </c>
+      <c r="C229" t="s">
+        <v>14</v>
+      </c>
+      <c r="D229" t="s">
+        <v>54</v>
+      </c>
+      <c r="E229"/>
+      <c r="F229"/>
+      <c r="G229" t="n">
+        <v>0.000665178613114765</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.0193356982556131</v>
+      </c>
+      <c r="I229"/>
+      <c r="J229" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>36</v>
+      </c>
+      <c r="B230" t="s">
+        <v>13</v>
+      </c>
+      <c r="C230" t="s">
+        <v>16</v>
+      </c>
+      <c r="D230" t="s">
+        <v>51</v>
+      </c>
+      <c r="E230"/>
+      <c r="F230"/>
+      <c r="G230" t="n">
+        <v>0.00147293009676902</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.0273294773216034</v>
+      </c>
+      <c r="I230"/>
+      <c r="J230" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>36</v>
+      </c>
+      <c r="B231" t="s">
+        <v>13</v>
+      </c>
+      <c r="C231" t="s">
+        <v>16</v>
+      </c>
+      <c r="D231" t="s">
+        <v>52</v>
+      </c>
+      <c r="E231"/>
+      <c r="F231"/>
+      <c r="G231" t="n">
+        <v>0.00145338176945918</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.0272582267288296</v>
+      </c>
+      <c r="I231"/>
+      <c r="J231" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>36</v>
+      </c>
+      <c r="B232" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" t="s">
+        <v>16</v>
+      </c>
+      <c r="D232" t="s">
+        <v>53</v>
+      </c>
+      <c r="E232"/>
+      <c r="F232"/>
+      <c r="G232" t="n">
+        <v>0.00147087175869145</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.0272912291793638</v>
+      </c>
+      <c r="I232"/>
+      <c r="J232" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>36</v>
+      </c>
+      <c r="B233" t="s">
+        <v>13</v>
+      </c>
+      <c r="C233" t="s">
+        <v>16</v>
+      </c>
+      <c r="D233" t="s">
+        <v>54</v>
+      </c>
+      <c r="E233"/>
+      <c r="F233"/>
+      <c r="G233" t="n">
+        <v>0.00147326533405407</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.0274111584470025</v>
+      </c>
+      <c r="I233"/>
+      <c r="J233" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>36</v>
+      </c>
+      <c r="B234" t="s">
+        <v>18</v>
+      </c>
+      <c r="C234" t="s">
+        <v>19</v>
+      </c>
+      <c r="D234" t="s">
+        <v>51</v>
+      </c>
+      <c r="E234"/>
+      <c r="F234"/>
+      <c r="G234" t="n">
+        <v>0.000245667043006321</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.00909560831095478</v>
+      </c>
+      <c r="I234"/>
+      <c r="J234" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>36</v>
+      </c>
+      <c r="B235" t="s">
+        <v>18</v>
+      </c>
+      <c r="C235" t="s">
+        <v>19</v>
+      </c>
+      <c r="D235" t="s">
+        <v>52</v>
+      </c>
+      <c r="E235"/>
+      <c r="F235"/>
+      <c r="G235" t="n">
+        <v>0.000245508666508611</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.00912011750501952</v>
+      </c>
+      <c r="I235"/>
+      <c r="J235" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>36</v>
+      </c>
+      <c r="B236" t="s">
+        <v>18</v>
+      </c>
+      <c r="C236" t="s">
+        <v>19</v>
+      </c>
+      <c r="D236" t="s">
+        <v>53</v>
+      </c>
+      <c r="E236"/>
+      <c r="F236"/>
+      <c r="G236" t="n">
+        <v>0.000245235604131072</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.00908388898596218</v>
+      </c>
+      <c r="I236"/>
+      <c r="J236" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>36</v>
+      </c>
+      <c r="B237" t="s">
+        <v>18</v>
+      </c>
+      <c r="C237" t="s">
+        <v>19</v>
+      </c>
+      <c r="D237" t="s">
+        <v>54</v>
+      </c>
+      <c r="E237"/>
+      <c r="F237"/>
+      <c r="G237" t="n">
+        <v>0.000245926109953433</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.00909287451772852</v>
+      </c>
+      <c r="I237"/>
+      <c r="J237" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>36</v>
+      </c>
+      <c r="B238" t="s">
+        <v>18</v>
+      </c>
+      <c r="C238" t="s">
+        <v>21</v>
+      </c>
+      <c r="D238" t="s">
+        <v>51</v>
+      </c>
+      <c r="E238"/>
+      <c r="F238"/>
+      <c r="G238" t="n">
+        <v>0.000363177944662373</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.00922513747043332</v>
+      </c>
+      <c r="I238"/>
+      <c r="J238" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>36</v>
+      </c>
+      <c r="B239" t="s">
+        <v>18</v>
+      </c>
+      <c r="C239" t="s">
+        <v>21</v>
+      </c>
+      <c r="D239" t="s">
+        <v>52</v>
+      </c>
+      <c r="E239"/>
+      <c r="F239"/>
+      <c r="G239" t="n">
+        <v>0.00036313233845448</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.00927155021217419</v>
+      </c>
+      <c r="I239"/>
+      <c r="J239" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>36</v>
+      </c>
+      <c r="B240" t="s">
+        <v>18</v>
+      </c>
+      <c r="C240" t="s">
+        <v>21</v>
+      </c>
+      <c r="D240" t="s">
+        <v>53</v>
+      </c>
+      <c r="E240"/>
+      <c r="F240"/>
+      <c r="G240" t="n">
+        <v>0.000362668495333134</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.00922304700864093</v>
+      </c>
+      <c r="I240"/>
+      <c r="J240" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>36</v>
+      </c>
+      <c r="B241" t="s">
+        <v>18</v>
+      </c>
+      <c r="C241" t="s">
+        <v>21</v>
+      </c>
+      <c r="D241" t="s">
+        <v>54</v>
+      </c>
+      <c r="E241"/>
+      <c r="F241"/>
+      <c r="G241" t="n">
+        <v>0.000363574019713251</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.00924680370269485</v>
+      </c>
+      <c r="I241"/>
+      <c r="J241" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>36</v>
+      </c>
+      <c r="B242" t="s">
+        <v>18</v>
+      </c>
+      <c r="C242" t="s">
+        <v>23</v>
+      </c>
+      <c r="D242" t="s">
+        <v>51</v>
+      </c>
+      <c r="E242"/>
+      <c r="F242"/>
+      <c r="G242" t="n">
+        <v>0.000179094086592131</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.00885470430626591</v>
+      </c>
+      <c r="I242"/>
+      <c r="J242" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>36</v>
+      </c>
+      <c r="B243" t="s">
+        <v>18</v>
+      </c>
+      <c r="C243" t="s">
+        <v>23</v>
+      </c>
+      <c r="D243" t="s">
+        <v>52</v>
+      </c>
+      <c r="E243"/>
+      <c r="F243"/>
+      <c r="G243" t="n">
+        <v>0.0001790992604672</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0.00885761398843889</v>
+      </c>
+      <c r="I243"/>
+      <c r="J243" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>36</v>
+      </c>
+      <c r="B244" t="s">
+        <v>18</v>
+      </c>
+      <c r="C244" t="s">
+        <v>23</v>
+      </c>
+      <c r="D244" t="s">
+        <v>53</v>
+      </c>
+      <c r="E244"/>
+      <c r="F244"/>
+      <c r="G244" t="n">
+        <v>0.000179014583527614</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.00885171109735738</v>
+      </c>
+      <c r="I244"/>
+      <c r="J244" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>36</v>
+      </c>
+      <c r="B245" t="s">
+        <v>18</v>
+      </c>
+      <c r="C245" t="s">
+        <v>23</v>
+      </c>
+      <c r="D245" t="s">
+        <v>54</v>
+      </c>
+      <c r="E245"/>
+      <c r="F245"/>
+      <c r="G245" t="n">
+        <v>0.000179209259230544</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0.0088790851912377</v>
+      </c>
+      <c r="I245"/>
+      <c r="J245" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>36</v>
+      </c>
+      <c r="B246" t="s">
+        <v>18</v>
+      </c>
+      <c r="C246" t="s">
+        <v>25</v>
+      </c>
+      <c r="D246" t="s">
+        <v>51</v>
+      </c>
+      <c r="E246"/>
+      <c r="F246"/>
+      <c r="G246" t="n">
+        <v>0.000179093081742157</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0.00887060083092503</v>
+      </c>
+      <c r="I246"/>
+      <c r="J246" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>36</v>
+      </c>
+      <c r="B247" t="s">
+        <v>18</v>
+      </c>
+      <c r="C247" t="s">
+        <v>25</v>
+      </c>
+      <c r="D247" t="s">
+        <v>52</v>
+      </c>
+      <c r="E247"/>
+      <c r="F247"/>
+      <c r="G247" t="n">
+        <v>0.000180414799340363</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0.00892036372936892</v>
+      </c>
+      <c r="I247"/>
+      <c r="J247" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>36</v>
+      </c>
+      <c r="B248" t="s">
+        <v>18</v>
+      </c>
+      <c r="C248" t="s">
+        <v>25</v>
+      </c>
+      <c r="D248" t="s">
+        <v>53</v>
+      </c>
+      <c r="E248"/>
+      <c r="F248"/>
+      <c r="G248" t="n">
+        <v>0.000179241201890083</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0.00886856355378329</v>
+      </c>
+      <c r="I248"/>
+      <c r="J248" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>36</v>
+      </c>
+      <c r="B249" t="s">
+        <v>18</v>
+      </c>
+      <c r="C249" t="s">
+        <v>25</v>
+      </c>
+      <c r="D249" t="s">
+        <v>54</v>
+      </c>
+      <c r="E249"/>
+      <c r="F249"/>
+      <c r="G249" t="n">
+        <v>0.000179336892160008</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0.00888984575206539</v>
+      </c>
+      <c r="I249"/>
+      <c r="J249" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>36</v>
+      </c>
+      <c r="B250" t="s">
+        <v>18</v>
+      </c>
+      <c r="C250" t="s">
+        <v>27</v>
+      </c>
+      <c r="D250" t="s">
+        <v>51</v>
+      </c>
+      <c r="E250"/>
+      <c r="F250"/>
+      <c r="G250" t="n">
+        <v>0.000284230183519138</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0.0123020558685505</v>
+      </c>
+      <c r="I250"/>
+      <c r="J250" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>36</v>
+      </c>
+      <c r="B251" t="s">
+        <v>18</v>
+      </c>
+      <c r="C251" t="s">
+        <v>27</v>
+      </c>
+      <c r="D251" t="s">
+        <v>52</v>
+      </c>
+      <c r="E251"/>
+      <c r="F251"/>
+      <c r="G251" t="n">
+        <v>0.000283976912124149</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.0122938512280727</v>
+      </c>
+      <c r="I251"/>
+      <c r="J251" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>36</v>
+      </c>
+      <c r="B252" t="s">
+        <v>18</v>
+      </c>
+      <c r="C252" t="s">
+        <v>27</v>
+      </c>
+      <c r="D252" t="s">
+        <v>53</v>
+      </c>
+      <c r="E252"/>
+      <c r="F252"/>
+      <c r="G252" t="n">
+        <v>0.000283700990828039</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0.0122857668185328</v>
+      </c>
+      <c r="I252"/>
+      <c r="J252" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>36</v>
+      </c>
+      <c r="B253" t="s">
+        <v>18</v>
+      </c>
+      <c r="C253" t="s">
+        <v>27</v>
+      </c>
+      <c r="D253" t="s">
+        <v>54</v>
+      </c>
+      <c r="E253"/>
+      <c r="F253"/>
+      <c r="G253" t="n">
+        <v>0.000281795679579258</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0.0122357680340678</v>
+      </c>
+      <c r="I253"/>
+      <c r="J253" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>37</v>
+      </c>
+      <c r="B254" t="s">
+        <v>13</v>
+      </c>
+      <c r="C254" t="s">
+        <v>14</v>
+      </c>
+      <c r="D254" t="s">
+        <v>51</v>
+      </c>
+      <c r="E254"/>
+      <c r="F254"/>
+      <c r="G254" t="n">
+        <v>0.00222034506693136</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0.0375667427686673</v>
+      </c>
+      <c r="I254"/>
+      <c r="J254" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>37</v>
+      </c>
+      <c r="B255" t="s">
+        <v>13</v>
+      </c>
+      <c r="C255" t="s">
+        <v>14</v>
+      </c>
+      <c r="D255" t="s">
+        <v>52</v>
+      </c>
+      <c r="E255"/>
+      <c r="F255"/>
+      <c r="G255" t="n">
+        <v>0.00222974486755562</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0.0376444479794247</v>
+      </c>
+      <c r="I255"/>
+      <c r="J255" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>37</v>
+      </c>
+      <c r="B256" t="s">
+        <v>13</v>
+      </c>
+      <c r="C256" t="s">
+        <v>14</v>
+      </c>
+      <c r="D256" t="s">
+        <v>53</v>
+      </c>
+      <c r="E256"/>
+      <c r="F256"/>
+      <c r="G256" t="n">
+        <v>0.00222396599139518</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0.0375180818321421</v>
+      </c>
+      <c r="I256"/>
+      <c r="J256" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>37</v>
+      </c>
+      <c r="B257" t="s">
+        <v>13</v>
+      </c>
+      <c r="C257" t="s">
+        <v>14</v>
+      </c>
+      <c r="D257" t="s">
+        <v>54</v>
+      </c>
+      <c r="E257"/>
+      <c r="F257"/>
+      <c r="G257" t="n">
+        <v>0.00221853823235073</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0.0374711375783015</v>
+      </c>
+      <c r="I257"/>
+      <c r="J257" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>37</v>
+      </c>
+      <c r="B258" t="s">
+        <v>13</v>
+      </c>
+      <c r="C258" t="s">
+        <v>16</v>
+      </c>
+      <c r="D258" t="s">
+        <v>51</v>
+      </c>
+      <c r="E258"/>
+      <c r="F258"/>
+      <c r="G258" t="n">
+        <v>0.0018889546955675</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0.0330648105518514</v>
+      </c>
+      <c r="I258"/>
+      <c r="J258" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>37</v>
+      </c>
+      <c r="B259" t="s">
+        <v>13</v>
+      </c>
+      <c r="C259" t="s">
+        <v>16</v>
+      </c>
+      <c r="D259" t="s">
+        <v>52</v>
+      </c>
+      <c r="E259"/>
+      <c r="F259"/>
+      <c r="G259" t="n">
+        <v>0.00187455642187341</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0.0330824322389803</v>
+      </c>
+      <c r="I259"/>
+      <c r="J259" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>37</v>
+      </c>
+      <c r="B260" t="s">
+        <v>13</v>
+      </c>
+      <c r="C260" t="s">
+        <v>16</v>
+      </c>
+      <c r="D260" t="s">
+        <v>53</v>
+      </c>
+      <c r="E260"/>
+      <c r="F260"/>
+      <c r="G260" t="n">
+        <v>0.00190037166372581</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0.0333650463944738</v>
+      </c>
+      <c r="I260"/>
+      <c r="J260" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>37</v>
+      </c>
+      <c r="B261" t="s">
+        <v>13</v>
+      </c>
+      <c r="C261" t="s">
+        <v>16</v>
+      </c>
+      <c r="D261" t="s">
+        <v>54</v>
+      </c>
+      <c r="E261"/>
+      <c r="F261"/>
+      <c r="G261" t="n">
+        <v>0.00188641551977872</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0.0331862106513104</v>
+      </c>
+      <c r="I261"/>
+      <c r="J261" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>37</v>
+      </c>
+      <c r="B262" t="s">
+        <v>18</v>
+      </c>
+      <c r="C262" t="s">
+        <v>19</v>
+      </c>
+      <c r="D262" t="s">
+        <v>51</v>
+      </c>
+      <c r="E262"/>
+      <c r="F262"/>
+      <c r="G262" t="n">
+        <v>0.000514533718051439</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0.0151166361185263</v>
+      </c>
+      <c r="I262"/>
+      <c r="J262" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>37</v>
+      </c>
+      <c r="B263" t="s">
+        <v>18</v>
+      </c>
+      <c r="C263" t="s">
+        <v>19</v>
+      </c>
+      <c r="D263" t="s">
+        <v>52</v>
+      </c>
+      <c r="E263"/>
+      <c r="F263"/>
+      <c r="G263" t="n">
+        <v>0.000515440328913552</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0.0151339042580849</v>
+      </c>
+      <c r="I263"/>
+      <c r="J263" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>37</v>
+      </c>
+      <c r="B264" t="s">
+        <v>18</v>
+      </c>
+      <c r="C264" t="s">
+        <v>19</v>
+      </c>
+      <c r="D264" t="s">
+        <v>53</v>
+      </c>
+      <c r="E264"/>
+      <c r="F264"/>
+      <c r="G264" t="n">
+        <v>0.000514905484997201</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0.0151514742124416</v>
+      </c>
+      <c r="I264"/>
+      <c r="J264" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>37</v>
+      </c>
+      <c r="B265" t="s">
+        <v>18</v>
+      </c>
+      <c r="C265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D265" t="s">
+        <v>54</v>
+      </c>
+      <c r="E265"/>
+      <c r="F265"/>
+      <c r="G265" t="n">
+        <v>0.000515239765876212</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0.0151179041015629</v>
+      </c>
+      <c r="I265"/>
+      <c r="J265" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>37</v>
+      </c>
+      <c r="B266" t="s">
+        <v>18</v>
+      </c>
+      <c r="C266" t="s">
+        <v>21</v>
+      </c>
+      <c r="D266" t="s">
+        <v>51</v>
+      </c>
+      <c r="E266"/>
+      <c r="F266"/>
+      <c r="G266" t="n">
+        <v>0.000640830207937886</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0.0152817485280177</v>
+      </c>
+      <c r="I266"/>
+      <c r="J266" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>37</v>
+      </c>
+      <c r="B267" t="s">
+        <v>18</v>
+      </c>
+      <c r="C267" t="s">
+        <v>21</v>
+      </c>
+      <c r="D267" t="s">
+        <v>52</v>
+      </c>
+      <c r="E267"/>
+      <c r="F267"/>
+      <c r="G267" t="n">
+        <v>0.000640258379930802</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0.0152913933628545</v>
+      </c>
+      <c r="I267"/>
+      <c r="J267" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>37</v>
+      </c>
+      <c r="B268" t="s">
+        <v>18</v>
+      </c>
+      <c r="C268" t="s">
+        <v>21</v>
+      </c>
+      <c r="D268" t="s">
+        <v>53</v>
+      </c>
+      <c r="E268"/>
+      <c r="F268"/>
+      <c r="G268" t="n">
+        <v>0.000642016778103838</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0.015293282567136</v>
+      </c>
+      <c r="I268"/>
+      <c r="J268" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>37</v>
+      </c>
+      <c r="B269" t="s">
+        <v>18</v>
+      </c>
+      <c r="C269" t="s">
+        <v>21</v>
+      </c>
+      <c r="D269" t="s">
+        <v>54</v>
+      </c>
+      <c r="E269"/>
+      <c r="F269"/>
+      <c r="G269" t="n">
+        <v>0.000645805505998343</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.0153264316435137</v>
+      </c>
+      <c r="I269"/>
+      <c r="J269" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>37</v>
+      </c>
+      <c r="B270" t="s">
+        <v>18</v>
+      </c>
+      <c r="C270" t="s">
+        <v>23</v>
+      </c>
+      <c r="D270" t="s">
+        <v>51</v>
+      </c>
+      <c r="E270"/>
+      <c r="F270"/>
+      <c r="G270" t="n">
+        <v>0.000436907508801859</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0.0149200441915959</v>
+      </c>
+      <c r="I270"/>
+      <c r="J270" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>37</v>
+      </c>
+      <c r="B271" t="s">
+        <v>18</v>
+      </c>
+      <c r="C271" t="s">
+        <v>23</v>
+      </c>
+      <c r="D271" t="s">
+        <v>52</v>
+      </c>
+      <c r="E271"/>
+      <c r="F271"/>
+      <c r="G271" t="n">
+        <v>0.000437400990245494</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.0149021126991485</v>
+      </c>
+      <c r="I271"/>
+      <c r="J271" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>37</v>
+      </c>
+      <c r="B272" t="s">
+        <v>18</v>
+      </c>
+      <c r="C272" t="s">
+        <v>23</v>
+      </c>
+      <c r="D272" t="s">
+        <v>53</v>
+      </c>
+      <c r="E272"/>
+      <c r="F272"/>
+      <c r="G272" t="n">
+        <v>0.000438974027144353</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.0149692419247107</v>
+      </c>
+      <c r="I272"/>
+      <c r="J272" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>37</v>
+      </c>
+      <c r="B273" t="s">
+        <v>18</v>
+      </c>
+      <c r="C273" t="s">
+        <v>23</v>
+      </c>
+      <c r="D273" t="s">
+        <v>54</v>
+      </c>
+      <c r="E273"/>
+      <c r="F273"/>
+      <c r="G273" t="n">
+        <v>0.000439562419615105</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0.0149611573815002</v>
+      </c>
+      <c r="I273"/>
+      <c r="J273" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>37</v>
+      </c>
+      <c r="B274" t="s">
+        <v>18</v>
+      </c>
+      <c r="C274" t="s">
+        <v>25</v>
+      </c>
+      <c r="D274" t="s">
+        <v>51</v>
+      </c>
+      <c r="E274"/>
+      <c r="F274"/>
+      <c r="G274" t="n">
+        <v>0.000440239772668997</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0.0149475624463968</v>
+      </c>
+      <c r="I274"/>
+      <c r="J274" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>37</v>
+      </c>
+      <c r="B275" t="s">
+        <v>18</v>
+      </c>
+      <c r="C275" t="s">
+        <v>25</v>
+      </c>
+      <c r="D275" t="s">
+        <v>52</v>
+      </c>
+      <c r="E275"/>
+      <c r="F275"/>
+      <c r="G275" t="n">
+        <v>0.000440801401507655</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0.0149916547717679</v>
+      </c>
+      <c r="I275"/>
+      <c r="J275" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>37</v>
+      </c>
+      <c r="B276" t="s">
+        <v>18</v>
+      </c>
+      <c r="C276" t="s">
+        <v>25</v>
+      </c>
+      <c r="D276" t="s">
+        <v>53</v>
+      </c>
+      <c r="E276"/>
+      <c r="F276"/>
+      <c r="G276" t="n">
+        <v>0.000442869623975716</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0.014981017447499</v>
+      </c>
+      <c r="I276"/>
+      <c r="J276" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>37</v>
+      </c>
+      <c r="B277" t="s">
+        <v>18</v>
+      </c>
+      <c r="C277" t="s">
+        <v>25</v>
+      </c>
+      <c r="D277" t="s">
+        <v>54</v>
+      </c>
+      <c r="E277"/>
+      <c r="F277"/>
+      <c r="G277" t="n">
+        <v>0.000439274651804825</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0.0149516270836447</v>
+      </c>
+      <c r="I277"/>
+      <c r="J277" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>37</v>
+      </c>
+      <c r="B278" t="s">
+        <v>18</v>
+      </c>
+      <c r="C278" t="s">
+        <v>27</v>
+      </c>
+      <c r="D278" t="s">
+        <v>51</v>
+      </c>
+      <c r="E278"/>
+      <c r="F278"/>
+      <c r="G278" t="n">
+        <v>0.000528522689644326</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0.0166735460634388</v>
+      </c>
+      <c r="I278"/>
+      <c r="J278" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>37</v>
+      </c>
+      <c r="B279" t="s">
+        <v>18</v>
+      </c>
+      <c r="C279" t="s">
+        <v>27</v>
+      </c>
+      <c r="D279" t="s">
+        <v>52</v>
+      </c>
+      <c r="E279"/>
+      <c r="F279"/>
+      <c r="G279" t="n">
+        <v>0.000527247019961752</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0.016649749741123</v>
+      </c>
+      <c r="I279"/>
+      <c r="J279" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>37</v>
+      </c>
+      <c r="B280" t="s">
+        <v>18</v>
+      </c>
+      <c r="C280" t="s">
+        <v>27</v>
+      </c>
+      <c r="D280" t="s">
+        <v>53</v>
+      </c>
+      <c r="E280"/>
+      <c r="F280"/>
+      <c r="G280" t="n">
+        <v>0.000524877128533772</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0.0166054349794582</v>
+      </c>
+      <c r="I280"/>
+      <c r="J280" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>37</v>
+      </c>
+      <c r="B281" t="s">
+        <v>18</v>
+      </c>
+      <c r="C281" t="s">
+        <v>27</v>
+      </c>
+      <c r="D281" t="s">
+        <v>54</v>
+      </c>
+      <c r="E281"/>
+      <c r="F281"/>
+      <c r="G281" t="n">
+        <v>0.000527821145493357</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0.0166312672261733</v>
+      </c>
+      <c r="I281"/>
+      <c r="J281" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>38</v>
+      </c>
+      <c r="B282" t="s">
+        <v>13</v>
+      </c>
+      <c r="C282" t="s">
+        <v>14</v>
+      </c>
+      <c r="D282" t="s">
+        <v>51</v>
+      </c>
+      <c r="E282"/>
+      <c r="F282"/>
+      <c r="G282" t="n">
+        <v>0.00070411440216239</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0.0196794423566483</v>
+      </c>
+      <c r="I282"/>
+      <c r="J282" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>38</v>
+      </c>
+      <c r="B283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C283" t="s">
+        <v>14</v>
+      </c>
+      <c r="D283" t="s">
+        <v>52</v>
+      </c>
+      <c r="E283"/>
+      <c r="F283"/>
+      <c r="G283" t="n">
+        <v>0.000707769054580787</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0.0197841079457453</v>
+      </c>
+      <c r="I283"/>
+      <c r="J283" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>38</v>
+      </c>
+      <c r="B284" t="s">
+        <v>13</v>
+      </c>
+      <c r="C284" t="s">
+        <v>14</v>
+      </c>
+      <c r="D284" t="s">
+        <v>53</v>
+      </c>
+      <c r="E284"/>
+      <c r="F284"/>
+      <c r="G284" t="n">
+        <v>0.000705675444861752</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0.0197220483991037</v>
+      </c>
+      <c r="I284"/>
+      <c r="J284" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>38</v>
+      </c>
+      <c r="B285" t="s">
+        <v>13</v>
+      </c>
+      <c r="C285" t="s">
+        <v>14</v>
+      </c>
+      <c r="D285" t="s">
+        <v>54</v>
+      </c>
+      <c r="E285"/>
+      <c r="F285"/>
+      <c r="G285" t="n">
+        <v>0.000695121189078302</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0.0194886958785798</v>
+      </c>
+      <c r="I285"/>
+      <c r="J285" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>38</v>
+      </c>
+      <c r="B286" t="s">
+        <v>13</v>
+      </c>
+      <c r="C286" t="s">
+        <v>16</v>
+      </c>
+      <c r="D286" t="s">
+        <v>51</v>
+      </c>
+      <c r="E286"/>
+      <c r="F286"/>
+      <c r="G286" t="n">
+        <v>0.00117788518234075</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0.0232288802362696</v>
+      </c>
+      <c r="I286"/>
+      <c r="J286" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>38</v>
+      </c>
+      <c r="B287" t="s">
+        <v>13</v>
+      </c>
+      <c r="C287" t="s">
+        <v>16</v>
+      </c>
+      <c r="D287" t="s">
+        <v>52</v>
+      </c>
+      <c r="E287"/>
+      <c r="F287"/>
+      <c r="G287" t="n">
+        <v>0.00117303493704195</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0.0231616501701721</v>
+      </c>
+      <c r="I287"/>
+      <c r="J287" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>38</v>
+      </c>
+      <c r="B288" t="s">
+        <v>13</v>
+      </c>
+      <c r="C288" t="s">
+        <v>16</v>
+      </c>
+      <c r="D288" t="s">
+        <v>53</v>
+      </c>
+      <c r="E288"/>
+      <c r="F288"/>
+      <c r="G288" t="n">
+        <v>0.00117005142071227</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0.0232863371780439</v>
+      </c>
+      <c r="I288"/>
+      <c r="J288" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>38</v>
+      </c>
+      <c r="B289" t="s">
+        <v>13</v>
+      </c>
+      <c r="C289" t="s">
+        <v>16</v>
+      </c>
+      <c r="D289" t="s">
+        <v>54</v>
+      </c>
+      <c r="E289"/>
+      <c r="F289"/>
+      <c r="G289" t="n">
+        <v>0.00119066653109012</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0.0233782537376481</v>
+      </c>
+      <c r="I289"/>
+      <c r="J289" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>38</v>
+      </c>
+      <c r="B290" t="s">
+        <v>18</v>
+      </c>
+      <c r="C290" t="s">
+        <v>19</v>
+      </c>
+      <c r="D290" t="s">
+        <v>51</v>
+      </c>
+      <c r="E290"/>
+      <c r="F290"/>
+      <c r="G290" t="n">
+        <v>0.000267010375005786</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0.00940153435834409</v>
+      </c>
+      <c r="I290"/>
+      <c r="J290" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>38</v>
+      </c>
+      <c r="B291" t="s">
+        <v>18</v>
+      </c>
+      <c r="C291" t="s">
+        <v>19</v>
+      </c>
+      <c r="D291" t="s">
+        <v>52</v>
+      </c>
+      <c r="E291"/>
+      <c r="F291"/>
+      <c r="G291" t="n">
+        <v>0.0002661307046103</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0.00937078107353905</v>
+      </c>
+      <c r="I291"/>
+      <c r="J291" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>38</v>
+      </c>
+      <c r="B292" t="s">
+        <v>18</v>
+      </c>
+      <c r="C292" t="s">
+        <v>19</v>
+      </c>
+      <c r="D292" t="s">
+        <v>53</v>
+      </c>
+      <c r="E292"/>
+      <c r="F292"/>
+      <c r="G292" t="n">
+        <v>0.000267080134588328</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0.00938632489551913</v>
+      </c>
+      <c r="I292"/>
+      <c r="J292" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>38</v>
+      </c>
+      <c r="B293" t="s">
+        <v>18</v>
+      </c>
+      <c r="C293" t="s">
+        <v>19</v>
+      </c>
+      <c r="D293" t="s">
+        <v>54</v>
+      </c>
+      <c r="E293"/>
+      <c r="F293"/>
+      <c r="G293" t="n">
+        <v>0.000268782673121551</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0.00941393563579777</v>
+      </c>
+      <c r="I293"/>
+      <c r="J293" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>38</v>
+      </c>
+      <c r="B294" t="s">
+        <v>18</v>
+      </c>
+      <c r="C294" t="s">
+        <v>21</v>
+      </c>
+      <c r="D294" t="s">
+        <v>51</v>
+      </c>
+      <c r="E294"/>
+      <c r="F294"/>
+      <c r="G294" t="n">
+        <v>0.000381651812090491</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0.00950991135700453</v>
+      </c>
+      <c r="I294"/>
+      <c r="J294" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>38</v>
+      </c>
+      <c r="B295" t="s">
+        <v>18</v>
+      </c>
+      <c r="C295" t="s">
+        <v>21</v>
+      </c>
+      <c r="D295" t="s">
+        <v>52</v>
+      </c>
+      <c r="E295"/>
+      <c r="F295"/>
+      <c r="G295" t="n">
+        <v>0.000384637421848706</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0.00958194764415019</v>
+      </c>
+      <c r="I295"/>
+      <c r="J295" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>38</v>
+      </c>
+      <c r="B296" t="s">
+        <v>18</v>
+      </c>
+      <c r="C296" t="s">
+        <v>21</v>
+      </c>
+      <c r="D296" t="s">
+        <v>53</v>
+      </c>
+      <c r="E296"/>
+      <c r="F296"/>
+      <c r="G296" t="n">
+        <v>0.000382977512560856</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0.00952928113782215</v>
+      </c>
+      <c r="I296"/>
+      <c r="J296" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>38</v>
+      </c>
+      <c r="B297" t="s">
+        <v>18</v>
+      </c>
+      <c r="C297" t="s">
+        <v>21</v>
+      </c>
+      <c r="D297" t="s">
+        <v>54</v>
+      </c>
+      <c r="E297"/>
+      <c r="F297"/>
+      <c r="G297" t="n">
+        <v>0.000384151550277469</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0.00958593436865354</v>
+      </c>
+      <c r="I297"/>
+      <c r="J297" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>38</v>
+      </c>
+      <c r="B298" t="s">
+        <v>18</v>
+      </c>
+      <c r="C298" t="s">
+        <v>23</v>
+      </c>
+      <c r="D298" t="s">
+        <v>51</v>
+      </c>
+      <c r="E298"/>
+      <c r="F298"/>
+      <c r="G298" t="n">
+        <v>0.000203079140737354</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0.00918072600219778</v>
+      </c>
+      <c r="I298"/>
+      <c r="J298" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>38</v>
+      </c>
+      <c r="B299" t="s">
+        <v>18</v>
+      </c>
+      <c r="C299" t="s">
+        <v>23</v>
+      </c>
+      <c r="D299" t="s">
+        <v>52</v>
+      </c>
+      <c r="E299"/>
+      <c r="F299"/>
+      <c r="G299" t="n">
+        <v>0.000203975252866073</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0.00920397260927467</v>
+      </c>
+      <c r="I299"/>
+      <c r="J299" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>38</v>
+      </c>
+      <c r="B300" t="s">
+        <v>18</v>
+      </c>
+      <c r="C300" t="s">
+        <v>23</v>
+      </c>
+      <c r="D300" t="s">
+        <v>53</v>
+      </c>
+      <c r="E300"/>
+      <c r="F300"/>
+      <c r="G300" t="n">
+        <v>0.000202054082550471</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0.00916177081136317</v>
+      </c>
+      <c r="I300"/>
+      <c r="J300" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>38</v>
+      </c>
+      <c r="B301" t="s">
+        <v>18</v>
+      </c>
+      <c r="C301" t="s">
+        <v>23</v>
+      </c>
+      <c r="D301" t="s">
+        <v>54</v>
+      </c>
+      <c r="E301"/>
+      <c r="F301"/>
+      <c r="G301" t="n">
+        <v>0.000203819966730454</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0.00919849175452202</v>
+      </c>
+      <c r="I301"/>
+      <c r="J301" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>38</v>
+      </c>
+      <c r="B302" t="s">
+        <v>18</v>
+      </c>
+      <c r="C302" t="s">
+        <v>25</v>
+      </c>
+      <c r="D302" t="s">
+        <v>51</v>
+      </c>
+      <c r="E302"/>
+      <c r="F302"/>
+      <c r="G302" t="n">
+        <v>0.00020229645644614</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0.00917672302291868</v>
+      </c>
+      <c r="I302"/>
+      <c r="J302" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>38</v>
+      </c>
+      <c r="B303" t="s">
+        <v>18</v>
+      </c>
+      <c r="C303" t="s">
+        <v>25</v>
+      </c>
+      <c r="D303" t="s">
+        <v>52</v>
+      </c>
+      <c r="E303"/>
+      <c r="F303"/>
+      <c r="G303" t="n">
+        <v>0.00020373007730466</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0.00921828681196115</v>
+      </c>
+      <c r="I303"/>
+      <c r="J303" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>38</v>
+      </c>
+      <c r="B304" t="s">
+        <v>18</v>
+      </c>
+      <c r="C304" t="s">
+        <v>25</v>
+      </c>
+      <c r="D304" t="s">
+        <v>53</v>
+      </c>
+      <c r="E304"/>
+      <c r="F304"/>
+      <c r="G304" t="n">
+        <v>0.000202890710948747</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0.00917617232216271</v>
+      </c>
+      <c r="I304"/>
+      <c r="J304" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>38</v>
+      </c>
+      <c r="B305" t="s">
+        <v>18</v>
+      </c>
+      <c r="C305" t="s">
+        <v>25</v>
+      </c>
+      <c r="D305" t="s">
+        <v>54</v>
+      </c>
+      <c r="E305"/>
+      <c r="F305"/>
+      <c r="G305" t="n">
+        <v>0.000202763208249227</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0.00919822767957409</v>
+      </c>
+      <c r="I305"/>
+      <c r="J305" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>38</v>
+      </c>
+      <c r="B306" t="s">
+        <v>18</v>
+      </c>
+      <c r="C306" t="s">
+        <v>27</v>
+      </c>
+      <c r="D306" t="s">
+        <v>51</v>
+      </c>
+      <c r="E306"/>
+      <c r="F306"/>
+      <c r="G306" t="n">
+        <v>0.000315033808339458</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0.0129531707253145</v>
+      </c>
+      <c r="I306"/>
+      <c r="J306" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>38</v>
+      </c>
+      <c r="B307" t="s">
+        <v>18</v>
+      </c>
+      <c r="C307" t="s">
+        <v>27</v>
+      </c>
+      <c r="D307" t="s">
+        <v>52</v>
+      </c>
+      <c r="E307"/>
+      <c r="F307"/>
+      <c r="G307" t="n">
+        <v>0.000314830321269798</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0.0129224656595199</v>
+      </c>
+      <c r="I307"/>
+      <c r="J307" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>38</v>
+      </c>
+      <c r="B308" t="s">
+        <v>18</v>
+      </c>
+      <c r="C308" t="s">
+        <v>27</v>
+      </c>
+      <c r="D308" t="s">
+        <v>53</v>
+      </c>
+      <c r="E308"/>
+      <c r="F308"/>
+      <c r="G308" t="n">
+        <v>0.000314769139770439</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0.0129234500292938</v>
+      </c>
+      <c r="I308"/>
+      <c r="J308" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>38</v>
+      </c>
+      <c r="B309" t="s">
+        <v>18</v>
+      </c>
+      <c r="C309" t="s">
+        <v>27</v>
+      </c>
+      <c r="D309" t="s">
+        <v>54</v>
+      </c>
+      <c r="E309"/>
+      <c r="F309"/>
+      <c r="G309" t="n">
+        <v>0.000316640054414869</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0.0129641190031284</v>
+      </c>
+      <c r="I309"/>
+      <c r="J309" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>39</v>
+      </c>
+      <c r="B310" t="s">
+        <v>13</v>
+      </c>
+      <c r="C310" t="s">
+        <v>14</v>
+      </c>
+      <c r="D310" t="s">
+        <v>51</v>
+      </c>
+      <c r="E310"/>
+      <c r="F310"/>
+      <c r="G310" t="n">
+        <v>0.00264908621603129</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0.0395380211134714</v>
+      </c>
+      <c r="I310"/>
+      <c r="J310" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>39</v>
+      </c>
+      <c r="B311" t="s">
+        <v>13</v>
+      </c>
+      <c r="C311" t="s">
+        <v>14</v>
+      </c>
+      <c r="D311" t="s">
+        <v>52</v>
+      </c>
+      <c r="E311"/>
+      <c r="F311"/>
+      <c r="G311" t="n">
+        <v>0.00265368151762362</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0.0396173482857403</v>
+      </c>
+      <c r="I311"/>
+      <c r="J311" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>39</v>
+      </c>
+      <c r="B312" t="s">
+        <v>13</v>
+      </c>
+      <c r="C312" t="s">
+        <v>14</v>
+      </c>
+      <c r="D312" t="s">
+        <v>53</v>
+      </c>
+      <c r="E312"/>
+      <c r="F312"/>
+      <c r="G312" t="n">
+        <v>0.00263829428268923</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0.0394877944442211</v>
+      </c>
+      <c r="I312"/>
+      <c r="J312" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>39</v>
+      </c>
+      <c r="B313" t="s">
+        <v>13</v>
+      </c>
+      <c r="C313" t="s">
+        <v>14</v>
+      </c>
+      <c r="D313" t="s">
+        <v>54</v>
+      </c>
+      <c r="E313"/>
+      <c r="F313"/>
+      <c r="G313" t="n">
+        <v>0.00266680163467614</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0.0398686205905827</v>
+      </c>
+      <c r="I313"/>
+      <c r="J313" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>39</v>
+      </c>
+      <c r="B314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314" t="s">
+        <v>16</v>
+      </c>
+      <c r="D314" t="s">
+        <v>51</v>
+      </c>
+      <c r="E314"/>
+      <c r="F314"/>
+      <c r="G314" t="n">
+        <v>0.00109361025451632</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0.0251284767636314</v>
+      </c>
+      <c r="I314"/>
+      <c r="J314" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>39</v>
+      </c>
+      <c r="B315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C315" t="s">
+        <v>16</v>
+      </c>
+      <c r="D315" t="s">
+        <v>52</v>
+      </c>
+      <c r="E315"/>
+      <c r="F315"/>
+      <c r="G315" t="n">
+        <v>0.0010987841194942</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0.0250568515967064</v>
+      </c>
+      <c r="I315"/>
+      <c r="J315" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>39</v>
+      </c>
+      <c r="B316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" t="s">
+        <v>16</v>
+      </c>
+      <c r="D316" t="s">
+        <v>53</v>
+      </c>
+      <c r="E316"/>
+      <c r="F316"/>
+      <c r="G316" t="n">
+        <v>0.00109943898237892</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0.0253935864123892</v>
+      </c>
+      <c r="I316"/>
+      <c r="J316" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>39</v>
+      </c>
+      <c r="B317" t="s">
+        <v>13</v>
+      </c>
+      <c r="C317" t="s">
+        <v>16</v>
+      </c>
+      <c r="D317" t="s">
+        <v>54</v>
+      </c>
+      <c r="E317"/>
+      <c r="F317"/>
+      <c r="G317" t="n">
+        <v>0.00109919167580229</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0.0252153462937176</v>
+      </c>
+      <c r="I317"/>
+      <c r="J317" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>39</v>
+      </c>
+      <c r="B318" t="s">
+        <v>18</v>
+      </c>
+      <c r="C318" t="s">
+        <v>19</v>
+      </c>
+      <c r="D318" t="s">
+        <v>51</v>
+      </c>
+      <c r="E318"/>
+      <c r="F318"/>
+      <c r="G318" t="n">
+        <v>0.000582332833114269</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0.0163983845440508</v>
+      </c>
+      <c r="I318"/>
+      <c r="J318" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>39</v>
+      </c>
+      <c r="B319" t="s">
+        <v>18</v>
+      </c>
+      <c r="C319" t="s">
+        <v>19</v>
+      </c>
+      <c r="D319" t="s">
+        <v>52</v>
+      </c>
+      <c r="E319"/>
+      <c r="F319"/>
+      <c r="G319" t="n">
+        <v>0.000581350924409201</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0.0164257639698158</v>
+      </c>
+      <c r="I319"/>
+      <c r="J319" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>39</v>
+      </c>
+      <c r="B320" t="s">
+        <v>18</v>
+      </c>
+      <c r="C320" t="s">
+        <v>19</v>
+      </c>
+      <c r="D320" t="s">
+        <v>53</v>
+      </c>
+      <c r="E320"/>
+      <c r="F320"/>
+      <c r="G320" t="n">
+        <v>0.000582494628436274</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0.0164309395323363</v>
+      </c>
+      <c r="I320"/>
+      <c r="J320" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>39</v>
+      </c>
+      <c r="B321" t="s">
+        <v>18</v>
+      </c>
+      <c r="C321" t="s">
+        <v>19</v>
+      </c>
+      <c r="D321" t="s">
+        <v>54</v>
+      </c>
+      <c r="E321"/>
+      <c r="F321"/>
+      <c r="G321" t="n">
+        <v>0.000582846251377214</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0.0164117970227086</v>
+      </c>
+      <c r="I321"/>
+      <c r="J321" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>39</v>
+      </c>
+      <c r="B322" t="s">
+        <v>18</v>
+      </c>
+      <c r="C322" t="s">
+        <v>21</v>
+      </c>
+      <c r="D322" t="s">
+        <v>51</v>
+      </c>
+      <c r="E322"/>
+      <c r="F322"/>
+      <c r="G322" t="n">
+        <v>0.000704045661935989</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0.0165742922810511</v>
+      </c>
+      <c r="I322"/>
+      <c r="J322" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>39</v>
+      </c>
+      <c r="B323" t="s">
+        <v>18</v>
+      </c>
+      <c r="C323" t="s">
+        <v>21</v>
+      </c>
+      <c r="D323" t="s">
+        <v>52</v>
+      </c>
+      <c r="E323"/>
+      <c r="F323"/>
+      <c r="G323" t="n">
+        <v>0.000698666394060779</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0.0165534995761449</v>
+      </c>
+      <c r="I323"/>
+      <c r="J323" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>39</v>
+      </c>
+      <c r="B324" t="s">
+        <v>18</v>
+      </c>
+      <c r="C324" t="s">
+        <v>21</v>
+      </c>
+      <c r="D324" t="s">
+        <v>53</v>
+      </c>
+      <c r="E324"/>
+      <c r="F324"/>
+      <c r="G324" t="n">
+        <v>0.000703156717183897</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0.0165429703438941</v>
+      </c>
+      <c r="I324"/>
+      <c r="J324" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>39</v>
+      </c>
+      <c r="B325" t="s">
+        <v>18</v>
+      </c>
+      <c r="C325" t="s">
+        <v>21</v>
+      </c>
+      <c r="D325" t="s">
+        <v>54</v>
+      </c>
+      <c r="E325"/>
+      <c r="F325"/>
+      <c r="G325" t="n">
+        <v>0.000703096841472074</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0.0165296594022499</v>
+      </c>
+      <c r="I325"/>
+      <c r="J325" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>39</v>
+      </c>
+      <c r="B326" t="s">
+        <v>18</v>
+      </c>
+      <c r="C326" t="s">
+        <v>23</v>
+      </c>
+      <c r="D326" t="s">
+        <v>51</v>
+      </c>
+      <c r="E326"/>
+      <c r="F326"/>
+      <c r="G326" t="n">
+        <v>0.000516610233084458</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0.016207231896124</v>
+      </c>
+      <c r="I326"/>
+      <c r="J326" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>39</v>
+      </c>
+      <c r="B327" t="s">
+        <v>18</v>
+      </c>
+      <c r="C327" t="s">
+        <v>23</v>
+      </c>
+      <c r="D327" t="s">
+        <v>52</v>
+      </c>
+      <c r="E327"/>
+      <c r="F327"/>
+      <c r="G327" t="n">
+        <v>0.000516594746054939</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0.0162158535756479</v>
+      </c>
+      <c r="I327"/>
+      <c r="J327" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>39</v>
+      </c>
+      <c r="B328" t="s">
+        <v>18</v>
+      </c>
+      <c r="C328" t="s">
+        <v>23</v>
+      </c>
+      <c r="D328" t="s">
+        <v>53</v>
+      </c>
+      <c r="E328"/>
+      <c r="F328"/>
+      <c r="G328" t="n">
+        <v>0.000513262261743514</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0.0161382927968462</v>
+      </c>
+      <c r="I328"/>
+      <c r="J328" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>39</v>
+      </c>
+      <c r="B329" t="s">
+        <v>18</v>
+      </c>
+      <c r="C329" t="s">
+        <v>23</v>
+      </c>
+      <c r="D329" t="s">
+        <v>54</v>
+      </c>
+      <c r="E329"/>
+      <c r="F329"/>
+      <c r="G329" t="n">
+        <v>0.000515760320382338</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0.0161686910394189</v>
+      </c>
+      <c r="I329"/>
+      <c r="J329" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>39</v>
+      </c>
+      <c r="B330" t="s">
+        <v>18</v>
+      </c>
+      <c r="C330" t="s">
+        <v>25</v>
+      </c>
+      <c r="D330" t="s">
+        <v>51</v>
+      </c>
+      <c r="E330"/>
+      <c r="F330"/>
+      <c r="G330" t="n">
+        <v>0.000516258147487233</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0.016184083399079</v>
+      </c>
+      <c r="I330"/>
+      <c r="J330" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>39</v>
+      </c>
+      <c r="B331" t="s">
+        <v>18</v>
+      </c>
+      <c r="C331" t="s">
+        <v>25</v>
+      </c>
+      <c r="D331" t="s">
+        <v>52</v>
+      </c>
+      <c r="E331"/>
+      <c r="F331"/>
+      <c r="G331" t="n">
+        <v>0.000514770195512859</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0.0161854871931729</v>
+      </c>
+      <c r="I331"/>
+      <c r="J331" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>39</v>
+      </c>
+      <c r="B332" t="s">
+        <v>18</v>
+      </c>
+      <c r="C332" t="s">
+        <v>25</v>
+      </c>
+      <c r="D332" t="s">
+        <v>53</v>
+      </c>
+      <c r="E332"/>
+      <c r="F332"/>
+      <c r="G332" t="n">
+        <v>0.000517292357147806</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0.0162066221381579</v>
+      </c>
+      <c r="I332"/>
+      <c r="J332" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>39</v>
+      </c>
+      <c r="B333" t="s">
+        <v>18</v>
+      </c>
+      <c r="C333" t="s">
+        <v>25</v>
+      </c>
+      <c r="D333" t="s">
+        <v>54</v>
+      </c>
+      <c r="E333"/>
+      <c r="F333"/>
+      <c r="G333" t="n">
+        <v>0.000513457611305057</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0.0161762135502516</v>
+      </c>
+      <c r="I333"/>
+      <c r="J333" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>39</v>
+      </c>
+      <c r="B334" t="s">
+        <v>18</v>
+      </c>
+      <c r="C334" t="s">
+        <v>27</v>
+      </c>
+      <c r="D334" t="s">
+        <v>51</v>
+      </c>
+      <c r="E334"/>
+      <c r="F334"/>
+      <c r="G334" t="n">
+        <v>0.000473090273945446</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0.0158824979442953</v>
+      </c>
+      <c r="I334"/>
+      <c r="J334" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>39</v>
+      </c>
+      <c r="B335" t="s">
+        <v>18</v>
+      </c>
+      <c r="C335" t="s">
+        <v>27</v>
+      </c>
+      <c r="D335" t="s">
+        <v>52</v>
+      </c>
+      <c r="E335"/>
+      <c r="F335"/>
+      <c r="G335" t="n">
+        <v>0.000475307077472086</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0.0159183925724936</v>
+      </c>
+      <c r="I335"/>
+      <c r="J335" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>39</v>
+      </c>
+      <c r="B336" t="s">
+        <v>18</v>
+      </c>
+      <c r="C336" t="s">
+        <v>27</v>
+      </c>
+      <c r="D336" t="s">
+        <v>53</v>
+      </c>
+      <c r="E336"/>
+      <c r="F336"/>
+      <c r="G336" t="n">
+        <v>0.000470733480231767</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0.0158365255178594</v>
+      </c>
+      <c r="I336"/>
+      <c r="J336" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>39</v>
+      </c>
+      <c r="B337" t="s">
+        <v>18</v>
+      </c>
+      <c r="C337" t="s">
+        <v>27</v>
+      </c>
+      <c r="D337" t="s">
+        <v>54</v>
+      </c>
+      <c r="E337"/>
+      <c r="F337"/>
+      <c r="G337" t="n">
+        <v>0.00048581664370594</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0.0161947088315407</v>
+      </c>
+      <c r="I337"/>
+      <c r="J337" t="n">
         <v>904</v>
       </c>
     </row>
@@ -6569,19 +12383,19 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
@@ -6589,16 +12403,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00119809867253835</v>
+        <v>0.00102575218626251</v>
       </c>
       <c r="F2" t="e">
         <v>#NUM!</v>
@@ -6609,16 +12423,16 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001199111891896</v>
+        <v>0.00102114188842137</v>
       </c>
       <c r="F3" t="e">
         <v>#NUM!</v>
@@ -6629,16 +12443,16 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00119954088899831</v>
+        <v>0.00102337050718631</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -6649,16 +12463,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D5" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0011959589624099</v>
+        <v>0.00102608526714088</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -6669,16 +12483,16 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D6" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00146957614366458</v>
+        <v>0.00111322095273585</v>
       </c>
       <c r="F6" t="e">
         <v>#NUM!</v>
@@ -6689,16 +12503,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D7" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00147559748199105</v>
+        <v>0.00111758615835052</v>
       </c>
       <c r="F7" t="e">
         <v>#NUM!</v>
@@ -6709,16 +12523,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00146812549072999</v>
+        <v>0.00111181465518843</v>
       </c>
       <c r="F8" t="e">
         <v>#NUM!</v>
@@ -6729,16 +12543,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D9" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0014690332222688</v>
+        <v>0.00111984376508934</v>
       </c>
       <c r="F9" t="e">
         <v>#NUM!</v>
@@ -6749,16 +12563,16 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D10" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000402160896320226</v>
+        <v>0.000338693094962634</v>
       </c>
       <c r="F10" t="e">
         <v>#NUM!</v>
@@ -6769,16 +12583,16 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D11" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000404571293534656</v>
+        <v>0.000340154260899959</v>
       </c>
       <c r="F11" t="e">
         <v>#NUM!</v>
@@ -6789,16 +12603,16 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D12" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000408737426099211</v>
+        <v>0.000340581884273816</v>
       </c>
       <c r="F12" t="e">
         <v>#NUM!</v>
@@ -6809,16 +12623,16 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D13" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000401469279908919</v>
+        <v>0.000337850401369121</v>
       </c>
       <c r="F13" t="e">
         <v>#NUM!</v>
@@ -6829,16 +12643,16 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D14" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000441462183266898</v>
+        <v>0.000338215498148319</v>
       </c>
       <c r="F14" t="e">
         <v>#NUM!</v>
@@ -6849,16 +12663,16 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D15" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E15" t="n">
-        <v>202.290892146031</v>
+        <v>99.6645640388995</v>
       </c>
       <c r="F15" t="e">
         <v>#NUM!</v>
@@ -6869,16 +12683,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D16" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000441530167018193</v>
+        <v>0.000339177343615847</v>
       </c>
       <c r="F16" t="e">
         <v>#NUM!</v>
@@ -6889,16 +12703,16 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D17" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000440679610808023</v>
+        <v>0.000338535827246057</v>
       </c>
       <c r="F17" t="e">
         <v>#NUM!</v>
@@ -6909,16 +12723,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D18" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0005625495594148</v>
+        <v>0.000459554557516552</v>
       </c>
       <c r="F18" t="e">
         <v>#NUM!</v>
@@ -6929,16 +12743,16 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E19" t="n">
-        <v>217.599485462393</v>
+        <v>92.2498596616622</v>
       </c>
       <c r="F19" t="e">
         <v>#NUM!</v>
@@ -6949,16 +12763,16 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000562132201910548</v>
+        <v>0.000460117238493245</v>
       </c>
       <c r="F20" t="e">
         <v>#NUM!</v>
@@ -6969,16 +12783,16 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D21" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000563038312353689</v>
+        <v>0.00045801792648301</v>
       </c>
       <c r="F21" t="e">
         <v>#NUM!</v>
@@ -6989,16 +12803,16 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D22" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000371729895957673</v>
+        <v>0.000269034555515956</v>
       </c>
       <c r="F22" t="e">
         <v>#NUM!</v>
@@ -7009,16 +12823,16 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D23" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E23" t="n">
-        <v>218.176586542214</v>
+        <v>99.1318714434489</v>
       </c>
       <c r="F23" t="e">
         <v>#NUM!</v>
@@ -7029,16 +12843,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D24" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00037277928184426</v>
+        <v>0.000269936014251864</v>
       </c>
       <c r="F24" t="e">
         <v>#NUM!</v>
@@ -7049,16 +12863,16 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000371235313507152</v>
+        <v>0.00026900054528273</v>
       </c>
       <c r="F25" t="e">
         <v>#NUM!</v>
@@ -7069,16 +12883,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D26" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000372377998551685</v>
+        <v>0.000270485981846681</v>
       </c>
       <c r="F26" t="e">
         <v>#NUM!</v>
@@ -7089,16 +12903,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D27" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E27" t="n">
-        <v>164.798644452561</v>
+        <v>89.6971619384713</v>
       </c>
       <c r="F27" t="e">
         <v>#NUM!</v>
@@ -7109,16 +12923,16 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D28" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000372188689967515</v>
+        <v>0.000269639427812933</v>
       </c>
       <c r="F28" t="e">
         <v>#NUM!</v>
@@ -7129,16 +12943,16 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D29" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000372127472085542</v>
+        <v>0.000269866090308313</v>
       </c>
       <c r="F29" t="e">
         <v>#NUM!</v>
